--- a/mdrt/MDRT.xlsx
+++ b/mdrt/MDRT.xlsx
@@ -5,17 +5,17 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/mdrt/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/mdrt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0BCEB1A-E465-4047-AF5D-3C1305B84EFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7CBD6F7-4FC7-E84B-A4FD-27DA3370E8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="1480" windowWidth="24460" windowHeight="15320" xr2:uid="{263D14F0-BAEF-1E4F-83AF-E2F80B31AC70}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -423,9 +423,6 @@
     <t>GUZJ9701303Y5</t>
   </si>
   <si>
-    <t>Avance del 1 de enero al 25 de febrero de 2026.</t>
-  </si>
-  <si>
     <t>Cancelacion de Pólizas2</t>
   </si>
   <si>
@@ -466,6 +463,9 @@
   </si>
   <si>
     <t>Columna15</t>
+  </si>
+  <si>
+    <t>Avance del 1 de enero al 28 de febrero de 2026.</t>
   </si>
 </sst>
 </file>
@@ -474,12 +474,12 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="7">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="dd/mm/yy;@"/>
-    <numFmt numFmtId="166" formatCode="d\-mmm\-yy"/>
-    <numFmt numFmtId="167" formatCode="#,##0.0"/>
-    <numFmt numFmtId="168" formatCode="dd/mm/yyyy;@"/>
-    <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="170" formatCode="0.0%"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="165" formatCode="d\-mmm\-yy"/>
+    <numFmt numFmtId="166" formatCode="#,##0.0"/>
+    <numFmt numFmtId="167" formatCode="dd/mm/yyyy;@"/>
+    <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="169" formatCode="0.0%"/>
   </numFmts>
   <fonts count="11" x14ac:knownFonts="1">
     <font>
@@ -702,11 +702,11 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -725,7 +725,7 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -748,22 +748,22 @@
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="right"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="169" fontId="7" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -788,32 +788,144 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="45">
+  <dxfs count="49">
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color auto="1"/>
-        <name val="Arial"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
+      <border>
+        <left style="hair">
+          <color rgb="FF002060"/>
+        </left>
+        <right style="hair">
+          <color rgb="FF002060"/>
+        </right>
+        <top style="hair">
+          <color rgb="FF002060"/>
+        </top>
+        <bottom style="hair">
+          <color rgb="FF002060"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <fill>
-        <patternFill patternType="none">
-          <fgColor indexed="64"/>
-          <bgColor indexed="65"/>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
         </patternFill>
       </fill>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
+      <border>
+        <left style="hair">
+          <color rgb="FF002060"/>
+        </left>
+        <right style="hair">
+          <color rgb="FF002060"/>
+        </right>
+        <top style="hair">
+          <color rgb="FF002060"/>
+        </top>
+        <bottom style="hair">
+          <color rgb="FF002060"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color rgb="FF002060"/>
+        </left>
+        <right style="hair">
+          <color rgb="FF002060"/>
+        </right>
+        <top style="hair">
+          <color rgb="FF002060"/>
+        </top>
+        <bottom style="hair">
+          <color rgb="FF002060"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color rgb="FF002060"/>
+        </left>
+        <right style="hair">
+          <color rgb="FF002060"/>
+        </right>
+        <top style="hair">
+          <color rgb="FF002060"/>
+        </top>
+        <bottom style="hair">
+          <color rgb="FF002060"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -962,7 +1074,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -989,7 +1101,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1016,7 +1128,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1043,7 +1155,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1070,7 +1182,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1097,7 +1209,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1124,7 +1236,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="170" formatCode="0.0%"/>
+      <numFmt numFmtId="169" formatCode="0.0%"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1151,7 +1263,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1178,7 +1290,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1205,7 +1317,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1232,7 +1344,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1259,7 +1371,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1286,7 +1398,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1313,7 +1425,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1340,7 +1452,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1367,7 +1479,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1394,7 +1506,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1420,7 +1532,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1446,7 +1558,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1472,7 +1584,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="170" formatCode="0.0%"/>
+      <numFmt numFmtId="169" formatCode="0.0%"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1499,7 +1611,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1526,7 +1638,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1553,7 +1665,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1580,7 +1692,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1607,7 +1719,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1633,7 +1745,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1659,7 +1771,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="169" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+      <numFmt numFmtId="168" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;??_-;_-@_-"/>
       <fill>
         <patternFill patternType="none">
           <fgColor indexed="64"/>
@@ -1686,7 +1798,7 @@
         <family val="2"/>
         <scheme val="none"/>
       </font>
-      <numFmt numFmtId="168" formatCode="dd/mm/yyyy;@"/>
+      <numFmt numFmtId="167" formatCode="dd/mm/yyyy;@"/>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
     </dxf>
@@ -1828,73 +1940,30 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
-      <border>
-        <left style="hair">
-          <color rgb="FF002060"/>
-        </left>
-        <right style="hair">
-          <color rgb="FF002060"/>
-        </right>
-        <top style="hair">
-          <color rgb="FF002060"/>
-        </top>
-        <bottom style="hair">
-          <color rgb="FF002060"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color auto="1"/>
+        <name val="Arial"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
       <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
+        <patternFill patternType="none">
+          <fgColor indexed="64"/>
+          <bgColor indexed="65"/>
         </patternFill>
       </fill>
-      <border>
-        <left style="hair">
-          <color rgb="FF002060"/>
-        </left>
-        <right style="hair">
-          <color rgb="FF002060"/>
-        </right>
-        <top style="hair">
-          <color rgb="FF002060"/>
-        </top>
-        <bottom style="hair">
-          <color rgb="FF002060"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-      </border>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1910,49 +1979,49 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}" name="Tabla1" displayName="Tabla1" ref="A4:AN53" totalsRowShown="0" dataDxfId="0" dataCellStyle="Millares">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}" name="Tabla1" displayName="Tabla1" ref="A4:AN53" totalsRowShown="0" dataDxfId="48" dataCellStyle="Millares">
   <autoFilter ref="A4:AN53" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}"/>
   <tableColumns count="40">
-    <tableColumn id="1" xr3:uid="{1B45D68F-9E92-9A48-B147-43382D17EADB}" name="Dir / Zona" dataDxfId="40"/>
-    <tableColumn id="2" xr3:uid="{8141432D-DFE6-034B-8474-F9783519965C}" name="Oficina" dataDxfId="39"/>
-    <tableColumn id="3" xr3:uid="{3026117E-099F-6549-A16F-3CA4F85DA282}" name="Mat" dataDxfId="38"/>
-    <tableColumn id="4" xr3:uid="{80621F5B-C573-8944-AF37-DC364F1BE0A9}" name="Suc" dataDxfId="37"/>
-    <tableColumn id="5" xr3:uid="{9D7D11D1-2D98-5646-92D8-F8703E85240A}" name="Promotor / Partner" dataDxfId="36"/>
-    <tableColumn id="6" xr3:uid="{870F3B42-A14B-1947-827D-9A6082152D25}" name="Asesor" dataDxfId="35"/>
-    <tableColumn id="7" xr3:uid="{CA38BEAA-FBC9-474E-8C66-960105DEBCF2}" name="Nombre del Asesor" dataDxfId="34"/>
-    <tableColumn id="8" xr3:uid="{8B8898BF-4E49-0543-9598-18FF2D3F6340}" name="Conexión" dataDxfId="33"/>
-    <tableColumn id="9" xr3:uid="{49ED1251-337D-EC49-A858-207AB60B673C}" name="Grupo" dataDxfId="32" dataCellStyle="Millares"/>
-    <tableColumn id="10" xr3:uid="{26692A66-EA2C-DD40-AAC8-07A5FE32BC7D}" name="Vida Individual" dataDxfId="31" dataCellStyle="Millares"/>
-    <tableColumn id="11" xr3:uid="{45DC445E-D43B-394B-91CD-B3001CC307CC}" name="Vida G&amp;C" dataDxfId="30" dataCellStyle="Millares"/>
-    <tableColumn id="12" xr3:uid="{953B1F2A-AB88-8A40-B82F-B5DBE8FAEA70}" name="Segudescuento" dataDxfId="29" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{27E03CF4-3925-2045-BF66-C5BB1ECC7061}" name="Aportaciones Adicionales (AVEs)" dataDxfId="28" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{7375183C-90AB-0B47-A516-65079E7802F1}" name="Cancelacion de Pólizas" dataDxfId="27" dataCellStyle="Millares"/>
-    <tableColumn id="15" xr3:uid="{B0F3DBFB-9B00-894E-8929-BF5CA63336C6}" name="Total de Productos Ilimitados" dataDxfId="26" dataCellStyle="Millares"/>
-    <tableColumn id="16" xr3:uid="{3C9D5C71-B64C-434C-8D65-968245DAE09C}" name="%Vida vs Meta" dataDxfId="25" dataCellStyle="Porcentaje"/>
-    <tableColumn id="17" xr3:uid="{088A86A3-8B28-DE4E-A384-CA0EA913DA34}" name="GMM Individual" dataDxfId="24" dataCellStyle="Millares"/>
-    <tableColumn id="18" xr3:uid="{A8791E9D-69D9-C844-AE4C-8AEEFA976B8B}" name="GMM G&amp;C" dataDxfId="23" dataCellStyle="Millares"/>
-    <tableColumn id="19" xr3:uid="{0FFCB5A1-F8D9-2344-9DC7-667454959C98}" name="Cancelacion de Pólizas2" dataDxfId="22" dataCellStyle="Millares"/>
-    <tableColumn id="20" xr3:uid="{FDCA43A0-92B9-954B-B283-ABAD7C194405}" name="Total Productos Limitados" dataDxfId="21" dataCellStyle="Millares"/>
-    <tableColumn id="21" xr3:uid="{7C93BB8B-9213-EA49-A648-EF5192999BF7}" name="Tope personales" dataDxfId="20" dataCellStyle="Millares"/>
-    <tableColumn id="22" xr3:uid="{70D3FAB6-79FB-994B-AB69-F0BBB15C6AFD}" name="Total Prima" dataDxfId="19" dataCellStyle="Millares"/>
-    <tableColumn id="23" xr3:uid="{0E0D17EB-06B5-AF45-9773-7D3921FC5B9C}" name="Vida Individual3" dataDxfId="18" dataCellStyle="Millares"/>
-    <tableColumn id="24" xr3:uid="{2A25EC7F-F387-9948-8D9A-38BFD2316AB4}" name="Vida G&amp;C4" dataDxfId="17" dataCellStyle="Millares"/>
-    <tableColumn id="25" xr3:uid="{F7E8005C-762C-7146-A541-3589C41B3DA2}" name="Segudescuento5" dataDxfId="16" dataCellStyle="Millares"/>
-    <tableColumn id="26" xr3:uid="{278BB65E-357A-1D4C-B1D0-5880BBD354CD}" name="Aportaciones Adicionales (AVEs)6" dataDxfId="15" dataCellStyle="Millares"/>
-    <tableColumn id="27" xr3:uid="{0490A388-0C84-C043-A7E8-E5DC8A03AF3F}" name="Cancelacion de Pólizas7" dataDxfId="14" dataCellStyle="Millares"/>
-    <tableColumn id="28" xr3:uid="{C06E1BE2-8968-A045-B8AB-E420B9B469A1}" name="Total de Productos Ilimitados8" dataDxfId="13" dataCellStyle="Millares"/>
-    <tableColumn id="29" xr3:uid="{BEBE08BA-F641-3141-BCA9-713FD1C7CEC2}" name="%Vida vs Meta9" dataDxfId="12" dataCellStyle="Porcentaje"/>
-    <tableColumn id="30" xr3:uid="{E7FB912B-27FD-1345-845F-E51E648031F5}" name="GMM Individual10" dataDxfId="11" dataCellStyle="Millares"/>
-    <tableColumn id="31" xr3:uid="{D5FF299C-A405-CE44-B4CD-CED400EFE81F}" name="GMM G&amp;C11" dataDxfId="10" dataCellStyle="Millares"/>
-    <tableColumn id="32" xr3:uid="{D7EFF89B-8E34-EA46-B72C-61EE3166E416}" name="Cancelacion de Pólizas12" dataDxfId="9" dataCellStyle="Millares"/>
-    <tableColumn id="33" xr3:uid="{81E1798B-3D20-E748-BDAB-7A2A6F5BF33B}" name="Total Productos Limitados13" dataDxfId="8" dataCellStyle="Millares"/>
-    <tableColumn id="34" xr3:uid="{7A820362-E31F-4D41-B400-9AD11AE00577}" name="Tope personales14" dataDxfId="7" dataCellStyle="Millares"/>
-    <tableColumn id="35" xr3:uid="{09E5F95B-08D0-B946-B14E-3F06BC9C57F0}" name="Total Comisión" dataDxfId="6" dataCellStyle="Millares"/>
-    <tableColumn id="36" xr3:uid="{523C81DC-6FA9-A24D-AF9B-9D74B552A8BA}" name="Columna15" dataDxfId="5" dataCellStyle="Millares"/>
-    <tableColumn id="37" xr3:uid="{ACF68D6F-CC4F-F94A-A3AE-C7407A1AC3DE}" name="Camino Prima" dataDxfId="4" dataCellStyle="Millares"/>
-    <tableColumn id="38" xr3:uid="{39FE9301-7AE9-0A42-B79D-CA4998AB76AE}" name="OBSERVACIÓN" dataDxfId="3" dataCellStyle="Millares"/>
-    <tableColumn id="39" xr3:uid="{99E25200-803C-E54D-88BD-27CB86CAED40}" name="Camino  Comisión" dataDxfId="2" dataCellStyle="Millares"/>
-    <tableColumn id="40" xr3:uid="{45B29C50-720D-8F4E-9803-310BA4AC814E}" name="NIVEL_x000a_" dataDxfId="1" dataCellStyle="Millares"/>
+    <tableColumn id="1" xr3:uid="{1B45D68F-9E92-9A48-B147-43382D17EADB}" name="Dir / Zona" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{8141432D-DFE6-034B-8474-F9783519965C}" name="Oficina" dataDxfId="46"/>
+    <tableColumn id="3" xr3:uid="{3026117E-099F-6549-A16F-3CA4F85DA282}" name="Mat" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{80621F5B-C573-8944-AF37-DC364F1BE0A9}" name="Suc" dataDxfId="44"/>
+    <tableColumn id="5" xr3:uid="{9D7D11D1-2D98-5646-92D8-F8703E85240A}" name="Promotor / Partner" dataDxfId="43"/>
+    <tableColumn id="6" xr3:uid="{870F3B42-A14B-1947-827D-9A6082152D25}" name="Asesor" dataDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{CA38BEAA-FBC9-474E-8C66-960105DEBCF2}" name="Nombre del Asesor" dataDxfId="41"/>
+    <tableColumn id="8" xr3:uid="{8B8898BF-4E49-0543-9598-18FF2D3F6340}" name="Conexión" dataDxfId="40"/>
+    <tableColumn id="9" xr3:uid="{49ED1251-337D-EC49-A858-207AB60B673C}" name="Grupo" dataDxfId="39" dataCellStyle="Millares"/>
+    <tableColumn id="10" xr3:uid="{26692A66-EA2C-DD40-AAC8-07A5FE32BC7D}" name="Vida Individual" dataDxfId="38" dataCellStyle="Millares"/>
+    <tableColumn id="11" xr3:uid="{45DC445E-D43B-394B-91CD-B3001CC307CC}" name="Vida G&amp;C" dataDxfId="37" dataCellStyle="Millares"/>
+    <tableColumn id="12" xr3:uid="{953B1F2A-AB88-8A40-B82F-B5DBE8FAEA70}" name="Segudescuento" dataDxfId="36" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{27E03CF4-3925-2045-BF66-C5BB1ECC7061}" name="Aportaciones Adicionales (AVEs)" dataDxfId="35" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{7375183C-90AB-0B47-A516-65079E7802F1}" name="Cancelacion de Pólizas" dataDxfId="34" dataCellStyle="Millares"/>
+    <tableColumn id="15" xr3:uid="{B0F3DBFB-9B00-894E-8929-BF5CA63336C6}" name="Total de Productos Ilimitados" dataDxfId="33" dataCellStyle="Millares"/>
+    <tableColumn id="16" xr3:uid="{3C9D5C71-B64C-434C-8D65-968245DAE09C}" name="%Vida vs Meta" dataDxfId="32" dataCellStyle="Porcentaje"/>
+    <tableColumn id="17" xr3:uid="{088A86A3-8B28-DE4E-A384-CA0EA913DA34}" name="GMM Individual" dataDxfId="31" dataCellStyle="Millares"/>
+    <tableColumn id="18" xr3:uid="{A8791E9D-69D9-C844-AE4C-8AEEFA976B8B}" name="GMM G&amp;C" dataDxfId="30" dataCellStyle="Millares"/>
+    <tableColumn id="19" xr3:uid="{0FFCB5A1-F8D9-2344-9DC7-667454959C98}" name="Cancelacion de Pólizas2" dataDxfId="29" dataCellStyle="Millares"/>
+    <tableColumn id="20" xr3:uid="{FDCA43A0-92B9-954B-B283-ABAD7C194405}" name="Total Productos Limitados" dataDxfId="28" dataCellStyle="Millares"/>
+    <tableColumn id="21" xr3:uid="{7C93BB8B-9213-EA49-A648-EF5192999BF7}" name="Tope personales" dataDxfId="27" dataCellStyle="Millares"/>
+    <tableColumn id="22" xr3:uid="{70D3FAB6-79FB-994B-AB69-F0BBB15C6AFD}" name="Total Prima" dataDxfId="26" dataCellStyle="Millares"/>
+    <tableColumn id="23" xr3:uid="{0E0D17EB-06B5-AF45-9773-7D3921FC5B9C}" name="Vida Individual3" dataDxfId="25" dataCellStyle="Millares"/>
+    <tableColumn id="24" xr3:uid="{2A25EC7F-F387-9948-8D9A-38BFD2316AB4}" name="Vida G&amp;C4" dataDxfId="24" dataCellStyle="Millares"/>
+    <tableColumn id="25" xr3:uid="{F7E8005C-762C-7146-A541-3589C41B3DA2}" name="Segudescuento5" dataDxfId="23" dataCellStyle="Millares"/>
+    <tableColumn id="26" xr3:uid="{278BB65E-357A-1D4C-B1D0-5880BBD354CD}" name="Aportaciones Adicionales (AVEs)6" dataDxfId="22" dataCellStyle="Millares"/>
+    <tableColumn id="27" xr3:uid="{0490A388-0C84-C043-A7E8-E5DC8A03AF3F}" name="Cancelacion de Pólizas7" dataDxfId="21" dataCellStyle="Millares"/>
+    <tableColumn id="28" xr3:uid="{C06E1BE2-8968-A045-B8AB-E420B9B469A1}" name="Total de Productos Ilimitados8" dataDxfId="20" dataCellStyle="Millares"/>
+    <tableColumn id="29" xr3:uid="{BEBE08BA-F641-3141-BCA9-713FD1C7CEC2}" name="%Vida vs Meta9" dataDxfId="19" dataCellStyle="Porcentaje"/>
+    <tableColumn id="30" xr3:uid="{E7FB912B-27FD-1345-845F-E51E648031F5}" name="GMM Individual10" dataDxfId="18" dataCellStyle="Millares"/>
+    <tableColumn id="31" xr3:uid="{D5FF299C-A405-CE44-B4CD-CED400EFE81F}" name="GMM G&amp;C11" dataDxfId="17" dataCellStyle="Millares"/>
+    <tableColumn id="32" xr3:uid="{D7EFF89B-8E34-EA46-B72C-61EE3166E416}" name="Cancelacion de Pólizas12" dataDxfId="16" dataCellStyle="Millares"/>
+    <tableColumn id="33" xr3:uid="{81E1798B-3D20-E748-BDAB-7A2A6F5BF33B}" name="Total Productos Limitados13" dataDxfId="15" dataCellStyle="Millares"/>
+    <tableColumn id="34" xr3:uid="{7A820362-E31F-4D41-B400-9AD11AE00577}" name="Tope personales14" dataDxfId="14" dataCellStyle="Millares"/>
+    <tableColumn id="35" xr3:uid="{09E5F95B-08D0-B946-B14E-3F06BC9C57F0}" name="Total Comisión" dataDxfId="13" dataCellStyle="Millares"/>
+    <tableColumn id="36" xr3:uid="{523C81DC-6FA9-A24D-AF9B-9D74B552A8BA}" name="Columna15" dataDxfId="12" dataCellStyle="Millares"/>
+    <tableColumn id="37" xr3:uid="{ACF68D6F-CC4F-F94A-A3AE-C7407A1AC3DE}" name="Camino Prima" dataDxfId="11" dataCellStyle="Millares"/>
+    <tableColumn id="38" xr3:uid="{39FE9301-7AE9-0A42-B79D-CA4998AB76AE}" name="OBSERVACIÓN" dataDxfId="10" dataCellStyle="Millares"/>
+    <tableColumn id="39" xr3:uid="{99E25200-803C-E54D-88BD-27CB86CAED40}" name="Camino  Comisión" dataDxfId="9" dataCellStyle="Millares"/>
+    <tableColumn id="40" xr3:uid="{45B29C50-720D-8F4E-9803-310BA4AC814E}" name="NIVEL_x000a_" dataDxfId="8" dataCellStyle="Millares"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2315,10 +2384,10 @@
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A1" s="36" t="s">
-        <v>128</v>
+        <v>142</v>
       </c>
     </row>
-    <row r="4" spans="1:40" ht="70" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:40" ht="28" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -2374,7 +2443,7 @@
         <v>17</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="T4" s="4" t="s">
         <v>18</v>
@@ -2386,46 +2455,46 @@
         <v>20</v>
       </c>
       <c r="W4" s="6" t="s">
+        <v>129</v>
+      </c>
+      <c r="X4" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="X4" s="6" t="s">
+      <c r="Y4" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Z4" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="Z4" s="6" t="s">
+      <c r="AA4" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="AA4" s="6" t="s">
+      <c r="AB4" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="AB4" s="7" t="s">
+      <c r="AC4" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="AC4" s="8" t="s">
+      <c r="AD4" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="AD4" s="6" t="s">
+      <c r="AE4" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="AE4" s="6" t="s">
+      <c r="AF4" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="AF4" s="6" t="s">
+      <c r="AG4" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="AG4" s="6" t="s">
+      <c r="AH4" s="6" t="s">
         <v>140</v>
-      </c>
-      <c r="AH4" s="6" t="s">
-        <v>141</v>
       </c>
       <c r="AI4" s="9" t="s">
         <v>21</v>
       </c>
       <c r="AJ4" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="AK4" s="11" t="s">
         <v>22</v>
@@ -2511,7 +2580,7 @@
         <v>30</v>
       </c>
       <c r="J6" s="30">
-        <v>35879.760000000002</v>
+        <v>85231.8</v>
       </c>
       <c r="K6" s="30">
         <v>0</v>
@@ -2520,19 +2589,19 @@
         <v>0</v>
       </c>
       <c r="M6" s="31">
-        <v>111971.47</v>
+        <v>111996.34</v>
       </c>
       <c r="N6" s="31">
         <v>0</v>
       </c>
       <c r="O6" s="29">
-        <v>147851.23000000001</v>
+        <v>197228.14</v>
       </c>
       <c r="P6" s="32">
-        <v>8.1699999999999995E-2</v>
+        <v>0.1089</v>
       </c>
       <c r="Q6" s="30">
-        <v>213214.24</v>
+        <v>234634.12</v>
       </c>
       <c r="R6" s="30">
         <v>0</v>
@@ -2541,16 +2610,16 @@
         <v>0</v>
       </c>
       <c r="T6" s="29">
-        <v>213214.24</v>
+        <v>234634.12</v>
       </c>
       <c r="U6" s="29">
         <v>0</v>
       </c>
       <c r="V6" s="29">
-        <v>361065.47</v>
+        <v>431862.26</v>
       </c>
       <c r="W6" s="29">
-        <v>13140.84</v>
+        <v>31315.439999999999</v>
       </c>
       <c r="X6" s="29">
         <v>0</v>
@@ -2559,19 +2628,19 @@
         <v>0</v>
       </c>
       <c r="Z6" s="31">
-        <v>6075.98</v>
+        <v>6079.3</v>
       </c>
       <c r="AA6" s="31">
         <v>0</v>
       </c>
       <c r="AB6" s="29">
-        <v>19216.82</v>
+        <v>37394.74</v>
       </c>
       <c r="AC6" s="32">
-        <v>2.12E-2</v>
+        <v>4.1300000000000003E-2</v>
       </c>
       <c r="AD6" s="29">
-        <v>46376.36</v>
+        <v>51259.519999999997</v>
       </c>
       <c r="AE6" s="29">
         <v>0</v>
@@ -2580,13 +2649,13 @@
         <v>0</v>
       </c>
       <c r="AG6" s="29">
-        <v>46376.36</v>
+        <v>51259.519999999997</v>
       </c>
       <c r="AH6" s="29">
         <v>0</v>
       </c>
       <c r="AI6" s="29">
-        <v>65593.179999999993</v>
+        <v>88654.26</v>
       </c>
       <c r="AJ6" s="33" t="s">
         <v>31</v>
@@ -2652,7 +2721,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="30">
-        <v>155985.26999999999</v>
+        <v>187050.51</v>
       </c>
       <c r="R7" s="30">
         <v>0</v>
@@ -2661,13 +2730,13 @@
         <v>0</v>
       </c>
       <c r="T7" s="29">
-        <v>155985.26999999999</v>
+        <v>187050.51</v>
       </c>
       <c r="U7" s="29">
         <v>0</v>
       </c>
       <c r="V7" s="29">
-        <v>155985.26999999999</v>
+        <v>187050.51</v>
       </c>
       <c r="W7" s="29">
         <v>0</v>
@@ -2691,7 +2760,7 @@
         <v>0</v>
       </c>
       <c r="AD7" s="29">
-        <v>20574.02</v>
+        <v>27056.3</v>
       </c>
       <c r="AE7" s="29">
         <v>0</v>
@@ -2700,13 +2769,13 @@
         <v>0</v>
       </c>
       <c r="AG7" s="29">
-        <v>20574.02</v>
+        <v>27056.3</v>
       </c>
       <c r="AH7" s="29">
         <v>0</v>
       </c>
       <c r="AI7" s="29">
-        <v>20574.02</v>
+        <v>27056.3</v>
       </c>
       <c r="AJ7" s="33" t="s">
         <v>35</v>
@@ -2727,25 +2796,25 @@
         <v>2043</v>
       </c>
       <c r="D8" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F8" s="27">
-        <v>94156</v>
+        <v>110453</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H8" s="28">
-        <v>44159</v>
+        <v>45600</v>
       </c>
       <c r="I8" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J8" s="30">
-        <v>111482.82</v>
+        <v>160127.31</v>
       </c>
       <c r="K8" s="30">
         <v>0</v>
@@ -2754,19 +2823,19 @@
         <v>0</v>
       </c>
       <c r="M8" s="31">
-        <v>1420.84</v>
+        <v>182.07</v>
       </c>
       <c r="N8" s="31">
         <v>0</v>
       </c>
       <c r="O8" s="29">
-        <v>112903.66</v>
+        <v>160309.38</v>
       </c>
       <c r="P8" s="32">
-        <v>6.2399999999999997E-2</v>
+        <v>8.8499999999999995E-2</v>
       </c>
       <c r="Q8" s="30">
-        <v>27671.29</v>
+        <v>0</v>
       </c>
       <c r="R8" s="30">
         <v>0</v>
@@ -2775,16 +2844,16 @@
         <v>0</v>
       </c>
       <c r="T8" s="29">
-        <v>27671.29</v>
+        <v>0</v>
       </c>
       <c r="U8" s="29">
         <v>0</v>
       </c>
       <c r="V8" s="29">
-        <v>140574.95000000001</v>
+        <v>160309.38</v>
       </c>
       <c r="W8" s="29">
-        <v>30100.36</v>
+        <v>53991.06</v>
       </c>
       <c r="X8" s="29">
         <v>0</v>
@@ -2793,19 +2862,19 @@
         <v>0</v>
       </c>
       <c r="Z8" s="31">
-        <v>356.94</v>
+        <v>24.28</v>
       </c>
       <c r="AA8" s="31">
         <v>0</v>
       </c>
       <c r="AB8" s="29">
-        <v>30457.3</v>
+        <v>54015.34</v>
       </c>
       <c r="AC8" s="32">
-        <v>3.3599999999999998E-2</v>
+        <v>5.9700000000000003E-2</v>
       </c>
       <c r="AD8" s="29">
-        <v>4203.3999999999996</v>
+        <v>0</v>
       </c>
       <c r="AE8" s="29">
         <v>0</v>
@@ -2814,16 +2883,16 @@
         <v>0</v>
       </c>
       <c r="AG8" s="29">
-        <v>4203.3999999999996</v>
+        <v>0</v>
       </c>
       <c r="AH8" s="29">
         <v>0</v>
       </c>
       <c r="AI8" s="29">
-        <v>34660.699999999997</v>
+        <v>54015.34</v>
       </c>
       <c r="AJ8" s="33" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="AK8" s="34"/>
       <c r="AL8" s="34"/>
@@ -2847,19 +2916,19 @@
         <v>28</v>
       </c>
       <c r="F9" s="27">
-        <v>90355</v>
+        <v>94156</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="H9" s="28">
-        <v>43949</v>
+        <v>44159</v>
       </c>
       <c r="I9" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J9" s="30">
-        <v>126885.75999999999</v>
+        <v>111482.82</v>
       </c>
       <c r="K9" s="30">
         <v>0</v>
@@ -2868,19 +2937,19 @@
         <v>0</v>
       </c>
       <c r="M9" s="31">
-        <v>12467.08</v>
+        <v>1420.84</v>
       </c>
       <c r="N9" s="31">
         <v>0</v>
       </c>
       <c r="O9" s="29">
-        <v>139352.84</v>
+        <v>112903.66</v>
       </c>
       <c r="P9" s="32">
-        <v>7.6999999999999999E-2</v>
+        <v>6.2399999999999997E-2</v>
       </c>
       <c r="Q9" s="30">
-        <v>0</v>
+        <v>27671.29</v>
       </c>
       <c r="R9" s="30">
         <v>0</v>
@@ -2889,16 +2958,16 @@
         <v>0</v>
       </c>
       <c r="T9" s="29">
-        <v>0</v>
+        <v>27671.29</v>
       </c>
       <c r="U9" s="29">
         <v>0</v>
       </c>
       <c r="V9" s="29">
-        <v>139352.84</v>
+        <v>140574.95000000001</v>
       </c>
       <c r="W9" s="29">
-        <v>50742.080000000002</v>
+        <v>30100.36</v>
       </c>
       <c r="X9" s="29">
         <v>0</v>
@@ -2907,19 +2976,19 @@
         <v>0</v>
       </c>
       <c r="Z9" s="31">
-        <v>662.1</v>
+        <v>380.49</v>
       </c>
       <c r="AA9" s="31">
         <v>0</v>
       </c>
       <c r="AB9" s="29">
-        <v>51404.18</v>
+        <v>30480.85</v>
       </c>
       <c r="AC9" s="32">
-        <v>5.6800000000000003E-2</v>
+        <v>3.3700000000000001E-2</v>
       </c>
       <c r="AD9" s="29">
-        <v>0</v>
+        <v>4203.3999999999996</v>
       </c>
       <c r="AE9" s="29">
         <v>0</v>
@@ -2928,16 +2997,16 @@
         <v>0</v>
       </c>
       <c r="AG9" s="29">
-        <v>0</v>
+        <v>4203.3999999999996</v>
       </c>
       <c r="AH9" s="29">
         <v>0</v>
       </c>
       <c r="AI9" s="29">
-        <v>51404.18</v>
+        <v>34684.25</v>
       </c>
       <c r="AJ9" s="33" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="AK9" s="34"/>
       <c r="AL9" s="34"/>
@@ -2955,25 +3024,25 @@
         <v>2043</v>
       </c>
       <c r="D10" s="26">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F10" s="27">
-        <v>110453</v>
+        <v>90355</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="H10" s="28">
-        <v>45600</v>
+        <v>43949</v>
       </c>
       <c r="I10" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J10" s="30">
-        <v>136817.79</v>
+        <v>126885.75999999999</v>
       </c>
       <c r="K10" s="30">
         <v>0</v>
@@ -2982,16 +3051,16 @@
         <v>0</v>
       </c>
       <c r="M10" s="31">
-        <v>182.07</v>
+        <v>12467.08</v>
       </c>
       <c r="N10" s="31">
         <v>0</v>
       </c>
       <c r="O10" s="29">
-        <v>136999.85999999999</v>
+        <v>139352.84</v>
       </c>
       <c r="P10" s="32">
-        <v>7.5700000000000003E-2</v>
+        <v>7.6999999999999999E-2</v>
       </c>
       <c r="Q10" s="30">
         <v>0</v>
@@ -3009,10 +3078,10 @@
         <v>0</v>
       </c>
       <c r="V10" s="29">
-        <v>136999.85999999999</v>
+        <v>139352.84</v>
       </c>
       <c r="W10" s="29">
-        <v>45916.74</v>
+        <v>50742.080000000002</v>
       </c>
       <c r="X10" s="29">
         <v>0</v>
@@ -3021,16 +3090,16 @@
         <v>0</v>
       </c>
       <c r="Z10" s="31">
-        <v>24.28</v>
+        <v>691.39</v>
       </c>
       <c r="AA10" s="31">
         <v>0</v>
       </c>
       <c r="AB10" s="29">
-        <v>45941.02</v>
+        <v>51433.47</v>
       </c>
       <c r="AC10" s="32">
-        <v>5.0799999999999998E-2</v>
+        <v>5.6800000000000003E-2</v>
       </c>
       <c r="AD10" s="29">
         <v>0</v>
@@ -3048,10 +3117,10 @@
         <v>0</v>
       </c>
       <c r="AI10" s="29">
-        <v>45941.02</v>
+        <v>51433.47</v>
       </c>
       <c r="AJ10" s="33" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="AK10" s="34"/>
       <c r="AL10" s="34"/>
@@ -3069,25 +3138,25 @@
         <v>2043</v>
       </c>
       <c r="D11" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E11" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F11" s="27">
-        <v>104718</v>
+        <v>80122</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="H11" s="28">
-        <v>45264</v>
+        <v>43371</v>
       </c>
       <c r="I11" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J11" s="30">
-        <v>86224.02</v>
+        <v>44654.68</v>
       </c>
       <c r="K11" s="30">
         <v>0</v>
@@ -3096,19 +3165,19 @@
         <v>0</v>
       </c>
       <c r="M11" s="31">
-        <v>206.11</v>
+        <v>80288.14</v>
       </c>
       <c r="N11" s="31">
         <v>0</v>
       </c>
       <c r="O11" s="29">
-        <v>86430.13</v>
+        <v>124942.82</v>
       </c>
       <c r="P11" s="32">
-        <v>4.7699999999999999E-2</v>
+        <v>6.9000000000000006E-2</v>
       </c>
       <c r="Q11" s="30">
-        <v>31773.599999999999</v>
+        <v>0</v>
       </c>
       <c r="R11" s="30">
         <v>0</v>
@@ -3117,16 +3186,16 @@
         <v>0</v>
       </c>
       <c r="T11" s="29">
-        <v>31773.599999999999</v>
+        <v>0</v>
       </c>
       <c r="U11" s="29">
         <v>0</v>
       </c>
       <c r="V11" s="29">
-        <v>118203.73</v>
+        <v>124942.82</v>
       </c>
       <c r="W11" s="29">
-        <v>26969.599999999999</v>
+        <v>15543.06</v>
       </c>
       <c r="X11" s="29">
         <v>0</v>
@@ -3135,19 +3204,19 @@
         <v>0</v>
       </c>
       <c r="Z11" s="31">
-        <v>3.48</v>
+        <v>4401.03</v>
       </c>
       <c r="AA11" s="31">
         <v>0</v>
       </c>
       <c r="AB11" s="29">
-        <v>26973.08</v>
+        <v>19944.09</v>
       </c>
       <c r="AC11" s="32">
-        <v>2.98E-2</v>
+        <v>2.1999999999999999E-2</v>
       </c>
       <c r="AD11" s="29">
-        <v>6601.68</v>
+        <v>0</v>
       </c>
       <c r="AE11" s="29">
         <v>0</v>
@@ -3156,16 +3225,16 @@
         <v>0</v>
       </c>
       <c r="AG11" s="29">
-        <v>6601.68</v>
+        <v>0</v>
       </c>
       <c r="AH11" s="29">
         <v>0</v>
       </c>
       <c r="AI11" s="29">
-        <v>33574.76</v>
+        <v>19944.09</v>
       </c>
       <c r="AJ11" s="33" t="s">
-        <v>43</v>
+        <v>47</v>
       </c>
       <c r="AK11" s="34"/>
       <c r="AL11" s="34"/>
@@ -3183,25 +3252,25 @@
         <v>2043</v>
       </c>
       <c r="D12" s="26">
-        <v>2856</v>
+        <v>2692</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="27">
-        <v>115047</v>
+        <v>104718</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H12" s="28">
-        <v>45944</v>
+        <v>45264</v>
       </c>
       <c r="I12" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J12" s="30">
-        <v>0</v>
+        <v>86224.02</v>
       </c>
       <c r="K12" s="30">
         <v>0</v>
@@ -3210,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="M12" s="31">
-        <v>139.01</v>
+        <v>338.11</v>
       </c>
       <c r="N12" s="31">
         <v>0</v>
       </c>
       <c r="O12" s="29">
-        <v>51459.14</v>
+        <v>86562.13</v>
       </c>
       <c r="P12" s="32">
-        <v>2.8400000000000002E-2</v>
+        <v>4.7800000000000002E-2</v>
       </c>
       <c r="Q12" s="30">
-        <v>40110.959999999999</v>
+        <v>31773.599999999999</v>
       </c>
       <c r="R12" s="30">
         <v>0</v>
@@ -3231,16 +3300,16 @@
         <v>0</v>
       </c>
       <c r="T12" s="29">
-        <v>49236.79</v>
+        <v>31773.599999999999</v>
       </c>
       <c r="U12" s="29">
-        <v>60445.96</v>
+        <v>0</v>
       </c>
       <c r="V12" s="29">
-        <v>100695.93</v>
+        <v>118335.73</v>
       </c>
       <c r="W12" s="29">
-        <v>0</v>
+        <v>26969.599999999999</v>
       </c>
       <c r="X12" s="29">
         <v>0</v>
@@ -3249,19 +3318,19 @@
         <v>0</v>
       </c>
       <c r="Z12" s="31">
-        <v>18.54</v>
+        <v>21.08</v>
       </c>
       <c r="AA12" s="31">
         <v>0</v>
       </c>
       <c r="AB12" s="29">
-        <v>15414.58</v>
+        <v>26990.68</v>
       </c>
       <c r="AC12" s="32">
-        <v>1.7000000000000001E-2</v>
+        <v>2.98E-2</v>
       </c>
       <c r="AD12" s="29">
-        <v>8472.36</v>
+        <v>6601.68</v>
       </c>
       <c r="AE12" s="29">
         <v>0</v>
@@ -3270,16 +3339,16 @@
         <v>0</v>
       </c>
       <c r="AG12" s="29">
-        <v>10021.94</v>
+        <v>6601.68</v>
       </c>
       <c r="AH12" s="29">
-        <v>16945.62</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="29">
-        <v>25436.52</v>
+        <v>33592.36</v>
       </c>
       <c r="AJ12" s="33" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK12" s="34"/>
       <c r="AL12" s="34"/>
@@ -3297,25 +3366,25 @@
         <v>2043</v>
       </c>
       <c r="D13" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F13" s="27">
-        <v>80122</v>
+        <v>115047</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="H13" s="28">
-        <v>43371</v>
+        <v>45944</v>
       </c>
       <c r="I13" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J13" s="30">
-        <v>20532.36</v>
+        <v>0</v>
       </c>
       <c r="K13" s="30">
         <v>0</v>
@@ -3324,19 +3393,19 @@
         <v>0</v>
       </c>
       <c r="M13" s="31">
-        <v>80108.14</v>
+        <v>278.49</v>
       </c>
       <c r="N13" s="31">
         <v>0</v>
       </c>
       <c r="O13" s="29">
-        <v>100640.5</v>
+        <v>51598.62</v>
       </c>
       <c r="P13" s="32">
-        <v>5.5599999999999997E-2</v>
+        <v>2.8500000000000001E-2</v>
       </c>
       <c r="Q13" s="30">
-        <v>0</v>
+        <v>40110.959999999999</v>
       </c>
       <c r="R13" s="30">
         <v>0</v>
@@ -3345,16 +3414,16 @@
         <v>0</v>
       </c>
       <c r="T13" s="29">
-        <v>0</v>
+        <v>49236.79</v>
       </c>
       <c r="U13" s="29">
-        <v>0</v>
+        <v>60445.96</v>
       </c>
       <c r="V13" s="29">
-        <v>100640.5</v>
+        <v>100835.41</v>
       </c>
       <c r="W13" s="29">
-        <v>7028.04</v>
+        <v>0</v>
       </c>
       <c r="X13" s="29">
         <v>0</v>
@@ -3363,19 +3432,19 @@
         <v>0</v>
       </c>
       <c r="Z13" s="31">
-        <v>4392.03</v>
+        <v>37.14</v>
       </c>
       <c r="AA13" s="31">
         <v>0</v>
       </c>
       <c r="AB13" s="29">
-        <v>11420.07</v>
+        <v>15433.18</v>
       </c>
       <c r="AC13" s="32">
-        <v>1.26E-2</v>
+        <v>1.7000000000000001E-2</v>
       </c>
       <c r="AD13" s="29">
-        <v>0</v>
+        <v>8472.36</v>
       </c>
       <c r="AE13" s="29">
         <v>0</v>
@@ -3384,16 +3453,16 @@
         <v>0</v>
       </c>
       <c r="AG13" s="29">
-        <v>0</v>
+        <v>10021.94</v>
       </c>
       <c r="AH13" s="29">
-        <v>0</v>
+        <v>16945.62</v>
       </c>
       <c r="AI13" s="29">
-        <v>11420.07</v>
+        <v>25455.119999999999</v>
       </c>
       <c r="AJ13" s="33" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="AK13" s="34"/>
       <c r="AL13" s="34"/>
@@ -3552,13 +3621,13 @@
         <v>0</v>
       </c>
       <c r="M15" s="31">
-        <v>3492.91</v>
+        <v>3525.17</v>
       </c>
       <c r="N15" s="31">
         <v>0</v>
       </c>
       <c r="O15" s="29">
-        <v>65289.48</v>
+        <v>65321.74</v>
       </c>
       <c r="P15" s="32">
         <v>3.61E-2</v>
@@ -3579,7 +3648,7 @@
         <v>0</v>
       </c>
       <c r="V15" s="29">
-        <v>93826.98</v>
+        <v>93859.24</v>
       </c>
       <c r="W15" s="29">
         <v>18538.98</v>
@@ -3591,13 +3660,13 @@
         <v>0</v>
       </c>
       <c r="Z15" s="31">
-        <v>549.14</v>
+        <v>559.63</v>
       </c>
       <c r="AA15" s="31">
         <v>0</v>
       </c>
       <c r="AB15" s="29">
-        <v>19088.12</v>
+        <v>19098.61</v>
       </c>
       <c r="AC15" s="32">
         <v>2.1100000000000001E-2</v>
@@ -3618,7 +3687,7 @@
         <v>0</v>
       </c>
       <c r="AI15" s="29">
-        <v>25030.86</v>
+        <v>25041.35</v>
       </c>
       <c r="AJ15" s="33" t="s">
         <v>51</v>
@@ -3639,25 +3708,25 @@
         <v>2043</v>
       </c>
       <c r="D16" s="26">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E16" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F16" s="27">
-        <v>116060</v>
+        <v>115404</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H16" s="28">
-        <v>46010</v>
+        <v>45986</v>
       </c>
       <c r="I16" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J16" s="30">
-        <v>21769.200000000001</v>
+        <v>29852.74</v>
       </c>
       <c r="K16" s="30">
         <v>0</v>
@@ -3672,13 +3741,13 @@
         <v>0</v>
       </c>
       <c r="O16" s="29">
-        <v>52038.66</v>
+        <v>29852.74</v>
       </c>
       <c r="P16" s="32">
-        <v>2.87E-2</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="Q16" s="30">
-        <v>30604.240000000002</v>
+        <v>53684.13</v>
       </c>
       <c r="R16" s="30">
         <v>0</v>
@@ -3687,16 +3756,16 @@
         <v>0</v>
       </c>
       <c r="T16" s="29">
-        <v>30604.240000000002</v>
+        <v>53684.13</v>
       </c>
       <c r="U16" s="29">
-        <v>30269.46</v>
+        <v>0</v>
       </c>
       <c r="V16" s="29">
-        <v>82642.899999999994</v>
+        <v>83536.87</v>
       </c>
       <c r="W16" s="29">
-        <v>6774.12</v>
+        <v>10448.459999999999</v>
       </c>
       <c r="X16" s="29">
         <v>0</v>
@@ -3711,13 +3780,13 @@
         <v>0</v>
       </c>
       <c r="AB16" s="29">
-        <v>16652.57</v>
+        <v>10448.459999999999</v>
       </c>
       <c r="AC16" s="32">
-        <v>1.84E-2</v>
+        <v>1.15E-2</v>
       </c>
       <c r="AD16" s="29">
-        <v>6397.42</v>
+        <v>10754.34</v>
       </c>
       <c r="AE16" s="29">
         <v>0</v>
@@ -3726,16 +3795,16 @@
         <v>0</v>
       </c>
       <c r="AG16" s="29">
-        <v>6397.42</v>
+        <v>10754.34</v>
       </c>
       <c r="AH16" s="29">
-        <v>9878.4500000000007</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="29">
-        <v>23049.99</v>
+        <v>21202.799999999999</v>
       </c>
       <c r="AJ16" s="33" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="AK16" s="34"/>
       <c r="AL16" s="34"/>
@@ -3753,25 +3822,25 @@
         <v>2043</v>
       </c>
       <c r="D17" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E17" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F17" s="27">
-        <v>95148</v>
+        <v>116060</v>
       </c>
       <c r="G17" s="25" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="H17" s="28">
-        <v>44916</v>
+        <v>46010</v>
       </c>
       <c r="I17" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J17" s="30">
-        <v>46057.760000000002</v>
+        <v>21769.200000000001</v>
       </c>
       <c r="K17" s="30">
         <v>0</v>
@@ -3786,13 +3855,13 @@
         <v>0</v>
       </c>
       <c r="O17" s="29">
-        <v>46057.760000000002</v>
+        <v>52038.66</v>
       </c>
       <c r="P17" s="32">
-        <v>2.5399999999999999E-2</v>
+        <v>2.87E-2</v>
       </c>
       <c r="Q17" s="30">
-        <v>23133.08</v>
+        <v>30604.240000000002</v>
       </c>
       <c r="R17" s="30">
         <v>0</v>
@@ -3801,16 +3870,16 @@
         <v>0</v>
       </c>
       <c r="T17" s="29">
-        <v>23133.08</v>
+        <v>30604.240000000002</v>
       </c>
       <c r="U17" s="29">
-        <v>0</v>
+        <v>30269.46</v>
       </c>
       <c r="V17" s="29">
-        <v>69190.84</v>
+        <v>82642.899999999994</v>
       </c>
       <c r="W17" s="29">
-        <v>13817.33</v>
+        <v>6774.12</v>
       </c>
       <c r="X17" s="29">
         <v>0</v>
@@ -3825,13 +3894,13 @@
         <v>0</v>
       </c>
       <c r="AB17" s="29">
-        <v>13817.33</v>
+        <v>16652.57</v>
       </c>
       <c r="AC17" s="32">
-        <v>1.5299999999999999E-2</v>
+        <v>1.84E-2</v>
       </c>
       <c r="AD17" s="29">
-        <v>4744.3599999999997</v>
+        <v>6397.42</v>
       </c>
       <c r="AE17" s="29">
         <v>0</v>
@@ -3840,16 +3909,16 @@
         <v>0</v>
       </c>
       <c r="AG17" s="29">
-        <v>4744.3599999999997</v>
+        <v>6397.42</v>
       </c>
       <c r="AH17" s="29">
-        <v>0</v>
+        <v>9878.4500000000007</v>
       </c>
       <c r="AI17" s="29">
-        <v>18561.689999999999</v>
+        <v>23049.99</v>
       </c>
       <c r="AJ17" s="33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="AK17" s="34"/>
       <c r="AL17" s="34"/>
@@ -3894,16 +3963,16 @@
         <v>0</v>
       </c>
       <c r="M18" s="31">
-        <v>838.07</v>
+        <v>1677.22</v>
       </c>
       <c r="N18" s="31">
         <v>0</v>
       </c>
       <c r="O18" s="29">
-        <v>37748.76</v>
+        <v>38587.910000000003</v>
       </c>
       <c r="P18" s="32">
-        <v>2.0899999999999998E-2</v>
+        <v>2.1299999999999999E-2</v>
       </c>
       <c r="Q18" s="30">
         <v>27059.39</v>
@@ -3921,7 +3990,7 @@
         <v>0</v>
       </c>
       <c r="V18" s="29">
-        <v>64808.15</v>
+        <v>65647.3</v>
       </c>
       <c r="W18" s="29">
         <v>11073.21</v>
@@ -3933,16 +4002,16 @@
         <v>0</v>
       </c>
       <c r="Z18" s="31">
-        <v>111.74</v>
+        <v>223.62</v>
       </c>
       <c r="AA18" s="31">
         <v>0</v>
       </c>
       <c r="AB18" s="29">
-        <v>11184.95</v>
+        <v>11296.83</v>
       </c>
       <c r="AC18" s="32">
-        <v>1.24E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="AD18" s="29">
         <v>5601.07</v>
@@ -3960,7 +4029,7 @@
         <v>0</v>
       </c>
       <c r="AI18" s="29">
-        <v>16786.02</v>
+        <v>16897.900000000001</v>
       </c>
       <c r="AJ18" s="33" t="s">
         <v>57</v>
@@ -3987,19 +4056,19 @@
         <v>28</v>
       </c>
       <c r="F19" s="27">
-        <v>113450</v>
+        <v>104750</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="H19" s="28">
-        <v>45852</v>
+        <v>45236</v>
       </c>
       <c r="I19" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J19" s="30">
-        <v>58035.37</v>
+        <v>63710.97</v>
       </c>
       <c r="K19" s="30">
         <v>0</v>
@@ -4008,19 +4077,19 @@
         <v>0</v>
       </c>
       <c r="M19" s="31">
-        <v>180</v>
+        <v>590.1</v>
       </c>
       <c r="N19" s="31">
         <v>0</v>
       </c>
       <c r="O19" s="29">
-        <v>58215.37</v>
+        <v>64301.07</v>
       </c>
       <c r="P19" s="32">
-        <v>3.2199999999999999E-2</v>
+        <v>3.5499999999999997E-2</v>
       </c>
       <c r="Q19" s="30">
-        <v>0</v>
+        <v>987</v>
       </c>
       <c r="R19" s="30">
         <v>0</v>
@@ -4029,16 +4098,16 @@
         <v>0</v>
       </c>
       <c r="T19" s="29">
-        <v>0</v>
+        <v>987</v>
       </c>
       <c r="U19" s="29">
         <v>0</v>
       </c>
       <c r="V19" s="29">
-        <v>58215.37</v>
+        <v>65288.07</v>
       </c>
       <c r="W19" s="29">
-        <v>15669.55</v>
+        <v>24068.240000000002</v>
       </c>
       <c r="X19" s="29">
         <v>0</v>
@@ -4047,19 +4116,19 @@
         <v>0</v>
       </c>
       <c r="Z19" s="31">
-        <v>24</v>
+        <v>83.1</v>
       </c>
       <c r="AA19" s="31">
         <v>0</v>
       </c>
       <c r="AB19" s="29">
-        <v>15693.55</v>
+        <v>24151.34</v>
       </c>
       <c r="AC19" s="32">
-        <v>1.7299999999999999E-2</v>
+        <v>2.6700000000000002E-2</v>
       </c>
       <c r="AD19" s="29">
-        <v>0</v>
+        <v>166.6</v>
       </c>
       <c r="AE19" s="29">
         <v>0</v>
@@ -4068,16 +4137,16 @@
         <v>0</v>
       </c>
       <c r="AG19" s="29">
-        <v>0</v>
+        <v>166.6</v>
       </c>
       <c r="AH19" s="29">
         <v>0</v>
       </c>
       <c r="AI19" s="29">
-        <v>15693.55</v>
+        <v>24317.94</v>
       </c>
       <c r="AJ19" s="33" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="AK19" s="34"/>
       <c r="AL19" s="34"/>
@@ -4095,25 +4164,25 @@
         <v>2043</v>
       </c>
       <c r="D20" s="26">
-        <v>2043</v>
+        <v>2692</v>
       </c>
       <c r="E20" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="27">
-        <v>115404</v>
+        <v>113450</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="H20" s="28">
-        <v>45986</v>
+        <v>45852</v>
       </c>
       <c r="I20" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J20" s="30">
-        <v>29852.74</v>
+        <v>58035.37</v>
       </c>
       <c r="K20" s="30">
         <v>0</v>
@@ -4122,19 +4191,19 @@
         <v>0</v>
       </c>
       <c r="M20" s="31">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="N20" s="31">
         <v>0</v>
       </c>
       <c r="O20" s="29">
-        <v>29852.74</v>
+        <v>58215.37</v>
       </c>
       <c r="P20" s="32">
-        <v>1.6500000000000001E-2</v>
+        <v>3.2199999999999999E-2</v>
       </c>
       <c r="Q20" s="30">
-        <v>19189.169999999998</v>
+        <v>0</v>
       </c>
       <c r="R20" s="30">
         <v>0</v>
@@ -4143,16 +4212,16 @@
         <v>0</v>
       </c>
       <c r="T20" s="29">
-        <v>19189.169999999998</v>
+        <v>0</v>
       </c>
       <c r="U20" s="29">
         <v>0</v>
       </c>
       <c r="V20" s="29">
-        <v>49041.91</v>
+        <v>58215.37</v>
       </c>
       <c r="W20" s="29">
-        <v>10448.459999999999</v>
+        <v>15669.55</v>
       </c>
       <c r="X20" s="29">
         <v>0</v>
@@ -4161,19 +4230,19 @@
         <v>0</v>
       </c>
       <c r="Z20" s="31">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AA20" s="31">
         <v>0</v>
       </c>
       <c r="AB20" s="29">
-        <v>10448.459999999999</v>
+        <v>15693.55</v>
       </c>
       <c r="AC20" s="32">
-        <v>1.15E-2</v>
+        <v>1.7299999999999999E-2</v>
       </c>
       <c r="AD20" s="29">
-        <v>3517.62</v>
+        <v>0</v>
       </c>
       <c r="AE20" s="29">
         <v>0</v>
@@ -4182,16 +4251,16 @@
         <v>0</v>
       </c>
       <c r="AG20" s="29">
-        <v>3517.62</v>
+        <v>0</v>
       </c>
       <c r="AH20" s="29">
         <v>0</v>
       </c>
       <c r="AI20" s="29">
-        <v>13966.08</v>
+        <v>15693.55</v>
       </c>
       <c r="AJ20" s="33" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="AK20" s="34"/>
       <c r="AL20" s="34"/>
@@ -4209,25 +4278,25 @@
         <v>2043</v>
       </c>
       <c r="D21" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E21" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F21" s="27">
-        <v>104750</v>
+        <v>102825</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>62</v>
+        <v>86</v>
       </c>
       <c r="H21" s="28">
-        <v>45236</v>
+        <v>45117</v>
       </c>
       <c r="I21" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J21" s="30">
-        <v>43009.15</v>
+        <v>0</v>
       </c>
       <c r="K21" s="30">
         <v>0</v>
@@ -4236,19 +4305,19 @@
         <v>0</v>
       </c>
       <c r="M21" s="31">
-        <v>590.1</v>
+        <v>227.15</v>
       </c>
       <c r="N21" s="31">
         <v>0</v>
       </c>
       <c r="O21" s="29">
-        <v>43599.25</v>
+        <v>227.15</v>
       </c>
       <c r="P21" s="32">
-        <v>2.41E-2</v>
+        <v>1E-4</v>
       </c>
       <c r="Q21" s="30">
-        <v>987</v>
+        <v>52510.1</v>
       </c>
       <c r="R21" s="30">
         <v>0</v>
@@ -4257,16 +4326,16 @@
         <v>0</v>
       </c>
       <c r="T21" s="29">
-        <v>987</v>
+        <v>52510.1</v>
       </c>
       <c r="U21" s="29">
         <v>0</v>
       </c>
       <c r="V21" s="29">
-        <v>44586.25</v>
+        <v>52737.25</v>
       </c>
       <c r="W21" s="29">
-        <v>16822.599999999999</v>
+        <v>0</v>
       </c>
       <c r="X21" s="29">
         <v>0</v>
@@ -4275,19 +4344,19 @@
         <v>0</v>
       </c>
       <c r="Z21" s="31">
-        <v>65.599999999999994</v>
+        <v>75.72</v>
       </c>
       <c r="AA21" s="31">
         <v>0</v>
       </c>
       <c r="AB21" s="29">
-        <v>16888.2</v>
+        <v>75.72</v>
       </c>
       <c r="AC21" s="32">
-        <v>1.8700000000000001E-2</v>
+        <v>1E-4</v>
       </c>
       <c r="AD21" s="29">
-        <v>166.6</v>
+        <v>10881.11</v>
       </c>
       <c r="AE21" s="29">
         <v>0</v>
@@ -4296,16 +4365,16 @@
         <v>0</v>
       </c>
       <c r="AG21" s="29">
-        <v>166.6</v>
+        <v>10881.11</v>
       </c>
       <c r="AH21" s="29">
         <v>0</v>
       </c>
       <c r="AI21" s="29">
-        <v>17054.8</v>
+        <v>10956.83</v>
       </c>
       <c r="AJ21" s="33" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
       <c r="AK21" s="34"/>
       <c r="AL21" s="34"/>
@@ -5262,16 +5331,16 @@
         <v>0</v>
       </c>
       <c r="M30" s="31">
-        <v>639.07000000000005</v>
+        <v>1175.3900000000001</v>
       </c>
       <c r="N30" s="31">
         <v>0</v>
       </c>
       <c r="O30" s="29">
-        <v>639.07000000000005</v>
+        <v>1175.3900000000001</v>
       </c>
       <c r="P30" s="32">
-        <v>4.0000000000000002E-4</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="Q30" s="30">
         <v>0</v>
@@ -5289,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="29">
-        <v>639.07000000000005</v>
+        <v>1175.3900000000001</v>
       </c>
       <c r="W30" s="29">
         <v>0</v>
@@ -5301,16 +5370,16 @@
         <v>0</v>
       </c>
       <c r="Z30" s="31">
-        <v>85.19</v>
+        <v>210.02</v>
       </c>
       <c r="AA30" s="31">
         <v>0</v>
       </c>
       <c r="AB30" s="29">
-        <v>85.19</v>
+        <v>210.02</v>
       </c>
       <c r="AC30" s="32">
-        <v>1E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="AD30" s="29">
         <v>0</v>
@@ -5328,7 +5397,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="29">
-        <v>85.19</v>
+        <v>210.02</v>
       </c>
       <c r="AJ30" s="33" t="s">
         <v>81</v>
@@ -5583,13 +5652,13 @@
         <v>28</v>
       </c>
       <c r="F33" s="27">
-        <v>102825</v>
+        <v>108658</v>
       </c>
       <c r="G33" s="25" t="s">
-        <v>86</v>
+        <v>106</v>
       </c>
       <c r="H33" s="28">
-        <v>45117</v>
+        <v>45497</v>
       </c>
       <c r="I33" s="29" t="s">
         <v>30</v>
@@ -5604,13 +5673,13 @@
         <v>0</v>
       </c>
       <c r="M33" s="31">
-        <v>227.15</v>
+        <v>180.03</v>
       </c>
       <c r="N33" s="31">
         <v>0</v>
       </c>
       <c r="O33" s="29">
-        <v>227.15</v>
+        <v>180.03</v>
       </c>
       <c r="P33" s="32">
         <v>1E-4</v>
@@ -5631,7 +5700,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="29">
-        <v>227.15</v>
+        <v>180.03</v>
       </c>
       <c r="W33" s="29">
         <v>0</v>
@@ -5643,16 +5712,16 @@
         <v>0</v>
       </c>
       <c r="Z33" s="31">
-        <v>75.72</v>
+        <v>9</v>
       </c>
       <c r="AA33" s="31">
         <v>0</v>
       </c>
       <c r="AB33" s="29">
-        <v>75.72</v>
+        <v>9</v>
       </c>
       <c r="AC33" s="32">
-        <v>1E-4</v>
+        <v>0</v>
       </c>
       <c r="AD33" s="29">
         <v>0</v>
@@ -5670,10 +5739,10 @@
         <v>0</v>
       </c>
       <c r="AI33" s="29">
-        <v>75.72</v>
+        <v>9</v>
       </c>
       <c r="AJ33" s="33" t="s">
-        <v>87</v>
+        <v>107</v>
       </c>
       <c r="AK33" s="34"/>
       <c r="AL33" s="34"/>
@@ -5805,19 +5874,19 @@
         <v>2043</v>
       </c>
       <c r="D35" s="26">
-        <v>2511</v>
+        <v>2043</v>
       </c>
       <c r="E35" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F35" s="27">
-        <v>69684</v>
+        <v>109998</v>
       </c>
       <c r="G35" s="25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H35" s="28">
-        <v>44771</v>
+        <v>45596</v>
       </c>
       <c r="I35" s="29" t="s">
         <v>30</v>
@@ -5832,13 +5901,13 @@
         <v>0</v>
       </c>
       <c r="M35" s="31">
-        <v>142.55000000000001</v>
+        <v>162.5</v>
       </c>
       <c r="N35" s="31">
         <v>0</v>
       </c>
       <c r="O35" s="29">
-        <v>142.55000000000001</v>
+        <v>162.5</v>
       </c>
       <c r="P35" s="32">
         <v>1E-4</v>
@@ -5859,7 +5928,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="29">
-        <v>142.55000000000001</v>
+        <v>162.5</v>
       </c>
       <c r="W35" s="29">
         <v>0</v>
@@ -5871,13 +5940,13 @@
         <v>0</v>
       </c>
       <c r="Z35" s="31">
-        <v>19.010000000000002</v>
+        <v>21.66</v>
       </c>
       <c r="AA35" s="31">
         <v>0</v>
       </c>
       <c r="AB35" s="29">
-        <v>19.010000000000002</v>
+        <v>21.66</v>
       </c>
       <c r="AC35" s="32">
         <v>0</v>
@@ -5898,10 +5967,10 @@
         <v>0</v>
       </c>
       <c r="AI35" s="29">
-        <v>19.010000000000002</v>
+        <v>21.66</v>
       </c>
       <c r="AJ35" s="33" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AK35" s="34"/>
       <c r="AL35" s="34"/>
@@ -5919,19 +5988,19 @@
         <v>2043</v>
       </c>
       <c r="D36" s="26">
-        <v>2043</v>
+        <v>2511</v>
       </c>
       <c r="E36" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F36" s="27">
-        <v>109998</v>
+        <v>69684</v>
       </c>
       <c r="G36" s="25" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="H36" s="28">
-        <v>45596</v>
+        <v>44771</v>
       </c>
       <c r="I36" s="29" t="s">
         <v>30</v>
@@ -5946,16 +6015,16 @@
         <v>0</v>
       </c>
       <c r="M36" s="31">
-        <v>81.03</v>
+        <v>142.55000000000001</v>
       </c>
       <c r="N36" s="31">
         <v>0</v>
       </c>
       <c r="O36" s="29">
-        <v>81.03</v>
+        <v>142.55000000000001</v>
       </c>
       <c r="P36" s="32">
-        <v>0</v>
+        <v>1E-4</v>
       </c>
       <c r="Q36" s="30">
         <v>0</v>
@@ -5973,7 +6042,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="29">
-        <v>81.03</v>
+        <v>142.55000000000001</v>
       </c>
       <c r="W36" s="29">
         <v>0</v>
@@ -5985,13 +6054,13 @@
         <v>0</v>
       </c>
       <c r="Z36" s="31">
-        <v>10.8</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="AA36" s="31">
         <v>0</v>
       </c>
       <c r="AB36" s="29">
-        <v>10.8</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="AC36" s="32">
         <v>0</v>
@@ -6012,10 +6081,10 @@
         <v>0</v>
       </c>
       <c r="AI36" s="29">
-        <v>10.8</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="AJ36" s="33" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="AK36" s="34"/>
       <c r="AL36" s="34"/>
@@ -6723,13 +6792,13 @@
         <v>28</v>
       </c>
       <c r="F43" s="27">
-        <v>108658</v>
+        <v>109007</v>
       </c>
       <c r="G43" s="25" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="H43" s="28">
-        <v>45497</v>
+        <v>45525</v>
       </c>
       <c r="I43" s="29" t="s">
         <v>30</v>
@@ -6813,7 +6882,7 @@
         <v>0</v>
       </c>
       <c r="AJ43" s="33" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="AK43" s="34"/>
       <c r="AL43" s="34"/>
@@ -6831,19 +6900,19 @@
         <v>2043</v>
       </c>
       <c r="D44" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E44" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F44" s="27">
-        <v>109007</v>
+        <v>109819</v>
       </c>
       <c r="G44" s="25" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="H44" s="28">
-        <v>45525</v>
+        <v>45562</v>
       </c>
       <c r="I44" s="29" t="s">
         <v>30</v>
@@ -6927,7 +6996,7 @@
         <v>0</v>
       </c>
       <c r="AJ44" s="33" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="AK44" s="34"/>
       <c r="AL44" s="34"/>
@@ -6945,19 +7014,19 @@
         <v>2043</v>
       </c>
       <c r="D45" s="26">
-        <v>2856</v>
+        <v>2692</v>
       </c>
       <c r="E45" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F45" s="27">
-        <v>109819</v>
+        <v>110575</v>
       </c>
       <c r="G45" s="25" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="H45" s="28">
-        <v>45562</v>
+        <v>45583</v>
       </c>
       <c r="I45" s="29" t="s">
         <v>30</v>
@@ -7041,7 +7110,7 @@
         <v>0</v>
       </c>
       <c r="AJ45" s="33" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AK45" s="34"/>
       <c r="AL45" s="34"/>
@@ -7059,19 +7128,19 @@
         <v>2043</v>
       </c>
       <c r="D46" s="26">
-        <v>2692</v>
+        <v>2856</v>
       </c>
       <c r="E46" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="27">
-        <v>110575</v>
+        <v>111960</v>
       </c>
       <c r="G46" s="25" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H46" s="28">
-        <v>45583</v>
+        <v>45707</v>
       </c>
       <c r="I46" s="29" t="s">
         <v>30</v>
@@ -7155,7 +7224,7 @@
         <v>0</v>
       </c>
       <c r="AJ46" s="33" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="AK46" s="34"/>
       <c r="AL46" s="34"/>
@@ -7173,19 +7242,19 @@
         <v>2043</v>
       </c>
       <c r="D47" s="26">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E47" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F47" s="27">
-        <v>111960</v>
+        <v>112083</v>
       </c>
       <c r="G47" s="25" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="H47" s="28">
-        <v>45707</v>
+        <v>45736</v>
       </c>
       <c r="I47" s="29" t="s">
         <v>30</v>
@@ -7269,7 +7338,7 @@
         <v>0</v>
       </c>
       <c r="AJ47" s="33" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="AK47" s="34"/>
       <c r="AL47" s="34"/>
@@ -7287,19 +7356,19 @@
         <v>2043</v>
       </c>
       <c r="D48" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E48" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F48" s="27">
-        <v>112083</v>
+        <v>112522</v>
       </c>
       <c r="G48" s="25" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="H48" s="28">
-        <v>45736</v>
+        <v>45776</v>
       </c>
       <c r="I48" s="29" t="s">
         <v>30</v>
@@ -7383,7 +7452,7 @@
         <v>0</v>
       </c>
       <c r="AJ48" s="33" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="AK48" s="34"/>
       <c r="AL48" s="34"/>
@@ -7401,19 +7470,19 @@
         <v>2043</v>
       </c>
       <c r="D49" s="26">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E49" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F49" s="27">
-        <v>112522</v>
+        <v>113076</v>
       </c>
       <c r="G49" s="25" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H49" s="28">
-        <v>45776</v>
+        <v>45806</v>
       </c>
       <c r="I49" s="29" t="s">
         <v>30</v>
@@ -7497,7 +7566,7 @@
         <v>0</v>
       </c>
       <c r="AJ49" s="33" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="AK49" s="34"/>
       <c r="AL49" s="34"/>
@@ -7515,19 +7584,19 @@
         <v>2043</v>
       </c>
       <c r="D50" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E50" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F50" s="27">
-        <v>113076</v>
+        <v>114100</v>
       </c>
       <c r="G50" s="25" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="H50" s="28">
-        <v>45806</v>
+        <v>45863</v>
       </c>
       <c r="I50" s="29" t="s">
         <v>30</v>
@@ -7611,7 +7680,7 @@
         <v>0</v>
       </c>
       <c r="AJ50" s="33" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="AK50" s="34"/>
       <c r="AL50" s="34"/>
@@ -7629,19 +7698,19 @@
         <v>2043</v>
       </c>
       <c r="D51" s="26">
-        <v>2856</v>
+        <v>2692</v>
       </c>
       <c r="E51" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F51" s="27">
-        <v>114100</v>
+        <v>114157</v>
       </c>
       <c r="G51" s="25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="H51" s="28">
-        <v>45863</v>
+        <v>45904</v>
       </c>
       <c r="I51" s="29" t="s">
         <v>30</v>
@@ -7725,7 +7794,7 @@
         <v>0</v>
       </c>
       <c r="AJ51" s="33" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AK51" s="34"/>
       <c r="AL51" s="34"/>
@@ -7749,13 +7818,13 @@
         <v>28</v>
       </c>
       <c r="F52" s="27">
-        <v>114157</v>
+        <v>114431</v>
       </c>
       <c r="G52" s="25" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="H52" s="28">
-        <v>45904</v>
+        <v>45930</v>
       </c>
       <c r="I52" s="29" t="s">
         <v>30</v>
@@ -7839,7 +7908,7 @@
         <v>0</v>
       </c>
       <c r="AJ52" s="33" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AK52" s="34"/>
       <c r="AL52" s="34"/>
@@ -7857,25 +7926,25 @@
         <v>2043</v>
       </c>
       <c r="D53" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E53" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F53" s="27">
-        <v>114431</v>
+        <v>95148</v>
       </c>
       <c r="G53" s="25" t="s">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="H53" s="28">
-        <v>45930</v>
+        <v>44916</v>
       </c>
       <c r="I53" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J53" s="30">
-        <v>0</v>
+        <v>46057.760000000002</v>
       </c>
       <c r="K53" s="30">
         <v>0</v>
@@ -7890,31 +7959,31 @@
         <v>0</v>
       </c>
       <c r="O53" s="29">
-        <v>0</v>
+        <v>46057.760000000002</v>
       </c>
       <c r="P53" s="32">
-        <v>0</v>
+        <v>2.5399999999999999E-2</v>
       </c>
       <c r="Q53" s="30">
-        <v>0</v>
+        <v>23133.08</v>
       </c>
       <c r="R53" s="30">
         <v>0</v>
       </c>
       <c r="S53" s="30">
-        <v>0</v>
+        <v>69825</v>
       </c>
       <c r="T53" s="29">
-        <v>0</v>
+        <v>-46691.92</v>
       </c>
       <c r="U53" s="29">
         <v>0</v>
       </c>
       <c r="V53" s="29">
-        <v>0</v>
+        <v>-634.16</v>
       </c>
       <c r="W53" s="29">
-        <v>0</v>
+        <v>13817.33</v>
       </c>
       <c r="X53" s="29">
         <v>0</v>
@@ -7929,31 +7998,31 @@
         <v>0</v>
       </c>
       <c r="AB53" s="29">
-        <v>0</v>
+        <v>13817.33</v>
       </c>
       <c r="AC53" s="32">
-        <v>0</v>
+        <v>1.5299999999999999E-2</v>
       </c>
       <c r="AD53" s="29">
-        <v>0</v>
+        <v>4744.3599999999997</v>
       </c>
       <c r="AE53" s="29">
         <v>0</v>
       </c>
       <c r="AF53" s="29">
-        <v>0</v>
+        <v>15103</v>
       </c>
       <c r="AG53" s="29">
-        <v>0</v>
+        <v>-10358.64</v>
       </c>
       <c r="AH53" s="29">
         <v>0</v>
       </c>
       <c r="AI53" s="29">
-        <v>0</v>
+        <v>3458.69</v>
       </c>
       <c r="AJ53" s="33" t="s">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="AK53" s="34"/>
       <c r="AL53" s="34"/>
@@ -7962,22 +8031,22 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A6:AI53 AK6:AK53 AM6:AN53">
-    <cfRule type="expression" dxfId="44" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:V53 AI6:AI53 AN6:AN53">
-    <cfRule type="expression" dxfId="43" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL6:AL53">
-    <cfRule type="expression" dxfId="42" priority="2" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK43:AN53">
-    <cfRule type="expression" dxfId="41" priority="1" stopIfTrue="1">
+    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
       <formula>$B43&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>

--- a/mdrt/MDRT.xlsx
+++ b/mdrt/MDRT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/mdrt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7CBD6F7-4FC7-E84B-A4FD-27DA3370E8C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B94AFF-67B2-344F-B608-A57BA2AFDF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="1480" windowWidth="24460" windowHeight="15320" xr2:uid="{263D14F0-BAEF-1E4F-83AF-E2F80B31AC70}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{263D14F0-BAEF-1E4F-83AF-E2F80B31AC70}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="332" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="141">
   <si>
     <t>Dir / Zona</t>
   </si>
@@ -387,12 +387,6 @@
     <t>HEMC050122FT4</t>
   </si>
   <si>
-    <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
-  </si>
-  <si>
-    <t>OUFL8603105M2</t>
-  </si>
-  <si>
     <t>LAURA DOLORES MONTAÐO MONTAÐO</t>
   </si>
   <si>
@@ -465,7 +459,7 @@
     <t>Columna15</t>
   </si>
   <si>
-    <t>Avance del 1 de enero al 28 de febrero de 2026.</t>
+    <t>Avance del 1 de enero al 11 de marzo de 2026.</t>
   </si>
 </sst>
 </file>
@@ -2384,7 +2378,7 @@
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A1" s="36" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4" spans="1:40" ht="28" x14ac:dyDescent="0.2">
@@ -2443,7 +2437,7 @@
         <v>17</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="T4" s="4" t="s">
         <v>18</v>
@@ -2455,46 +2449,46 @@
         <v>20</v>
       </c>
       <c r="W4" s="6" t="s">
+        <v>127</v>
+      </c>
+      <c r="X4" s="6" t="s">
+        <v>128</v>
+      </c>
+      <c r="Y4" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="X4" s="6" t="s">
+      <c r="Z4" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="AA4" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="Z4" s="6" t="s">
+      <c r="AB4" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="AA4" s="6" t="s">
+      <c r="AC4" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="AB4" s="7" t="s">
+      <c r="AD4" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="AC4" s="8" t="s">
+      <c r="AE4" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="AD4" s="6" t="s">
+      <c r="AF4" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="AE4" s="6" t="s">
+      <c r="AG4" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="AF4" s="6" t="s">
+      <c r="AH4" s="6" t="s">
         <v>138</v>
-      </c>
-      <c r="AG4" s="6" t="s">
-        <v>139</v>
-      </c>
-      <c r="AH4" s="6" t="s">
-        <v>140</v>
       </c>
       <c r="AI4" s="9" t="s">
         <v>21</v>
       </c>
       <c r="AJ4" s="10" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="AK4" s="11" t="s">
         <v>22</v>
@@ -2580,7 +2574,7 @@
         <v>30</v>
       </c>
       <c r="J6" s="30">
-        <v>85231.8</v>
+        <v>421824.04</v>
       </c>
       <c r="K6" s="30">
         <v>0</v>
@@ -2589,19 +2583,19 @@
         <v>0</v>
       </c>
       <c r="M6" s="31">
-        <v>111996.34</v>
+        <v>112071.44</v>
       </c>
       <c r="N6" s="31">
         <v>0</v>
       </c>
       <c r="O6" s="29">
-        <v>197228.14</v>
+        <v>533895.48</v>
       </c>
       <c r="P6" s="32">
-        <v>0.1089</v>
+        <v>0.2949</v>
       </c>
       <c r="Q6" s="30">
-        <v>234634.12</v>
+        <v>338670.94</v>
       </c>
       <c r="R6" s="30">
         <v>0</v>
@@ -2610,16 +2604,16 @@
         <v>0</v>
       </c>
       <c r="T6" s="29">
-        <v>234634.12</v>
+        <v>338670.94</v>
       </c>
       <c r="U6" s="29">
         <v>0</v>
       </c>
       <c r="V6" s="29">
-        <v>431862.26</v>
+        <v>872566.42</v>
       </c>
       <c r="W6" s="29">
-        <v>31315.439999999999</v>
+        <v>149289.39000000001</v>
       </c>
       <c r="X6" s="29">
         <v>0</v>
@@ -2628,19 +2622,19 @@
         <v>0</v>
       </c>
       <c r="Z6" s="31">
-        <v>6079.3</v>
+        <v>6089.32</v>
       </c>
       <c r="AA6" s="31">
         <v>0</v>
       </c>
       <c r="AB6" s="29">
-        <v>37394.74</v>
+        <v>155378.71</v>
       </c>
       <c r="AC6" s="32">
-        <v>4.1300000000000003E-2</v>
+        <v>0.17169999999999999</v>
       </c>
       <c r="AD6" s="29">
-        <v>51259.519999999997</v>
+        <v>73124.62</v>
       </c>
       <c r="AE6" s="29">
         <v>0</v>
@@ -2649,13 +2643,13 @@
         <v>0</v>
       </c>
       <c r="AG6" s="29">
-        <v>51259.519999999997</v>
+        <v>73124.62</v>
       </c>
       <c r="AH6" s="29">
         <v>0</v>
       </c>
       <c r="AI6" s="29">
-        <v>88654.26</v>
+        <v>228503.33</v>
       </c>
       <c r="AJ6" s="33" t="s">
         <v>31</v>
@@ -2666,7 +2660,9 @@
       <c r="AL6" s="34" t="s">
         <v>33</v>
       </c>
-      <c r="AM6" s="34"/>
+      <c r="AM6" s="34" t="s">
+        <v>32</v>
+      </c>
       <c r="AN6" s="35" t="s">
         <v>32</v>
       </c>
@@ -2721,7 +2717,7 @@
         <v>0</v>
       </c>
       <c r="Q7" s="30">
-        <v>187050.51</v>
+        <v>235038.77</v>
       </c>
       <c r="R7" s="30">
         <v>0</v>
@@ -2730,13 +2726,13 @@
         <v>0</v>
       </c>
       <c r="T7" s="29">
-        <v>187050.51</v>
+        <v>235038.77</v>
       </c>
       <c r="U7" s="29">
         <v>0</v>
       </c>
       <c r="V7" s="29">
-        <v>187050.51</v>
+        <v>235038.77</v>
       </c>
       <c r="W7" s="29">
         <v>0</v>
@@ -2760,7 +2756,7 @@
         <v>0</v>
       </c>
       <c r="AD7" s="29">
-        <v>27056.3</v>
+        <v>37294.720000000001</v>
       </c>
       <c r="AE7" s="29">
         <v>0</v>
@@ -2769,13 +2765,13 @@
         <v>0</v>
       </c>
       <c r="AG7" s="29">
-        <v>27056.3</v>
+        <v>37294.720000000001</v>
       </c>
       <c r="AH7" s="29">
         <v>0</v>
       </c>
       <c r="AI7" s="29">
-        <v>27056.3</v>
+        <v>37294.720000000001</v>
       </c>
       <c r="AJ7" s="33" t="s">
         <v>35</v>
@@ -2814,7 +2810,7 @@
         <v>30</v>
       </c>
       <c r="J8" s="30">
-        <v>160127.31</v>
+        <v>206465.86</v>
       </c>
       <c r="K8" s="30">
         <v>0</v>
@@ -2823,16 +2819,16 @@
         <v>0</v>
       </c>
       <c r="M8" s="31">
-        <v>182.07</v>
+        <v>261.17</v>
       </c>
       <c r="N8" s="31">
         <v>0</v>
       </c>
       <c r="O8" s="29">
-        <v>160309.38</v>
+        <v>206727.03</v>
       </c>
       <c r="P8" s="32">
-        <v>8.8499999999999995E-2</v>
+        <v>0.1142</v>
       </c>
       <c r="Q8" s="30">
         <v>0</v>
@@ -2850,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="V8" s="29">
-        <v>160309.38</v>
+        <v>206727.03</v>
       </c>
       <c r="W8" s="29">
-        <v>53991.06</v>
+        <v>66502.47</v>
       </c>
       <c r="X8" s="29">
         <v>0</v>
@@ -2862,16 +2858,16 @@
         <v>0</v>
       </c>
       <c r="Z8" s="31">
-        <v>24.28</v>
+        <v>34.82</v>
       </c>
       <c r="AA8" s="31">
         <v>0</v>
       </c>
       <c r="AB8" s="29">
-        <v>54015.34</v>
+        <v>66537.289999999994</v>
       </c>
       <c r="AC8" s="32">
-        <v>5.9700000000000003E-2</v>
+        <v>7.3499999999999996E-2</v>
       </c>
       <c r="AD8" s="29">
         <v>0</v>
@@ -2889,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="29">
-        <v>54015.34</v>
+        <v>66537.289999999994</v>
       </c>
       <c r="AJ8" s="33" t="s">
         <v>41</v>
@@ -2937,19 +2933,19 @@
         <v>0</v>
       </c>
       <c r="M9" s="31">
-        <v>1420.84</v>
+        <v>1628.27</v>
       </c>
       <c r="N9" s="31">
         <v>0</v>
       </c>
       <c r="O9" s="29">
-        <v>112903.66</v>
+        <v>113111.09</v>
       </c>
       <c r="P9" s="32">
-        <v>6.2399999999999997E-2</v>
+        <v>6.25E-2</v>
       </c>
       <c r="Q9" s="30">
-        <v>27671.29</v>
+        <v>64612.59</v>
       </c>
       <c r="R9" s="30">
         <v>0</v>
@@ -2958,13 +2954,13 @@
         <v>0</v>
       </c>
       <c r="T9" s="29">
-        <v>27671.29</v>
+        <v>64612.59</v>
       </c>
       <c r="U9" s="29">
         <v>0</v>
       </c>
       <c r="V9" s="29">
-        <v>140574.95000000001</v>
+        <v>177723.68</v>
       </c>
       <c r="W9" s="29">
         <v>30100.36</v>
@@ -2976,19 +2972,19 @@
         <v>0</v>
       </c>
       <c r="Z9" s="31">
-        <v>380.49</v>
+        <v>384.6</v>
       </c>
       <c r="AA9" s="31">
         <v>0</v>
       </c>
       <c r="AB9" s="29">
-        <v>30480.85</v>
+        <v>30484.959999999999</v>
       </c>
       <c r="AC9" s="32">
         <v>3.3700000000000001E-2</v>
       </c>
       <c r="AD9" s="29">
-        <v>4203.3999999999996</v>
+        <v>11978.48</v>
       </c>
       <c r="AE9" s="29">
         <v>0</v>
@@ -2997,13 +2993,13 @@
         <v>0</v>
       </c>
       <c r="AG9" s="29">
-        <v>4203.3999999999996</v>
+        <v>11978.48</v>
       </c>
       <c r="AH9" s="29">
         <v>0</v>
       </c>
       <c r="AI9" s="29">
-        <v>34684.25</v>
+        <v>42463.44</v>
       </c>
       <c r="AJ9" s="33" t="s">
         <v>37</v>
@@ -3024,25 +3020,25 @@
         <v>2043</v>
       </c>
       <c r="D10" s="26">
-        <v>2043</v>
+        <v>2692</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F10" s="27">
-        <v>90355</v>
+        <v>104750</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>38</v>
+        <v>62</v>
       </c>
       <c r="H10" s="28">
-        <v>43949</v>
+        <v>45236</v>
       </c>
       <c r="I10" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J10" s="30">
-        <v>126885.75999999999</v>
+        <v>63710.97</v>
       </c>
       <c r="K10" s="30">
         <v>0</v>
@@ -3051,19 +3047,19 @@
         <v>0</v>
       </c>
       <c r="M10" s="31">
-        <v>12467.08</v>
+        <v>863.39</v>
       </c>
       <c r="N10" s="31">
         <v>0</v>
       </c>
       <c r="O10" s="29">
-        <v>139352.84</v>
+        <v>64574.36</v>
       </c>
       <c r="P10" s="32">
-        <v>7.6999999999999999E-2</v>
+        <v>3.5700000000000003E-2</v>
       </c>
       <c r="Q10" s="30">
-        <v>0</v>
+        <v>105832.02</v>
       </c>
       <c r="R10" s="30">
         <v>0</v>
@@ -3072,16 +3068,16 @@
         <v>0</v>
       </c>
       <c r="T10" s="29">
-        <v>0</v>
+        <v>105832.02</v>
       </c>
       <c r="U10" s="29">
         <v>0</v>
       </c>
       <c r="V10" s="29">
-        <v>139352.84</v>
+        <v>170406.38</v>
       </c>
       <c r="W10" s="29">
-        <v>50742.080000000002</v>
+        <v>24068.240000000002</v>
       </c>
       <c r="X10" s="29">
         <v>0</v>
@@ -3090,19 +3086,19 @@
         <v>0</v>
       </c>
       <c r="Z10" s="31">
-        <v>691.39</v>
+        <v>102.04</v>
       </c>
       <c r="AA10" s="31">
         <v>0</v>
       </c>
       <c r="AB10" s="29">
-        <v>51433.47</v>
+        <v>24170.28</v>
       </c>
       <c r="AC10" s="32">
-        <v>5.6800000000000003E-2</v>
+        <v>2.6700000000000002E-2</v>
       </c>
       <c r="AD10" s="29">
-        <v>0</v>
+        <v>12800.69</v>
       </c>
       <c r="AE10" s="29">
         <v>0</v>
@@ -3111,16 +3107,16 @@
         <v>0</v>
       </c>
       <c r="AG10" s="29">
-        <v>0</v>
+        <v>12800.69</v>
       </c>
       <c r="AH10" s="29">
         <v>0</v>
       </c>
       <c r="AI10" s="29">
-        <v>51433.47</v>
+        <v>36970.97</v>
       </c>
       <c r="AJ10" s="33" t="s">
-        <v>39</v>
+        <v>63</v>
       </c>
       <c r="AK10" s="34"/>
       <c r="AL10" s="34"/>
@@ -3156,7 +3152,7 @@
         <v>30</v>
       </c>
       <c r="J11" s="30">
-        <v>44654.68</v>
+        <v>75285.279999999999</v>
       </c>
       <c r="K11" s="30">
         <v>0</v>
@@ -3165,16 +3161,16 @@
         <v>0</v>
       </c>
       <c r="M11" s="31">
-        <v>80288.14</v>
+        <v>86219.62</v>
       </c>
       <c r="N11" s="31">
         <v>0</v>
       </c>
       <c r="O11" s="29">
-        <v>124942.82</v>
+        <v>161504.9</v>
       </c>
       <c r="P11" s="32">
-        <v>6.9000000000000006E-2</v>
+        <v>8.9200000000000002E-2</v>
       </c>
       <c r="Q11" s="30">
         <v>0</v>
@@ -3192,10 +3188,10 @@
         <v>0</v>
       </c>
       <c r="V11" s="29">
-        <v>124942.82</v>
+        <v>161504.9</v>
       </c>
       <c r="W11" s="29">
-        <v>15543.06</v>
+        <v>25150.62</v>
       </c>
       <c r="X11" s="29">
         <v>0</v>
@@ -3204,16 +3200,16 @@
         <v>0</v>
       </c>
       <c r="Z11" s="31">
-        <v>4401.03</v>
+        <v>5178.3900000000003</v>
       </c>
       <c r="AA11" s="31">
         <v>0</v>
       </c>
       <c r="AB11" s="29">
-        <v>19944.09</v>
+        <v>30329.01</v>
       </c>
       <c r="AC11" s="32">
-        <v>2.1999999999999999E-2</v>
+        <v>3.3500000000000002E-2</v>
       </c>
       <c r="AD11" s="29">
         <v>0</v>
@@ -3231,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="29">
-        <v>19944.09</v>
+        <v>30329.01</v>
       </c>
       <c r="AJ11" s="33" t="s">
         <v>47</v>
@@ -3252,25 +3248,25 @@
         <v>2043</v>
       </c>
       <c r="D12" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E12" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F12" s="27">
-        <v>104718</v>
+        <v>90355</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H12" s="28">
-        <v>45264</v>
+        <v>43949</v>
       </c>
       <c r="I12" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J12" s="30">
-        <v>86224.02</v>
+        <v>126885.75999999999</v>
       </c>
       <c r="K12" s="30">
         <v>0</v>
@@ -3279,19 +3275,19 @@
         <v>0</v>
       </c>
       <c r="M12" s="31">
-        <v>338.11</v>
+        <v>21689.7</v>
       </c>
       <c r="N12" s="31">
         <v>0</v>
       </c>
       <c r="O12" s="29">
-        <v>86562.13</v>
+        <v>148575.46</v>
       </c>
       <c r="P12" s="32">
-        <v>4.7800000000000002E-2</v>
+        <v>8.2100000000000006E-2</v>
       </c>
       <c r="Q12" s="30">
-        <v>31773.599999999999</v>
+        <v>0</v>
       </c>
       <c r="R12" s="30">
         <v>0</v>
@@ -3300,16 +3296,16 @@
         <v>0</v>
       </c>
       <c r="T12" s="29">
-        <v>31773.599999999999</v>
+        <v>0</v>
       </c>
       <c r="U12" s="29">
         <v>0</v>
       </c>
       <c r="V12" s="29">
-        <v>118335.73</v>
+        <v>148575.46</v>
       </c>
       <c r="W12" s="29">
-        <v>26969.599999999999</v>
+        <v>50742.080000000002</v>
       </c>
       <c r="X12" s="29">
         <v>0</v>
@@ -3318,19 +3314,19 @@
         <v>0</v>
       </c>
       <c r="Z12" s="31">
-        <v>21.08</v>
+        <v>1141.54</v>
       </c>
       <c r="AA12" s="31">
         <v>0</v>
       </c>
       <c r="AB12" s="29">
-        <v>26990.68</v>
+        <v>51883.62</v>
       </c>
       <c r="AC12" s="32">
-        <v>2.98E-2</v>
+        <v>5.7299999999999997E-2</v>
       </c>
       <c r="AD12" s="29">
-        <v>6601.68</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="29">
         <v>0</v>
@@ -3339,16 +3335,16 @@
         <v>0</v>
       </c>
       <c r="AG12" s="29">
-        <v>6601.68</v>
+        <v>0</v>
       </c>
       <c r="AH12" s="29">
         <v>0</v>
       </c>
       <c r="AI12" s="29">
-        <v>33592.36</v>
+        <v>51883.62</v>
       </c>
       <c r="AJ12" s="33" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="AK12" s="34"/>
       <c r="AL12" s="34"/>
@@ -3366,25 +3362,25 @@
         <v>2043</v>
       </c>
       <c r="D13" s="26">
-        <v>2856</v>
+        <v>2692</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F13" s="27">
-        <v>115047</v>
+        <v>104718</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H13" s="28">
-        <v>45944</v>
+        <v>45264</v>
       </c>
       <c r="I13" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J13" s="30">
-        <v>0</v>
+        <v>86224.02</v>
       </c>
       <c r="K13" s="30">
         <v>0</v>
@@ -3393,19 +3389,19 @@
         <v>0</v>
       </c>
       <c r="M13" s="31">
-        <v>278.49</v>
+        <v>338.11</v>
       </c>
       <c r="N13" s="31">
         <v>0</v>
       </c>
       <c r="O13" s="29">
-        <v>51598.62</v>
+        <v>86562.13</v>
       </c>
       <c r="P13" s="32">
-        <v>2.8500000000000001E-2</v>
+        <v>4.7800000000000002E-2</v>
       </c>
       <c r="Q13" s="30">
-        <v>40110.959999999999</v>
+        <v>31773.599999999999</v>
       </c>
       <c r="R13" s="30">
         <v>0</v>
@@ -3414,16 +3410,16 @@
         <v>0</v>
       </c>
       <c r="T13" s="29">
-        <v>49236.79</v>
+        <v>31773.599999999999</v>
       </c>
       <c r="U13" s="29">
-        <v>60445.96</v>
+        <v>0</v>
       </c>
       <c r="V13" s="29">
-        <v>100835.41</v>
+        <v>118335.73</v>
       </c>
       <c r="W13" s="29">
-        <v>0</v>
+        <v>26969.599999999999</v>
       </c>
       <c r="X13" s="29">
         <v>0</v>
@@ -3432,19 +3428,19 @@
         <v>0</v>
       </c>
       <c r="Z13" s="31">
-        <v>37.14</v>
+        <v>21.08</v>
       </c>
       <c r="AA13" s="31">
         <v>0</v>
       </c>
       <c r="AB13" s="29">
-        <v>15433.18</v>
+        <v>26990.68</v>
       </c>
       <c r="AC13" s="32">
-        <v>1.7000000000000001E-2</v>
+        <v>2.98E-2</v>
       </c>
       <c r="AD13" s="29">
-        <v>8472.36</v>
+        <v>6601.68</v>
       </c>
       <c r="AE13" s="29">
         <v>0</v>
@@ -3453,16 +3449,16 @@
         <v>0</v>
       </c>
       <c r="AG13" s="29">
-        <v>10021.94</v>
+        <v>6601.68</v>
       </c>
       <c r="AH13" s="29">
-        <v>16945.62</v>
+        <v>0</v>
       </c>
       <c r="AI13" s="29">
-        <v>25455.119999999999</v>
+        <v>33592.36</v>
       </c>
       <c r="AJ13" s="33" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK13" s="34"/>
       <c r="AL13" s="34"/>
@@ -3486,19 +3482,19 @@
         <v>28</v>
       </c>
       <c r="F14" s="27">
-        <v>107488</v>
+        <v>47116</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="H14" s="28">
-        <v>45440</v>
+        <v>44616</v>
       </c>
       <c r="I14" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J14" s="30">
-        <v>0</v>
+        <v>61796.57</v>
       </c>
       <c r="K14" s="30">
         <v>0</v>
@@ -3507,19 +3503,19 @@
         <v>0</v>
       </c>
       <c r="M14" s="31">
-        <v>157.72</v>
+        <v>4230.62</v>
       </c>
       <c r="N14" s="31">
         <v>0</v>
       </c>
       <c r="O14" s="29">
-        <v>157.72</v>
+        <v>66027.19</v>
       </c>
       <c r="P14" s="32">
-        <v>1E-4</v>
+        <v>3.6499999999999998E-2</v>
       </c>
       <c r="Q14" s="30">
-        <v>98471.17</v>
+        <v>50792.35</v>
       </c>
       <c r="R14" s="30">
         <v>0</v>
@@ -3528,16 +3524,16 @@
         <v>0</v>
       </c>
       <c r="T14" s="29">
-        <v>98471.17</v>
+        <v>50792.35</v>
       </c>
       <c r="U14" s="29">
         <v>0</v>
       </c>
       <c r="V14" s="29">
-        <v>98628.89</v>
+        <v>116819.54</v>
       </c>
       <c r="W14" s="29">
-        <v>0</v>
+        <v>18538.98</v>
       </c>
       <c r="X14" s="29">
         <v>0</v>
@@ -3546,19 +3542,19 @@
         <v>0</v>
       </c>
       <c r="Z14" s="31">
-        <v>21.03</v>
+        <v>647.51</v>
       </c>
       <c r="AA14" s="31">
         <v>0</v>
       </c>
       <c r="AB14" s="29">
-        <v>21.03</v>
+        <v>19186.490000000002</v>
       </c>
       <c r="AC14" s="32">
-        <v>0</v>
+        <v>2.12E-2</v>
       </c>
       <c r="AD14" s="29">
-        <v>21311.65</v>
+        <v>9868.51</v>
       </c>
       <c r="AE14" s="29">
         <v>0</v>
@@ -3567,16 +3563,16 @@
         <v>0</v>
       </c>
       <c r="AG14" s="29">
-        <v>21311.65</v>
+        <v>9868.51</v>
       </c>
       <c r="AH14" s="29">
         <v>0</v>
       </c>
       <c r="AI14" s="29">
-        <v>21332.68</v>
+        <v>29055</v>
       </c>
       <c r="AJ14" s="33" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="AK14" s="34"/>
       <c r="AL14" s="34"/>
@@ -3594,25 +3590,25 @@
         <v>2043</v>
       </c>
       <c r="D15" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E15" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F15" s="27">
-        <v>47116</v>
+        <v>115047</v>
       </c>
       <c r="G15" s="25" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H15" s="28">
-        <v>44616</v>
+        <v>45944</v>
       </c>
       <c r="I15" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J15" s="30">
-        <v>61796.57</v>
+        <v>0</v>
       </c>
       <c r="K15" s="30">
         <v>0</v>
@@ -3621,19 +3617,19 @@
         <v>0</v>
       </c>
       <c r="M15" s="31">
-        <v>3525.17</v>
+        <v>701.1</v>
       </c>
       <c r="N15" s="31">
         <v>0</v>
       </c>
       <c r="O15" s="29">
-        <v>65321.74</v>
+        <v>52021.23</v>
       </c>
       <c r="P15" s="32">
-        <v>3.61E-2</v>
+        <v>2.87E-2</v>
       </c>
       <c r="Q15" s="30">
-        <v>28537.5</v>
+        <v>40110.959999999999</v>
       </c>
       <c r="R15" s="30">
         <v>0</v>
@@ -3642,16 +3638,16 @@
         <v>0</v>
       </c>
       <c r="T15" s="29">
-        <v>28537.5</v>
+        <v>49236.79</v>
       </c>
       <c r="U15" s="29">
-        <v>0</v>
+        <v>60445.96</v>
       </c>
       <c r="V15" s="29">
-        <v>93859.24</v>
+        <v>101258.02</v>
       </c>
       <c r="W15" s="29">
-        <v>18538.98</v>
+        <v>0</v>
       </c>
       <c r="X15" s="29">
         <v>0</v>
@@ -3660,19 +3656,19 @@
         <v>0</v>
       </c>
       <c r="Z15" s="31">
-        <v>559.63</v>
+        <v>93.49</v>
       </c>
       <c r="AA15" s="31">
         <v>0</v>
       </c>
       <c r="AB15" s="29">
-        <v>19098.61</v>
+        <v>15489.53</v>
       </c>
       <c r="AC15" s="32">
-        <v>2.1100000000000001E-2</v>
+        <v>1.7100000000000001E-2</v>
       </c>
       <c r="AD15" s="29">
-        <v>5942.74</v>
+        <v>8472.36</v>
       </c>
       <c r="AE15" s="29">
         <v>0</v>
@@ -3681,16 +3677,16 @@
         <v>0</v>
       </c>
       <c r="AG15" s="29">
-        <v>5942.74</v>
+        <v>10021.94</v>
       </c>
       <c r="AH15" s="29">
-        <v>0</v>
+        <v>16945.62</v>
       </c>
       <c r="AI15" s="29">
-        <v>25041.35</v>
+        <v>25511.47</v>
       </c>
       <c r="AJ15" s="33" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AK15" s="34"/>
       <c r="AL15" s="34"/>
@@ -3714,19 +3710,19 @@
         <v>28</v>
       </c>
       <c r="F16" s="27">
-        <v>115404</v>
+        <v>107488</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H16" s="28">
-        <v>45986</v>
+        <v>45440</v>
       </c>
       <c r="I16" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J16" s="30">
-        <v>29852.74</v>
+        <v>0</v>
       </c>
       <c r="K16" s="30">
         <v>0</v>
@@ -3735,19 +3731,19 @@
         <v>0</v>
       </c>
       <c r="M16" s="31">
-        <v>0</v>
+        <v>157.72</v>
       </c>
       <c r="N16" s="31">
         <v>0</v>
       </c>
       <c r="O16" s="29">
-        <v>29852.74</v>
+        <v>157.72</v>
       </c>
       <c r="P16" s="32">
-        <v>1.6500000000000001E-2</v>
+        <v>1E-4</v>
       </c>
       <c r="Q16" s="30">
-        <v>53684.13</v>
+        <v>98471.17</v>
       </c>
       <c r="R16" s="30">
         <v>0</v>
@@ -3756,16 +3752,16 @@
         <v>0</v>
       </c>
       <c r="T16" s="29">
-        <v>53684.13</v>
+        <v>98471.17</v>
       </c>
       <c r="U16" s="29">
         <v>0</v>
       </c>
       <c r="V16" s="29">
-        <v>83536.87</v>
+        <v>98628.89</v>
       </c>
       <c r="W16" s="29">
-        <v>10448.459999999999</v>
+        <v>0</v>
       </c>
       <c r="X16" s="29">
         <v>0</v>
@@ -3774,19 +3770,19 @@
         <v>0</v>
       </c>
       <c r="Z16" s="31">
-        <v>0</v>
+        <v>21.03</v>
       </c>
       <c r="AA16" s="31">
         <v>0</v>
       </c>
       <c r="AB16" s="29">
-        <v>10448.459999999999</v>
+        <v>21.03</v>
       </c>
       <c r="AC16" s="32">
-        <v>1.15E-2</v>
+        <v>0</v>
       </c>
       <c r="AD16" s="29">
-        <v>10754.34</v>
+        <v>21311.65</v>
       </c>
       <c r="AE16" s="29">
         <v>0</v>
@@ -3795,16 +3791,16 @@
         <v>0</v>
       </c>
       <c r="AG16" s="29">
-        <v>10754.34</v>
+        <v>21311.65</v>
       </c>
       <c r="AH16" s="29">
         <v>0</v>
       </c>
       <c r="AI16" s="29">
-        <v>21202.799999999999</v>
+        <v>21332.68</v>
       </c>
       <c r="AJ16" s="33" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="AK16" s="34"/>
       <c r="AL16" s="34"/>
@@ -3822,25 +3818,25 @@
         <v>2043</v>
       </c>
       <c r="D17" s="26">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E17" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F17" s="27">
-        <v>116060</v>
+        <v>115404</v>
       </c>
       <c r="G17" s="25" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H17" s="28">
-        <v>46010</v>
+        <v>45986</v>
       </c>
       <c r="I17" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J17" s="30">
-        <v>21769.200000000001</v>
+        <v>29852.74</v>
       </c>
       <c r="K17" s="30">
         <v>0</v>
@@ -3855,13 +3851,13 @@
         <v>0</v>
       </c>
       <c r="O17" s="29">
-        <v>52038.66</v>
+        <v>29852.74</v>
       </c>
       <c r="P17" s="32">
-        <v>2.87E-2</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="Q17" s="30">
-        <v>30604.240000000002</v>
+        <v>53684.13</v>
       </c>
       <c r="R17" s="30">
         <v>0</v>
@@ -3870,16 +3866,16 @@
         <v>0</v>
       </c>
       <c r="T17" s="29">
-        <v>30604.240000000002</v>
+        <v>53684.13</v>
       </c>
       <c r="U17" s="29">
-        <v>30269.46</v>
+        <v>0</v>
       </c>
       <c r="V17" s="29">
-        <v>82642.899999999994</v>
+        <v>83536.87</v>
       </c>
       <c r="W17" s="29">
-        <v>6774.12</v>
+        <v>10448.459999999999</v>
       </c>
       <c r="X17" s="29">
         <v>0</v>
@@ -3894,13 +3890,13 @@
         <v>0</v>
       </c>
       <c r="AB17" s="29">
-        <v>16652.57</v>
+        <v>10448.459999999999</v>
       </c>
       <c r="AC17" s="32">
-        <v>1.84E-2</v>
+        <v>1.15E-2</v>
       </c>
       <c r="AD17" s="29">
-        <v>6397.42</v>
+        <v>10754.34</v>
       </c>
       <c r="AE17" s="29">
         <v>0</v>
@@ -3909,16 +3905,16 @@
         <v>0</v>
       </c>
       <c r="AG17" s="29">
-        <v>6397.42</v>
+        <v>10754.34</v>
       </c>
       <c r="AH17" s="29">
-        <v>9878.4500000000007</v>
+        <v>0</v>
       </c>
       <c r="AI17" s="29">
-        <v>23049.99</v>
+        <v>21202.799999999999</v>
       </c>
       <c r="AJ17" s="33" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="AK17" s="34"/>
       <c r="AL17" s="34"/>
@@ -3936,25 +3932,25 @@
         <v>2043</v>
       </c>
       <c r="D18" s="26">
-        <v>2692</v>
+        <v>2856</v>
       </c>
       <c r="E18" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F18" s="27">
-        <v>108404</v>
+        <v>116060</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="H18" s="28">
-        <v>45467</v>
+        <v>46010</v>
       </c>
       <c r="I18" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J18" s="30">
-        <v>36910.69</v>
+        <v>21769.200000000001</v>
       </c>
       <c r="K18" s="30">
         <v>0</v>
@@ -3963,19 +3959,19 @@
         <v>0</v>
       </c>
       <c r="M18" s="31">
-        <v>1677.22</v>
+        <v>0</v>
       </c>
       <c r="N18" s="31">
         <v>0</v>
       </c>
       <c r="O18" s="29">
-        <v>38587.910000000003</v>
+        <v>52038.66</v>
       </c>
       <c r="P18" s="32">
-        <v>2.1299999999999999E-2</v>
+        <v>2.87E-2</v>
       </c>
       <c r="Q18" s="30">
-        <v>27059.39</v>
+        <v>30604.240000000002</v>
       </c>
       <c r="R18" s="30">
         <v>0</v>
@@ -3984,16 +3980,16 @@
         <v>0</v>
       </c>
       <c r="T18" s="29">
-        <v>27059.39</v>
+        <v>30604.240000000002</v>
       </c>
       <c r="U18" s="29">
-        <v>0</v>
+        <v>30269.46</v>
       </c>
       <c r="V18" s="29">
-        <v>65647.3</v>
+        <v>82642.899999999994</v>
       </c>
       <c r="W18" s="29">
-        <v>11073.21</v>
+        <v>6774.12</v>
       </c>
       <c r="X18" s="29">
         <v>0</v>
@@ -4002,19 +3998,19 @@
         <v>0</v>
       </c>
       <c r="Z18" s="31">
-        <v>223.62</v>
+        <v>0</v>
       </c>
       <c r="AA18" s="31">
         <v>0</v>
       </c>
       <c r="AB18" s="29">
-        <v>11296.83</v>
+        <v>16652.57</v>
       </c>
       <c r="AC18" s="32">
-        <v>1.2500000000000001E-2</v>
+        <v>1.84E-2</v>
       </c>
       <c r="AD18" s="29">
-        <v>5601.07</v>
+        <v>6397.42</v>
       </c>
       <c r="AE18" s="29">
         <v>0</v>
@@ -4023,16 +4019,16 @@
         <v>0</v>
       </c>
       <c r="AG18" s="29">
-        <v>5601.07</v>
+        <v>6397.42</v>
       </c>
       <c r="AH18" s="29">
-        <v>0</v>
+        <v>9878.4500000000007</v>
       </c>
       <c r="AI18" s="29">
-        <v>16897.900000000001</v>
+        <v>23049.99</v>
       </c>
       <c r="AJ18" s="33" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="AK18" s="34"/>
       <c r="AL18" s="34"/>
@@ -4056,19 +4052,19 @@
         <v>28</v>
       </c>
       <c r="F19" s="27">
-        <v>104750</v>
+        <v>108404</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="H19" s="28">
-        <v>45236</v>
+        <v>45467</v>
       </c>
       <c r="I19" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J19" s="30">
-        <v>63710.97</v>
+        <v>36910.69</v>
       </c>
       <c r="K19" s="30">
         <v>0</v>
@@ -4077,19 +4073,19 @@
         <v>0</v>
       </c>
       <c r="M19" s="31">
-        <v>590.1</v>
+        <v>4677.22</v>
       </c>
       <c r="N19" s="31">
         <v>0</v>
       </c>
       <c r="O19" s="29">
-        <v>64301.07</v>
+        <v>41587.910000000003</v>
       </c>
       <c r="P19" s="32">
-        <v>3.5499999999999997E-2</v>
+        <v>2.3E-2</v>
       </c>
       <c r="Q19" s="30">
-        <v>987</v>
+        <v>27059.39</v>
       </c>
       <c r="R19" s="30">
         <v>0</v>
@@ -4098,16 +4094,16 @@
         <v>0</v>
       </c>
       <c r="T19" s="29">
-        <v>987</v>
+        <v>27059.39</v>
       </c>
       <c r="U19" s="29">
         <v>0</v>
       </c>
       <c r="V19" s="29">
-        <v>65288.07</v>
+        <v>68647.3</v>
       </c>
       <c r="W19" s="29">
-        <v>24068.240000000002</v>
+        <v>11073.21</v>
       </c>
       <c r="X19" s="29">
         <v>0</v>
@@ -4116,19 +4112,19 @@
         <v>0</v>
       </c>
       <c r="Z19" s="31">
-        <v>83.1</v>
+        <v>373.62</v>
       </c>
       <c r="AA19" s="31">
         <v>0</v>
       </c>
       <c r="AB19" s="29">
-        <v>24151.34</v>
+        <v>11446.83</v>
       </c>
       <c r="AC19" s="32">
-        <v>2.6700000000000002E-2</v>
+        <v>1.26E-2</v>
       </c>
       <c r="AD19" s="29">
-        <v>166.6</v>
+        <v>5601.07</v>
       </c>
       <c r="AE19" s="29">
         <v>0</v>
@@ -4137,16 +4133,16 @@
         <v>0</v>
       </c>
       <c r="AG19" s="29">
-        <v>166.6</v>
+        <v>5601.07</v>
       </c>
       <c r="AH19" s="29">
         <v>0</v>
       </c>
       <c r="AI19" s="29">
-        <v>24317.94</v>
+        <v>17047.900000000001</v>
       </c>
       <c r="AJ19" s="33" t="s">
-        <v>63</v>
+        <v>57</v>
       </c>
       <c r="AK19" s="34"/>
       <c r="AL19" s="34"/>
@@ -4305,16 +4301,16 @@
         <v>0</v>
       </c>
       <c r="M21" s="31">
-        <v>227.15</v>
+        <v>455.37</v>
       </c>
       <c r="N21" s="31">
         <v>0</v>
       </c>
       <c r="O21" s="29">
-        <v>227.15</v>
+        <v>455.37</v>
       </c>
       <c r="P21" s="32">
-        <v>1E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="Q21" s="30">
         <v>52510.1</v>
@@ -4332,7 +4328,7 @@
         <v>0</v>
       </c>
       <c r="V21" s="29">
-        <v>52737.25</v>
+        <v>52965.47</v>
       </c>
       <c r="W21" s="29">
         <v>0</v>
@@ -4344,16 +4340,16 @@
         <v>0</v>
       </c>
       <c r="Z21" s="31">
-        <v>75.72</v>
+        <v>151.79</v>
       </c>
       <c r="AA21" s="31">
         <v>0</v>
       </c>
       <c r="AB21" s="29">
-        <v>75.72</v>
+        <v>151.79</v>
       </c>
       <c r="AC21" s="32">
-        <v>1E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="AD21" s="29">
         <v>10881.11</v>
@@ -4371,7 +4367,7 @@
         <v>0</v>
       </c>
       <c r="AI21" s="29">
-        <v>10956.83</v>
+        <v>11032.9</v>
       </c>
       <c r="AJ21" s="33" t="s">
         <v>87</v>
@@ -4398,19 +4394,19 @@
         <v>28</v>
       </c>
       <c r="F22" s="27">
-        <v>88234</v>
+        <v>105696</v>
       </c>
       <c r="G22" s="25" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="H22" s="28">
-        <v>43794</v>
+        <v>45279</v>
       </c>
       <c r="I22" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J22" s="30">
-        <v>0</v>
+        <v>30829.7</v>
       </c>
       <c r="K22" s="30">
         <v>0</v>
@@ -4419,19 +4415,19 @@
         <v>0</v>
       </c>
       <c r="M22" s="31">
-        <v>504.08</v>
+        <v>985.92</v>
       </c>
       <c r="N22" s="31">
         <v>0</v>
       </c>
       <c r="O22" s="29">
-        <v>504.08</v>
+        <v>31815.62</v>
       </c>
       <c r="P22" s="32">
-        <v>2.9999999999999997E-4</v>
+        <v>1.7600000000000001E-2</v>
       </c>
       <c r="Q22" s="30">
-        <v>40309.919999999998</v>
+        <v>16178.04</v>
       </c>
       <c r="R22" s="30">
         <v>0</v>
@@ -4440,16 +4436,16 @@
         <v>0</v>
       </c>
       <c r="T22" s="29">
-        <v>40309.919999999998</v>
+        <v>16178.04</v>
       </c>
       <c r="U22" s="29">
         <v>0</v>
       </c>
       <c r="V22" s="29">
-        <v>40814</v>
+        <v>47993.66</v>
       </c>
       <c r="W22" s="29">
-        <v>0</v>
+        <v>9451.7999999999993</v>
       </c>
       <c r="X22" s="29">
         <v>0</v>
@@ -4458,19 +4454,19 @@
         <v>0</v>
       </c>
       <c r="Z22" s="31">
-        <v>67.209999999999994</v>
+        <v>78.27</v>
       </c>
       <c r="AA22" s="31">
         <v>0</v>
       </c>
       <c r="AB22" s="29">
-        <v>67.209999999999994</v>
+        <v>9530.07</v>
       </c>
       <c r="AC22" s="32">
-        <v>1E-4</v>
+        <v>1.0500000000000001E-2</v>
       </c>
       <c r="AD22" s="29">
-        <v>8479.68</v>
+        <v>3240.17</v>
       </c>
       <c r="AE22" s="29">
         <v>0</v>
@@ -4479,16 +4475,16 @@
         <v>0</v>
       </c>
       <c r="AG22" s="29">
-        <v>8479.68</v>
+        <v>3240.17</v>
       </c>
       <c r="AH22" s="29">
         <v>0</v>
       </c>
       <c r="AI22" s="29">
-        <v>8546.89</v>
+        <v>12770.24</v>
       </c>
       <c r="AJ22" s="33" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="AK22" s="34"/>
       <c r="AL22" s="34"/>
@@ -4506,25 +4502,25 @@
         <v>2043</v>
       </c>
       <c r="D23" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E23" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F23" s="27">
-        <v>108405</v>
+        <v>88234</v>
       </c>
       <c r="G23" s="25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H23" s="28">
-        <v>45471</v>
+        <v>43794</v>
       </c>
       <c r="I23" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J23" s="30">
-        <v>36157.08</v>
+        <v>0</v>
       </c>
       <c r="K23" s="30">
         <v>0</v>
@@ -4533,19 +4529,19 @@
         <v>0</v>
       </c>
       <c r="M23" s="31">
-        <v>0.6</v>
+        <v>879.63</v>
       </c>
       <c r="N23" s="31">
         <v>0</v>
       </c>
       <c r="O23" s="29">
-        <v>36157.68</v>
+        <v>879.63</v>
       </c>
       <c r="P23" s="32">
-        <v>0.02</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q23" s="30">
-        <v>0</v>
+        <v>40309.919999999998</v>
       </c>
       <c r="R23" s="30">
         <v>0</v>
@@ -4554,16 +4550,16 @@
         <v>0</v>
       </c>
       <c r="T23" s="29">
-        <v>0</v>
+        <v>40309.919999999998</v>
       </c>
       <c r="U23" s="29">
         <v>0</v>
       </c>
       <c r="V23" s="29">
-        <v>36157.68</v>
+        <v>41189.550000000003</v>
       </c>
       <c r="W23" s="29">
-        <v>10847.12</v>
+        <v>0</v>
       </c>
       <c r="X23" s="29">
         <v>0</v>
@@ -4572,19 +4568,19 @@
         <v>0</v>
       </c>
       <c r="Z23" s="31">
-        <v>0.08</v>
+        <v>117.28</v>
       </c>
       <c r="AA23" s="31">
         <v>0</v>
       </c>
       <c r="AB23" s="29">
-        <v>10847.2</v>
+        <v>117.28</v>
       </c>
       <c r="AC23" s="32">
-        <v>1.2E-2</v>
+        <v>1E-4</v>
       </c>
       <c r="AD23" s="29">
-        <v>0</v>
+        <v>8479.68</v>
       </c>
       <c r="AE23" s="29">
         <v>0</v>
@@ -4593,16 +4589,16 @@
         <v>0</v>
       </c>
       <c r="AG23" s="29">
-        <v>0</v>
+        <v>8479.68</v>
       </c>
       <c r="AH23" s="29">
         <v>0</v>
       </c>
       <c r="AI23" s="29">
-        <v>10847.2</v>
+        <v>8596.9599999999991</v>
       </c>
       <c r="AJ23" s="33" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AK23" s="34"/>
       <c r="AL23" s="34"/>
@@ -4620,25 +4616,25 @@
         <v>2043</v>
       </c>
       <c r="D24" s="26">
-        <v>2043</v>
+        <v>2692</v>
       </c>
       <c r="E24" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F24" s="27">
-        <v>105696</v>
+        <v>108405</v>
       </c>
       <c r="G24" s="25" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H24" s="28">
-        <v>45279</v>
+        <v>45471</v>
       </c>
       <c r="I24" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J24" s="30">
-        <v>30829.7</v>
+        <v>36157.08</v>
       </c>
       <c r="K24" s="30">
         <v>0</v>
@@ -4647,16 +4643,16 @@
         <v>0</v>
       </c>
       <c r="M24" s="31">
-        <v>985.92</v>
+        <v>0.6</v>
       </c>
       <c r="N24" s="31">
         <v>0</v>
       </c>
       <c r="O24" s="29">
-        <v>31815.62</v>
+        <v>36157.68</v>
       </c>
       <c r="P24" s="32">
-        <v>1.7600000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="Q24" s="30">
         <v>0</v>
@@ -4674,10 +4670,10 @@
         <v>0</v>
       </c>
       <c r="V24" s="29">
-        <v>31815.62</v>
+        <v>36157.68</v>
       </c>
       <c r="W24" s="29">
-        <v>9451.7999999999993</v>
+        <v>10847.12</v>
       </c>
       <c r="X24" s="29">
         <v>0</v>
@@ -4686,16 +4682,16 @@
         <v>0</v>
       </c>
       <c r="Z24" s="31">
-        <v>78.27</v>
+        <v>0.08</v>
       </c>
       <c r="AA24" s="31">
         <v>0</v>
       </c>
       <c r="AB24" s="29">
-        <v>9530.07</v>
+        <v>10847.2</v>
       </c>
       <c r="AC24" s="32">
-        <v>1.0500000000000001E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="AD24" s="29">
         <v>0</v>
@@ -4713,10 +4709,10 @@
         <v>0</v>
       </c>
       <c r="AI24" s="29">
-        <v>9530.07</v>
+        <v>10847.2</v>
       </c>
       <c r="AJ24" s="33" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="AK24" s="34"/>
       <c r="AL24" s="34"/>
@@ -4989,13 +4985,13 @@
         <v>0</v>
       </c>
       <c r="M27" s="31">
-        <v>2386.1999999999998</v>
+        <v>2420.09</v>
       </c>
       <c r="N27" s="31">
         <v>0</v>
       </c>
       <c r="O27" s="29">
-        <v>2386.1999999999998</v>
+        <v>2420.09</v>
       </c>
       <c r="P27" s="32">
         <v>1.2999999999999999E-3</v>
@@ -5016,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="29">
-        <v>25426.12</v>
+        <v>25460.01</v>
       </c>
       <c r="W27" s="29">
         <v>0</v>
@@ -5028,13 +5024,13 @@
         <v>0</v>
       </c>
       <c r="Z27" s="31">
-        <v>318.16000000000003</v>
+        <v>322.68</v>
       </c>
       <c r="AA27" s="31">
         <v>0</v>
       </c>
       <c r="AB27" s="29">
-        <v>318.16000000000003</v>
+        <v>322.68</v>
       </c>
       <c r="AC27" s="32">
         <v>4.0000000000000002E-4</v>
@@ -5055,7 +5051,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="29">
-        <v>5012.9399999999996</v>
+        <v>5017.46</v>
       </c>
       <c r="AJ27" s="33" t="s">
         <v>75</v>
@@ -5217,16 +5213,16 @@
         <v>0</v>
       </c>
       <c r="M29" s="31">
-        <v>2700.41</v>
+        <v>3720.52</v>
       </c>
       <c r="N29" s="31">
         <v>0</v>
       </c>
       <c r="O29" s="29">
-        <v>2700.41</v>
+        <v>3720.52</v>
       </c>
       <c r="P29" s="32">
-        <v>1.5E-3</v>
+        <v>2.0999999999999999E-3</v>
       </c>
       <c r="Q29" s="30">
         <v>0</v>
@@ -5244,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="29">
-        <v>2700.41</v>
+        <v>3720.52</v>
       </c>
       <c r="W29" s="29">
         <v>0</v>
@@ -5256,16 +5252,16 @@
         <v>0</v>
       </c>
       <c r="Z29" s="31">
-        <v>260.02</v>
+        <v>346.03</v>
       </c>
       <c r="AA29" s="31">
         <v>0</v>
       </c>
       <c r="AB29" s="29">
-        <v>260.02</v>
+        <v>346.03</v>
       </c>
       <c r="AC29" s="32">
-        <v>2.9999999999999997E-4</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="AD29" s="29">
         <v>0</v>
@@ -5283,7 +5279,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="29">
-        <v>260.02</v>
+        <v>346.03</v>
       </c>
       <c r="AJ29" s="33" t="s">
         <v>79</v>
@@ -5331,16 +5327,16 @@
         <v>0</v>
       </c>
       <c r="M30" s="31">
-        <v>1175.3900000000001</v>
+        <v>2480.0300000000002</v>
       </c>
       <c r="N30" s="31">
         <v>0</v>
       </c>
       <c r="O30" s="29">
-        <v>1175.3900000000001</v>
+        <v>2480.0300000000002</v>
       </c>
       <c r="P30" s="32">
-        <v>5.9999999999999995E-4</v>
+        <v>1.4E-3</v>
       </c>
       <c r="Q30" s="30">
         <v>0</v>
@@ -5358,7 +5354,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="29">
-        <v>1175.3900000000001</v>
+        <v>2480.0300000000002</v>
       </c>
       <c r="W30" s="29">
         <v>0</v>
@@ -5370,16 +5366,16 @@
         <v>0</v>
       </c>
       <c r="Z30" s="31">
-        <v>210.02</v>
+        <v>280.64</v>
       </c>
       <c r="AA30" s="31">
         <v>0</v>
       </c>
       <c r="AB30" s="29">
-        <v>210.02</v>
+        <v>280.64</v>
       </c>
       <c r="AC30" s="32">
-        <v>2.0000000000000001E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="AD30" s="29">
         <v>0</v>
@@ -5397,7 +5393,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="29">
-        <v>210.02</v>
+        <v>280.64</v>
       </c>
       <c r="AJ30" s="33" t="s">
         <v>81</v>
@@ -7242,19 +7238,19 @@
         <v>2043</v>
       </c>
       <c r="D47" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E47" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F47" s="27">
-        <v>112083</v>
+        <v>112522</v>
       </c>
       <c r="G47" s="25" t="s">
         <v>116</v>
       </c>
       <c r="H47" s="28">
-        <v>45736</v>
+        <v>45776</v>
       </c>
       <c r="I47" s="29" t="s">
         <v>30</v>
@@ -7356,19 +7352,19 @@
         <v>2043</v>
       </c>
       <c r="D48" s="26">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E48" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F48" s="27">
-        <v>112522</v>
+        <v>113076</v>
       </c>
       <c r="G48" s="25" t="s">
         <v>118</v>
       </c>
       <c r="H48" s="28">
-        <v>45776</v>
+        <v>45806</v>
       </c>
       <c r="I48" s="29" t="s">
         <v>30</v>
@@ -7470,19 +7466,19 @@
         <v>2043</v>
       </c>
       <c r="D49" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E49" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F49" s="27">
-        <v>113076</v>
+        <v>114100</v>
       </c>
       <c r="G49" s="25" t="s">
         <v>120</v>
       </c>
       <c r="H49" s="28">
-        <v>45806</v>
+        <v>45863</v>
       </c>
       <c r="I49" s="29" t="s">
         <v>30</v>
@@ -7584,19 +7580,19 @@
         <v>2043</v>
       </c>
       <c r="D50" s="26">
-        <v>2856</v>
+        <v>2692</v>
       </c>
       <c r="E50" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F50" s="27">
-        <v>114100</v>
+        <v>114157</v>
       </c>
       <c r="G50" s="25" t="s">
         <v>122</v>
       </c>
       <c r="H50" s="28">
-        <v>45863</v>
+        <v>45904</v>
       </c>
       <c r="I50" s="29" t="s">
         <v>30</v>
@@ -7704,13 +7700,13 @@
         <v>28</v>
       </c>
       <c r="F51" s="27">
-        <v>114157</v>
+        <v>114431</v>
       </c>
       <c r="G51" s="25" t="s">
         <v>124</v>
       </c>
       <c r="H51" s="28">
-        <v>45904</v>
+        <v>45930</v>
       </c>
       <c r="I51" s="29" t="s">
         <v>30</v>
@@ -7812,25 +7808,25 @@
         <v>2043</v>
       </c>
       <c r="D52" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E52" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F52" s="27">
-        <v>114431</v>
+        <v>95148</v>
       </c>
       <c r="G52" s="25" t="s">
-        <v>126</v>
+        <v>54</v>
       </c>
       <c r="H52" s="28">
-        <v>45930</v>
+        <v>44916</v>
       </c>
       <c r="I52" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J52" s="30">
-        <v>0</v>
+        <v>46057.760000000002</v>
       </c>
       <c r="K52" s="30">
         <v>0</v>
@@ -7845,31 +7841,31 @@
         <v>0</v>
       </c>
       <c r="O52" s="29">
-        <v>0</v>
+        <v>46057.760000000002</v>
       </c>
       <c r="P52" s="32">
-        <v>0</v>
+        <v>2.5399999999999999E-2</v>
       </c>
       <c r="Q52" s="30">
-        <v>0</v>
+        <v>23133.08</v>
       </c>
       <c r="R52" s="30">
         <v>0</v>
       </c>
       <c r="S52" s="30">
-        <v>0</v>
+        <v>69825</v>
       </c>
       <c r="T52" s="29">
-        <v>0</v>
+        <v>-46691.92</v>
       </c>
       <c r="U52" s="29">
         <v>0</v>
       </c>
       <c r="V52" s="29">
-        <v>0</v>
+        <v>-634.16</v>
       </c>
       <c r="W52" s="29">
-        <v>0</v>
+        <v>13817.33</v>
       </c>
       <c r="X52" s="29">
         <v>0</v>
@@ -7884,31 +7880,31 @@
         <v>0</v>
       </c>
       <c r="AB52" s="29">
-        <v>0</v>
+        <v>13817.33</v>
       </c>
       <c r="AC52" s="32">
-        <v>0</v>
+        <v>1.5299999999999999E-2</v>
       </c>
       <c r="AD52" s="29">
-        <v>0</v>
+        <v>4744.3599999999997</v>
       </c>
       <c r="AE52" s="29">
         <v>0</v>
       </c>
       <c r="AF52" s="29">
-        <v>0</v>
+        <v>15103</v>
       </c>
       <c r="AG52" s="29">
-        <v>0</v>
+        <v>-10358.64</v>
       </c>
       <c r="AH52" s="29">
         <v>0</v>
       </c>
       <c r="AI52" s="29">
-        <v>0</v>
+        <v>3458.69</v>
       </c>
       <c r="AJ52" s="33" t="s">
-        <v>127</v>
+        <v>55</v>
       </c>
       <c r="AK52" s="34"/>
       <c r="AL52" s="34"/>
@@ -7916,136 +7912,84 @@
       <c r="AN52" s="35"/>
     </row>
     <row r="53" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A53" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B53" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C53" s="26">
-        <v>2043</v>
-      </c>
-      <c r="D53" s="26">
-        <v>2043</v>
-      </c>
-      <c r="E53" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="F53" s="27">
-        <v>95148</v>
-      </c>
-      <c r="G53" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="H53" s="28">
-        <v>44916</v>
-      </c>
-      <c r="I53" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="J53" s="30">
-        <v>46057.760000000002</v>
-      </c>
-      <c r="K53" s="30">
-        <v>0</v>
-      </c>
-      <c r="L53" s="29">
-        <v>0</v>
-      </c>
-      <c r="M53" s="31">
-        <v>0</v>
-      </c>
-      <c r="N53" s="31">
-        <v>0</v>
-      </c>
-      <c r="O53" s="29">
-        <v>46057.760000000002</v>
-      </c>
-      <c r="P53" s="32">
-        <v>2.5399999999999999E-2</v>
-      </c>
-      <c r="Q53" s="30">
-        <v>23133.08</v>
-      </c>
-      <c r="R53" s="30">
-        <v>0</v>
-      </c>
-      <c r="S53" s="30">
-        <v>69825</v>
-      </c>
-      <c r="T53" s="29">
-        <v>-46691.92</v>
-      </c>
-      <c r="U53" s="29">
-        <v>0</v>
-      </c>
-      <c r="V53" s="29">
-        <v>-634.16</v>
-      </c>
-      <c r="W53" s="29">
-        <v>13817.33</v>
-      </c>
-      <c r="X53" s="29">
-        <v>0</v>
-      </c>
-      <c r="Y53" s="29">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA53" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB53" s="29">
-        <v>13817.33</v>
-      </c>
-      <c r="AC53" s="32">
-        <v>1.5299999999999999E-2</v>
-      </c>
-      <c r="AD53" s="29">
-        <v>4744.3599999999997</v>
-      </c>
-      <c r="AE53" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF53" s="29">
-        <v>15103</v>
-      </c>
-      <c r="AG53" s="29">
-        <v>-10358.64</v>
-      </c>
-      <c r="AH53" s="29">
-        <v>0</v>
-      </c>
-      <c r="AI53" s="29">
-        <v>3458.69</v>
-      </c>
-      <c r="AJ53" s="33" t="s">
-        <v>55</v>
-      </c>
+      <c r="A53" s="25"/>
+      <c r="B53" s="25"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="25"/>
+      <c r="H53" s="28"/>
+      <c r="I53" s="29"/>
+      <c r="J53" s="30"/>
+      <c r="K53" s="30"/>
+      <c r="L53" s="29"/>
+      <c r="M53" s="31"/>
+      <c r="N53" s="31"/>
+      <c r="O53" s="29"/>
+      <c r="P53" s="32"/>
+      <c r="Q53" s="30"/>
+      <c r="R53" s="30"/>
+      <c r="S53" s="30"/>
+      <c r="T53" s="29"/>
+      <c r="U53" s="29"/>
+      <c r="V53" s="29"/>
+      <c r="W53" s="29"/>
+      <c r="X53" s="29"/>
+      <c r="Y53" s="29"/>
+      <c r="Z53" s="31"/>
+      <c r="AA53" s="31"/>
+      <c r="AB53" s="29"/>
+      <c r="AC53" s="32"/>
+      <c r="AD53" s="29"/>
+      <c r="AE53" s="29"/>
+      <c r="AF53" s="29"/>
+      <c r="AG53" s="29"/>
+      <c r="AH53" s="29"/>
+      <c r="AI53" s="29"/>
+      <c r="AJ53" s="33"/>
       <c r="AK53" s="34"/>
       <c r="AL53" s="34"/>
       <c r="AM53" s="34"/>
       <c r="AN53" s="35"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A6:AI53 AK6:AK53 AM6:AN53">
+  <conditionalFormatting sqref="A53:AI53 AM53:AN53 AK53">
+    <cfRule type="expression" dxfId="7" priority="8" stopIfTrue="1">
+      <formula>$B53&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK53:AN53">
+    <cfRule type="expression" dxfId="6" priority="5" stopIfTrue="1">
+      <formula>$B53&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL53">
+    <cfRule type="expression" dxfId="5" priority="6" stopIfTrue="1">
+      <formula>$B53&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN53 V53 AI53">
+    <cfRule type="expression" dxfId="4" priority="7" stopIfTrue="1">
+      <formula>$B53&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A6:AI52 AK6:AK52 AM6:AN52">
     <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V6:V53 AI6:AI53 AN6:AN53">
+  <conditionalFormatting sqref="V6:V52 AI6:AI52 AN6:AN52">
     <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL6:AL53">
+  <conditionalFormatting sqref="AL6:AL52">
     <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK43:AN53">
+  <conditionalFormatting sqref="AK43:AN52">
     <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
       <formula>$B43&lt;&gt;""</formula>
     </cfRule>

--- a/mdrt/MDRT.xlsx
+++ b/mdrt/MDRT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/mdrt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3B94AFF-67B2-344F-B608-A57BA2AFDF96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14FFC621-F7FC-AB48-881D-D168DB48E4AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" xr2:uid="{263D14F0-BAEF-1E4F-83AF-E2F80B31AC70}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16360" xr2:uid="{263D14F0-BAEF-1E4F-83AF-E2F80B31AC70}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -273,12 +273,6 @@
     <t>DAFF900319M12</t>
   </si>
   <si>
-    <t>ALEJANDRA IVETTE PEDROZA MACIAS</t>
-  </si>
-  <si>
-    <t>PEMA790227NA0</t>
-  </si>
-  <si>
     <t>JORGE ALBERTO PRECIADO GONZALEZ</t>
   </si>
   <si>
@@ -459,7 +453,13 @@
     <t>Columna15</t>
   </si>
   <si>
-    <t>Avance del 1 de enero al 11 de marzo de 2026.</t>
+    <t>MARIA FERNANDA RIOS BERNAL</t>
+  </si>
+  <si>
+    <t>RIBF8912215D9</t>
+  </si>
+  <si>
+    <t>Avance del 1 de enero al 13 de marzo de 2026.</t>
   </si>
 </sst>
 </file>
@@ -2437,7 +2437,7 @@
         <v>17</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="T4" s="4" t="s">
         <v>18</v>
@@ -2449,46 +2449,46 @@
         <v>20</v>
       </c>
       <c r="W4" s="6" t="s">
+        <v>125</v>
+      </c>
+      <c r="X4" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="Y4" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="X4" s="6" t="s">
+      <c r="Z4" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="AA4" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="Z4" s="6" t="s">
+      <c r="AB4" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="AA4" s="6" t="s">
+      <c r="AC4" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="AB4" s="7" t="s">
+      <c r="AD4" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="AC4" s="8" t="s">
+      <c r="AE4" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="AD4" s="6" t="s">
+      <c r="AF4" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="AE4" s="6" t="s">
+      <c r="AG4" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="AF4" s="6" t="s">
+      <c r="AH4" s="6" t="s">
         <v>136</v>
-      </c>
-      <c r="AG4" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="AH4" s="6" t="s">
-        <v>138</v>
       </c>
       <c r="AI4" s="9" t="s">
         <v>21</v>
       </c>
       <c r="AJ4" s="10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="AK4" s="11" t="s">
         <v>22</v>
@@ -3161,16 +3161,16 @@
         <v>0</v>
       </c>
       <c r="M11" s="31">
-        <v>86219.62</v>
+        <v>86755.99</v>
       </c>
       <c r="N11" s="31">
         <v>0</v>
       </c>
       <c r="O11" s="29">
-        <v>161504.9</v>
+        <v>162041.26999999999</v>
       </c>
       <c r="P11" s="32">
-        <v>8.9200000000000002E-2</v>
+        <v>8.9499999999999996E-2</v>
       </c>
       <c r="Q11" s="30">
         <v>0</v>
@@ -3188,7 +3188,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="29">
-        <v>161504.9</v>
+        <v>162041.26999999999</v>
       </c>
       <c r="W11" s="29">
         <v>25150.62</v>
@@ -3200,16 +3200,16 @@
         <v>0</v>
       </c>
       <c r="Z11" s="31">
-        <v>5178.3900000000003</v>
+        <v>5224.8999999999996</v>
       </c>
       <c r="AA11" s="31">
         <v>0</v>
       </c>
       <c r="AB11" s="29">
-        <v>30329.01</v>
+        <v>30375.52</v>
       </c>
       <c r="AC11" s="32">
-        <v>3.3500000000000002E-2</v>
+        <v>3.3599999999999998E-2</v>
       </c>
       <c r="AD11" s="29">
         <v>0</v>
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="29">
-        <v>30329.01</v>
+        <v>30375.52</v>
       </c>
       <c r="AJ11" s="33" t="s">
         <v>47</v>
@@ -3380,7 +3380,7 @@
         <v>30</v>
       </c>
       <c r="J13" s="30">
-        <v>86224.02</v>
+        <v>112348.82</v>
       </c>
       <c r="K13" s="30">
         <v>0</v>
@@ -3389,16 +3389,16 @@
         <v>0</v>
       </c>
       <c r="M13" s="31">
-        <v>338.11</v>
+        <v>2010.37</v>
       </c>
       <c r="N13" s="31">
         <v>0</v>
       </c>
       <c r="O13" s="29">
-        <v>86562.13</v>
+        <v>114359.19</v>
       </c>
       <c r="P13" s="32">
-        <v>4.7800000000000002E-2</v>
+        <v>6.3200000000000006E-2</v>
       </c>
       <c r="Q13" s="30">
         <v>31773.599999999999</v>
@@ -3416,10 +3416,10 @@
         <v>0</v>
       </c>
       <c r="V13" s="29">
-        <v>118335.73</v>
+        <v>146132.79</v>
       </c>
       <c r="W13" s="29">
-        <v>26969.599999999999</v>
+        <v>34992.42</v>
       </c>
       <c r="X13" s="29">
         <v>0</v>
@@ -3428,16 +3428,16 @@
         <v>0</v>
       </c>
       <c r="Z13" s="31">
-        <v>21.08</v>
+        <v>244.05</v>
       </c>
       <c r="AA13" s="31">
         <v>0</v>
       </c>
       <c r="AB13" s="29">
-        <v>26990.68</v>
+        <v>35236.47</v>
       </c>
       <c r="AC13" s="32">
-        <v>2.98E-2</v>
+        <v>3.8899999999999997E-2</v>
       </c>
       <c r="AD13" s="29">
         <v>6601.68</v>
@@ -3455,7 +3455,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="29">
-        <v>33592.36</v>
+        <v>41838.15</v>
       </c>
       <c r="AJ13" s="33" t="s">
         <v>43</v>
@@ -4283,7 +4283,7 @@
         <v>102825</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="H21" s="28">
         <v>45117</v>
@@ -4370,7 +4370,7 @@
         <v>11032.9</v>
       </c>
       <c r="AJ21" s="33" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="AK21" s="34"/>
       <c r="AL21" s="34"/>
@@ -5192,13 +5192,13 @@
         <v>28</v>
       </c>
       <c r="F29" s="27">
-        <v>81618</v>
+        <v>104343</v>
       </c>
       <c r="G29" s="25" t="s">
         <v>78</v>
       </c>
       <c r="H29" s="28">
-        <v>43447</v>
+        <v>45201</v>
       </c>
       <c r="I29" s="29" t="s">
         <v>30</v>
@@ -5213,16 +5213,16 @@
         <v>0</v>
       </c>
       <c r="M29" s="31">
-        <v>3720.52</v>
+        <v>2480.0300000000002</v>
       </c>
       <c r="N29" s="31">
         <v>0</v>
       </c>
       <c r="O29" s="29">
-        <v>3720.52</v>
+        <v>2480.0300000000002</v>
       </c>
       <c r="P29" s="32">
-        <v>2.0999999999999999E-3</v>
+        <v>1.4E-3</v>
       </c>
       <c r="Q29" s="30">
         <v>0</v>
@@ -5240,7 +5240,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="29">
-        <v>3720.52</v>
+        <v>2480.0300000000002</v>
       </c>
       <c r="W29" s="29">
         <v>0</v>
@@ -5252,16 +5252,16 @@
         <v>0</v>
       </c>
       <c r="Z29" s="31">
-        <v>346.03</v>
+        <v>280.64</v>
       </c>
       <c r="AA29" s="31">
         <v>0</v>
       </c>
       <c r="AB29" s="29">
-        <v>346.03</v>
+        <v>280.64</v>
       </c>
       <c r="AC29" s="32">
-        <v>4.0000000000000002E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="AD29" s="29">
         <v>0</v>
@@ -5279,7 +5279,7 @@
         <v>0</v>
       </c>
       <c r="AI29" s="29">
-        <v>346.03</v>
+        <v>280.64</v>
       </c>
       <c r="AJ29" s="33" t="s">
         <v>79</v>
@@ -5306,13 +5306,13 @@
         <v>28</v>
       </c>
       <c r="F30" s="27">
-        <v>104343</v>
+        <v>106018</v>
       </c>
       <c r="G30" s="25" t="s">
         <v>80</v>
       </c>
       <c r="H30" s="28">
-        <v>45201</v>
+        <v>45344</v>
       </c>
       <c r="I30" s="29" t="s">
         <v>30</v>
@@ -5327,16 +5327,16 @@
         <v>0</v>
       </c>
       <c r="M30" s="31">
-        <v>2480.0300000000002</v>
+        <v>426.22</v>
       </c>
       <c r="N30" s="31">
         <v>0</v>
       </c>
       <c r="O30" s="29">
-        <v>2480.0300000000002</v>
+        <v>426.22</v>
       </c>
       <c r="P30" s="32">
-        <v>1.4E-3</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="Q30" s="30">
         <v>0</v>
@@ -5354,7 +5354,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="29">
-        <v>2480.0300000000002</v>
+        <v>426.22</v>
       </c>
       <c r="W30" s="29">
         <v>0</v>
@@ -5366,16 +5366,16 @@
         <v>0</v>
       </c>
       <c r="Z30" s="31">
-        <v>280.64</v>
+        <v>56.83</v>
       </c>
       <c r="AA30" s="31">
         <v>0</v>
       </c>
       <c r="AB30" s="29">
-        <v>280.64</v>
+        <v>56.83</v>
       </c>
       <c r="AC30" s="32">
-        <v>2.9999999999999997E-4</v>
+        <v>1E-4</v>
       </c>
       <c r="AD30" s="29">
         <v>0</v>
@@ -5393,7 +5393,7 @@
         <v>0</v>
       </c>
       <c r="AI30" s="29">
-        <v>280.64</v>
+        <v>56.83</v>
       </c>
       <c r="AJ30" s="33" t="s">
         <v>81</v>
@@ -5414,19 +5414,19 @@
         <v>2043</v>
       </c>
       <c r="D31" s="26">
-        <v>2043</v>
+        <v>2511</v>
       </c>
       <c r="E31" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F31" s="27">
-        <v>106018</v>
+        <v>63441</v>
       </c>
       <c r="G31" s="25" t="s">
         <v>82</v>
       </c>
       <c r="H31" s="28">
-        <v>45344</v>
+        <v>44733</v>
       </c>
       <c r="I31" s="29" t="s">
         <v>30</v>
@@ -5441,13 +5441,13 @@
         <v>0</v>
       </c>
       <c r="M31" s="31">
-        <v>426.22</v>
+        <v>300.06</v>
       </c>
       <c r="N31" s="31">
         <v>0</v>
       </c>
       <c r="O31" s="29">
-        <v>426.22</v>
+        <v>300.06</v>
       </c>
       <c r="P31" s="32">
         <v>2.0000000000000001E-4</v>
@@ -5468,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="29">
-        <v>426.22</v>
+        <v>300.06</v>
       </c>
       <c r="W31" s="29">
         <v>0</v>
@@ -5480,16 +5480,16 @@
         <v>0</v>
       </c>
       <c r="Z31" s="31">
-        <v>56.83</v>
+        <v>15</v>
       </c>
       <c r="AA31" s="31">
         <v>0</v>
       </c>
       <c r="AB31" s="29">
-        <v>56.83</v>
+        <v>15</v>
       </c>
       <c r="AC31" s="32">
-        <v>1E-4</v>
+        <v>0</v>
       </c>
       <c r="AD31" s="29">
         <v>0</v>
@@ -5507,7 +5507,7 @@
         <v>0</v>
       </c>
       <c r="AI31" s="29">
-        <v>56.83</v>
+        <v>15</v>
       </c>
       <c r="AJ31" s="33" t="s">
         <v>83</v>
@@ -5528,19 +5528,19 @@
         <v>2043</v>
       </c>
       <c r="D32" s="26">
-        <v>2511</v>
+        <v>2043</v>
       </c>
       <c r="E32" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F32" s="27">
-        <v>63441</v>
+        <v>108658</v>
       </c>
       <c r="G32" s="25" t="s">
-        <v>84</v>
+        <v>104</v>
       </c>
       <c r="H32" s="28">
-        <v>44733</v>
+        <v>45497</v>
       </c>
       <c r="I32" s="29" t="s">
         <v>30</v>
@@ -5555,16 +5555,16 @@
         <v>0</v>
       </c>
       <c r="M32" s="31">
-        <v>300.06</v>
+        <v>180.03</v>
       </c>
       <c r="N32" s="31">
         <v>0</v>
       </c>
       <c r="O32" s="29">
-        <v>300.06</v>
+        <v>180.03</v>
       </c>
       <c r="P32" s="32">
-        <v>2.0000000000000001E-4</v>
+        <v>1E-4</v>
       </c>
       <c r="Q32" s="30">
         <v>0</v>
@@ -5582,7 +5582,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="29">
-        <v>300.06</v>
+        <v>180.03</v>
       </c>
       <c r="W32" s="29">
         <v>0</v>
@@ -5594,13 +5594,13 @@
         <v>0</v>
       </c>
       <c r="Z32" s="31">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AA32" s="31">
         <v>0</v>
       </c>
       <c r="AB32" s="29">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AC32" s="32">
         <v>0</v>
@@ -5621,10 +5621,10 @@
         <v>0</v>
       </c>
       <c r="AI32" s="29">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="AJ32" s="33" t="s">
-        <v>85</v>
+        <v>105</v>
       </c>
       <c r="AK32" s="34"/>
       <c r="AL32" s="34"/>
@@ -5648,13 +5648,13 @@
         <v>28</v>
       </c>
       <c r="F33" s="27">
-        <v>108658</v>
+        <v>65046</v>
       </c>
       <c r="G33" s="25" t="s">
-        <v>106</v>
+        <v>86</v>
       </c>
       <c r="H33" s="28">
-        <v>45497</v>
+        <v>44763</v>
       </c>
       <c r="I33" s="29" t="s">
         <v>30</v>
@@ -5669,13 +5669,13 @@
         <v>0</v>
       </c>
       <c r="M33" s="31">
-        <v>180.03</v>
+        <v>180</v>
       </c>
       <c r="N33" s="31">
         <v>0</v>
       </c>
       <c r="O33" s="29">
-        <v>180.03</v>
+        <v>180</v>
       </c>
       <c r="P33" s="32">
         <v>1E-4</v>
@@ -5696,7 +5696,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="29">
-        <v>180.03</v>
+        <v>180</v>
       </c>
       <c r="W33" s="29">
         <v>0</v>
@@ -5738,7 +5738,7 @@
         <v>9</v>
       </c>
       <c r="AJ33" s="33" t="s">
-        <v>107</v>
+        <v>87</v>
       </c>
       <c r="AK33" s="34"/>
       <c r="AL33" s="34"/>
@@ -5762,13 +5762,13 @@
         <v>28</v>
       </c>
       <c r="F34" s="27">
-        <v>65046</v>
+        <v>109998</v>
       </c>
       <c r="G34" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H34" s="28">
-        <v>44763</v>
+        <v>45596</v>
       </c>
       <c r="I34" s="29" t="s">
         <v>30</v>
@@ -5783,13 +5783,13 @@
         <v>0</v>
       </c>
       <c r="M34" s="31">
-        <v>180</v>
+        <v>162.5</v>
       </c>
       <c r="N34" s="31">
         <v>0</v>
       </c>
       <c r="O34" s="29">
-        <v>180</v>
+        <v>162.5</v>
       </c>
       <c r="P34" s="32">
         <v>1E-4</v>
@@ -5810,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="29">
-        <v>180</v>
+        <v>162.5</v>
       </c>
       <c r="W34" s="29">
         <v>0</v>
@@ -5822,13 +5822,13 @@
         <v>0</v>
       </c>
       <c r="Z34" s="31">
-        <v>9</v>
+        <v>21.66</v>
       </c>
       <c r="AA34" s="31">
         <v>0</v>
       </c>
       <c r="AB34" s="29">
-        <v>9</v>
+        <v>21.66</v>
       </c>
       <c r="AC34" s="32">
         <v>0</v>
@@ -5849,10 +5849,10 @@
         <v>0</v>
       </c>
       <c r="AI34" s="29">
-        <v>9</v>
+        <v>21.66</v>
       </c>
       <c r="AJ34" s="33" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AK34" s="34"/>
       <c r="AL34" s="34"/>
@@ -5870,19 +5870,19 @@
         <v>2043</v>
       </c>
       <c r="D35" s="26">
-        <v>2043</v>
+        <v>2511</v>
       </c>
       <c r="E35" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F35" s="27">
-        <v>109998</v>
+        <v>69684</v>
       </c>
       <c r="G35" s="25" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H35" s="28">
-        <v>45596</v>
+        <v>44771</v>
       </c>
       <c r="I35" s="29" t="s">
         <v>30</v>
@@ -5897,13 +5897,13 @@
         <v>0</v>
       </c>
       <c r="M35" s="31">
-        <v>162.5</v>
+        <v>142.55000000000001</v>
       </c>
       <c r="N35" s="31">
         <v>0</v>
       </c>
       <c r="O35" s="29">
-        <v>162.5</v>
+        <v>142.55000000000001</v>
       </c>
       <c r="P35" s="32">
         <v>1E-4</v>
@@ -5924,7 +5924,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="29">
-        <v>162.5</v>
+        <v>142.55000000000001</v>
       </c>
       <c r="W35" s="29">
         <v>0</v>
@@ -5936,13 +5936,13 @@
         <v>0</v>
       </c>
       <c r="Z35" s="31">
-        <v>21.66</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="AA35" s="31">
         <v>0</v>
       </c>
       <c r="AB35" s="29">
-        <v>21.66</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="AC35" s="32">
         <v>0</v>
@@ -5963,10 +5963,10 @@
         <v>0</v>
       </c>
       <c r="AI35" s="29">
-        <v>21.66</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="AJ35" s="33" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AK35" s="34"/>
       <c r="AL35" s="34"/>
@@ -5990,13 +5990,13 @@
         <v>28</v>
       </c>
       <c r="F36" s="27">
-        <v>69684</v>
+        <v>59120</v>
       </c>
       <c r="G36" s="25" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H36" s="28">
-        <v>44771</v>
+        <v>44708</v>
       </c>
       <c r="I36" s="29" t="s">
         <v>30</v>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="M36" s="31">
-        <v>142.55000000000001</v>
+        <v>0</v>
       </c>
       <c r="N36" s="31">
         <v>0</v>
       </c>
       <c r="O36" s="29">
-        <v>142.55000000000001</v>
+        <v>0</v>
       </c>
       <c r="P36" s="32">
-        <v>1E-4</v>
+        <v>0</v>
       </c>
       <c r="Q36" s="30">
         <v>0</v>
@@ -6038,7 +6038,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="29">
-        <v>142.55000000000001</v>
+        <v>0</v>
       </c>
       <c r="W36" s="29">
         <v>0</v>
@@ -6050,13 +6050,13 @@
         <v>0</v>
       </c>
       <c r="Z36" s="31">
-        <v>19.010000000000002</v>
+        <v>0</v>
       </c>
       <c r="AA36" s="31">
         <v>0</v>
       </c>
       <c r="AB36" s="29">
-        <v>19.010000000000002</v>
+        <v>0</v>
       </c>
       <c r="AC36" s="32">
         <v>0</v>
@@ -6077,10 +6077,10 @@
         <v>0</v>
       </c>
       <c r="AI36" s="29">
-        <v>19.010000000000002</v>
+        <v>0</v>
       </c>
       <c r="AJ36" s="33" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="AK36" s="34"/>
       <c r="AL36" s="34"/>
@@ -6098,22 +6098,22 @@
         <v>2043</v>
       </c>
       <c r="D37" s="26">
-        <v>2511</v>
+        <v>2043</v>
       </c>
       <c r="E37" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F37" s="27">
-        <v>59120</v>
+        <v>64502</v>
       </c>
       <c r="G37" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="H37" s="28">
+        <v>42173</v>
+      </c>
+      <c r="I37" s="29" t="s">
         <v>94</v>
-      </c>
-      <c r="H37" s="28">
-        <v>44708</v>
-      </c>
-      <c r="I37" s="29" t="s">
-        <v>30</v>
       </c>
       <c r="J37" s="30">
         <v>0</v>
@@ -6212,22 +6212,22 @@
         <v>2043</v>
       </c>
       <c r="D38" s="26">
-        <v>2043</v>
+        <v>2511</v>
       </c>
       <c r="E38" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F38" s="27">
-        <v>64502</v>
+        <v>81044</v>
       </c>
       <c r="G38" s="25" t="s">
-        <v>28</v>
+        <v>96</v>
       </c>
       <c r="H38" s="28">
-        <v>42173</v>
+        <v>44872</v>
       </c>
       <c r="I38" s="29" t="s">
-        <v>96</v>
+        <v>30</v>
       </c>
       <c r="J38" s="30">
         <v>0</v>
@@ -6326,19 +6326,19 @@
         <v>2043</v>
       </c>
       <c r="D39" s="26">
-        <v>2511</v>
+        <v>2043</v>
       </c>
       <c r="E39" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F39" s="27">
-        <v>81044</v>
+        <v>90177</v>
       </c>
       <c r="G39" s="25" t="s">
         <v>98</v>
       </c>
       <c r="H39" s="28">
-        <v>44872</v>
+        <v>43949</v>
       </c>
       <c r="I39" s="29" t="s">
         <v>30</v>
@@ -6446,13 +6446,13 @@
         <v>28</v>
       </c>
       <c r="F40" s="27">
-        <v>90177</v>
+        <v>94205</v>
       </c>
       <c r="G40" s="25" t="s">
         <v>100</v>
       </c>
       <c r="H40" s="28">
-        <v>43949</v>
+        <v>44116</v>
       </c>
       <c r="I40" s="29" t="s">
         <v>30</v>
@@ -6560,13 +6560,13 @@
         <v>28</v>
       </c>
       <c r="F41" s="27">
-        <v>94205</v>
+        <v>101640</v>
       </c>
       <c r="G41" s="25" t="s">
         <v>102</v>
       </c>
       <c r="H41" s="28">
-        <v>44116</v>
+        <v>45104</v>
       </c>
       <c r="I41" s="29" t="s">
         <v>30</v>
@@ -6674,13 +6674,13 @@
         <v>28</v>
       </c>
       <c r="F42" s="27">
-        <v>101640</v>
+        <v>103982</v>
       </c>
       <c r="G42" s="25" t="s">
-        <v>104</v>
+        <v>138</v>
       </c>
       <c r="H42" s="28">
-        <v>45104</v>
+        <v>45216</v>
       </c>
       <c r="I42" s="29" t="s">
         <v>30</v>
@@ -6764,7 +6764,7 @@
         <v>0</v>
       </c>
       <c r="AJ42" s="33" t="s">
-        <v>105</v>
+        <v>139</v>
       </c>
       <c r="AK42" s="34"/>
       <c r="AL42" s="34"/>
@@ -6791,7 +6791,7 @@
         <v>109007</v>
       </c>
       <c r="G43" s="25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H43" s="28">
         <v>45525</v>
@@ -6878,7 +6878,7 @@
         <v>0</v>
       </c>
       <c r="AJ43" s="33" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AK43" s="34"/>
       <c r="AL43" s="34"/>
@@ -6905,7 +6905,7 @@
         <v>109819</v>
       </c>
       <c r="G44" s="25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H44" s="28">
         <v>45562</v>
@@ -6992,7 +6992,7 @@
         <v>0</v>
       </c>
       <c r="AJ44" s="33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK44" s="34"/>
       <c r="AL44" s="34"/>
@@ -7019,7 +7019,7 @@
         <v>110575</v>
       </c>
       <c r="G45" s="25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H45" s="28">
         <v>45583</v>
@@ -7106,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="AJ45" s="33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AK45" s="34"/>
       <c r="AL45" s="34"/>
@@ -7133,7 +7133,7 @@
         <v>111960</v>
       </c>
       <c r="G46" s="25" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H46" s="28">
         <v>45707</v>
@@ -7220,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="AJ46" s="33" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK46" s="34"/>
       <c r="AL46" s="34"/>
@@ -7247,7 +7247,7 @@
         <v>112522</v>
       </c>
       <c r="G47" s="25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H47" s="28">
         <v>45776</v>
@@ -7334,7 +7334,7 @@
         <v>0</v>
       </c>
       <c r="AJ47" s="33" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AK47" s="34"/>
       <c r="AL47" s="34"/>
@@ -7361,7 +7361,7 @@
         <v>113076</v>
       </c>
       <c r="G48" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H48" s="28">
         <v>45806</v>
@@ -7448,7 +7448,7 @@
         <v>0</v>
       </c>
       <c r="AJ48" s="33" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AK48" s="34"/>
       <c r="AL48" s="34"/>
@@ -7475,7 +7475,7 @@
         <v>114100</v>
       </c>
       <c r="G49" s="25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H49" s="28">
         <v>45863</v>
@@ -7562,7 +7562,7 @@
         <v>0</v>
       </c>
       <c r="AJ49" s="33" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AK49" s="34"/>
       <c r="AL49" s="34"/>
@@ -7589,7 +7589,7 @@
         <v>114157</v>
       </c>
       <c r="G50" s="25" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="H50" s="28">
         <v>45904</v>
@@ -7676,7 +7676,7 @@
         <v>0</v>
       </c>
       <c r="AJ50" s="33" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="AK50" s="34"/>
       <c r="AL50" s="34"/>
@@ -7703,7 +7703,7 @@
         <v>114431</v>
       </c>
       <c r="G51" s="25" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="H51" s="28">
         <v>45930</v>
@@ -7790,7 +7790,7 @@
         <v>0</v>
       </c>
       <c r="AJ51" s="33" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AK51" s="34"/>
       <c r="AL51" s="34"/>
@@ -7989,9 +7989,9 @@
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK43:AN52">
+  <conditionalFormatting sqref="AK42:AN52">
     <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
-      <formula>$B43&lt;&gt;""</formula>
+      <formula>$B42&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/mdrt/MDRT.xlsx
+++ b/mdrt/MDRT.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/mdrt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14FFC621-F7FC-AB48-881D-D168DB48E4AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9329A4D-53C9-514F-8A7D-FF47ACBF46BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16360" xr2:uid="{263D14F0-BAEF-1E4F-83AF-E2F80B31AC70}"/>
+    <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{263D14F0-BAEF-1E4F-83AF-E2F80B31AC70}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -459,7 +459,7 @@
     <t>RIBF8912215D9</t>
   </si>
   <si>
-    <t>Avance del 1 de enero al 13 de marzo de 2026.</t>
+    <t>Avance del 1 de enero al 18 de marzo de 2026.</t>
   </si>
 </sst>
 </file>
@@ -782,7 +782,23 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="49">
+  <dxfs count="50">
+    <dxf>
+      <border>
+        <left style="hair">
+          <color rgb="FF002060"/>
+        </left>
+        <right style="hair">
+          <color rgb="FF002060"/>
+        </right>
+        <top style="hair">
+          <color rgb="FF002060"/>
+        </top>
+        <bottom style="hair">
+          <color rgb="FF002060"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <border>
         <left style="hair">
@@ -1973,49 +1989,49 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}" name="Tabla1" displayName="Tabla1" ref="A4:AN53" totalsRowShown="0" dataDxfId="48" dataCellStyle="Millares">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}" name="Tabla1" displayName="Tabla1" ref="A4:AN53" totalsRowShown="0" dataDxfId="49" dataCellStyle="Millares">
   <autoFilter ref="A4:AN53" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}"/>
   <tableColumns count="40">
-    <tableColumn id="1" xr3:uid="{1B45D68F-9E92-9A48-B147-43382D17EADB}" name="Dir / Zona" dataDxfId="47"/>
-    <tableColumn id="2" xr3:uid="{8141432D-DFE6-034B-8474-F9783519965C}" name="Oficina" dataDxfId="46"/>
-    <tableColumn id="3" xr3:uid="{3026117E-099F-6549-A16F-3CA4F85DA282}" name="Mat" dataDxfId="45"/>
-    <tableColumn id="4" xr3:uid="{80621F5B-C573-8944-AF37-DC364F1BE0A9}" name="Suc" dataDxfId="44"/>
-    <tableColumn id="5" xr3:uid="{9D7D11D1-2D98-5646-92D8-F8703E85240A}" name="Promotor / Partner" dataDxfId="43"/>
-    <tableColumn id="6" xr3:uid="{870F3B42-A14B-1947-827D-9A6082152D25}" name="Asesor" dataDxfId="42"/>
-    <tableColumn id="7" xr3:uid="{CA38BEAA-FBC9-474E-8C66-960105DEBCF2}" name="Nombre del Asesor" dataDxfId="41"/>
-    <tableColumn id="8" xr3:uid="{8B8898BF-4E49-0543-9598-18FF2D3F6340}" name="Conexión" dataDxfId="40"/>
-    <tableColumn id="9" xr3:uid="{49ED1251-337D-EC49-A858-207AB60B673C}" name="Grupo" dataDxfId="39" dataCellStyle="Millares"/>
-    <tableColumn id="10" xr3:uid="{26692A66-EA2C-DD40-AAC8-07A5FE32BC7D}" name="Vida Individual" dataDxfId="38" dataCellStyle="Millares"/>
-    <tableColumn id="11" xr3:uid="{45DC445E-D43B-394B-91CD-B3001CC307CC}" name="Vida G&amp;C" dataDxfId="37" dataCellStyle="Millares"/>
-    <tableColumn id="12" xr3:uid="{953B1F2A-AB88-8A40-B82F-B5DBE8FAEA70}" name="Segudescuento" dataDxfId="36" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{27E03CF4-3925-2045-BF66-C5BB1ECC7061}" name="Aportaciones Adicionales (AVEs)" dataDxfId="35" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{7375183C-90AB-0B47-A516-65079E7802F1}" name="Cancelacion de Pólizas" dataDxfId="34" dataCellStyle="Millares"/>
-    <tableColumn id="15" xr3:uid="{B0F3DBFB-9B00-894E-8929-BF5CA63336C6}" name="Total de Productos Ilimitados" dataDxfId="33" dataCellStyle="Millares"/>
-    <tableColumn id="16" xr3:uid="{3C9D5C71-B64C-434C-8D65-968245DAE09C}" name="%Vida vs Meta" dataDxfId="32" dataCellStyle="Porcentaje"/>
-    <tableColumn id="17" xr3:uid="{088A86A3-8B28-DE4E-A384-CA0EA913DA34}" name="GMM Individual" dataDxfId="31" dataCellStyle="Millares"/>
-    <tableColumn id="18" xr3:uid="{A8791E9D-69D9-C844-AE4C-8AEEFA976B8B}" name="GMM G&amp;C" dataDxfId="30" dataCellStyle="Millares"/>
-    <tableColumn id="19" xr3:uid="{0FFCB5A1-F8D9-2344-9DC7-667454959C98}" name="Cancelacion de Pólizas2" dataDxfId="29" dataCellStyle="Millares"/>
-    <tableColumn id="20" xr3:uid="{FDCA43A0-92B9-954B-B283-ABAD7C194405}" name="Total Productos Limitados" dataDxfId="28" dataCellStyle="Millares"/>
-    <tableColumn id="21" xr3:uid="{7C93BB8B-9213-EA49-A648-EF5192999BF7}" name="Tope personales" dataDxfId="27" dataCellStyle="Millares"/>
-    <tableColumn id="22" xr3:uid="{70D3FAB6-79FB-994B-AB69-F0BBB15C6AFD}" name="Total Prima" dataDxfId="26" dataCellStyle="Millares"/>
-    <tableColumn id="23" xr3:uid="{0E0D17EB-06B5-AF45-9773-7D3921FC5B9C}" name="Vida Individual3" dataDxfId="25" dataCellStyle="Millares"/>
-    <tableColumn id="24" xr3:uid="{2A25EC7F-F387-9948-8D9A-38BFD2316AB4}" name="Vida G&amp;C4" dataDxfId="24" dataCellStyle="Millares"/>
-    <tableColumn id="25" xr3:uid="{F7E8005C-762C-7146-A541-3589C41B3DA2}" name="Segudescuento5" dataDxfId="23" dataCellStyle="Millares"/>
-    <tableColumn id="26" xr3:uid="{278BB65E-357A-1D4C-B1D0-5880BBD354CD}" name="Aportaciones Adicionales (AVEs)6" dataDxfId="22" dataCellStyle="Millares"/>
-    <tableColumn id="27" xr3:uid="{0490A388-0C84-C043-A7E8-E5DC8A03AF3F}" name="Cancelacion de Pólizas7" dataDxfId="21" dataCellStyle="Millares"/>
-    <tableColumn id="28" xr3:uid="{C06E1BE2-8968-A045-B8AB-E420B9B469A1}" name="Total de Productos Ilimitados8" dataDxfId="20" dataCellStyle="Millares"/>
-    <tableColumn id="29" xr3:uid="{BEBE08BA-F641-3141-BCA9-713FD1C7CEC2}" name="%Vida vs Meta9" dataDxfId="19" dataCellStyle="Porcentaje"/>
-    <tableColumn id="30" xr3:uid="{E7FB912B-27FD-1345-845F-E51E648031F5}" name="GMM Individual10" dataDxfId="18" dataCellStyle="Millares"/>
-    <tableColumn id="31" xr3:uid="{D5FF299C-A405-CE44-B4CD-CED400EFE81F}" name="GMM G&amp;C11" dataDxfId="17" dataCellStyle="Millares"/>
-    <tableColumn id="32" xr3:uid="{D7EFF89B-8E34-EA46-B72C-61EE3166E416}" name="Cancelacion de Pólizas12" dataDxfId="16" dataCellStyle="Millares"/>
-    <tableColumn id="33" xr3:uid="{81E1798B-3D20-E748-BDAB-7A2A6F5BF33B}" name="Total Productos Limitados13" dataDxfId="15" dataCellStyle="Millares"/>
-    <tableColumn id="34" xr3:uid="{7A820362-E31F-4D41-B400-9AD11AE00577}" name="Tope personales14" dataDxfId="14" dataCellStyle="Millares"/>
-    <tableColumn id="35" xr3:uid="{09E5F95B-08D0-B946-B14E-3F06BC9C57F0}" name="Total Comisión" dataDxfId="13" dataCellStyle="Millares"/>
-    <tableColumn id="36" xr3:uid="{523C81DC-6FA9-A24D-AF9B-9D74B552A8BA}" name="Columna15" dataDxfId="12" dataCellStyle="Millares"/>
-    <tableColumn id="37" xr3:uid="{ACF68D6F-CC4F-F94A-A3AE-C7407A1AC3DE}" name="Camino Prima" dataDxfId="11" dataCellStyle="Millares"/>
-    <tableColumn id="38" xr3:uid="{39FE9301-7AE9-0A42-B79D-CA4998AB76AE}" name="OBSERVACIÓN" dataDxfId="10" dataCellStyle="Millares"/>
-    <tableColumn id="39" xr3:uid="{99E25200-803C-E54D-88BD-27CB86CAED40}" name="Camino  Comisión" dataDxfId="9" dataCellStyle="Millares"/>
-    <tableColumn id="40" xr3:uid="{45B29C50-720D-8F4E-9803-310BA4AC814E}" name="NIVEL_x000a_" dataDxfId="8" dataCellStyle="Millares"/>
+    <tableColumn id="1" xr3:uid="{1B45D68F-9E92-9A48-B147-43382D17EADB}" name="Dir / Zona" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{8141432D-DFE6-034B-8474-F9783519965C}" name="Oficina" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{3026117E-099F-6549-A16F-3CA4F85DA282}" name="Mat" dataDxfId="46"/>
+    <tableColumn id="4" xr3:uid="{80621F5B-C573-8944-AF37-DC364F1BE0A9}" name="Suc" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{9D7D11D1-2D98-5646-92D8-F8703E85240A}" name="Promotor / Partner" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{870F3B42-A14B-1947-827D-9A6082152D25}" name="Asesor" dataDxfId="43"/>
+    <tableColumn id="7" xr3:uid="{CA38BEAA-FBC9-474E-8C66-960105DEBCF2}" name="Nombre del Asesor" dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{8B8898BF-4E49-0543-9598-18FF2D3F6340}" name="Conexión" dataDxfId="41"/>
+    <tableColumn id="9" xr3:uid="{49ED1251-337D-EC49-A858-207AB60B673C}" name="Grupo" dataDxfId="40" dataCellStyle="Millares"/>
+    <tableColumn id="10" xr3:uid="{26692A66-EA2C-DD40-AAC8-07A5FE32BC7D}" name="Vida Individual" dataDxfId="39" dataCellStyle="Millares"/>
+    <tableColumn id="11" xr3:uid="{45DC445E-D43B-394B-91CD-B3001CC307CC}" name="Vida G&amp;C" dataDxfId="38" dataCellStyle="Millares"/>
+    <tableColumn id="12" xr3:uid="{953B1F2A-AB88-8A40-B82F-B5DBE8FAEA70}" name="Segudescuento" dataDxfId="37" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{27E03CF4-3925-2045-BF66-C5BB1ECC7061}" name="Aportaciones Adicionales (AVEs)" dataDxfId="36" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{7375183C-90AB-0B47-A516-65079E7802F1}" name="Cancelacion de Pólizas" dataDxfId="35" dataCellStyle="Millares"/>
+    <tableColumn id="15" xr3:uid="{B0F3DBFB-9B00-894E-8929-BF5CA63336C6}" name="Total de Productos Ilimitados" dataDxfId="34" dataCellStyle="Millares"/>
+    <tableColumn id="16" xr3:uid="{3C9D5C71-B64C-434C-8D65-968245DAE09C}" name="%Vida vs Meta" dataDxfId="33" dataCellStyle="Porcentaje"/>
+    <tableColumn id="17" xr3:uid="{088A86A3-8B28-DE4E-A384-CA0EA913DA34}" name="GMM Individual" dataDxfId="32" dataCellStyle="Millares"/>
+    <tableColumn id="18" xr3:uid="{A8791E9D-69D9-C844-AE4C-8AEEFA976B8B}" name="GMM G&amp;C" dataDxfId="31" dataCellStyle="Millares"/>
+    <tableColumn id="19" xr3:uid="{0FFCB5A1-F8D9-2344-9DC7-667454959C98}" name="Cancelacion de Pólizas2" dataDxfId="30" dataCellStyle="Millares"/>
+    <tableColumn id="20" xr3:uid="{FDCA43A0-92B9-954B-B283-ABAD7C194405}" name="Total Productos Limitados" dataDxfId="29" dataCellStyle="Millares"/>
+    <tableColumn id="21" xr3:uid="{7C93BB8B-9213-EA49-A648-EF5192999BF7}" name="Tope personales" dataDxfId="28" dataCellStyle="Millares"/>
+    <tableColumn id="22" xr3:uid="{70D3FAB6-79FB-994B-AB69-F0BBB15C6AFD}" name="Total Prima" dataDxfId="27" dataCellStyle="Millares"/>
+    <tableColumn id="23" xr3:uid="{0E0D17EB-06B5-AF45-9773-7D3921FC5B9C}" name="Vida Individual3" dataDxfId="26" dataCellStyle="Millares"/>
+    <tableColumn id="24" xr3:uid="{2A25EC7F-F387-9948-8D9A-38BFD2316AB4}" name="Vida G&amp;C4" dataDxfId="25" dataCellStyle="Millares"/>
+    <tableColumn id="25" xr3:uid="{F7E8005C-762C-7146-A541-3589C41B3DA2}" name="Segudescuento5" dataDxfId="24" dataCellStyle="Millares"/>
+    <tableColumn id="26" xr3:uid="{278BB65E-357A-1D4C-B1D0-5880BBD354CD}" name="Aportaciones Adicionales (AVEs)6" dataDxfId="23" dataCellStyle="Millares"/>
+    <tableColumn id="27" xr3:uid="{0490A388-0C84-C043-A7E8-E5DC8A03AF3F}" name="Cancelacion de Pólizas7" dataDxfId="22" dataCellStyle="Millares"/>
+    <tableColumn id="28" xr3:uid="{C06E1BE2-8968-A045-B8AB-E420B9B469A1}" name="Total de Productos Ilimitados8" dataDxfId="21" dataCellStyle="Millares"/>
+    <tableColumn id="29" xr3:uid="{BEBE08BA-F641-3141-BCA9-713FD1C7CEC2}" name="%Vida vs Meta9" dataDxfId="20" dataCellStyle="Porcentaje"/>
+    <tableColumn id="30" xr3:uid="{E7FB912B-27FD-1345-845F-E51E648031F5}" name="GMM Individual10" dataDxfId="19" dataCellStyle="Millares"/>
+    <tableColumn id="31" xr3:uid="{D5FF299C-A405-CE44-B4CD-CED400EFE81F}" name="GMM G&amp;C11" dataDxfId="18" dataCellStyle="Millares"/>
+    <tableColumn id="32" xr3:uid="{D7EFF89B-8E34-EA46-B72C-61EE3166E416}" name="Cancelacion de Pólizas12" dataDxfId="17" dataCellStyle="Millares"/>
+    <tableColumn id="33" xr3:uid="{81E1798B-3D20-E748-BDAB-7A2A6F5BF33B}" name="Total Productos Limitados13" dataDxfId="16" dataCellStyle="Millares"/>
+    <tableColumn id="34" xr3:uid="{7A820362-E31F-4D41-B400-9AD11AE00577}" name="Tope personales14" dataDxfId="15" dataCellStyle="Millares"/>
+    <tableColumn id="35" xr3:uid="{09E5F95B-08D0-B946-B14E-3F06BC9C57F0}" name="Total Comisión" dataDxfId="14" dataCellStyle="Millares"/>
+    <tableColumn id="36" xr3:uid="{523C81DC-6FA9-A24D-AF9B-9D74B552A8BA}" name="Columna15" dataDxfId="13" dataCellStyle="Millares"/>
+    <tableColumn id="37" xr3:uid="{ACF68D6F-CC4F-F94A-A3AE-C7407A1AC3DE}" name="Camino Prima" dataDxfId="12" dataCellStyle="Millares"/>
+    <tableColumn id="38" xr3:uid="{39FE9301-7AE9-0A42-B79D-CA4998AB76AE}" name="OBSERVACIÓN" dataDxfId="11" dataCellStyle="Millares"/>
+    <tableColumn id="39" xr3:uid="{99E25200-803C-E54D-88BD-27CB86CAED40}" name="Camino  Comisión" dataDxfId="10" dataCellStyle="Millares"/>
+    <tableColumn id="40" xr3:uid="{45B29C50-720D-8F4E-9803-310BA4AC814E}" name="NIVEL_x000a_" dataDxfId="9" dataCellStyle="Millares"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2574,7 +2590,7 @@
         <v>30</v>
       </c>
       <c r="J6" s="30">
-        <v>421824.04</v>
+        <v>550040.93999999994</v>
       </c>
       <c r="K6" s="30">
         <v>0</v>
@@ -2583,16 +2599,16 @@
         <v>0</v>
       </c>
       <c r="M6" s="31">
-        <v>112071.44</v>
+        <v>112411.41</v>
       </c>
       <c r="N6" s="31">
         <v>0</v>
       </c>
       <c r="O6" s="29">
-        <v>533895.48</v>
+        <v>662452.35</v>
       </c>
       <c r="P6" s="32">
-        <v>0.2949</v>
+        <v>0.3659</v>
       </c>
       <c r="Q6" s="30">
         <v>338670.94</v>
@@ -2610,10 +2626,10 @@
         <v>0</v>
       </c>
       <c r="V6" s="29">
-        <v>872566.42</v>
+        <v>1001123.29</v>
       </c>
       <c r="W6" s="29">
-        <v>149289.39000000001</v>
+        <v>192846.25</v>
       </c>
       <c r="X6" s="29">
         <v>0</v>
@@ -2622,16 +2638,16 @@
         <v>0</v>
       </c>
       <c r="Z6" s="31">
-        <v>6089.32</v>
+        <v>6134.65</v>
       </c>
       <c r="AA6" s="31">
         <v>0</v>
       </c>
       <c r="AB6" s="29">
-        <v>155378.71</v>
+        <v>198980.9</v>
       </c>
       <c r="AC6" s="32">
-        <v>0.17169999999999999</v>
+        <v>0.2198</v>
       </c>
       <c r="AD6" s="29">
         <v>73124.62</v>
@@ -2649,7 +2665,7 @@
         <v>0</v>
       </c>
       <c r="AI6" s="29">
-        <v>228503.33</v>
+        <v>272105.52</v>
       </c>
       <c r="AJ6" s="33" t="s">
         <v>31</v>
@@ -2792,25 +2808,25 @@
         <v>2043</v>
       </c>
       <c r="D8" s="26">
-        <v>2856</v>
+        <v>2692</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F8" s="27">
-        <v>110453</v>
+        <v>104750</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>40</v>
+        <v>62</v>
       </c>
       <c r="H8" s="28">
-        <v>45600</v>
+        <v>45236</v>
       </c>
       <c r="I8" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J8" s="30">
-        <v>206465.86</v>
+        <v>63710.97</v>
       </c>
       <c r="K8" s="30">
         <v>0</v>
@@ -2819,19 +2835,19 @@
         <v>0</v>
       </c>
       <c r="M8" s="31">
-        <v>261.17</v>
+        <v>941.93</v>
       </c>
       <c r="N8" s="31">
         <v>0</v>
       </c>
       <c r="O8" s="29">
-        <v>206727.03</v>
+        <v>64652.9</v>
       </c>
       <c r="P8" s="32">
-        <v>0.1142</v>
+        <v>3.5700000000000003E-2</v>
       </c>
       <c r="Q8" s="30">
-        <v>0</v>
+        <v>145683.81</v>
       </c>
       <c r="R8" s="30">
         <v>0</v>
@@ -2840,16 +2856,16 @@
         <v>0</v>
       </c>
       <c r="T8" s="29">
-        <v>0</v>
+        <v>145683.81</v>
       </c>
       <c r="U8" s="29">
         <v>0</v>
       </c>
       <c r="V8" s="29">
-        <v>206727.03</v>
+        <v>210336.71</v>
       </c>
       <c r="W8" s="29">
-        <v>66502.47</v>
+        <v>24068.240000000002</v>
       </c>
       <c r="X8" s="29">
         <v>0</v>
@@ -2858,19 +2874,19 @@
         <v>0</v>
       </c>
       <c r="Z8" s="31">
-        <v>34.82</v>
+        <v>112.51</v>
       </c>
       <c r="AA8" s="31">
         <v>0</v>
       </c>
       <c r="AB8" s="29">
-        <v>66537.289999999994</v>
+        <v>24180.75</v>
       </c>
       <c r="AC8" s="32">
-        <v>7.3499999999999996E-2</v>
+        <v>2.6700000000000002E-2</v>
       </c>
       <c r="AD8" s="29">
-        <v>0</v>
+        <v>21216.080000000002</v>
       </c>
       <c r="AE8" s="29">
         <v>0</v>
@@ -2879,16 +2895,16 @@
         <v>0</v>
       </c>
       <c r="AG8" s="29">
-        <v>0</v>
+        <v>21216.080000000002</v>
       </c>
       <c r="AH8" s="29">
         <v>0</v>
       </c>
       <c r="AI8" s="29">
-        <v>66537.289999999994</v>
+        <v>45396.83</v>
       </c>
       <c r="AJ8" s="33" t="s">
-        <v>41</v>
+        <v>63</v>
       </c>
       <c r="AK8" s="34"/>
       <c r="AL8" s="34"/>
@@ -2906,25 +2922,25 @@
         <v>2043</v>
       </c>
       <c r="D9" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F9" s="27">
-        <v>94156</v>
+        <v>110453</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H9" s="28">
-        <v>44159</v>
+        <v>45600</v>
       </c>
       <c r="I9" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J9" s="30">
-        <v>111482.82</v>
+        <v>206465.86</v>
       </c>
       <c r="K9" s="30">
         <v>0</v>
@@ -2933,19 +2949,19 @@
         <v>0</v>
       </c>
       <c r="M9" s="31">
-        <v>1628.27</v>
+        <v>261.77</v>
       </c>
       <c r="N9" s="31">
         <v>0</v>
       </c>
       <c r="O9" s="29">
-        <v>113111.09</v>
+        <v>206727.63</v>
       </c>
       <c r="P9" s="32">
-        <v>6.25E-2</v>
+        <v>0.1142</v>
       </c>
       <c r="Q9" s="30">
-        <v>64612.59</v>
+        <v>0</v>
       </c>
       <c r="R9" s="30">
         <v>0</v>
@@ -2954,16 +2970,16 @@
         <v>0</v>
       </c>
       <c r="T9" s="29">
-        <v>64612.59</v>
+        <v>0</v>
       </c>
       <c r="U9" s="29">
         <v>0</v>
       </c>
       <c r="V9" s="29">
-        <v>177723.68</v>
+        <v>206727.63</v>
       </c>
       <c r="W9" s="29">
-        <v>30100.36</v>
+        <v>66502.47</v>
       </c>
       <c r="X9" s="29">
         <v>0</v>
@@ -2972,19 +2988,19 @@
         <v>0</v>
       </c>
       <c r="Z9" s="31">
-        <v>384.6</v>
+        <v>34.9</v>
       </c>
       <c r="AA9" s="31">
         <v>0</v>
       </c>
       <c r="AB9" s="29">
-        <v>30484.959999999999</v>
+        <v>66537.37</v>
       </c>
       <c r="AC9" s="32">
-        <v>3.3700000000000001E-2</v>
+        <v>7.3499999999999996E-2</v>
       </c>
       <c r="AD9" s="29">
-        <v>11978.48</v>
+        <v>0</v>
       </c>
       <c r="AE9" s="29">
         <v>0</v>
@@ -2993,16 +3009,16 @@
         <v>0</v>
       </c>
       <c r="AG9" s="29">
-        <v>11978.48</v>
+        <v>0</v>
       </c>
       <c r="AH9" s="29">
         <v>0</v>
       </c>
       <c r="AI9" s="29">
-        <v>42463.44</v>
+        <v>66537.37</v>
       </c>
       <c r="AJ9" s="33" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="AK9" s="34"/>
       <c r="AL9" s="34"/>
@@ -3020,25 +3036,25 @@
         <v>2043</v>
       </c>
       <c r="D10" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F10" s="27">
-        <v>104750</v>
+        <v>94156</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>62</v>
+        <v>36</v>
       </c>
       <c r="H10" s="28">
-        <v>45236</v>
+        <v>44159</v>
       </c>
       <c r="I10" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J10" s="30">
-        <v>63710.97</v>
+        <v>111482.82</v>
       </c>
       <c r="K10" s="30">
         <v>0</v>
@@ -3047,19 +3063,19 @@
         <v>0</v>
       </c>
       <c r="M10" s="31">
-        <v>863.39</v>
+        <v>1811.26</v>
       </c>
       <c r="N10" s="31">
         <v>0</v>
       </c>
       <c r="O10" s="29">
-        <v>64574.36</v>
+        <v>113294.08</v>
       </c>
       <c r="P10" s="32">
-        <v>3.5700000000000003E-2</v>
+        <v>6.2600000000000003E-2</v>
       </c>
       <c r="Q10" s="30">
-        <v>105832.02</v>
+        <v>64612.59</v>
       </c>
       <c r="R10" s="30">
         <v>0</v>
@@ -3068,16 +3084,16 @@
         <v>0</v>
       </c>
       <c r="T10" s="29">
-        <v>105832.02</v>
+        <v>64612.59</v>
       </c>
       <c r="U10" s="29">
         <v>0</v>
       </c>
       <c r="V10" s="29">
-        <v>170406.38</v>
+        <v>177906.67</v>
       </c>
       <c r="W10" s="29">
-        <v>24068.240000000002</v>
+        <v>30100.36</v>
       </c>
       <c r="X10" s="29">
         <v>0</v>
@@ -3086,19 +3102,19 @@
         <v>0</v>
       </c>
       <c r="Z10" s="31">
-        <v>102.04</v>
+        <v>409</v>
       </c>
       <c r="AA10" s="31">
         <v>0</v>
       </c>
       <c r="AB10" s="29">
-        <v>24170.28</v>
+        <v>30509.360000000001</v>
       </c>
       <c r="AC10" s="32">
-        <v>2.6700000000000002E-2</v>
+        <v>3.3700000000000001E-2</v>
       </c>
       <c r="AD10" s="29">
-        <v>12800.69</v>
+        <v>11978.48</v>
       </c>
       <c r="AE10" s="29">
         <v>0</v>
@@ -3107,16 +3123,16 @@
         <v>0</v>
       </c>
       <c r="AG10" s="29">
-        <v>12800.69</v>
+        <v>11978.48</v>
       </c>
       <c r="AH10" s="29">
         <v>0</v>
       </c>
       <c r="AI10" s="29">
-        <v>36970.97</v>
+        <v>42487.839999999997</v>
       </c>
       <c r="AJ10" s="33" t="s">
-        <v>63</v>
+        <v>37</v>
       </c>
       <c r="AK10" s="34"/>
       <c r="AL10" s="34"/>
@@ -3161,16 +3177,16 @@
         <v>0</v>
       </c>
       <c r="M11" s="31">
-        <v>86755.99</v>
+        <v>87080.35</v>
       </c>
       <c r="N11" s="31">
         <v>0</v>
       </c>
       <c r="O11" s="29">
-        <v>162041.26999999999</v>
+        <v>162365.63</v>
       </c>
       <c r="P11" s="32">
-        <v>8.9499999999999996E-2</v>
+        <v>8.9700000000000002E-2</v>
       </c>
       <c r="Q11" s="30">
         <v>0</v>
@@ -3188,7 +3204,7 @@
         <v>0</v>
       </c>
       <c r="V11" s="29">
-        <v>162041.26999999999</v>
+        <v>162365.63</v>
       </c>
       <c r="W11" s="29">
         <v>25150.62</v>
@@ -3200,13 +3216,13 @@
         <v>0</v>
       </c>
       <c r="Z11" s="31">
-        <v>5224.8999999999996</v>
+        <v>5241.12</v>
       </c>
       <c r="AA11" s="31">
         <v>0</v>
       </c>
       <c r="AB11" s="29">
-        <v>30375.52</v>
+        <v>30391.74</v>
       </c>
       <c r="AC11" s="32">
         <v>3.3599999999999998E-2</v>
@@ -3227,7 +3243,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="29">
-        <v>30375.52</v>
+        <v>30391.74</v>
       </c>
       <c r="AJ11" s="33" t="s">
         <v>47</v>
@@ -3275,13 +3291,13 @@
         <v>0</v>
       </c>
       <c r="M12" s="31">
-        <v>21689.7</v>
+        <v>21694.07</v>
       </c>
       <c r="N12" s="31">
         <v>0</v>
       </c>
       <c r="O12" s="29">
-        <v>148575.46</v>
+        <v>148579.82999999999</v>
       </c>
       <c r="P12" s="32">
         <v>8.2100000000000006E-2</v>
@@ -3302,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="29">
-        <v>148575.46</v>
+        <v>148579.82999999999</v>
       </c>
       <c r="W12" s="29">
         <v>50742.080000000002</v>
@@ -3314,13 +3330,13 @@
         <v>0</v>
       </c>
       <c r="Z12" s="31">
-        <v>1141.54</v>
+        <v>1142.1199999999999</v>
       </c>
       <c r="AA12" s="31">
         <v>0</v>
       </c>
       <c r="AB12" s="29">
-        <v>51883.62</v>
+        <v>51884.2</v>
       </c>
       <c r="AC12" s="32">
         <v>5.7299999999999997E-2</v>
@@ -3341,7 +3357,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="29">
-        <v>51883.62</v>
+        <v>51884.2</v>
       </c>
       <c r="AJ12" s="33" t="s">
         <v>39</v>
@@ -3389,16 +3405,16 @@
         <v>0</v>
       </c>
       <c r="M13" s="31">
-        <v>2010.37</v>
+        <v>2640.94</v>
       </c>
       <c r="N13" s="31">
         <v>0</v>
       </c>
       <c r="O13" s="29">
-        <v>114359.19</v>
+        <v>114989.75999999999</v>
       </c>
       <c r="P13" s="32">
-        <v>6.3200000000000006E-2</v>
+        <v>6.3500000000000001E-2</v>
       </c>
       <c r="Q13" s="30">
         <v>31773.599999999999</v>
@@ -3416,7 +3432,7 @@
         <v>0</v>
       </c>
       <c r="V13" s="29">
-        <v>146132.79</v>
+        <v>146763.35999999999</v>
       </c>
       <c r="W13" s="29">
         <v>34992.42</v>
@@ -3428,16 +3444,16 @@
         <v>0</v>
       </c>
       <c r="Z13" s="31">
-        <v>244.05</v>
+        <v>275.58</v>
       </c>
       <c r="AA13" s="31">
         <v>0</v>
       </c>
       <c r="AB13" s="29">
-        <v>35236.47</v>
+        <v>35268</v>
       </c>
       <c r="AC13" s="32">
-        <v>3.8899999999999997E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="AD13" s="29">
         <v>6601.68</v>
@@ -3455,7 +3471,7 @@
         <v>0</v>
       </c>
       <c r="AI13" s="29">
-        <v>41838.15</v>
+        <v>41869.68</v>
       </c>
       <c r="AJ13" s="33" t="s">
         <v>43</v>
@@ -3503,16 +3519,16 @@
         <v>0</v>
       </c>
       <c r="M14" s="31">
-        <v>4230.62</v>
+        <v>4762.41</v>
       </c>
       <c r="N14" s="31">
         <v>0</v>
       </c>
       <c r="O14" s="29">
-        <v>66027.19</v>
+        <v>66558.98</v>
       </c>
       <c r="P14" s="32">
-        <v>3.6499999999999998E-2</v>
+        <v>3.6799999999999999E-2</v>
       </c>
       <c r="Q14" s="30">
         <v>50792.35</v>
@@ -3530,7 +3546,7 @@
         <v>0</v>
       </c>
       <c r="V14" s="29">
-        <v>116819.54</v>
+        <v>117351.33</v>
       </c>
       <c r="W14" s="29">
         <v>18538.98</v>
@@ -3542,16 +3558,16 @@
         <v>0</v>
       </c>
       <c r="Z14" s="31">
-        <v>647.51</v>
+        <v>760.42</v>
       </c>
       <c r="AA14" s="31">
         <v>0</v>
       </c>
       <c r="AB14" s="29">
-        <v>19186.490000000002</v>
+        <v>19299.400000000001</v>
       </c>
       <c r="AC14" s="32">
-        <v>2.12E-2</v>
+        <v>2.1299999999999999E-2</v>
       </c>
       <c r="AD14" s="29">
         <v>9868.51</v>
@@ -3569,7 +3585,7 @@
         <v>0</v>
       </c>
       <c r="AI14" s="29">
-        <v>29055</v>
+        <v>29167.91</v>
       </c>
       <c r="AJ14" s="33" t="s">
         <v>51</v>
@@ -4187,16 +4203,16 @@
         <v>0</v>
       </c>
       <c r="M20" s="31">
-        <v>180</v>
+        <v>540</v>
       </c>
       <c r="N20" s="31">
         <v>0</v>
       </c>
       <c r="O20" s="29">
-        <v>58215.37</v>
+        <v>58575.37</v>
       </c>
       <c r="P20" s="32">
-        <v>3.2199999999999999E-2</v>
+        <v>3.2399999999999998E-2</v>
       </c>
       <c r="Q20" s="30">
         <v>0</v>
@@ -4214,7 +4230,7 @@
         <v>0</v>
       </c>
       <c r="V20" s="29">
-        <v>58215.37</v>
+        <v>58575.37</v>
       </c>
       <c r="W20" s="29">
         <v>15669.55</v>
@@ -4226,16 +4242,16 @@
         <v>0</v>
       </c>
       <c r="Z20" s="31">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="AA20" s="31">
         <v>0</v>
       </c>
       <c r="AB20" s="29">
-        <v>15693.55</v>
+        <v>15711.55</v>
       </c>
       <c r="AC20" s="32">
-        <v>1.7299999999999999E-2</v>
+        <v>1.7399999999999999E-2</v>
       </c>
       <c r="AD20" s="29">
         <v>0</v>
@@ -4253,7 +4269,7 @@
         <v>0</v>
       </c>
       <c r="AI20" s="29">
-        <v>15693.55</v>
+        <v>15711.55</v>
       </c>
       <c r="AJ20" s="33" t="s">
         <v>59</v>
@@ -4415,16 +4431,16 @@
         <v>0</v>
       </c>
       <c r="M22" s="31">
-        <v>985.92</v>
+        <v>1174.3900000000001</v>
       </c>
       <c r="N22" s="31">
         <v>0</v>
       </c>
       <c r="O22" s="29">
-        <v>31815.62</v>
+        <v>32004.09</v>
       </c>
       <c r="P22" s="32">
-        <v>1.7600000000000001E-2</v>
+        <v>1.77E-2</v>
       </c>
       <c r="Q22" s="30">
         <v>16178.04</v>
@@ -4442,7 +4458,7 @@
         <v>0</v>
       </c>
       <c r="V22" s="29">
-        <v>47993.66</v>
+        <v>48182.13</v>
       </c>
       <c r="W22" s="29">
         <v>9451.7999999999993</v>
@@ -4454,16 +4470,16 @@
         <v>0</v>
       </c>
       <c r="Z22" s="31">
-        <v>78.27</v>
+        <v>103.4</v>
       </c>
       <c r="AA22" s="31">
         <v>0</v>
       </c>
       <c r="AB22" s="29">
-        <v>9530.07</v>
+        <v>9555.2000000000007</v>
       </c>
       <c r="AC22" s="32">
-        <v>1.0500000000000001E-2</v>
+        <v>1.06E-2</v>
       </c>
       <c r="AD22" s="29">
         <v>3240.17</v>
@@ -4481,7 +4497,7 @@
         <v>0</v>
       </c>
       <c r="AI22" s="29">
-        <v>12770.24</v>
+        <v>12795.37</v>
       </c>
       <c r="AJ22" s="33" t="s">
         <v>69</v>
@@ -4736,19 +4752,19 @@
         <v>28</v>
       </c>
       <c r="F25" s="27">
-        <v>100677</v>
+        <v>106018</v>
       </c>
       <c r="G25" s="25" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H25" s="28">
-        <v>44999</v>
+        <v>45344</v>
       </c>
       <c r="I25" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J25" s="30">
-        <v>0</v>
+        <v>34230.339999999997</v>
       </c>
       <c r="K25" s="30">
         <v>0</v>
@@ -4757,19 +4773,19 @@
         <v>0</v>
       </c>
       <c r="M25" s="31">
-        <v>1621.42</v>
+        <v>426.22</v>
       </c>
       <c r="N25" s="31">
         <v>0</v>
       </c>
       <c r="O25" s="29">
-        <v>1621.42</v>
+        <v>34656.559999999998</v>
       </c>
       <c r="P25" s="32">
-        <v>8.9999999999999998E-4</v>
+        <v>1.9099999999999999E-2</v>
       </c>
       <c r="Q25" s="30">
-        <v>29685.599999999999</v>
+        <v>0</v>
       </c>
       <c r="R25" s="30">
         <v>0</v>
@@ -4778,16 +4794,16 @@
         <v>0</v>
       </c>
       <c r="T25" s="29">
-        <v>29685.599999999999</v>
+        <v>0</v>
       </c>
       <c r="U25" s="29">
         <v>0</v>
       </c>
       <c r="V25" s="29">
-        <v>31307.02</v>
+        <v>34656.559999999998</v>
       </c>
       <c r="W25" s="29">
-        <v>0</v>
+        <v>10269.11</v>
       </c>
       <c r="X25" s="29">
         <v>0</v>
@@ -4796,19 +4812,19 @@
         <v>0</v>
       </c>
       <c r="Z25" s="31">
-        <v>102.91</v>
+        <v>56.83</v>
       </c>
       <c r="AA25" s="31">
         <v>0</v>
       </c>
       <c r="AB25" s="29">
-        <v>102.91</v>
+        <v>10325.94</v>
       </c>
       <c r="AC25" s="32">
-        <v>1E-4</v>
+        <v>1.14E-2</v>
       </c>
       <c r="AD25" s="29">
-        <v>6178.8</v>
+        <v>0</v>
       </c>
       <c r="AE25" s="29">
         <v>0</v>
@@ -4817,16 +4833,16 @@
         <v>0</v>
       </c>
       <c r="AG25" s="29">
-        <v>6178.8</v>
+        <v>0</v>
       </c>
       <c r="AH25" s="29">
         <v>0</v>
       </c>
       <c r="AI25" s="29">
-        <v>6281.71</v>
+        <v>10325.94</v>
       </c>
       <c r="AJ25" s="33" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AK25" s="34"/>
       <c r="AL25" s="34"/>
@@ -4850,13 +4866,13 @@
         <v>28</v>
       </c>
       <c r="F26" s="27">
-        <v>110105</v>
+        <v>100677</v>
       </c>
       <c r="G26" s="25" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="H26" s="28">
-        <v>45560</v>
+        <v>44999</v>
       </c>
       <c r="I26" s="29" t="s">
         <v>30</v>
@@ -4871,19 +4887,19 @@
         <v>0</v>
       </c>
       <c r="M26" s="31">
-        <v>960</v>
+        <v>1621.42</v>
       </c>
       <c r="N26" s="31">
         <v>0</v>
       </c>
       <c r="O26" s="29">
-        <v>960</v>
+        <v>1621.42</v>
       </c>
       <c r="P26" s="32">
-        <v>5.0000000000000001E-4</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="Q26" s="30">
-        <v>25046.54</v>
+        <v>29685.599999999999</v>
       </c>
       <c r="R26" s="30">
         <v>0</v>
@@ -4892,13 +4908,13 @@
         <v>0</v>
       </c>
       <c r="T26" s="29">
-        <v>25046.54</v>
+        <v>29685.599999999999</v>
       </c>
       <c r="U26" s="29">
         <v>0</v>
       </c>
       <c r="V26" s="29">
-        <v>26006.54</v>
+        <v>31307.02</v>
       </c>
       <c r="W26" s="29">
         <v>0</v>
@@ -4910,19 +4926,19 @@
         <v>0</v>
       </c>
       <c r="Z26" s="31">
-        <v>48</v>
+        <v>102.91</v>
       </c>
       <c r="AA26" s="31">
         <v>0</v>
       </c>
       <c r="AB26" s="29">
-        <v>48</v>
+        <v>102.91</v>
       </c>
       <c r="AC26" s="32">
         <v>1E-4</v>
       </c>
       <c r="AD26" s="29">
-        <v>5158.24</v>
+        <v>6178.8</v>
       </c>
       <c r="AE26" s="29">
         <v>0</v>
@@ -4931,16 +4947,16 @@
         <v>0</v>
       </c>
       <c r="AG26" s="29">
-        <v>5158.24</v>
+        <v>6178.8</v>
       </c>
       <c r="AH26" s="29">
         <v>0</v>
       </c>
       <c r="AI26" s="29">
-        <v>5206.24</v>
+        <v>6281.71</v>
       </c>
       <c r="AJ26" s="33" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AK26" s="34"/>
       <c r="AL26" s="34"/>
@@ -4985,16 +5001,16 @@
         <v>0</v>
       </c>
       <c r="M27" s="31">
-        <v>2420.09</v>
+        <v>4023.53</v>
       </c>
       <c r="N27" s="31">
         <v>0</v>
       </c>
       <c r="O27" s="29">
-        <v>2420.09</v>
+        <v>4023.53</v>
       </c>
       <c r="P27" s="32">
-        <v>1.2999999999999999E-3</v>
+        <v>2.2000000000000001E-3</v>
       </c>
       <c r="Q27" s="30">
         <v>23039.919999999998</v>
@@ -5012,7 +5028,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="29">
-        <v>25460.01</v>
+        <v>27063.45</v>
       </c>
       <c r="W27" s="29">
         <v>0</v>
@@ -5024,16 +5040,16 @@
         <v>0</v>
       </c>
       <c r="Z27" s="31">
-        <v>322.68</v>
+        <v>411.48</v>
       </c>
       <c r="AA27" s="31">
         <v>0</v>
       </c>
       <c r="AB27" s="29">
-        <v>322.68</v>
+        <v>411.48</v>
       </c>
       <c r="AC27" s="32">
-        <v>4.0000000000000002E-4</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AD27" s="29">
         <v>4694.78</v>
@@ -5051,7 +5067,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="29">
-        <v>5017.46</v>
+        <v>5106.26</v>
       </c>
       <c r="AJ27" s="33" t="s">
         <v>75</v>
@@ -5078,13 +5094,13 @@
         <v>28</v>
       </c>
       <c r="F28" s="27">
-        <v>98797</v>
+        <v>110105</v>
       </c>
       <c r="G28" s="25" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="H28" s="28">
-        <v>44342</v>
+        <v>45560</v>
       </c>
       <c r="I28" s="29" t="s">
         <v>30</v>
@@ -5099,19 +5115,19 @@
         <v>0</v>
       </c>
       <c r="M28" s="31">
-        <v>12001.3</v>
+        <v>960</v>
       </c>
       <c r="N28" s="31">
         <v>0</v>
       </c>
       <c r="O28" s="29">
-        <v>12001.3</v>
+        <v>960</v>
       </c>
       <c r="P28" s="32">
-        <v>6.6E-3</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q28" s="30">
-        <v>0</v>
+        <v>25046.54</v>
       </c>
       <c r="R28" s="30">
         <v>0</v>
@@ -5120,13 +5136,13 @@
         <v>0</v>
       </c>
       <c r="T28" s="29">
-        <v>0</v>
+        <v>25046.54</v>
       </c>
       <c r="U28" s="29">
         <v>0</v>
       </c>
       <c r="V28" s="29">
-        <v>12001.3</v>
+        <v>26006.54</v>
       </c>
       <c r="W28" s="29">
         <v>0</v>
@@ -5138,19 +5154,19 @@
         <v>0</v>
       </c>
       <c r="Z28" s="31">
-        <v>600.05999999999995</v>
+        <v>48</v>
       </c>
       <c r="AA28" s="31">
         <v>0</v>
       </c>
       <c r="AB28" s="29">
-        <v>600.05999999999995</v>
+        <v>48</v>
       </c>
       <c r="AC28" s="32">
-        <v>6.9999999999999999E-4</v>
+        <v>1E-4</v>
       </c>
       <c r="AD28" s="29">
-        <v>0</v>
+        <v>5158.24</v>
       </c>
       <c r="AE28" s="29">
         <v>0</v>
@@ -5159,16 +5175,16 @@
         <v>0</v>
       </c>
       <c r="AG28" s="29">
-        <v>0</v>
+        <v>5158.24</v>
       </c>
       <c r="AH28" s="29">
         <v>0</v>
       </c>
       <c r="AI28" s="29">
-        <v>600.05999999999995</v>
+        <v>5206.24</v>
       </c>
       <c r="AJ28" s="33" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="AK28" s="34"/>
       <c r="AL28" s="34"/>
@@ -5192,13 +5208,13 @@
         <v>28</v>
       </c>
       <c r="F29" s="27">
-        <v>104343</v>
+        <v>98797</v>
       </c>
       <c r="G29" s="25" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="H29" s="28">
-        <v>45201</v>
+        <v>44342</v>
       </c>
       <c r="I29" s="29" t="s">
         <v>30</v>
@@ -5213,16 +5229,16 @@
         <v>0</v>
       </c>
       <c r="M29" s="31">
-        <v>2480.0300000000002</v>
+        <v>12001.3</v>
       </c>
       <c r="N29" s="31">
         <v>0</v>
       </c>
       <c r="O29" s="29">
-        <v>2480.0300000000002</v>
+        <v>12001.3</v>
       </c>
       <c r="P29" s="32">
-        <v>1.4E-3</v>
+        <v>6.6E-3</v>
       </c>
       <c r="Q29" s="30">
         <v>0</v>
@@ -5240,7 +5256,7 @@
         <v>0</v>
       </c>
       <c r="V29" s="29">
-        <v>2480.0300000000002</v>
+        <v>12001.3</v>
       </c>
       <c r="W29" s="29">
         <v>0</v>
@@ -5252,16 +5268,16 @@
         <v>0</v>
       </c>
       <c r="Z29" s="31">
-        <v>280.64</v>
+        <v>600.05999999999995</v>
       </c>
       <c r="AA29" s="31">
         <v>0</v>
       </c>
       <c r="AB29" s="29">
-        <v>280.64</v>
+        <v>600.05999999999995</v>
       </c>
       <c r="AC29" s="32">
-        <v>2.9999999999999997E-4</v>
+        <v>6.9999999999999999E-4</v>
       </c>
       <c r="AD29" s="29">
         <v>0</v>
@@ -5279,10 +5295,10 @@
         <v>0</v>
       </c>
       <c r="AI29" s="29">
-        <v>280.64</v>
+        <v>600.05999999999995</v>
       </c>
       <c r="AJ29" s="33" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="AK29" s="34"/>
       <c r="AL29" s="34"/>
@@ -5306,13 +5322,13 @@
         <v>28</v>
       </c>
       <c r="F30" s="27">
-        <v>106018</v>
+        <v>104343</v>
       </c>
       <c r="G30" s="25" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H30" s="28">
-        <v>45344</v>
+        <v>45201</v>
       </c>
       <c r="I30" s="29" t="s">
         <v>30</v>
@@ -5327,16 +5343,16 @@
         <v>0</v>
       </c>
       <c r="M30" s="31">
-        <v>426.22</v>
+        <v>2480.0300000000002</v>
       </c>
       <c r="N30" s="31">
         <v>0</v>
       </c>
       <c r="O30" s="29">
-        <v>426.22</v>
+        <v>2480.0300000000002</v>
       </c>
       <c r="P30" s="32">
-        <v>2.0000000000000001E-4</v>
+        <v>1.4E-3</v>
       </c>
       <c r="Q30" s="30">
         <v>0</v>
@@ -5354,7 +5370,7 @@
         <v>0</v>
       </c>
       <c r="V30" s="29">
-        <v>426.22</v>
+        <v>2480.0300000000002</v>
       </c>
       <c r="W30" s="29">
         <v>0</v>
@@ -5366,16 +5382,16 @@
         <v>0</v>
       </c>
       <c r="Z30" s="31">
-        <v>56.83</v>
+        <v>280.64</v>
       </c>
       <c r="AA30" s="31">
         <v>0</v>
       </c>
       <c r="AB30" s="29">
-        <v>56.83</v>
+        <v>280.64</v>
       </c>
       <c r="AC30" s="32">
-        <v>1E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="AD30" s="29">
         <v>0</v>
@@ -5393,10 +5409,10 @@
         <v>0</v>
       </c>
       <c r="AI30" s="29">
-        <v>56.83</v>
+        <v>280.64</v>
       </c>
       <c r="AJ30" s="33" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="AK30" s="34"/>
       <c r="AL30" s="34"/>
@@ -7955,38 +7971,43 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A53:AI53 AM53:AN53 AK53">
-    <cfRule type="expression" dxfId="7" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="8" priority="9" stopIfTrue="1">
       <formula>$B53&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK53:AN53">
-    <cfRule type="expression" dxfId="6" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="6" stopIfTrue="1">
       <formula>$B53&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL53">
-    <cfRule type="expression" dxfId="5" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="7" stopIfTrue="1">
       <formula>$B53&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN53 V53 AI53">
-    <cfRule type="expression" dxfId="4" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="8" stopIfTrue="1">
       <formula>$B53&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:AI52 AK6:AK52 AM6:AN52">
+    <cfRule type="expression" dxfId="4" priority="5" stopIfTrue="1">
+      <formula>$B6&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V6:V52 AI6:AI52 AN6:AN52">
     <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V6:V52 AI6:AI52 AN6:AN52">
+  <conditionalFormatting sqref="AL6:AL52">
     <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL6:AL52">
+  <conditionalFormatting sqref="AK41:AN41">
     <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
-      <formula>$B6&lt;&gt;""</formula>
+      <formula>$B41&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK42:AN52">

--- a/mdrt/MDRT.xlsx
+++ b/mdrt/MDRT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/mdrt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9329A4D-53C9-514F-8A7D-FF47ACBF46BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F831C410-6B00-8C4F-9081-628C0ED4BC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{263D14F0-BAEF-1E4F-83AF-E2F80B31AC70}"/>
   </bookViews>
@@ -459,7 +459,7 @@
     <t>RIBF8912215D9</t>
   </si>
   <si>
-    <t>Avance del 1 de enero al 18 de marzo de 2026.</t>
+    <t>Avance del 1 de enero al 25 de marzo de 2026.</t>
   </si>
 </sst>
 </file>
@@ -782,23 +782,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="50">
-    <dxf>
-      <border>
-        <left style="hair">
-          <color rgb="FF002060"/>
-        </left>
-        <right style="hair">
-          <color rgb="FF002060"/>
-        </right>
-        <top style="hair">
-          <color rgb="FF002060"/>
-        </top>
-        <bottom style="hair">
-          <color rgb="FF002060"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="49">
     <dxf>
       <border>
         <left style="hair">
@@ -1989,49 +1973,49 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}" name="Tabla1" displayName="Tabla1" ref="A4:AN53" totalsRowShown="0" dataDxfId="49" dataCellStyle="Millares">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}" name="Tabla1" displayName="Tabla1" ref="A4:AN53" totalsRowShown="0" dataDxfId="48" dataCellStyle="Millares">
   <autoFilter ref="A4:AN53" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}"/>
   <tableColumns count="40">
-    <tableColumn id="1" xr3:uid="{1B45D68F-9E92-9A48-B147-43382D17EADB}" name="Dir / Zona" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{8141432D-DFE6-034B-8474-F9783519965C}" name="Oficina" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{3026117E-099F-6549-A16F-3CA4F85DA282}" name="Mat" dataDxfId="46"/>
-    <tableColumn id="4" xr3:uid="{80621F5B-C573-8944-AF37-DC364F1BE0A9}" name="Suc" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{9D7D11D1-2D98-5646-92D8-F8703E85240A}" name="Promotor / Partner" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{870F3B42-A14B-1947-827D-9A6082152D25}" name="Asesor" dataDxfId="43"/>
-    <tableColumn id="7" xr3:uid="{CA38BEAA-FBC9-474E-8C66-960105DEBCF2}" name="Nombre del Asesor" dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{8B8898BF-4E49-0543-9598-18FF2D3F6340}" name="Conexión" dataDxfId="41"/>
-    <tableColumn id="9" xr3:uid="{49ED1251-337D-EC49-A858-207AB60B673C}" name="Grupo" dataDxfId="40" dataCellStyle="Millares"/>
-    <tableColumn id="10" xr3:uid="{26692A66-EA2C-DD40-AAC8-07A5FE32BC7D}" name="Vida Individual" dataDxfId="39" dataCellStyle="Millares"/>
-    <tableColumn id="11" xr3:uid="{45DC445E-D43B-394B-91CD-B3001CC307CC}" name="Vida G&amp;C" dataDxfId="38" dataCellStyle="Millares"/>
-    <tableColumn id="12" xr3:uid="{953B1F2A-AB88-8A40-B82F-B5DBE8FAEA70}" name="Segudescuento" dataDxfId="37" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{27E03CF4-3925-2045-BF66-C5BB1ECC7061}" name="Aportaciones Adicionales (AVEs)" dataDxfId="36" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{7375183C-90AB-0B47-A516-65079E7802F1}" name="Cancelacion de Pólizas" dataDxfId="35" dataCellStyle="Millares"/>
-    <tableColumn id="15" xr3:uid="{B0F3DBFB-9B00-894E-8929-BF5CA63336C6}" name="Total de Productos Ilimitados" dataDxfId="34" dataCellStyle="Millares"/>
-    <tableColumn id="16" xr3:uid="{3C9D5C71-B64C-434C-8D65-968245DAE09C}" name="%Vida vs Meta" dataDxfId="33" dataCellStyle="Porcentaje"/>
-    <tableColumn id="17" xr3:uid="{088A86A3-8B28-DE4E-A384-CA0EA913DA34}" name="GMM Individual" dataDxfId="32" dataCellStyle="Millares"/>
-    <tableColumn id="18" xr3:uid="{A8791E9D-69D9-C844-AE4C-8AEEFA976B8B}" name="GMM G&amp;C" dataDxfId="31" dataCellStyle="Millares"/>
-    <tableColumn id="19" xr3:uid="{0FFCB5A1-F8D9-2344-9DC7-667454959C98}" name="Cancelacion de Pólizas2" dataDxfId="30" dataCellStyle="Millares"/>
-    <tableColumn id="20" xr3:uid="{FDCA43A0-92B9-954B-B283-ABAD7C194405}" name="Total Productos Limitados" dataDxfId="29" dataCellStyle="Millares"/>
-    <tableColumn id="21" xr3:uid="{7C93BB8B-9213-EA49-A648-EF5192999BF7}" name="Tope personales" dataDxfId="28" dataCellStyle="Millares"/>
-    <tableColumn id="22" xr3:uid="{70D3FAB6-79FB-994B-AB69-F0BBB15C6AFD}" name="Total Prima" dataDxfId="27" dataCellStyle="Millares"/>
-    <tableColumn id="23" xr3:uid="{0E0D17EB-06B5-AF45-9773-7D3921FC5B9C}" name="Vida Individual3" dataDxfId="26" dataCellStyle="Millares"/>
-    <tableColumn id="24" xr3:uid="{2A25EC7F-F387-9948-8D9A-38BFD2316AB4}" name="Vida G&amp;C4" dataDxfId="25" dataCellStyle="Millares"/>
-    <tableColumn id="25" xr3:uid="{F7E8005C-762C-7146-A541-3589C41B3DA2}" name="Segudescuento5" dataDxfId="24" dataCellStyle="Millares"/>
-    <tableColumn id="26" xr3:uid="{278BB65E-357A-1D4C-B1D0-5880BBD354CD}" name="Aportaciones Adicionales (AVEs)6" dataDxfId="23" dataCellStyle="Millares"/>
-    <tableColumn id="27" xr3:uid="{0490A388-0C84-C043-A7E8-E5DC8A03AF3F}" name="Cancelacion de Pólizas7" dataDxfId="22" dataCellStyle="Millares"/>
-    <tableColumn id="28" xr3:uid="{C06E1BE2-8968-A045-B8AB-E420B9B469A1}" name="Total de Productos Ilimitados8" dataDxfId="21" dataCellStyle="Millares"/>
-    <tableColumn id="29" xr3:uid="{BEBE08BA-F641-3141-BCA9-713FD1C7CEC2}" name="%Vida vs Meta9" dataDxfId="20" dataCellStyle="Porcentaje"/>
-    <tableColumn id="30" xr3:uid="{E7FB912B-27FD-1345-845F-E51E648031F5}" name="GMM Individual10" dataDxfId="19" dataCellStyle="Millares"/>
-    <tableColumn id="31" xr3:uid="{D5FF299C-A405-CE44-B4CD-CED400EFE81F}" name="GMM G&amp;C11" dataDxfId="18" dataCellStyle="Millares"/>
-    <tableColumn id="32" xr3:uid="{D7EFF89B-8E34-EA46-B72C-61EE3166E416}" name="Cancelacion de Pólizas12" dataDxfId="17" dataCellStyle="Millares"/>
-    <tableColumn id="33" xr3:uid="{81E1798B-3D20-E748-BDAB-7A2A6F5BF33B}" name="Total Productos Limitados13" dataDxfId="16" dataCellStyle="Millares"/>
-    <tableColumn id="34" xr3:uid="{7A820362-E31F-4D41-B400-9AD11AE00577}" name="Tope personales14" dataDxfId="15" dataCellStyle="Millares"/>
-    <tableColumn id="35" xr3:uid="{09E5F95B-08D0-B946-B14E-3F06BC9C57F0}" name="Total Comisión" dataDxfId="14" dataCellStyle="Millares"/>
-    <tableColumn id="36" xr3:uid="{523C81DC-6FA9-A24D-AF9B-9D74B552A8BA}" name="Columna15" dataDxfId="13" dataCellStyle="Millares"/>
-    <tableColumn id="37" xr3:uid="{ACF68D6F-CC4F-F94A-A3AE-C7407A1AC3DE}" name="Camino Prima" dataDxfId="12" dataCellStyle="Millares"/>
-    <tableColumn id="38" xr3:uid="{39FE9301-7AE9-0A42-B79D-CA4998AB76AE}" name="OBSERVACIÓN" dataDxfId="11" dataCellStyle="Millares"/>
-    <tableColumn id="39" xr3:uid="{99E25200-803C-E54D-88BD-27CB86CAED40}" name="Camino  Comisión" dataDxfId="10" dataCellStyle="Millares"/>
-    <tableColumn id="40" xr3:uid="{45B29C50-720D-8F4E-9803-310BA4AC814E}" name="NIVEL_x000a_" dataDxfId="9" dataCellStyle="Millares"/>
+    <tableColumn id="1" xr3:uid="{1B45D68F-9E92-9A48-B147-43382D17EADB}" name="Dir / Zona" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{8141432D-DFE6-034B-8474-F9783519965C}" name="Oficina" dataDxfId="46"/>
+    <tableColumn id="3" xr3:uid="{3026117E-099F-6549-A16F-3CA4F85DA282}" name="Mat" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{80621F5B-C573-8944-AF37-DC364F1BE0A9}" name="Suc" dataDxfId="44"/>
+    <tableColumn id="5" xr3:uid="{9D7D11D1-2D98-5646-92D8-F8703E85240A}" name="Promotor / Partner" dataDxfId="43"/>
+    <tableColumn id="6" xr3:uid="{870F3B42-A14B-1947-827D-9A6082152D25}" name="Asesor" dataDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{CA38BEAA-FBC9-474E-8C66-960105DEBCF2}" name="Nombre del Asesor" dataDxfId="41"/>
+    <tableColumn id="8" xr3:uid="{8B8898BF-4E49-0543-9598-18FF2D3F6340}" name="Conexión" dataDxfId="40"/>
+    <tableColumn id="9" xr3:uid="{49ED1251-337D-EC49-A858-207AB60B673C}" name="Grupo" dataDxfId="39" dataCellStyle="Millares"/>
+    <tableColumn id="10" xr3:uid="{26692A66-EA2C-DD40-AAC8-07A5FE32BC7D}" name="Vida Individual" dataDxfId="38" dataCellStyle="Millares"/>
+    <tableColumn id="11" xr3:uid="{45DC445E-D43B-394B-91CD-B3001CC307CC}" name="Vida G&amp;C" dataDxfId="37" dataCellStyle="Millares"/>
+    <tableColumn id="12" xr3:uid="{953B1F2A-AB88-8A40-B82F-B5DBE8FAEA70}" name="Segudescuento" dataDxfId="36" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{27E03CF4-3925-2045-BF66-C5BB1ECC7061}" name="Aportaciones Adicionales (AVEs)" dataDxfId="35" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{7375183C-90AB-0B47-A516-65079E7802F1}" name="Cancelacion de Pólizas" dataDxfId="34" dataCellStyle="Millares"/>
+    <tableColumn id="15" xr3:uid="{B0F3DBFB-9B00-894E-8929-BF5CA63336C6}" name="Total de Productos Ilimitados" dataDxfId="33" dataCellStyle="Millares"/>
+    <tableColumn id="16" xr3:uid="{3C9D5C71-B64C-434C-8D65-968245DAE09C}" name="%Vida vs Meta" dataDxfId="32" dataCellStyle="Porcentaje"/>
+    <tableColumn id="17" xr3:uid="{088A86A3-8B28-DE4E-A384-CA0EA913DA34}" name="GMM Individual" dataDxfId="31" dataCellStyle="Millares"/>
+    <tableColumn id="18" xr3:uid="{A8791E9D-69D9-C844-AE4C-8AEEFA976B8B}" name="GMM G&amp;C" dataDxfId="30" dataCellStyle="Millares"/>
+    <tableColumn id="19" xr3:uid="{0FFCB5A1-F8D9-2344-9DC7-667454959C98}" name="Cancelacion de Pólizas2" dataDxfId="29" dataCellStyle="Millares"/>
+    <tableColumn id="20" xr3:uid="{FDCA43A0-92B9-954B-B283-ABAD7C194405}" name="Total Productos Limitados" dataDxfId="28" dataCellStyle="Millares"/>
+    <tableColumn id="21" xr3:uid="{7C93BB8B-9213-EA49-A648-EF5192999BF7}" name="Tope personales" dataDxfId="27" dataCellStyle="Millares"/>
+    <tableColumn id="22" xr3:uid="{70D3FAB6-79FB-994B-AB69-F0BBB15C6AFD}" name="Total Prima" dataDxfId="26" dataCellStyle="Millares"/>
+    <tableColumn id="23" xr3:uid="{0E0D17EB-06B5-AF45-9773-7D3921FC5B9C}" name="Vida Individual3" dataDxfId="25" dataCellStyle="Millares"/>
+    <tableColumn id="24" xr3:uid="{2A25EC7F-F387-9948-8D9A-38BFD2316AB4}" name="Vida G&amp;C4" dataDxfId="24" dataCellStyle="Millares"/>
+    <tableColumn id="25" xr3:uid="{F7E8005C-762C-7146-A541-3589C41B3DA2}" name="Segudescuento5" dataDxfId="23" dataCellStyle="Millares"/>
+    <tableColumn id="26" xr3:uid="{278BB65E-357A-1D4C-B1D0-5880BBD354CD}" name="Aportaciones Adicionales (AVEs)6" dataDxfId="22" dataCellStyle="Millares"/>
+    <tableColumn id="27" xr3:uid="{0490A388-0C84-C043-A7E8-E5DC8A03AF3F}" name="Cancelacion de Pólizas7" dataDxfId="21" dataCellStyle="Millares"/>
+    <tableColumn id="28" xr3:uid="{C06E1BE2-8968-A045-B8AB-E420B9B469A1}" name="Total de Productos Ilimitados8" dataDxfId="20" dataCellStyle="Millares"/>
+    <tableColumn id="29" xr3:uid="{BEBE08BA-F641-3141-BCA9-713FD1C7CEC2}" name="%Vida vs Meta9" dataDxfId="19" dataCellStyle="Porcentaje"/>
+    <tableColumn id="30" xr3:uid="{E7FB912B-27FD-1345-845F-E51E648031F5}" name="GMM Individual10" dataDxfId="18" dataCellStyle="Millares"/>
+    <tableColumn id="31" xr3:uid="{D5FF299C-A405-CE44-B4CD-CED400EFE81F}" name="GMM G&amp;C11" dataDxfId="17" dataCellStyle="Millares"/>
+    <tableColumn id="32" xr3:uid="{D7EFF89B-8E34-EA46-B72C-61EE3166E416}" name="Cancelacion de Pólizas12" dataDxfId="16" dataCellStyle="Millares"/>
+    <tableColumn id="33" xr3:uid="{81E1798B-3D20-E748-BDAB-7A2A6F5BF33B}" name="Total Productos Limitados13" dataDxfId="15" dataCellStyle="Millares"/>
+    <tableColumn id="34" xr3:uid="{7A820362-E31F-4D41-B400-9AD11AE00577}" name="Tope personales14" dataDxfId="14" dataCellStyle="Millares"/>
+    <tableColumn id="35" xr3:uid="{09E5F95B-08D0-B946-B14E-3F06BC9C57F0}" name="Total Comisión" dataDxfId="13" dataCellStyle="Millares"/>
+    <tableColumn id="36" xr3:uid="{523C81DC-6FA9-A24D-AF9B-9D74B552A8BA}" name="Columna15" dataDxfId="12" dataCellStyle="Millares"/>
+    <tableColumn id="37" xr3:uid="{ACF68D6F-CC4F-F94A-A3AE-C7407A1AC3DE}" name="Camino Prima" dataDxfId="11" dataCellStyle="Millares"/>
+    <tableColumn id="38" xr3:uid="{39FE9301-7AE9-0A42-B79D-CA4998AB76AE}" name="OBSERVACIÓN" dataDxfId="10" dataCellStyle="Millares"/>
+    <tableColumn id="39" xr3:uid="{99E25200-803C-E54D-88BD-27CB86CAED40}" name="Camino  Comisión" dataDxfId="9" dataCellStyle="Millares"/>
+    <tableColumn id="40" xr3:uid="{45B29C50-720D-8F4E-9803-310BA4AC814E}" name="NIVEL_x000a_" dataDxfId="8" dataCellStyle="Millares"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2599,16 +2583,16 @@
         <v>0</v>
       </c>
       <c r="M6" s="31">
-        <v>112411.41</v>
+        <v>113328.4</v>
       </c>
       <c r="N6" s="31">
         <v>0</v>
       </c>
       <c r="O6" s="29">
-        <v>662452.35</v>
+        <v>663369.34</v>
       </c>
       <c r="P6" s="32">
-        <v>0.3659</v>
+        <v>0.3664</v>
       </c>
       <c r="Q6" s="30">
         <v>338670.94</v>
@@ -2617,16 +2601,16 @@
         <v>0</v>
       </c>
       <c r="S6" s="30">
-        <v>0</v>
+        <v>13875</v>
       </c>
       <c r="T6" s="29">
-        <v>338670.94</v>
+        <v>324795.94</v>
       </c>
       <c r="U6" s="29">
         <v>0</v>
       </c>
       <c r="V6" s="29">
-        <v>1001123.29</v>
+        <v>988165.28</v>
       </c>
       <c r="W6" s="29">
         <v>192846.25</v>
@@ -2638,16 +2622,16 @@
         <v>0</v>
       </c>
       <c r="Z6" s="31">
-        <v>6134.65</v>
+        <v>6414.89</v>
       </c>
       <c r="AA6" s="31">
         <v>0</v>
       </c>
       <c r="AB6" s="29">
-        <v>198980.9</v>
+        <v>199261.14</v>
       </c>
       <c r="AC6" s="32">
-        <v>0.2198</v>
+        <v>0.22009999999999999</v>
       </c>
       <c r="AD6" s="29">
         <v>73124.62</v>
@@ -2656,16 +2640,16 @@
         <v>0</v>
       </c>
       <c r="AF6" s="29">
-        <v>0</v>
+        <v>2848</v>
       </c>
       <c r="AG6" s="29">
-        <v>73124.62</v>
+        <v>70276.62</v>
       </c>
       <c r="AH6" s="29">
         <v>0</v>
       </c>
       <c r="AI6" s="29">
-        <v>272105.52</v>
+        <v>269537.76</v>
       </c>
       <c r="AJ6" s="33" t="s">
         <v>31</v>
@@ -2694,25 +2678,25 @@
         <v>2043</v>
       </c>
       <c r="D7" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E7" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F7" s="27">
-        <v>111056</v>
+        <v>80122</v>
       </c>
       <c r="G7" s="25" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="H7" s="28">
-        <v>45639</v>
+        <v>43371</v>
       </c>
       <c r="I7" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J7" s="30">
-        <v>0</v>
+        <v>200525.76</v>
       </c>
       <c r="K7" s="30">
         <v>0</v>
@@ -2721,19 +2705,19 @@
         <v>0</v>
       </c>
       <c r="M7" s="31">
-        <v>0</v>
+        <v>88228.15</v>
       </c>
       <c r="N7" s="31">
         <v>0</v>
       </c>
       <c r="O7" s="29">
-        <v>0</v>
+        <v>288753.90999999997</v>
       </c>
       <c r="P7" s="32">
-        <v>0</v>
+        <v>0.1595</v>
       </c>
       <c r="Q7" s="30">
-        <v>235038.77</v>
+        <v>0</v>
       </c>
       <c r="R7" s="30">
         <v>0</v>
@@ -2742,16 +2726,16 @@
         <v>0</v>
       </c>
       <c r="T7" s="29">
-        <v>235038.77</v>
+        <v>0</v>
       </c>
       <c r="U7" s="29">
         <v>0</v>
       </c>
       <c r="V7" s="29">
-        <v>235038.77</v>
+        <v>288753.90999999997</v>
       </c>
       <c r="W7" s="29">
-        <v>0</v>
+        <v>53337.3</v>
       </c>
       <c r="X7" s="29">
         <v>0</v>
@@ -2760,19 +2744,19 @@
         <v>0</v>
       </c>
       <c r="Z7" s="31">
-        <v>0</v>
+        <v>5364.22</v>
       </c>
       <c r="AA7" s="31">
         <v>0</v>
       </c>
       <c r="AB7" s="29">
-        <v>0</v>
+        <v>58701.52</v>
       </c>
       <c r="AC7" s="32">
-        <v>0</v>
+        <v>6.4799999999999996E-2</v>
       </c>
       <c r="AD7" s="29">
-        <v>37294.720000000001</v>
+        <v>0</v>
       </c>
       <c r="AE7" s="29">
         <v>0</v>
@@ -2781,16 +2765,16 @@
         <v>0</v>
       </c>
       <c r="AG7" s="29">
-        <v>37294.720000000001</v>
+        <v>0</v>
       </c>
       <c r="AH7" s="29">
         <v>0</v>
       </c>
       <c r="AI7" s="29">
-        <v>37294.720000000001</v>
+        <v>58701.52</v>
       </c>
       <c r="AJ7" s="33" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="AK7" s="34"/>
       <c r="AL7" s="34"/>
@@ -2826,7 +2810,7 @@
         <v>30</v>
       </c>
       <c r="J8" s="30">
-        <v>63710.97</v>
+        <v>127806.03</v>
       </c>
       <c r="K8" s="30">
         <v>0</v>
@@ -2835,16 +2819,16 @@
         <v>0</v>
       </c>
       <c r="M8" s="31">
-        <v>941.93</v>
+        <v>1020.54</v>
       </c>
       <c r="N8" s="31">
         <v>0</v>
       </c>
       <c r="O8" s="29">
-        <v>64652.9</v>
+        <v>128826.57</v>
       </c>
       <c r="P8" s="32">
-        <v>3.5700000000000003E-2</v>
+        <v>7.1199999999999999E-2</v>
       </c>
       <c r="Q8" s="30">
         <v>145683.81</v>
@@ -2862,10 +2846,10 @@
         <v>0</v>
       </c>
       <c r="V8" s="29">
-        <v>210336.71</v>
+        <v>274510.38</v>
       </c>
       <c r="W8" s="29">
-        <v>24068.240000000002</v>
+        <v>45752.84</v>
       </c>
       <c r="X8" s="29">
         <v>0</v>
@@ -2874,16 +2858,16 @@
         <v>0</v>
       </c>
       <c r="Z8" s="31">
-        <v>112.51</v>
+        <v>122.99</v>
       </c>
       <c r="AA8" s="31">
         <v>0</v>
       </c>
       <c r="AB8" s="29">
-        <v>24180.75</v>
+        <v>45875.83</v>
       </c>
       <c r="AC8" s="32">
-        <v>2.6700000000000002E-2</v>
+        <v>5.0700000000000002E-2</v>
       </c>
       <c r="AD8" s="29">
         <v>21216.080000000002</v>
@@ -2901,7 +2885,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="29">
-        <v>45396.83</v>
+        <v>67091.91</v>
       </c>
       <c r="AJ8" s="33" t="s">
         <v>63</v>
@@ -2922,25 +2906,25 @@
         <v>2043</v>
       </c>
       <c r="D9" s="26">
-        <v>2856</v>
+        <v>2692</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F9" s="27">
-        <v>110453</v>
+        <v>111056</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="H9" s="28">
-        <v>45600</v>
+        <v>45639</v>
       </c>
       <c r="I9" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J9" s="30">
-        <v>206465.86</v>
+        <v>0</v>
       </c>
       <c r="K9" s="30">
         <v>0</v>
@@ -2949,19 +2933,19 @@
         <v>0</v>
       </c>
       <c r="M9" s="31">
-        <v>261.77</v>
+        <v>0</v>
       </c>
       <c r="N9" s="31">
         <v>0</v>
       </c>
       <c r="O9" s="29">
-        <v>206727.63</v>
+        <v>0</v>
       </c>
       <c r="P9" s="32">
-        <v>0.1142</v>
+        <v>0</v>
       </c>
       <c r="Q9" s="30">
-        <v>0</v>
+        <v>235038.77</v>
       </c>
       <c r="R9" s="30">
         <v>0</v>
@@ -2970,16 +2954,16 @@
         <v>0</v>
       </c>
       <c r="T9" s="29">
-        <v>0</v>
+        <v>235038.77</v>
       </c>
       <c r="U9" s="29">
         <v>0</v>
       </c>
       <c r="V9" s="29">
-        <v>206727.63</v>
+        <v>235038.77</v>
       </c>
       <c r="W9" s="29">
-        <v>66502.47</v>
+        <v>0</v>
       </c>
       <c r="X9" s="29">
         <v>0</v>
@@ -2988,19 +2972,19 @@
         <v>0</v>
       </c>
       <c r="Z9" s="31">
-        <v>34.9</v>
+        <v>0</v>
       </c>
       <c r="AA9" s="31">
         <v>0</v>
       </c>
       <c r="AB9" s="29">
-        <v>66537.37</v>
+        <v>0</v>
       </c>
       <c r="AC9" s="32">
-        <v>7.3499999999999996E-2</v>
+        <v>0</v>
       </c>
       <c r="AD9" s="29">
-        <v>0</v>
+        <v>37294.720000000001</v>
       </c>
       <c r="AE9" s="29">
         <v>0</v>
@@ -3009,16 +2993,16 @@
         <v>0</v>
       </c>
       <c r="AG9" s="29">
-        <v>0</v>
+        <v>37294.720000000001</v>
       </c>
       <c r="AH9" s="29">
         <v>0</v>
       </c>
       <c r="AI9" s="29">
-        <v>66537.37</v>
+        <v>37294.720000000001</v>
       </c>
       <c r="AJ9" s="33" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="AK9" s="34"/>
       <c r="AL9" s="34"/>
@@ -3036,25 +3020,25 @@
         <v>2043</v>
       </c>
       <c r="D10" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F10" s="27">
-        <v>94156</v>
+        <v>110453</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="H10" s="28">
-        <v>44159</v>
+        <v>45600</v>
       </c>
       <c r="I10" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J10" s="30">
-        <v>111482.82</v>
+        <v>206465.86</v>
       </c>
       <c r="K10" s="30">
         <v>0</v>
@@ -3063,19 +3047,19 @@
         <v>0</v>
       </c>
       <c r="M10" s="31">
-        <v>1811.26</v>
+        <v>261.77</v>
       </c>
       <c r="N10" s="31">
         <v>0</v>
       </c>
       <c r="O10" s="29">
-        <v>113294.08</v>
+        <v>206727.63</v>
       </c>
       <c r="P10" s="32">
-        <v>6.2600000000000003E-2</v>
+        <v>0.1142</v>
       </c>
       <c r="Q10" s="30">
-        <v>64612.59</v>
+        <v>0</v>
       </c>
       <c r="R10" s="30">
         <v>0</v>
@@ -3084,16 +3068,16 @@
         <v>0</v>
       </c>
       <c r="T10" s="29">
-        <v>64612.59</v>
+        <v>0</v>
       </c>
       <c r="U10" s="29">
         <v>0</v>
       </c>
       <c r="V10" s="29">
-        <v>177906.67</v>
+        <v>206727.63</v>
       </c>
       <c r="W10" s="29">
-        <v>30100.36</v>
+        <v>66502.47</v>
       </c>
       <c r="X10" s="29">
         <v>0</v>
@@ -3102,19 +3086,19 @@
         <v>0</v>
       </c>
       <c r="Z10" s="31">
-        <v>409</v>
+        <v>34.9</v>
       </c>
       <c r="AA10" s="31">
         <v>0</v>
       </c>
       <c r="AB10" s="29">
-        <v>30509.360000000001</v>
+        <v>66537.37</v>
       </c>
       <c r="AC10" s="32">
-        <v>3.3700000000000001E-2</v>
+        <v>7.3499999999999996E-2</v>
       </c>
       <c r="AD10" s="29">
-        <v>11978.48</v>
+        <v>0</v>
       </c>
       <c r="AE10" s="29">
         <v>0</v>
@@ -3123,16 +3107,16 @@
         <v>0</v>
       </c>
       <c r="AG10" s="29">
-        <v>11978.48</v>
+        <v>0</v>
       </c>
       <c r="AH10" s="29">
         <v>0</v>
       </c>
       <c r="AI10" s="29">
-        <v>42487.839999999997</v>
+        <v>66537.37</v>
       </c>
       <c r="AJ10" s="33" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="AK10" s="34"/>
       <c r="AL10" s="34"/>
@@ -3156,19 +3140,19 @@
         <v>28</v>
       </c>
       <c r="F11" s="27">
-        <v>80122</v>
+        <v>94156</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="H11" s="28">
-        <v>43371</v>
+        <v>44159</v>
       </c>
       <c r="I11" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J11" s="30">
-        <v>75285.279999999999</v>
+        <v>111482.82</v>
       </c>
       <c r="K11" s="30">
         <v>0</v>
@@ -3177,19 +3161,19 @@
         <v>0</v>
       </c>
       <c r="M11" s="31">
-        <v>87080.35</v>
+        <v>2291.8200000000002</v>
       </c>
       <c r="N11" s="31">
         <v>0</v>
       </c>
       <c r="O11" s="29">
-        <v>162365.63</v>
+        <v>113774.64</v>
       </c>
       <c r="P11" s="32">
-        <v>8.9700000000000002E-2</v>
+        <v>6.2799999999999995E-2</v>
       </c>
       <c r="Q11" s="30">
-        <v>0</v>
+        <v>64612.59</v>
       </c>
       <c r="R11" s="30">
         <v>0</v>
@@ -3198,16 +3182,16 @@
         <v>0</v>
       </c>
       <c r="T11" s="29">
-        <v>0</v>
+        <v>64612.59</v>
       </c>
       <c r="U11" s="29">
         <v>0</v>
       </c>
       <c r="V11" s="29">
-        <v>162365.63</v>
+        <v>178387.23</v>
       </c>
       <c r="W11" s="29">
-        <v>25150.62</v>
+        <v>30100.36</v>
       </c>
       <c r="X11" s="29">
         <v>0</v>
@@ -3216,19 +3200,19 @@
         <v>0</v>
       </c>
       <c r="Z11" s="31">
-        <v>5241.12</v>
+        <v>569.19000000000005</v>
       </c>
       <c r="AA11" s="31">
         <v>0</v>
       </c>
       <c r="AB11" s="29">
-        <v>30391.74</v>
+        <v>30669.55</v>
       </c>
       <c r="AC11" s="32">
-        <v>3.3599999999999998E-2</v>
+        <v>3.39E-2</v>
       </c>
       <c r="AD11" s="29">
-        <v>0</v>
+        <v>11978.48</v>
       </c>
       <c r="AE11" s="29">
         <v>0</v>
@@ -3237,16 +3221,16 @@
         <v>0</v>
       </c>
       <c r="AG11" s="29">
-        <v>0</v>
+        <v>11978.48</v>
       </c>
       <c r="AH11" s="29">
         <v>0</v>
       </c>
       <c r="AI11" s="29">
-        <v>30391.74</v>
+        <v>42648.03</v>
       </c>
       <c r="AJ11" s="33" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
       <c r="AK11" s="34"/>
       <c r="AL11" s="34"/>
@@ -3291,16 +3275,16 @@
         <v>0</v>
       </c>
       <c r="M12" s="31">
-        <v>21694.07</v>
+        <v>22390.68</v>
       </c>
       <c r="N12" s="31">
         <v>0</v>
       </c>
       <c r="O12" s="29">
-        <v>148579.82999999999</v>
+        <v>149276.44</v>
       </c>
       <c r="P12" s="32">
-        <v>8.2100000000000006E-2</v>
+        <v>8.2500000000000004E-2</v>
       </c>
       <c r="Q12" s="30">
         <v>0</v>
@@ -3318,7 +3302,7 @@
         <v>0</v>
       </c>
       <c r="V12" s="29">
-        <v>148579.82999999999</v>
+        <v>149276.44</v>
       </c>
       <c r="W12" s="29">
         <v>50742.080000000002</v>
@@ -3330,16 +3314,16 @@
         <v>0</v>
       </c>
       <c r="Z12" s="31">
-        <v>1142.1199999999999</v>
+        <v>1235</v>
       </c>
       <c r="AA12" s="31">
         <v>0</v>
       </c>
       <c r="AB12" s="29">
-        <v>51884.2</v>
+        <v>51977.08</v>
       </c>
       <c r="AC12" s="32">
-        <v>5.7299999999999997E-2</v>
+        <v>5.74E-2</v>
       </c>
       <c r="AD12" s="29">
         <v>0</v>
@@ -3357,7 +3341,7 @@
         <v>0</v>
       </c>
       <c r="AI12" s="29">
-        <v>51884.2</v>
+        <v>51977.08</v>
       </c>
       <c r="AJ12" s="33" t="s">
         <v>39</v>
@@ -3492,25 +3476,25 @@
         <v>2043</v>
       </c>
       <c r="D14" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E14" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F14" s="27">
-        <v>47116</v>
+        <v>115047</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H14" s="28">
-        <v>44616</v>
+        <v>45944</v>
       </c>
       <c r="I14" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J14" s="30">
-        <v>61796.57</v>
+        <v>24598.61</v>
       </c>
       <c r="K14" s="30">
         <v>0</v>
@@ -3519,19 +3503,19 @@
         <v>0</v>
       </c>
       <c r="M14" s="31">
-        <v>4762.41</v>
+        <v>701.1</v>
       </c>
       <c r="N14" s="31">
         <v>0</v>
       </c>
       <c r="O14" s="29">
-        <v>66558.98</v>
+        <v>76619.839999999997</v>
       </c>
       <c r="P14" s="32">
-        <v>3.6799999999999999E-2</v>
+        <v>4.2299999999999997E-2</v>
       </c>
       <c r="Q14" s="30">
-        <v>50792.35</v>
+        <v>40110.959999999999</v>
       </c>
       <c r="R14" s="30">
         <v>0</v>
@@ -3540,16 +3524,16 @@
         <v>0</v>
       </c>
       <c r="T14" s="29">
-        <v>50792.35</v>
+        <v>49236.79</v>
       </c>
       <c r="U14" s="29">
-        <v>0</v>
+        <v>60445.96</v>
       </c>
       <c r="V14" s="29">
-        <v>117351.33</v>
+        <v>125856.63</v>
       </c>
       <c r="W14" s="29">
-        <v>18538.98</v>
+        <v>7564.38</v>
       </c>
       <c r="X14" s="29">
         <v>0</v>
@@ -3558,19 +3542,19 @@
         <v>0</v>
       </c>
       <c r="Z14" s="31">
-        <v>760.42</v>
+        <v>93.49</v>
       </c>
       <c r="AA14" s="31">
         <v>0</v>
       </c>
       <c r="AB14" s="29">
-        <v>19299.400000000001</v>
+        <v>23053.91</v>
       </c>
       <c r="AC14" s="32">
-        <v>2.1299999999999999E-2</v>
+        <v>2.5499999999999998E-2</v>
       </c>
       <c r="AD14" s="29">
-        <v>9868.51</v>
+        <v>8472.36</v>
       </c>
       <c r="AE14" s="29">
         <v>0</v>
@@ -3579,16 +3563,16 @@
         <v>0</v>
       </c>
       <c r="AG14" s="29">
-        <v>9868.51</v>
+        <v>10021.94</v>
       </c>
       <c r="AH14" s="29">
-        <v>0</v>
+        <v>16945.62</v>
       </c>
       <c r="AI14" s="29">
-        <v>29167.91</v>
+        <v>33075.85</v>
       </c>
       <c r="AJ14" s="33" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AK14" s="34"/>
       <c r="AL14" s="34"/>
@@ -3606,25 +3590,25 @@
         <v>2043</v>
       </c>
       <c r="D15" s="26">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E15" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F15" s="27">
-        <v>115047</v>
+        <v>47116</v>
       </c>
       <c r="G15" s="25" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H15" s="28">
-        <v>45944</v>
+        <v>44616</v>
       </c>
       <c r="I15" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J15" s="30">
-        <v>0</v>
+        <v>61796.57</v>
       </c>
       <c r="K15" s="30">
         <v>0</v>
@@ -3633,19 +3617,19 @@
         <v>0</v>
       </c>
       <c r="M15" s="31">
-        <v>701.1</v>
+        <v>5030</v>
       </c>
       <c r="N15" s="31">
         <v>0</v>
       </c>
       <c r="O15" s="29">
-        <v>52021.23</v>
+        <v>66826.570000000007</v>
       </c>
       <c r="P15" s="32">
-        <v>2.87E-2</v>
+        <v>3.6900000000000002E-2</v>
       </c>
       <c r="Q15" s="30">
-        <v>40110.959999999999</v>
+        <v>50792.35</v>
       </c>
       <c r="R15" s="30">
         <v>0</v>
@@ -3654,16 +3638,16 @@
         <v>0</v>
       </c>
       <c r="T15" s="29">
-        <v>49236.79</v>
+        <v>50792.35</v>
       </c>
       <c r="U15" s="29">
-        <v>60445.96</v>
+        <v>0</v>
       </c>
       <c r="V15" s="29">
-        <v>101258.02</v>
+        <v>117618.92</v>
       </c>
       <c r="W15" s="29">
-        <v>0</v>
+        <v>18538.98</v>
       </c>
       <c r="X15" s="29">
         <v>0</v>
@@ -3672,19 +3656,19 @@
         <v>0</v>
       </c>
       <c r="Z15" s="31">
-        <v>93.49</v>
+        <v>796.1</v>
       </c>
       <c r="AA15" s="31">
         <v>0</v>
       </c>
       <c r="AB15" s="29">
-        <v>15489.53</v>
+        <v>19335.080000000002</v>
       </c>
       <c r="AC15" s="32">
-        <v>1.7100000000000001E-2</v>
+        <v>2.1399999999999999E-2</v>
       </c>
       <c r="AD15" s="29">
-        <v>8472.36</v>
+        <v>9868.51</v>
       </c>
       <c r="AE15" s="29">
         <v>0</v>
@@ -3693,16 +3677,16 @@
         <v>0</v>
       </c>
       <c r="AG15" s="29">
-        <v>10021.94</v>
+        <v>9868.51</v>
       </c>
       <c r="AH15" s="29">
-        <v>16945.62</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="29">
-        <v>25511.47</v>
+        <v>29203.59</v>
       </c>
       <c r="AJ15" s="33" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AK15" s="34"/>
       <c r="AL15" s="34"/>
@@ -3726,19 +3710,19 @@
         <v>28</v>
       </c>
       <c r="F16" s="27">
-        <v>107488</v>
+        <v>115404</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H16" s="28">
-        <v>45440</v>
+        <v>45986</v>
       </c>
       <c r="I16" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J16" s="30">
-        <v>0</v>
+        <v>29852.74</v>
       </c>
       <c r="K16" s="30">
         <v>0</v>
@@ -3747,19 +3731,19 @@
         <v>0</v>
       </c>
       <c r="M16" s="31">
-        <v>157.72</v>
+        <v>0</v>
       </c>
       <c r="N16" s="31">
         <v>0</v>
       </c>
       <c r="O16" s="29">
-        <v>157.72</v>
+        <v>29852.74</v>
       </c>
       <c r="P16" s="32">
-        <v>1E-4</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="Q16" s="30">
-        <v>98471.17</v>
+        <v>79361.350000000006</v>
       </c>
       <c r="R16" s="30">
         <v>0</v>
@@ -3768,16 +3752,16 @@
         <v>0</v>
       </c>
       <c r="T16" s="29">
-        <v>98471.17</v>
+        <v>79361.350000000006</v>
       </c>
       <c r="U16" s="29">
         <v>0</v>
       </c>
       <c r="V16" s="29">
-        <v>98628.89</v>
+        <v>109214.09</v>
       </c>
       <c r="W16" s="29">
-        <v>0</v>
+        <v>10448.459999999999</v>
       </c>
       <c r="X16" s="29">
         <v>0</v>
@@ -3786,19 +3770,19 @@
         <v>0</v>
       </c>
       <c r="Z16" s="31">
-        <v>21.03</v>
+        <v>0</v>
       </c>
       <c r="AA16" s="31">
         <v>0</v>
       </c>
       <c r="AB16" s="29">
-        <v>21.03</v>
+        <v>10448.459999999999</v>
       </c>
       <c r="AC16" s="32">
-        <v>0</v>
+        <v>1.15E-2</v>
       </c>
       <c r="AD16" s="29">
-        <v>21311.65</v>
+        <v>16033.12</v>
       </c>
       <c r="AE16" s="29">
         <v>0</v>
@@ -3807,16 +3791,16 @@
         <v>0</v>
       </c>
       <c r="AG16" s="29">
-        <v>21311.65</v>
+        <v>16033.12</v>
       </c>
       <c r="AH16" s="29">
         <v>0</v>
       </c>
       <c r="AI16" s="29">
-        <v>21332.68</v>
+        <v>26481.58</v>
       </c>
       <c r="AJ16" s="33" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="AK16" s="34"/>
       <c r="AL16" s="34"/>
@@ -3840,19 +3824,19 @@
         <v>28</v>
       </c>
       <c r="F17" s="27">
-        <v>115404</v>
+        <v>107488</v>
       </c>
       <c r="G17" s="25" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="H17" s="28">
-        <v>45986</v>
+        <v>45440</v>
       </c>
       <c r="I17" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J17" s="30">
-        <v>29852.74</v>
+        <v>0</v>
       </c>
       <c r="K17" s="30">
         <v>0</v>
@@ -3861,19 +3845,19 @@
         <v>0</v>
       </c>
       <c r="M17" s="31">
-        <v>0</v>
+        <v>157.72</v>
       </c>
       <c r="N17" s="31">
         <v>0</v>
       </c>
       <c r="O17" s="29">
-        <v>29852.74</v>
+        <v>157.72</v>
       </c>
       <c r="P17" s="32">
-        <v>1.6500000000000001E-2</v>
+        <v>1E-4</v>
       </c>
       <c r="Q17" s="30">
-        <v>53684.13</v>
+        <v>98471.17</v>
       </c>
       <c r="R17" s="30">
         <v>0</v>
@@ -3882,16 +3866,16 @@
         <v>0</v>
       </c>
       <c r="T17" s="29">
-        <v>53684.13</v>
+        <v>98471.17</v>
       </c>
       <c r="U17" s="29">
         <v>0</v>
       </c>
       <c r="V17" s="29">
-        <v>83536.87</v>
+        <v>98628.89</v>
       </c>
       <c r="W17" s="29">
-        <v>10448.459999999999</v>
+        <v>0</v>
       </c>
       <c r="X17" s="29">
         <v>0</v>
@@ -3900,19 +3884,19 @@
         <v>0</v>
       </c>
       <c r="Z17" s="31">
-        <v>0</v>
+        <v>21.03</v>
       </c>
       <c r="AA17" s="31">
         <v>0</v>
       </c>
       <c r="AB17" s="29">
-        <v>10448.459999999999</v>
+        <v>21.03</v>
       </c>
       <c r="AC17" s="32">
-        <v>1.15E-2</v>
+        <v>0</v>
       </c>
       <c r="AD17" s="29">
-        <v>10754.34</v>
+        <v>21311.65</v>
       </c>
       <c r="AE17" s="29">
         <v>0</v>
@@ -3921,16 +3905,16 @@
         <v>0</v>
       </c>
       <c r="AG17" s="29">
-        <v>10754.34</v>
+        <v>21311.65</v>
       </c>
       <c r="AH17" s="29">
         <v>0</v>
       </c>
       <c r="AI17" s="29">
-        <v>21202.799999999999</v>
+        <v>21332.68</v>
       </c>
       <c r="AJ17" s="33" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="AK17" s="34"/>
       <c r="AL17" s="34"/>
@@ -4062,25 +4046,25 @@
         <v>2043</v>
       </c>
       <c r="D19" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E19" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F19" s="27">
-        <v>108404</v>
+        <v>105696</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H19" s="28">
-        <v>45467</v>
+        <v>45279</v>
       </c>
       <c r="I19" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J19" s="30">
-        <v>36910.69</v>
+        <v>62837.82</v>
       </c>
       <c r="K19" s="30">
         <v>0</v>
@@ -4089,19 +4073,19 @@
         <v>0</v>
       </c>
       <c r="M19" s="31">
-        <v>4677.22</v>
+        <v>1354.39</v>
       </c>
       <c r="N19" s="31">
         <v>0</v>
       </c>
       <c r="O19" s="29">
-        <v>41587.910000000003</v>
+        <v>64192.21</v>
       </c>
       <c r="P19" s="32">
-        <v>2.3E-2</v>
+        <v>3.5499999999999997E-2</v>
       </c>
       <c r="Q19" s="30">
-        <v>27059.39</v>
+        <v>16178.04</v>
       </c>
       <c r="R19" s="30">
         <v>0</v>
@@ -4110,16 +4094,16 @@
         <v>0</v>
       </c>
       <c r="T19" s="29">
-        <v>27059.39</v>
+        <v>16178.04</v>
       </c>
       <c r="U19" s="29">
         <v>0</v>
       </c>
       <c r="V19" s="29">
-        <v>68647.3</v>
+        <v>80370.25</v>
       </c>
       <c r="W19" s="29">
-        <v>11073.21</v>
+        <v>20942.14</v>
       </c>
       <c r="X19" s="29">
         <v>0</v>
@@ -4128,19 +4112,19 @@
         <v>0</v>
       </c>
       <c r="Z19" s="31">
-        <v>373.62</v>
+        <v>112.4</v>
       </c>
       <c r="AA19" s="31">
         <v>0</v>
       </c>
       <c r="AB19" s="29">
-        <v>11446.83</v>
+        <v>21054.54</v>
       </c>
       <c r="AC19" s="32">
-        <v>1.26E-2</v>
+        <v>2.3300000000000001E-2</v>
       </c>
       <c r="AD19" s="29">
-        <v>5601.07</v>
+        <v>3240.17</v>
       </c>
       <c r="AE19" s="29">
         <v>0</v>
@@ -4149,16 +4133,16 @@
         <v>0</v>
       </c>
       <c r="AG19" s="29">
-        <v>5601.07</v>
+        <v>3240.17</v>
       </c>
       <c r="AH19" s="29">
         <v>0</v>
       </c>
       <c r="AI19" s="29">
-        <v>17047.900000000001</v>
+        <v>24294.71</v>
       </c>
       <c r="AJ19" s="33" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="AK19" s="34"/>
       <c r="AL19" s="34"/>
@@ -4182,19 +4166,19 @@
         <v>28</v>
       </c>
       <c r="F20" s="27">
-        <v>113450</v>
+        <v>108404</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H20" s="28">
-        <v>45852</v>
+        <v>45467</v>
       </c>
       <c r="I20" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J20" s="30">
-        <v>58035.37</v>
+        <v>36910.69</v>
       </c>
       <c r="K20" s="30">
         <v>0</v>
@@ -4203,19 +4187,19 @@
         <v>0</v>
       </c>
       <c r="M20" s="31">
-        <v>540</v>
+        <v>7677.21</v>
       </c>
       <c r="N20" s="31">
         <v>0</v>
       </c>
       <c r="O20" s="29">
-        <v>58575.37</v>
+        <v>44587.9</v>
       </c>
       <c r="P20" s="32">
-        <v>3.2399999999999998E-2</v>
+        <v>2.46E-2</v>
       </c>
       <c r="Q20" s="30">
-        <v>0</v>
+        <v>27059.39</v>
       </c>
       <c r="R20" s="30">
         <v>0</v>
@@ -4224,16 +4208,16 @@
         <v>0</v>
       </c>
       <c r="T20" s="29">
-        <v>0</v>
+        <v>27059.39</v>
       </c>
       <c r="U20" s="29">
         <v>0</v>
       </c>
       <c r="V20" s="29">
-        <v>58575.37</v>
+        <v>71647.289999999994</v>
       </c>
       <c r="W20" s="29">
-        <v>15669.55</v>
+        <v>11073.21</v>
       </c>
       <c r="X20" s="29">
         <v>0</v>
@@ -4242,19 +4226,19 @@
         <v>0</v>
       </c>
       <c r="Z20" s="31">
-        <v>42</v>
+        <v>773.62</v>
       </c>
       <c r="AA20" s="31">
         <v>0</v>
       </c>
       <c r="AB20" s="29">
-        <v>15711.55</v>
+        <v>11846.83</v>
       </c>
       <c r="AC20" s="32">
-        <v>1.7399999999999999E-2</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="AD20" s="29">
-        <v>0</v>
+        <v>5601.07</v>
       </c>
       <c r="AE20" s="29">
         <v>0</v>
@@ -4263,16 +4247,16 @@
         <v>0</v>
       </c>
       <c r="AG20" s="29">
-        <v>0</v>
+        <v>5601.07</v>
       </c>
       <c r="AH20" s="29">
         <v>0</v>
       </c>
       <c r="AI20" s="29">
-        <v>15711.55</v>
+        <v>17447.900000000001</v>
       </c>
       <c r="AJ20" s="33" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AK20" s="34"/>
       <c r="AL20" s="34"/>
@@ -4290,25 +4274,25 @@
         <v>2043</v>
       </c>
       <c r="D21" s="26">
-        <v>2043</v>
+        <v>2692</v>
       </c>
       <c r="E21" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F21" s="27">
-        <v>102825</v>
+        <v>113450</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="H21" s="28">
-        <v>45117</v>
+        <v>45852</v>
       </c>
       <c r="I21" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J21" s="30">
-        <v>0</v>
+        <v>58035.37</v>
       </c>
       <c r="K21" s="30">
         <v>0</v>
@@ -4317,19 +4301,19 @@
         <v>0</v>
       </c>
       <c r="M21" s="31">
-        <v>455.37</v>
+        <v>540</v>
       </c>
       <c r="N21" s="31">
         <v>0</v>
       </c>
       <c r="O21" s="29">
-        <v>455.37</v>
+        <v>58575.37</v>
       </c>
       <c r="P21" s="32">
-        <v>2.9999999999999997E-4</v>
+        <v>3.2399999999999998E-2</v>
       </c>
       <c r="Q21" s="30">
-        <v>52510.1</v>
+        <v>0</v>
       </c>
       <c r="R21" s="30">
         <v>0</v>
@@ -4338,16 +4322,16 @@
         <v>0</v>
       </c>
       <c r="T21" s="29">
-        <v>52510.1</v>
+        <v>0</v>
       </c>
       <c r="U21" s="29">
         <v>0</v>
       </c>
       <c r="V21" s="29">
-        <v>52965.47</v>
+        <v>58575.37</v>
       </c>
       <c r="W21" s="29">
-        <v>0</v>
+        <v>15669.55</v>
       </c>
       <c r="X21" s="29">
         <v>0</v>
@@ -4356,19 +4340,19 @@
         <v>0</v>
       </c>
       <c r="Z21" s="31">
-        <v>151.79</v>
+        <v>42</v>
       </c>
       <c r="AA21" s="31">
         <v>0</v>
       </c>
       <c r="AB21" s="29">
-        <v>151.79</v>
+        <v>15711.55</v>
       </c>
       <c r="AC21" s="32">
-        <v>2.0000000000000001E-4</v>
+        <v>1.7399999999999999E-2</v>
       </c>
       <c r="AD21" s="29">
-        <v>10881.11</v>
+        <v>0</v>
       </c>
       <c r="AE21" s="29">
         <v>0</v>
@@ -4377,16 +4361,16 @@
         <v>0</v>
       </c>
       <c r="AG21" s="29">
-        <v>10881.11</v>
+        <v>0</v>
       </c>
       <c r="AH21" s="29">
         <v>0</v>
       </c>
       <c r="AI21" s="29">
-        <v>11032.9</v>
+        <v>15711.55</v>
       </c>
       <c r="AJ21" s="33" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="AK21" s="34"/>
       <c r="AL21" s="34"/>
@@ -4410,19 +4394,19 @@
         <v>28</v>
       </c>
       <c r="F22" s="27">
-        <v>105696</v>
+        <v>102825</v>
       </c>
       <c r="G22" s="25" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="H22" s="28">
-        <v>45279</v>
+        <v>45117</v>
       </c>
       <c r="I22" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J22" s="30">
-        <v>30829.7</v>
+        <v>0</v>
       </c>
       <c r="K22" s="30">
         <v>0</v>
@@ -4431,19 +4415,19 @@
         <v>0</v>
       </c>
       <c r="M22" s="31">
-        <v>1174.3900000000001</v>
+        <v>455.37</v>
       </c>
       <c r="N22" s="31">
         <v>0</v>
       </c>
       <c r="O22" s="29">
-        <v>32004.09</v>
+        <v>455.37</v>
       </c>
       <c r="P22" s="32">
-        <v>1.77E-2</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="Q22" s="30">
-        <v>16178.04</v>
+        <v>52510.1</v>
       </c>
       <c r="R22" s="30">
         <v>0</v>
@@ -4452,16 +4436,16 @@
         <v>0</v>
       </c>
       <c r="T22" s="29">
-        <v>16178.04</v>
+        <v>52510.1</v>
       </c>
       <c r="U22" s="29">
         <v>0</v>
       </c>
       <c r="V22" s="29">
-        <v>48182.13</v>
+        <v>52965.47</v>
       </c>
       <c r="W22" s="29">
-        <v>9451.7999999999993</v>
+        <v>0</v>
       </c>
       <c r="X22" s="29">
         <v>0</v>
@@ -4470,19 +4454,19 @@
         <v>0</v>
       </c>
       <c r="Z22" s="31">
-        <v>103.4</v>
+        <v>151.79</v>
       </c>
       <c r="AA22" s="31">
         <v>0</v>
       </c>
       <c r="AB22" s="29">
-        <v>9555.2000000000007</v>
+        <v>151.79</v>
       </c>
       <c r="AC22" s="32">
-        <v>1.06E-2</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="AD22" s="29">
-        <v>3240.17</v>
+        <v>10881.11</v>
       </c>
       <c r="AE22" s="29">
         <v>0</v>
@@ -4491,16 +4475,16 @@
         <v>0</v>
       </c>
       <c r="AG22" s="29">
-        <v>3240.17</v>
+        <v>10881.11</v>
       </c>
       <c r="AH22" s="29">
         <v>0</v>
       </c>
       <c r="AI22" s="29">
-        <v>12795.37</v>
+        <v>11032.9</v>
       </c>
       <c r="AJ22" s="33" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="AK22" s="34"/>
       <c r="AL22" s="34"/>
@@ -5001,16 +4985,16 @@
         <v>0</v>
       </c>
       <c r="M27" s="31">
-        <v>4023.53</v>
+        <v>5216.63</v>
       </c>
       <c r="N27" s="31">
         <v>0</v>
       </c>
       <c r="O27" s="29">
-        <v>4023.53</v>
+        <v>5216.63</v>
       </c>
       <c r="P27" s="32">
-        <v>2.2000000000000001E-3</v>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="Q27" s="30">
         <v>23039.919999999998</v>
@@ -5028,7 +5012,7 @@
         <v>0</v>
       </c>
       <c r="V27" s="29">
-        <v>27063.45</v>
+        <v>28256.55</v>
       </c>
       <c r="W27" s="29">
         <v>0</v>
@@ -5040,16 +5024,16 @@
         <v>0</v>
       </c>
       <c r="Z27" s="31">
-        <v>411.48</v>
+        <v>570.55999999999995</v>
       </c>
       <c r="AA27" s="31">
         <v>0</v>
       </c>
       <c r="AB27" s="29">
-        <v>411.48</v>
+        <v>570.55999999999995</v>
       </c>
       <c r="AC27" s="32">
-        <v>5.0000000000000001E-4</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="AD27" s="29">
         <v>4694.78</v>
@@ -5067,7 +5051,7 @@
         <v>0</v>
       </c>
       <c r="AI27" s="29">
-        <v>5106.26</v>
+        <v>5265.34</v>
       </c>
       <c r="AJ27" s="33" t="s">
         <v>75</v>
@@ -5208,19 +5192,19 @@
         <v>28</v>
       </c>
       <c r="F29" s="27">
-        <v>98797</v>
+        <v>65046</v>
       </c>
       <c r="G29" s="25" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="H29" s="28">
-        <v>44342</v>
+        <v>44763</v>
       </c>
       <c r="I29" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J29" s="30">
-        <v>0</v>
+        <v>25330.85</v>
       </c>
       <c r="K29" s="30">
         <v>0</v>
@@ -5229,16 +5213,16 @@
         <v>0</v>
       </c>
       <c r="M29" s="31">
-        <v>12001.3</v>
+        <v>180</v>
       </c>
       <c r="N29" s="31">
         <v>0</v>
       </c>
       <c r="O29" s="29">
-        <v>12001.3</v>
+        <v>25510.85</v>
       </c>
       <c r="P29" s="32">
-        <v>6.6E-3</v>
+        <v>1.41E-2</v>
       </c>
       <c r="Q29" s="30">
         <v>0</v>
@@ -5256,10 +5240,10 @@
         <v>0</v>
       </c>
       <c r="V29" s="29">
-        <v>12001.3</v>
+        <v>25510.85</v>
       </c>
       <c r="W29" s="29">
-        <v>0</v>
+        <v>7651.85</v>
       </c>
       <c r="X29" s="29">
         <v>0</v>
@@ -5268,16 +5252,16 @@
         <v>0</v>
       </c>
       <c r="Z29" s="31">
-        <v>600.05999999999995</v>
+        <v>9</v>
       </c>
       <c r="AA29" s="31">
         <v>0</v>
       </c>
       <c r="AB29" s="29">
-        <v>600.05999999999995</v>
+        <v>7660.85</v>
       </c>
       <c r="AC29" s="32">
-        <v>6.9999999999999999E-4</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="AD29" s="29">
         <v>0</v>
@@ -5295,10 +5279,10 @@
         <v>0</v>
       </c>
       <c r="AI29" s="29">
-        <v>600.05999999999995</v>
+        <v>7660.85</v>
       </c>
       <c r="AJ29" s="33" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="AK29" s="34"/>
       <c r="AL29" s="34"/>
@@ -5316,25 +5300,25 @@
         <v>2043</v>
       </c>
       <c r="D30" s="26">
-        <v>2043</v>
+        <v>2692</v>
       </c>
       <c r="E30" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F30" s="27">
-        <v>104343</v>
+        <v>114157</v>
       </c>
       <c r="G30" s="25" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="H30" s="28">
-        <v>45201</v>
+        <v>45904</v>
       </c>
       <c r="I30" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J30" s="30">
-        <v>0</v>
+        <v>20303.28</v>
       </c>
       <c r="K30" s="30">
         <v>0</v>
@@ -5343,16 +5327,16 @@
         <v>0</v>
       </c>
       <c r="M30" s="31">
-        <v>2480.0300000000002</v>
+        <v>0</v>
       </c>
       <c r="N30" s="31">
         <v>0</v>
       </c>
       <c r="O30" s="29">
-        <v>2480.0300000000002</v>
+        <v>20303.28</v>
       </c>
       <c r="P30" s="32">
-        <v>1.4E-3</v>
+        <v>1.12E-2</v>
       </c>
       <c r="Q30" s="30">
         <v>0</v>
@@ -5370,10 +5354,10 @@
         <v>0</v>
       </c>
       <c r="V30" s="29">
-        <v>2480.0300000000002</v>
+        <v>20303.28</v>
       </c>
       <c r="W30" s="29">
-        <v>0</v>
+        <v>5307.72</v>
       </c>
       <c r="X30" s="29">
         <v>0</v>
@@ -5382,16 +5366,16 @@
         <v>0</v>
       </c>
       <c r="Z30" s="31">
-        <v>280.64</v>
+        <v>0</v>
       </c>
       <c r="AA30" s="31">
         <v>0</v>
       </c>
       <c r="AB30" s="29">
-        <v>280.64</v>
+        <v>5307.72</v>
       </c>
       <c r="AC30" s="32">
-        <v>2.9999999999999997E-4</v>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="AD30" s="29">
         <v>0</v>
@@ -5409,10 +5393,10 @@
         <v>0</v>
       </c>
       <c r="AI30" s="29">
-        <v>280.64</v>
+        <v>5307.72</v>
       </c>
       <c r="AJ30" s="33" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="AK30" s="34"/>
       <c r="AL30" s="34"/>
@@ -5430,19 +5414,19 @@
         <v>2043</v>
       </c>
       <c r="D31" s="26">
-        <v>2511</v>
+        <v>2043</v>
       </c>
       <c r="E31" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F31" s="27">
-        <v>63441</v>
+        <v>98797</v>
       </c>
       <c r="G31" s="25" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H31" s="28">
-        <v>44733</v>
+        <v>44342</v>
       </c>
       <c r="I31" s="29" t="s">
         <v>30</v>
@@ -5457,16 +5441,16 @@
         <v>0</v>
       </c>
       <c r="M31" s="31">
-        <v>300.06</v>
+        <v>18002.650000000001</v>
       </c>
       <c r="N31" s="31">
         <v>0</v>
       </c>
       <c r="O31" s="29">
-        <v>300.06</v>
+        <v>18002.650000000001</v>
       </c>
       <c r="P31" s="32">
-        <v>2.0000000000000001E-4</v>
+        <v>9.9000000000000008E-3</v>
       </c>
       <c r="Q31" s="30">
         <v>0</v>
@@ -5484,7 +5468,7 @@
         <v>0</v>
       </c>
       <c r="V31" s="29">
-        <v>300.06</v>
+        <v>18002.650000000001</v>
       </c>
       <c r="W31" s="29">
         <v>0</v>
@@ -5496,16 +5480,16 @@
         <v>0</v>
       </c>
       <c r="Z31" s="31">
-        <v>15</v>
+        <v>900.13</v>
       </c>
       <c r="AA31" s="31">
         <v>0</v>
       </c>
       <c r="AB31" s="29">
-        <v>15</v>
+        <v>900.13</v>
       </c>
       <c r="AC31" s="32">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="AD31" s="29">
         <v>0</v>
@@ -5523,10 +5507,10 @@
         <v>0</v>
       </c>
       <c r="AI31" s="29">
-        <v>15</v>
+        <v>900.13</v>
       </c>
       <c r="AJ31" s="33" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK31" s="34"/>
       <c r="AL31" s="34"/>
@@ -5550,13 +5534,13 @@
         <v>28</v>
       </c>
       <c r="F32" s="27">
-        <v>108658</v>
+        <v>104343</v>
       </c>
       <c r="G32" s="25" t="s">
-        <v>104</v>
+        <v>78</v>
       </c>
       <c r="H32" s="28">
-        <v>45497</v>
+        <v>45201</v>
       </c>
       <c r="I32" s="29" t="s">
         <v>30</v>
@@ -5571,16 +5555,16 @@
         <v>0</v>
       </c>
       <c r="M32" s="31">
-        <v>180.03</v>
+        <v>2480.0300000000002</v>
       </c>
       <c r="N32" s="31">
         <v>0</v>
       </c>
       <c r="O32" s="29">
-        <v>180.03</v>
+        <v>2480.0300000000002</v>
       </c>
       <c r="P32" s="32">
-        <v>1E-4</v>
+        <v>1.4E-3</v>
       </c>
       <c r="Q32" s="30">
         <v>0</v>
@@ -5598,7 +5582,7 @@
         <v>0</v>
       </c>
       <c r="V32" s="29">
-        <v>180.03</v>
+        <v>2480.0300000000002</v>
       </c>
       <c r="W32" s="29">
         <v>0</v>
@@ -5610,16 +5594,16 @@
         <v>0</v>
       </c>
       <c r="Z32" s="31">
-        <v>9</v>
+        <v>280.64</v>
       </c>
       <c r="AA32" s="31">
         <v>0</v>
       </c>
       <c r="AB32" s="29">
-        <v>9</v>
+        <v>280.64</v>
       </c>
       <c r="AC32" s="32">
-        <v>0</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="AD32" s="29">
         <v>0</v>
@@ -5637,10 +5621,10 @@
         <v>0</v>
       </c>
       <c r="AI32" s="29">
-        <v>9</v>
+        <v>280.64</v>
       </c>
       <c r="AJ32" s="33" t="s">
-        <v>105</v>
+        <v>79</v>
       </c>
       <c r="AK32" s="34"/>
       <c r="AL32" s="34"/>
@@ -5658,19 +5642,19 @@
         <v>2043</v>
       </c>
       <c r="D33" s="26">
-        <v>2043</v>
+        <v>2511</v>
       </c>
       <c r="E33" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F33" s="27">
-        <v>65046</v>
+        <v>63441</v>
       </c>
       <c r="G33" s="25" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="H33" s="28">
-        <v>44763</v>
+        <v>44733</v>
       </c>
       <c r="I33" s="29" t="s">
         <v>30</v>
@@ -5685,16 +5669,16 @@
         <v>0</v>
       </c>
       <c r="M33" s="31">
-        <v>180</v>
+        <v>300.06</v>
       </c>
       <c r="N33" s="31">
         <v>0</v>
       </c>
       <c r="O33" s="29">
-        <v>180</v>
+        <v>300.06</v>
       </c>
       <c r="P33" s="32">
-        <v>1E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="Q33" s="30">
         <v>0</v>
@@ -5712,7 +5696,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="29">
-        <v>180</v>
+        <v>300.06</v>
       </c>
       <c r="W33" s="29">
         <v>0</v>
@@ -5724,13 +5708,13 @@
         <v>0</v>
       </c>
       <c r="Z33" s="31">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AA33" s="31">
         <v>0</v>
       </c>
       <c r="AB33" s="29">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AC33" s="32">
         <v>0</v>
@@ -5751,10 +5735,10 @@
         <v>0</v>
       </c>
       <c r="AI33" s="29">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AJ33" s="33" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="AK33" s="34"/>
       <c r="AL33" s="34"/>
@@ -5778,13 +5762,13 @@
         <v>28</v>
       </c>
       <c r="F34" s="27">
-        <v>109998</v>
+        <v>108658</v>
       </c>
       <c r="G34" s="25" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H34" s="28">
-        <v>45596</v>
+        <v>45497</v>
       </c>
       <c r="I34" s="29" t="s">
         <v>30</v>
@@ -5799,13 +5783,13 @@
         <v>0</v>
       </c>
       <c r="M34" s="31">
-        <v>162.5</v>
+        <v>180.03</v>
       </c>
       <c r="N34" s="31">
         <v>0</v>
       </c>
       <c r="O34" s="29">
-        <v>162.5</v>
+        <v>180.03</v>
       </c>
       <c r="P34" s="32">
         <v>1E-4</v>
@@ -5826,7 +5810,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="29">
-        <v>162.5</v>
+        <v>180.03</v>
       </c>
       <c r="W34" s="29">
         <v>0</v>
@@ -5838,13 +5822,13 @@
         <v>0</v>
       </c>
       <c r="Z34" s="31">
-        <v>21.66</v>
+        <v>9</v>
       </c>
       <c r="AA34" s="31">
         <v>0</v>
       </c>
       <c r="AB34" s="29">
-        <v>21.66</v>
+        <v>9</v>
       </c>
       <c r="AC34" s="32">
         <v>0</v>
@@ -5865,10 +5849,10 @@
         <v>0</v>
       </c>
       <c r="AI34" s="29">
-        <v>21.66</v>
+        <v>9</v>
       </c>
       <c r="AJ34" s="33" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="AK34" s="34"/>
       <c r="AL34" s="34"/>
@@ -5886,19 +5870,19 @@
         <v>2043</v>
       </c>
       <c r="D35" s="26">
-        <v>2511</v>
+        <v>2043</v>
       </c>
       <c r="E35" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F35" s="27">
-        <v>69684</v>
+        <v>109998</v>
       </c>
       <c r="G35" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H35" s="28">
-        <v>44771</v>
+        <v>45596</v>
       </c>
       <c r="I35" s="29" t="s">
         <v>30</v>
@@ -5913,13 +5897,13 @@
         <v>0</v>
       </c>
       <c r="M35" s="31">
-        <v>142.55000000000001</v>
+        <v>162.5</v>
       </c>
       <c r="N35" s="31">
         <v>0</v>
       </c>
       <c r="O35" s="29">
-        <v>142.55000000000001</v>
+        <v>162.5</v>
       </c>
       <c r="P35" s="32">
         <v>1E-4</v>
@@ -5940,7 +5924,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="29">
-        <v>142.55000000000001</v>
+        <v>162.5</v>
       </c>
       <c r="W35" s="29">
         <v>0</v>
@@ -5952,13 +5936,13 @@
         <v>0</v>
       </c>
       <c r="Z35" s="31">
-        <v>19.010000000000002</v>
+        <v>21.66</v>
       </c>
       <c r="AA35" s="31">
         <v>0</v>
       </c>
       <c r="AB35" s="29">
-        <v>19.010000000000002</v>
+        <v>21.66</v>
       </c>
       <c r="AC35" s="32">
         <v>0</v>
@@ -5979,10 +5963,10 @@
         <v>0</v>
       </c>
       <c r="AI35" s="29">
-        <v>19.010000000000002</v>
+        <v>21.66</v>
       </c>
       <c r="AJ35" s="33" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AK35" s="34"/>
       <c r="AL35" s="34"/>
@@ -6006,13 +5990,13 @@
         <v>28</v>
       </c>
       <c r="F36" s="27">
-        <v>59120</v>
+        <v>69684</v>
       </c>
       <c r="G36" s="25" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H36" s="28">
-        <v>44708</v>
+        <v>44771</v>
       </c>
       <c r="I36" s="29" t="s">
         <v>30</v>
@@ -6027,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="M36" s="31">
-        <v>0</v>
+        <v>142.55000000000001</v>
       </c>
       <c r="N36" s="31">
         <v>0</v>
       </c>
       <c r="O36" s="29">
-        <v>0</v>
+        <v>142.55000000000001</v>
       </c>
       <c r="P36" s="32">
-        <v>0</v>
+        <v>1E-4</v>
       </c>
       <c r="Q36" s="30">
         <v>0</v>
@@ -6054,7 +6038,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="29">
-        <v>0</v>
+        <v>142.55000000000001</v>
       </c>
       <c r="W36" s="29">
         <v>0</v>
@@ -6066,13 +6050,13 @@
         <v>0</v>
       </c>
       <c r="Z36" s="31">
-        <v>0</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="AA36" s="31">
         <v>0</v>
       </c>
       <c r="AB36" s="29">
-        <v>0</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="AC36" s="32">
         <v>0</v>
@@ -6093,10 +6077,10 @@
         <v>0</v>
       </c>
       <c r="AI36" s="29">
-        <v>0</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="AJ36" s="33" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AK36" s="34"/>
       <c r="AL36" s="34"/>
@@ -6114,22 +6098,22 @@
         <v>2043</v>
       </c>
       <c r="D37" s="26">
-        <v>2043</v>
+        <v>2511</v>
       </c>
       <c r="E37" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F37" s="27">
-        <v>64502</v>
+        <v>59120</v>
       </c>
       <c r="G37" s="25" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="H37" s="28">
-        <v>42173</v>
+        <v>44708</v>
       </c>
       <c r="I37" s="29" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="J37" s="30">
         <v>0</v>
@@ -6210,7 +6194,7 @@
         <v>0</v>
       </c>
       <c r="AJ37" s="33" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AK37" s="34"/>
       <c r="AL37" s="34"/>
@@ -6228,22 +6212,22 @@
         <v>2043</v>
       </c>
       <c r="D38" s="26">
-        <v>2511</v>
+        <v>2043</v>
       </c>
       <c r="E38" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F38" s="27">
-        <v>81044</v>
+        <v>64502</v>
       </c>
       <c r="G38" s="25" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="H38" s="28">
-        <v>44872</v>
+        <v>42173</v>
       </c>
       <c r="I38" s="29" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="J38" s="30">
         <v>0</v>
@@ -6324,7 +6308,7 @@
         <v>0</v>
       </c>
       <c r="AJ38" s="33" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AK38" s="34"/>
       <c r="AL38" s="34"/>
@@ -6342,19 +6326,19 @@
         <v>2043</v>
       </c>
       <c r="D39" s="26">
-        <v>2043</v>
+        <v>2511</v>
       </c>
       <c r="E39" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F39" s="27">
-        <v>90177</v>
+        <v>81044</v>
       </c>
       <c r="G39" s="25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H39" s="28">
-        <v>43949</v>
+        <v>44872</v>
       </c>
       <c r="I39" s="29" t="s">
         <v>30</v>
@@ -6438,7 +6422,7 @@
         <v>0</v>
       </c>
       <c r="AJ39" s="33" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AK39" s="34"/>
       <c r="AL39" s="34"/>
@@ -6462,13 +6446,13 @@
         <v>28</v>
       </c>
       <c r="F40" s="27">
-        <v>94205</v>
+        <v>90177</v>
       </c>
       <c r="G40" s="25" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H40" s="28">
-        <v>44116</v>
+        <v>43949</v>
       </c>
       <c r="I40" s="29" t="s">
         <v>30</v>
@@ -6552,7 +6536,7 @@
         <v>0</v>
       </c>
       <c r="AJ40" s="33" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AK40" s="34"/>
       <c r="AL40" s="34"/>
@@ -6576,13 +6560,13 @@
         <v>28</v>
       </c>
       <c r="F41" s="27">
-        <v>101640</v>
+        <v>94205</v>
       </c>
       <c r="G41" s="25" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H41" s="28">
-        <v>45104</v>
+        <v>44116</v>
       </c>
       <c r="I41" s="29" t="s">
         <v>30</v>
@@ -6666,7 +6650,7 @@
         <v>0</v>
       </c>
       <c r="AJ41" s="33" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AK41" s="34"/>
       <c r="AL41" s="34"/>
@@ -6690,13 +6674,13 @@
         <v>28</v>
       </c>
       <c r="F42" s="27">
-        <v>103982</v>
+        <v>101640</v>
       </c>
       <c r="G42" s="25" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="H42" s="28">
-        <v>45216</v>
+        <v>45104</v>
       </c>
       <c r="I42" s="29" t="s">
         <v>30</v>
@@ -6780,7 +6764,7 @@
         <v>0</v>
       </c>
       <c r="AJ42" s="33" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="AK42" s="34"/>
       <c r="AL42" s="34"/>
@@ -6804,13 +6788,13 @@
         <v>28</v>
       </c>
       <c r="F43" s="27">
-        <v>109007</v>
+        <v>103982</v>
       </c>
       <c r="G43" s="25" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="H43" s="28">
-        <v>45525</v>
+        <v>45216</v>
       </c>
       <c r="I43" s="29" t="s">
         <v>30</v>
@@ -6894,7 +6878,7 @@
         <v>0</v>
       </c>
       <c r="AJ43" s="33" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="AK43" s="34"/>
       <c r="AL43" s="34"/>
@@ -6912,19 +6896,19 @@
         <v>2043</v>
       </c>
       <c r="D44" s="26">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E44" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F44" s="27">
-        <v>109819</v>
+        <v>109007</v>
       </c>
       <c r="G44" s="25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H44" s="28">
-        <v>45562</v>
+        <v>45525</v>
       </c>
       <c r="I44" s="29" t="s">
         <v>30</v>
@@ -7008,7 +6992,7 @@
         <v>0</v>
       </c>
       <c r="AJ44" s="33" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AK44" s="34"/>
       <c r="AL44" s="34"/>
@@ -7026,19 +7010,19 @@
         <v>2043</v>
       </c>
       <c r="D45" s="26">
-        <v>2692</v>
+        <v>2856</v>
       </c>
       <c r="E45" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F45" s="27">
-        <v>110575</v>
+        <v>109819</v>
       </c>
       <c r="G45" s="25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H45" s="28">
-        <v>45583</v>
+        <v>45562</v>
       </c>
       <c r="I45" s="29" t="s">
         <v>30</v>
@@ -7122,7 +7106,7 @@
         <v>0</v>
       </c>
       <c r="AJ45" s="33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK45" s="34"/>
       <c r="AL45" s="34"/>
@@ -7140,19 +7124,19 @@
         <v>2043</v>
       </c>
       <c r="D46" s="26">
-        <v>2856</v>
+        <v>2692</v>
       </c>
       <c r="E46" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="27">
-        <v>111960</v>
+        <v>110575</v>
       </c>
       <c r="G46" s="25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H46" s="28">
-        <v>45707</v>
+        <v>45583</v>
       </c>
       <c r="I46" s="29" t="s">
         <v>30</v>
@@ -7236,7 +7220,7 @@
         <v>0</v>
       </c>
       <c r="AJ46" s="33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AK46" s="34"/>
       <c r="AL46" s="34"/>
@@ -7260,13 +7244,13 @@
         <v>28</v>
       </c>
       <c r="F47" s="27">
-        <v>112522</v>
+        <v>111960</v>
       </c>
       <c r="G47" s="25" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H47" s="28">
-        <v>45776</v>
+        <v>45707</v>
       </c>
       <c r="I47" s="29" t="s">
         <v>30</v>
@@ -7350,7 +7334,7 @@
         <v>0</v>
       </c>
       <c r="AJ47" s="33" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK47" s="34"/>
       <c r="AL47" s="34"/>
@@ -7368,19 +7352,19 @@
         <v>2043</v>
       </c>
       <c r="D48" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E48" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F48" s="27">
-        <v>113076</v>
+        <v>112522</v>
       </c>
       <c r="G48" s="25" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="H48" s="28">
-        <v>45806</v>
+        <v>45776</v>
       </c>
       <c r="I48" s="29" t="s">
         <v>30</v>
@@ -7464,7 +7448,7 @@
         <v>0</v>
       </c>
       <c r="AJ48" s="33" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="AK48" s="34"/>
       <c r="AL48" s="34"/>
@@ -7482,19 +7466,19 @@
         <v>2043</v>
       </c>
       <c r="D49" s="26">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E49" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F49" s="27">
-        <v>114100</v>
+        <v>113076</v>
       </c>
       <c r="G49" s="25" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="H49" s="28">
-        <v>45863</v>
+        <v>45806</v>
       </c>
       <c r="I49" s="29" t="s">
         <v>30</v>
@@ -7578,7 +7562,7 @@
         <v>0</v>
       </c>
       <c r="AJ49" s="33" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="AK49" s="34"/>
       <c r="AL49" s="34"/>
@@ -7596,19 +7580,19 @@
         <v>2043</v>
       </c>
       <c r="D50" s="26">
-        <v>2692</v>
+        <v>2856</v>
       </c>
       <c r="E50" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F50" s="27">
-        <v>114157</v>
+        <v>114100</v>
       </c>
       <c r="G50" s="25" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="H50" s="28">
-        <v>45904</v>
+        <v>45863</v>
       </c>
       <c r="I50" s="29" t="s">
         <v>30</v>
@@ -7692,7 +7676,7 @@
         <v>0</v>
       </c>
       <c r="AJ50" s="33" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="AK50" s="34"/>
       <c r="AL50" s="34"/>
@@ -7710,25 +7694,25 @@
         <v>2043</v>
       </c>
       <c r="D51" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E51" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F51" s="27">
-        <v>114431</v>
+        <v>95148</v>
       </c>
       <c r="G51" s="25" t="s">
-        <v>122</v>
+        <v>54</v>
       </c>
       <c r="H51" s="28">
-        <v>45930</v>
+        <v>44916</v>
       </c>
       <c r="I51" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J51" s="30">
-        <v>0</v>
+        <v>46057.760000000002</v>
       </c>
       <c r="K51" s="30">
         <v>0</v>
@@ -7743,31 +7727,31 @@
         <v>0</v>
       </c>
       <c r="O51" s="29">
-        <v>0</v>
+        <v>46057.760000000002</v>
       </c>
       <c r="P51" s="32">
-        <v>0</v>
+        <v>2.5399999999999999E-2</v>
       </c>
       <c r="Q51" s="30">
-        <v>0</v>
+        <v>23133.08</v>
       </c>
       <c r="R51" s="30">
         <v>0</v>
       </c>
       <c r="S51" s="30">
-        <v>0</v>
+        <v>69825</v>
       </c>
       <c r="T51" s="29">
-        <v>0</v>
+        <v>-46691.92</v>
       </c>
       <c r="U51" s="29">
         <v>0</v>
       </c>
       <c r="V51" s="29">
-        <v>0</v>
+        <v>-634.16</v>
       </c>
       <c r="W51" s="29">
-        <v>0</v>
+        <v>13817.33</v>
       </c>
       <c r="X51" s="29">
         <v>0</v>
@@ -7782,31 +7766,31 @@
         <v>0</v>
       </c>
       <c r="AB51" s="29">
-        <v>0</v>
+        <v>13817.33</v>
       </c>
       <c r="AC51" s="32">
-        <v>0</v>
+        <v>1.5299999999999999E-2</v>
       </c>
       <c r="AD51" s="29">
-        <v>0</v>
+        <v>4744.3599999999997</v>
       </c>
       <c r="AE51" s="29">
         <v>0</v>
       </c>
       <c r="AF51" s="29">
-        <v>0</v>
+        <v>15103</v>
       </c>
       <c r="AG51" s="29">
-        <v>0</v>
+        <v>-10358.64</v>
       </c>
       <c r="AH51" s="29">
         <v>0</v>
       </c>
       <c r="AI51" s="29">
-        <v>0</v>
+        <v>3458.69</v>
       </c>
       <c r="AJ51" s="33" t="s">
-        <v>123</v>
+        <v>55</v>
       </c>
       <c r="AK51" s="34"/>
       <c r="AL51" s="34"/>
@@ -7824,25 +7808,25 @@
         <v>2043</v>
       </c>
       <c r="D52" s="26">
-        <v>2043</v>
+        <v>2692</v>
       </c>
       <c r="E52" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F52" s="27">
-        <v>95148</v>
+        <v>114431</v>
       </c>
       <c r="G52" s="25" t="s">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="H52" s="28">
-        <v>44916</v>
+        <v>45930</v>
       </c>
       <c r="I52" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J52" s="30">
-        <v>46057.760000000002</v>
+        <v>0</v>
       </c>
       <c r="K52" s="30">
         <v>0</v>
@@ -7854,34 +7838,34 @@
         <v>0</v>
       </c>
       <c r="N52" s="31">
-        <v>0</v>
+        <v>17664.759999999998</v>
       </c>
       <c r="O52" s="29">
-        <v>46057.760000000002</v>
+        <v>-17664.759999999998</v>
       </c>
       <c r="P52" s="32">
-        <v>2.5399999999999999E-2</v>
+        <v>-9.7999999999999997E-3</v>
       </c>
       <c r="Q52" s="30">
-        <v>23133.08</v>
+        <v>0</v>
       </c>
       <c r="R52" s="30">
         <v>0</v>
       </c>
       <c r="S52" s="30">
-        <v>69825</v>
+        <v>0</v>
       </c>
       <c r="T52" s="29">
-        <v>-46691.92</v>
+        <v>0</v>
       </c>
       <c r="U52" s="29">
         <v>0</v>
       </c>
       <c r="V52" s="29">
-        <v>-634.16</v>
+        <v>-17664.759999999998</v>
       </c>
       <c r="W52" s="29">
-        <v>13817.33</v>
+        <v>0</v>
       </c>
       <c r="X52" s="29">
         <v>0</v>
@@ -7893,34 +7877,34 @@
         <v>0</v>
       </c>
       <c r="AA52" s="31">
-        <v>0</v>
+        <v>5504.42</v>
       </c>
       <c r="AB52" s="29">
-        <v>13817.33</v>
+        <v>-5504.42</v>
       </c>
       <c r="AC52" s="32">
-        <v>1.5299999999999999E-2</v>
+        <v>-6.1000000000000004E-3</v>
       </c>
       <c r="AD52" s="29">
-        <v>4744.3599999999997</v>
+        <v>0</v>
       </c>
       <c r="AE52" s="29">
         <v>0</v>
       </c>
       <c r="AF52" s="29">
-        <v>15103</v>
+        <v>0</v>
       </c>
       <c r="AG52" s="29">
-        <v>-10358.64</v>
+        <v>0</v>
       </c>
       <c r="AH52" s="29">
         <v>0</v>
       </c>
       <c r="AI52" s="29">
-        <v>3458.69</v>
+        <v>-5504.42</v>
       </c>
       <c r="AJ52" s="33" t="s">
-        <v>55</v>
+        <v>123</v>
       </c>
       <c r="AK52" s="34"/>
       <c r="AL52" s="34"/>
@@ -7971,43 +7955,38 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="A53:AI53 AM53:AN53 AK53">
-    <cfRule type="expression" dxfId="8" priority="9" stopIfTrue="1">
+    <cfRule type="expression" dxfId="7" priority="9" stopIfTrue="1">
       <formula>$B53&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK53:AN53">
-    <cfRule type="expression" dxfId="7" priority="6" stopIfTrue="1">
+    <cfRule type="expression" dxfId="6" priority="5" stopIfTrue="1">
       <formula>$B53&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL53">
-    <cfRule type="expression" dxfId="6" priority="7" stopIfTrue="1">
+    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
       <formula>$B53&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AN53 V53 AI53">
-    <cfRule type="expression" dxfId="5" priority="8" stopIfTrue="1">
+    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
       <formula>$B53&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A6:AI52 AK6:AK52 AM6:AN52">
-    <cfRule type="expression" dxfId="4" priority="5" stopIfTrue="1">
+    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V6:V52 AI6:AI52 AN6:AN52">
-    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
+    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AL6:AL52">
-    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
+    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK41:AN41">
-    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
-      <formula>$B41&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AK42:AN52">

--- a/mdrt/MDRT.xlsx
+++ b/mdrt/MDRT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/mdrt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F831C410-6B00-8C4F-9081-628C0ED4BC61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A19AB92-40C5-C140-B632-93C170C618C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{263D14F0-BAEF-1E4F-83AF-E2F80B31AC70}"/>
   </bookViews>
@@ -782,76 +782,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="49">
-    <dxf>
-      <border>
-        <left style="hair">
-          <color rgb="FF002060"/>
-        </left>
-        <right style="hair">
-          <color rgb="FF002060"/>
-        </right>
-        <top style="hair">
-          <color rgb="FF002060"/>
-        </top>
-        <bottom style="hair">
-          <color rgb="FF002060"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color rgb="FF002060"/>
-        </left>
-        <right style="hair">
-          <color rgb="FF002060"/>
-        </right>
-        <top style="hair">
-          <color rgb="FF002060"/>
-        </top>
-        <bottom style="hair">
-          <color rgb="FF002060"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="45">
     <dxf>
       <fill>
         <patternFill>
@@ -1973,49 +1904,49 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}" name="Tabla1" displayName="Tabla1" ref="A4:AN53" totalsRowShown="0" dataDxfId="48" dataCellStyle="Millares">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}" name="Tabla1" displayName="Tabla1" ref="A4:AN53" totalsRowShown="0" dataDxfId="44" dataCellStyle="Millares">
   <autoFilter ref="A4:AN53" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}"/>
   <tableColumns count="40">
-    <tableColumn id="1" xr3:uid="{1B45D68F-9E92-9A48-B147-43382D17EADB}" name="Dir / Zona" dataDxfId="47"/>
-    <tableColumn id="2" xr3:uid="{8141432D-DFE6-034B-8474-F9783519965C}" name="Oficina" dataDxfId="46"/>
-    <tableColumn id="3" xr3:uid="{3026117E-099F-6549-A16F-3CA4F85DA282}" name="Mat" dataDxfId="45"/>
-    <tableColumn id="4" xr3:uid="{80621F5B-C573-8944-AF37-DC364F1BE0A9}" name="Suc" dataDxfId="44"/>
-    <tableColumn id="5" xr3:uid="{9D7D11D1-2D98-5646-92D8-F8703E85240A}" name="Promotor / Partner" dataDxfId="43"/>
-    <tableColumn id="6" xr3:uid="{870F3B42-A14B-1947-827D-9A6082152D25}" name="Asesor" dataDxfId="42"/>
-    <tableColumn id="7" xr3:uid="{CA38BEAA-FBC9-474E-8C66-960105DEBCF2}" name="Nombre del Asesor" dataDxfId="41"/>
-    <tableColumn id="8" xr3:uid="{8B8898BF-4E49-0543-9598-18FF2D3F6340}" name="Conexión" dataDxfId="40"/>
-    <tableColumn id="9" xr3:uid="{49ED1251-337D-EC49-A858-207AB60B673C}" name="Grupo" dataDxfId="39" dataCellStyle="Millares"/>
-    <tableColumn id="10" xr3:uid="{26692A66-EA2C-DD40-AAC8-07A5FE32BC7D}" name="Vida Individual" dataDxfId="38" dataCellStyle="Millares"/>
-    <tableColumn id="11" xr3:uid="{45DC445E-D43B-394B-91CD-B3001CC307CC}" name="Vida G&amp;C" dataDxfId="37" dataCellStyle="Millares"/>
-    <tableColumn id="12" xr3:uid="{953B1F2A-AB88-8A40-B82F-B5DBE8FAEA70}" name="Segudescuento" dataDxfId="36" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{27E03CF4-3925-2045-BF66-C5BB1ECC7061}" name="Aportaciones Adicionales (AVEs)" dataDxfId="35" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{7375183C-90AB-0B47-A516-65079E7802F1}" name="Cancelacion de Pólizas" dataDxfId="34" dataCellStyle="Millares"/>
-    <tableColumn id="15" xr3:uid="{B0F3DBFB-9B00-894E-8929-BF5CA63336C6}" name="Total de Productos Ilimitados" dataDxfId="33" dataCellStyle="Millares"/>
-    <tableColumn id="16" xr3:uid="{3C9D5C71-B64C-434C-8D65-968245DAE09C}" name="%Vida vs Meta" dataDxfId="32" dataCellStyle="Porcentaje"/>
-    <tableColumn id="17" xr3:uid="{088A86A3-8B28-DE4E-A384-CA0EA913DA34}" name="GMM Individual" dataDxfId="31" dataCellStyle="Millares"/>
-    <tableColumn id="18" xr3:uid="{A8791E9D-69D9-C844-AE4C-8AEEFA976B8B}" name="GMM G&amp;C" dataDxfId="30" dataCellStyle="Millares"/>
-    <tableColumn id="19" xr3:uid="{0FFCB5A1-F8D9-2344-9DC7-667454959C98}" name="Cancelacion de Pólizas2" dataDxfId="29" dataCellStyle="Millares"/>
-    <tableColumn id="20" xr3:uid="{FDCA43A0-92B9-954B-B283-ABAD7C194405}" name="Total Productos Limitados" dataDxfId="28" dataCellStyle="Millares"/>
-    <tableColumn id="21" xr3:uid="{7C93BB8B-9213-EA49-A648-EF5192999BF7}" name="Tope personales" dataDxfId="27" dataCellStyle="Millares"/>
-    <tableColumn id="22" xr3:uid="{70D3FAB6-79FB-994B-AB69-F0BBB15C6AFD}" name="Total Prima" dataDxfId="26" dataCellStyle="Millares"/>
-    <tableColumn id="23" xr3:uid="{0E0D17EB-06B5-AF45-9773-7D3921FC5B9C}" name="Vida Individual3" dataDxfId="25" dataCellStyle="Millares"/>
-    <tableColumn id="24" xr3:uid="{2A25EC7F-F387-9948-8D9A-38BFD2316AB4}" name="Vida G&amp;C4" dataDxfId="24" dataCellStyle="Millares"/>
-    <tableColumn id="25" xr3:uid="{F7E8005C-762C-7146-A541-3589C41B3DA2}" name="Segudescuento5" dataDxfId="23" dataCellStyle="Millares"/>
-    <tableColumn id="26" xr3:uid="{278BB65E-357A-1D4C-B1D0-5880BBD354CD}" name="Aportaciones Adicionales (AVEs)6" dataDxfId="22" dataCellStyle="Millares"/>
-    <tableColumn id="27" xr3:uid="{0490A388-0C84-C043-A7E8-E5DC8A03AF3F}" name="Cancelacion de Pólizas7" dataDxfId="21" dataCellStyle="Millares"/>
-    <tableColumn id="28" xr3:uid="{C06E1BE2-8968-A045-B8AB-E420B9B469A1}" name="Total de Productos Ilimitados8" dataDxfId="20" dataCellStyle="Millares"/>
-    <tableColumn id="29" xr3:uid="{BEBE08BA-F641-3141-BCA9-713FD1C7CEC2}" name="%Vida vs Meta9" dataDxfId="19" dataCellStyle="Porcentaje"/>
-    <tableColumn id="30" xr3:uid="{E7FB912B-27FD-1345-845F-E51E648031F5}" name="GMM Individual10" dataDxfId="18" dataCellStyle="Millares"/>
-    <tableColumn id="31" xr3:uid="{D5FF299C-A405-CE44-B4CD-CED400EFE81F}" name="GMM G&amp;C11" dataDxfId="17" dataCellStyle="Millares"/>
-    <tableColumn id="32" xr3:uid="{D7EFF89B-8E34-EA46-B72C-61EE3166E416}" name="Cancelacion de Pólizas12" dataDxfId="16" dataCellStyle="Millares"/>
-    <tableColumn id="33" xr3:uid="{81E1798B-3D20-E748-BDAB-7A2A6F5BF33B}" name="Total Productos Limitados13" dataDxfId="15" dataCellStyle="Millares"/>
-    <tableColumn id="34" xr3:uid="{7A820362-E31F-4D41-B400-9AD11AE00577}" name="Tope personales14" dataDxfId="14" dataCellStyle="Millares"/>
-    <tableColumn id="35" xr3:uid="{09E5F95B-08D0-B946-B14E-3F06BC9C57F0}" name="Total Comisión" dataDxfId="13" dataCellStyle="Millares"/>
-    <tableColumn id="36" xr3:uid="{523C81DC-6FA9-A24D-AF9B-9D74B552A8BA}" name="Columna15" dataDxfId="12" dataCellStyle="Millares"/>
-    <tableColumn id="37" xr3:uid="{ACF68D6F-CC4F-F94A-A3AE-C7407A1AC3DE}" name="Camino Prima" dataDxfId="11" dataCellStyle="Millares"/>
-    <tableColumn id="38" xr3:uid="{39FE9301-7AE9-0A42-B79D-CA4998AB76AE}" name="OBSERVACIÓN" dataDxfId="10" dataCellStyle="Millares"/>
-    <tableColumn id="39" xr3:uid="{99E25200-803C-E54D-88BD-27CB86CAED40}" name="Camino  Comisión" dataDxfId="9" dataCellStyle="Millares"/>
-    <tableColumn id="40" xr3:uid="{45B29C50-720D-8F4E-9803-310BA4AC814E}" name="NIVEL_x000a_" dataDxfId="8" dataCellStyle="Millares"/>
+    <tableColumn id="1" xr3:uid="{1B45D68F-9E92-9A48-B147-43382D17EADB}" name="Dir / Zona" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{8141432D-DFE6-034B-8474-F9783519965C}" name="Oficina" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{3026117E-099F-6549-A16F-3CA4F85DA282}" name="Mat" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{80621F5B-C573-8944-AF37-DC364F1BE0A9}" name="Suc" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{9D7D11D1-2D98-5646-92D8-F8703E85240A}" name="Promotor / Partner" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{870F3B42-A14B-1947-827D-9A6082152D25}" name="Asesor" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{CA38BEAA-FBC9-474E-8C66-960105DEBCF2}" name="Nombre del Asesor" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{8B8898BF-4E49-0543-9598-18FF2D3F6340}" name="Conexión" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{49ED1251-337D-EC49-A858-207AB60B673C}" name="Grupo" dataDxfId="35" dataCellStyle="Millares"/>
+    <tableColumn id="10" xr3:uid="{26692A66-EA2C-DD40-AAC8-07A5FE32BC7D}" name="Vida Individual" dataDxfId="34" dataCellStyle="Millares"/>
+    <tableColumn id="11" xr3:uid="{45DC445E-D43B-394B-91CD-B3001CC307CC}" name="Vida G&amp;C" dataDxfId="33" dataCellStyle="Millares"/>
+    <tableColumn id="12" xr3:uid="{953B1F2A-AB88-8A40-B82F-B5DBE8FAEA70}" name="Segudescuento" dataDxfId="32" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{27E03CF4-3925-2045-BF66-C5BB1ECC7061}" name="Aportaciones Adicionales (AVEs)" dataDxfId="31" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{7375183C-90AB-0B47-A516-65079E7802F1}" name="Cancelacion de Pólizas" dataDxfId="30" dataCellStyle="Millares"/>
+    <tableColumn id="15" xr3:uid="{B0F3DBFB-9B00-894E-8929-BF5CA63336C6}" name="Total de Productos Ilimitados" dataDxfId="29" dataCellStyle="Millares"/>
+    <tableColumn id="16" xr3:uid="{3C9D5C71-B64C-434C-8D65-968245DAE09C}" name="%Vida vs Meta" dataDxfId="28" dataCellStyle="Porcentaje"/>
+    <tableColumn id="17" xr3:uid="{088A86A3-8B28-DE4E-A384-CA0EA913DA34}" name="GMM Individual" dataDxfId="27" dataCellStyle="Millares"/>
+    <tableColumn id="18" xr3:uid="{A8791E9D-69D9-C844-AE4C-8AEEFA976B8B}" name="GMM G&amp;C" dataDxfId="26" dataCellStyle="Millares"/>
+    <tableColumn id="19" xr3:uid="{0FFCB5A1-F8D9-2344-9DC7-667454959C98}" name="Cancelacion de Pólizas2" dataDxfId="25" dataCellStyle="Millares"/>
+    <tableColumn id="20" xr3:uid="{FDCA43A0-92B9-954B-B283-ABAD7C194405}" name="Total Productos Limitados" dataDxfId="24" dataCellStyle="Millares"/>
+    <tableColumn id="21" xr3:uid="{7C93BB8B-9213-EA49-A648-EF5192999BF7}" name="Tope personales" dataDxfId="23" dataCellStyle="Millares"/>
+    <tableColumn id="22" xr3:uid="{70D3FAB6-79FB-994B-AB69-F0BBB15C6AFD}" name="Total Prima" dataDxfId="22" dataCellStyle="Millares"/>
+    <tableColumn id="23" xr3:uid="{0E0D17EB-06B5-AF45-9773-7D3921FC5B9C}" name="Vida Individual3" dataDxfId="21" dataCellStyle="Millares"/>
+    <tableColumn id="24" xr3:uid="{2A25EC7F-F387-9948-8D9A-38BFD2316AB4}" name="Vida G&amp;C4" dataDxfId="20" dataCellStyle="Millares"/>
+    <tableColumn id="25" xr3:uid="{F7E8005C-762C-7146-A541-3589C41B3DA2}" name="Segudescuento5" dataDxfId="19" dataCellStyle="Millares"/>
+    <tableColumn id="26" xr3:uid="{278BB65E-357A-1D4C-B1D0-5880BBD354CD}" name="Aportaciones Adicionales (AVEs)6" dataDxfId="18" dataCellStyle="Millares"/>
+    <tableColumn id="27" xr3:uid="{0490A388-0C84-C043-A7E8-E5DC8A03AF3F}" name="Cancelacion de Pólizas7" dataDxfId="17" dataCellStyle="Millares"/>
+    <tableColumn id="28" xr3:uid="{C06E1BE2-8968-A045-B8AB-E420B9B469A1}" name="Total de Productos Ilimitados8" dataDxfId="16" dataCellStyle="Millares"/>
+    <tableColumn id="29" xr3:uid="{BEBE08BA-F641-3141-BCA9-713FD1C7CEC2}" name="%Vida vs Meta9" dataDxfId="15" dataCellStyle="Porcentaje"/>
+    <tableColumn id="30" xr3:uid="{E7FB912B-27FD-1345-845F-E51E648031F5}" name="GMM Individual10" dataDxfId="14" dataCellStyle="Millares"/>
+    <tableColumn id="31" xr3:uid="{D5FF299C-A405-CE44-B4CD-CED400EFE81F}" name="GMM G&amp;C11" dataDxfId="13" dataCellStyle="Millares"/>
+    <tableColumn id="32" xr3:uid="{D7EFF89B-8E34-EA46-B72C-61EE3166E416}" name="Cancelacion de Pólizas12" dataDxfId="12" dataCellStyle="Millares"/>
+    <tableColumn id="33" xr3:uid="{81E1798B-3D20-E748-BDAB-7A2A6F5BF33B}" name="Total Productos Limitados13" dataDxfId="11" dataCellStyle="Millares"/>
+    <tableColumn id="34" xr3:uid="{7A820362-E31F-4D41-B400-9AD11AE00577}" name="Tope personales14" dataDxfId="10" dataCellStyle="Millares"/>
+    <tableColumn id="35" xr3:uid="{09E5F95B-08D0-B946-B14E-3F06BC9C57F0}" name="Total Comisión" dataDxfId="9" dataCellStyle="Millares"/>
+    <tableColumn id="36" xr3:uid="{523C81DC-6FA9-A24D-AF9B-9D74B552A8BA}" name="Columna15" dataDxfId="8" dataCellStyle="Millares"/>
+    <tableColumn id="37" xr3:uid="{ACF68D6F-CC4F-F94A-A3AE-C7407A1AC3DE}" name="Camino Prima" dataDxfId="7" dataCellStyle="Millares"/>
+    <tableColumn id="38" xr3:uid="{39FE9301-7AE9-0A42-B79D-CA4998AB76AE}" name="OBSERVACIÓN" dataDxfId="6" dataCellStyle="Millares"/>
+    <tableColumn id="39" xr3:uid="{99E25200-803C-E54D-88BD-27CB86CAED40}" name="Camino  Comisión" dataDxfId="5" dataCellStyle="Millares"/>
+    <tableColumn id="40" xr3:uid="{45B29C50-720D-8F4E-9803-310BA4AC814E}" name="NIVEL_x000a_" dataDxfId="4" dataCellStyle="Millares"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7954,44 +7885,24 @@
       <c r="AN53" s="35"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A53:AI53 AM53:AN53 AK53">
-    <cfRule type="expression" dxfId="7" priority="9" stopIfTrue="1">
-      <formula>$B53&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK53:AN53">
-    <cfRule type="expression" dxfId="6" priority="5" stopIfTrue="1">
-      <formula>$B53&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL53">
-    <cfRule type="expression" dxfId="5" priority="7" stopIfTrue="1">
-      <formula>$B53&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN53 V53 AI53">
-    <cfRule type="expression" dxfId="4" priority="8" stopIfTrue="1">
-      <formula>$B53&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A6:AI52 AK6:AK52 AM6:AN52">
+  <conditionalFormatting sqref="A6:AI53 AM6:AN53 AK6:AK53">
     <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V6:V52 AI6:AI52 AN6:AN52">
-    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
-      <formula>$B6&lt;&gt;""</formula>
+  <conditionalFormatting sqref="AK42:AN53">
+    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
+      <formula>$B42&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL6:AL52">
+  <conditionalFormatting sqref="AL6:AL53">
     <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK42:AN52">
-    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
-      <formula>$B42&lt;&gt;""</formula>
+  <conditionalFormatting sqref="AN6:AN53 V6:V53 AI6:AI53">
+    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
+      <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/mdrt/MDRT.xlsx
+++ b/mdrt/MDRT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/mdrt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A19AB92-40C5-C140-B632-93C170C618C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D653B46D-4888-A746-A9F3-5C925BE67C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{263D14F0-BAEF-1E4F-83AF-E2F80B31AC70}"/>
   </bookViews>
@@ -459,7 +459,7 @@
     <t>RIBF8912215D9</t>
   </si>
   <si>
-    <t>Avance del 1 de enero al 25 de marzo de 2026.</t>
+    <t>Avance del 1 de enero al 31 de marzo de 2026.</t>
   </si>
 </sst>
 </file>
@@ -782,7 +782,76 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="45">
+  <dxfs count="49">
+    <dxf>
+      <border>
+        <left style="hair">
+          <color rgb="FF002060"/>
+        </left>
+        <right style="hair">
+          <color rgb="FF002060"/>
+        </right>
+        <top style="hair">
+          <color rgb="FF002060"/>
+        </top>
+        <bottom style="hair">
+          <color rgb="FF002060"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color rgb="FF002060"/>
+        </left>
+        <right style="hair">
+          <color rgb="FF002060"/>
+        </right>
+        <top style="hair">
+          <color rgb="FF002060"/>
+        </top>
+        <bottom style="hair">
+          <color rgb="FF002060"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1904,49 +1973,49 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}" name="Tabla1" displayName="Tabla1" ref="A4:AN53" totalsRowShown="0" dataDxfId="44" dataCellStyle="Millares">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}" name="Tabla1" displayName="Tabla1" ref="A4:AN53" totalsRowShown="0" dataDxfId="48" dataCellStyle="Millares">
   <autoFilter ref="A4:AN53" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}"/>
   <tableColumns count="40">
-    <tableColumn id="1" xr3:uid="{1B45D68F-9E92-9A48-B147-43382D17EADB}" name="Dir / Zona" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{8141432D-DFE6-034B-8474-F9783519965C}" name="Oficina" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{3026117E-099F-6549-A16F-3CA4F85DA282}" name="Mat" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{80621F5B-C573-8944-AF37-DC364F1BE0A9}" name="Suc" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{9D7D11D1-2D98-5646-92D8-F8703E85240A}" name="Promotor / Partner" dataDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{870F3B42-A14B-1947-827D-9A6082152D25}" name="Asesor" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{CA38BEAA-FBC9-474E-8C66-960105DEBCF2}" name="Nombre del Asesor" dataDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{8B8898BF-4E49-0543-9598-18FF2D3F6340}" name="Conexión" dataDxfId="36"/>
-    <tableColumn id="9" xr3:uid="{49ED1251-337D-EC49-A858-207AB60B673C}" name="Grupo" dataDxfId="35" dataCellStyle="Millares"/>
-    <tableColumn id="10" xr3:uid="{26692A66-EA2C-DD40-AAC8-07A5FE32BC7D}" name="Vida Individual" dataDxfId="34" dataCellStyle="Millares"/>
-    <tableColumn id="11" xr3:uid="{45DC445E-D43B-394B-91CD-B3001CC307CC}" name="Vida G&amp;C" dataDxfId="33" dataCellStyle="Millares"/>
-    <tableColumn id="12" xr3:uid="{953B1F2A-AB88-8A40-B82F-B5DBE8FAEA70}" name="Segudescuento" dataDxfId="32" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{27E03CF4-3925-2045-BF66-C5BB1ECC7061}" name="Aportaciones Adicionales (AVEs)" dataDxfId="31" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{7375183C-90AB-0B47-A516-65079E7802F1}" name="Cancelacion de Pólizas" dataDxfId="30" dataCellStyle="Millares"/>
-    <tableColumn id="15" xr3:uid="{B0F3DBFB-9B00-894E-8929-BF5CA63336C6}" name="Total de Productos Ilimitados" dataDxfId="29" dataCellStyle="Millares"/>
-    <tableColumn id="16" xr3:uid="{3C9D5C71-B64C-434C-8D65-968245DAE09C}" name="%Vida vs Meta" dataDxfId="28" dataCellStyle="Porcentaje"/>
-    <tableColumn id="17" xr3:uid="{088A86A3-8B28-DE4E-A384-CA0EA913DA34}" name="GMM Individual" dataDxfId="27" dataCellStyle="Millares"/>
-    <tableColumn id="18" xr3:uid="{A8791E9D-69D9-C844-AE4C-8AEEFA976B8B}" name="GMM G&amp;C" dataDxfId="26" dataCellStyle="Millares"/>
-    <tableColumn id="19" xr3:uid="{0FFCB5A1-F8D9-2344-9DC7-667454959C98}" name="Cancelacion de Pólizas2" dataDxfId="25" dataCellStyle="Millares"/>
-    <tableColumn id="20" xr3:uid="{FDCA43A0-92B9-954B-B283-ABAD7C194405}" name="Total Productos Limitados" dataDxfId="24" dataCellStyle="Millares"/>
-    <tableColumn id="21" xr3:uid="{7C93BB8B-9213-EA49-A648-EF5192999BF7}" name="Tope personales" dataDxfId="23" dataCellStyle="Millares"/>
-    <tableColumn id="22" xr3:uid="{70D3FAB6-79FB-994B-AB69-F0BBB15C6AFD}" name="Total Prima" dataDxfId="22" dataCellStyle="Millares"/>
-    <tableColumn id="23" xr3:uid="{0E0D17EB-06B5-AF45-9773-7D3921FC5B9C}" name="Vida Individual3" dataDxfId="21" dataCellStyle="Millares"/>
-    <tableColumn id="24" xr3:uid="{2A25EC7F-F387-9948-8D9A-38BFD2316AB4}" name="Vida G&amp;C4" dataDxfId="20" dataCellStyle="Millares"/>
-    <tableColumn id="25" xr3:uid="{F7E8005C-762C-7146-A541-3589C41B3DA2}" name="Segudescuento5" dataDxfId="19" dataCellStyle="Millares"/>
-    <tableColumn id="26" xr3:uid="{278BB65E-357A-1D4C-B1D0-5880BBD354CD}" name="Aportaciones Adicionales (AVEs)6" dataDxfId="18" dataCellStyle="Millares"/>
-    <tableColumn id="27" xr3:uid="{0490A388-0C84-C043-A7E8-E5DC8A03AF3F}" name="Cancelacion de Pólizas7" dataDxfId="17" dataCellStyle="Millares"/>
-    <tableColumn id="28" xr3:uid="{C06E1BE2-8968-A045-B8AB-E420B9B469A1}" name="Total de Productos Ilimitados8" dataDxfId="16" dataCellStyle="Millares"/>
-    <tableColumn id="29" xr3:uid="{BEBE08BA-F641-3141-BCA9-713FD1C7CEC2}" name="%Vida vs Meta9" dataDxfId="15" dataCellStyle="Porcentaje"/>
-    <tableColumn id="30" xr3:uid="{E7FB912B-27FD-1345-845F-E51E648031F5}" name="GMM Individual10" dataDxfId="14" dataCellStyle="Millares"/>
-    <tableColumn id="31" xr3:uid="{D5FF299C-A405-CE44-B4CD-CED400EFE81F}" name="GMM G&amp;C11" dataDxfId="13" dataCellStyle="Millares"/>
-    <tableColumn id="32" xr3:uid="{D7EFF89B-8E34-EA46-B72C-61EE3166E416}" name="Cancelacion de Pólizas12" dataDxfId="12" dataCellStyle="Millares"/>
-    <tableColumn id="33" xr3:uid="{81E1798B-3D20-E748-BDAB-7A2A6F5BF33B}" name="Total Productos Limitados13" dataDxfId="11" dataCellStyle="Millares"/>
-    <tableColumn id="34" xr3:uid="{7A820362-E31F-4D41-B400-9AD11AE00577}" name="Tope personales14" dataDxfId="10" dataCellStyle="Millares"/>
-    <tableColumn id="35" xr3:uid="{09E5F95B-08D0-B946-B14E-3F06BC9C57F0}" name="Total Comisión" dataDxfId="9" dataCellStyle="Millares"/>
-    <tableColumn id="36" xr3:uid="{523C81DC-6FA9-A24D-AF9B-9D74B552A8BA}" name="Columna15" dataDxfId="8" dataCellStyle="Millares"/>
-    <tableColumn id="37" xr3:uid="{ACF68D6F-CC4F-F94A-A3AE-C7407A1AC3DE}" name="Camino Prima" dataDxfId="7" dataCellStyle="Millares"/>
-    <tableColumn id="38" xr3:uid="{39FE9301-7AE9-0A42-B79D-CA4998AB76AE}" name="OBSERVACIÓN" dataDxfId="6" dataCellStyle="Millares"/>
-    <tableColumn id="39" xr3:uid="{99E25200-803C-E54D-88BD-27CB86CAED40}" name="Camino  Comisión" dataDxfId="5" dataCellStyle="Millares"/>
-    <tableColumn id="40" xr3:uid="{45B29C50-720D-8F4E-9803-310BA4AC814E}" name="NIVEL_x000a_" dataDxfId="4" dataCellStyle="Millares"/>
+    <tableColumn id="1" xr3:uid="{1B45D68F-9E92-9A48-B147-43382D17EADB}" name="Dir / Zona" dataDxfId="47"/>
+    <tableColumn id="2" xr3:uid="{8141432D-DFE6-034B-8474-F9783519965C}" name="Oficina" dataDxfId="46"/>
+    <tableColumn id="3" xr3:uid="{3026117E-099F-6549-A16F-3CA4F85DA282}" name="Mat" dataDxfId="45"/>
+    <tableColumn id="4" xr3:uid="{80621F5B-C573-8944-AF37-DC364F1BE0A9}" name="Suc" dataDxfId="44"/>
+    <tableColumn id="5" xr3:uid="{9D7D11D1-2D98-5646-92D8-F8703E85240A}" name="Promotor / Partner" dataDxfId="43"/>
+    <tableColumn id="6" xr3:uid="{870F3B42-A14B-1947-827D-9A6082152D25}" name="Asesor" dataDxfId="42"/>
+    <tableColumn id="7" xr3:uid="{CA38BEAA-FBC9-474E-8C66-960105DEBCF2}" name="Nombre del Asesor" dataDxfId="41"/>
+    <tableColumn id="8" xr3:uid="{8B8898BF-4E49-0543-9598-18FF2D3F6340}" name="Conexión" dataDxfId="40"/>
+    <tableColumn id="9" xr3:uid="{49ED1251-337D-EC49-A858-207AB60B673C}" name="Grupo" dataDxfId="39" dataCellStyle="Millares"/>
+    <tableColumn id="10" xr3:uid="{26692A66-EA2C-DD40-AAC8-07A5FE32BC7D}" name="Vida Individual" dataDxfId="38" dataCellStyle="Millares"/>
+    <tableColumn id="11" xr3:uid="{45DC445E-D43B-394B-91CD-B3001CC307CC}" name="Vida G&amp;C" dataDxfId="37" dataCellStyle="Millares"/>
+    <tableColumn id="12" xr3:uid="{953B1F2A-AB88-8A40-B82F-B5DBE8FAEA70}" name="Segudescuento" dataDxfId="36" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{27E03CF4-3925-2045-BF66-C5BB1ECC7061}" name="Aportaciones Adicionales (AVEs)" dataDxfId="35" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{7375183C-90AB-0B47-A516-65079E7802F1}" name="Cancelacion de Pólizas" dataDxfId="34" dataCellStyle="Millares"/>
+    <tableColumn id="15" xr3:uid="{B0F3DBFB-9B00-894E-8929-BF5CA63336C6}" name="Total de Productos Ilimitados" dataDxfId="33" dataCellStyle="Millares"/>
+    <tableColumn id="16" xr3:uid="{3C9D5C71-B64C-434C-8D65-968245DAE09C}" name="%Vida vs Meta" dataDxfId="32" dataCellStyle="Porcentaje"/>
+    <tableColumn id="17" xr3:uid="{088A86A3-8B28-DE4E-A384-CA0EA913DA34}" name="GMM Individual" dataDxfId="31" dataCellStyle="Millares"/>
+    <tableColumn id="18" xr3:uid="{A8791E9D-69D9-C844-AE4C-8AEEFA976B8B}" name="GMM G&amp;C" dataDxfId="30" dataCellStyle="Millares"/>
+    <tableColumn id="19" xr3:uid="{0FFCB5A1-F8D9-2344-9DC7-667454959C98}" name="Cancelacion de Pólizas2" dataDxfId="29" dataCellStyle="Millares"/>
+    <tableColumn id="20" xr3:uid="{FDCA43A0-92B9-954B-B283-ABAD7C194405}" name="Total Productos Limitados" dataDxfId="28" dataCellStyle="Millares"/>
+    <tableColumn id="21" xr3:uid="{7C93BB8B-9213-EA49-A648-EF5192999BF7}" name="Tope personales" dataDxfId="27" dataCellStyle="Millares"/>
+    <tableColumn id="22" xr3:uid="{70D3FAB6-79FB-994B-AB69-F0BBB15C6AFD}" name="Total Prima" dataDxfId="26" dataCellStyle="Millares"/>
+    <tableColumn id="23" xr3:uid="{0E0D17EB-06B5-AF45-9773-7D3921FC5B9C}" name="Vida Individual3" dataDxfId="25" dataCellStyle="Millares"/>
+    <tableColumn id="24" xr3:uid="{2A25EC7F-F387-9948-8D9A-38BFD2316AB4}" name="Vida G&amp;C4" dataDxfId="24" dataCellStyle="Millares"/>
+    <tableColumn id="25" xr3:uid="{F7E8005C-762C-7146-A541-3589C41B3DA2}" name="Segudescuento5" dataDxfId="23" dataCellStyle="Millares"/>
+    <tableColumn id="26" xr3:uid="{278BB65E-357A-1D4C-B1D0-5880BBD354CD}" name="Aportaciones Adicionales (AVEs)6" dataDxfId="22" dataCellStyle="Millares"/>
+    <tableColumn id="27" xr3:uid="{0490A388-0C84-C043-A7E8-E5DC8A03AF3F}" name="Cancelacion de Pólizas7" dataDxfId="21" dataCellStyle="Millares"/>
+    <tableColumn id="28" xr3:uid="{C06E1BE2-8968-A045-B8AB-E420B9B469A1}" name="Total de Productos Ilimitados8" dataDxfId="20" dataCellStyle="Millares"/>
+    <tableColumn id="29" xr3:uid="{BEBE08BA-F641-3141-BCA9-713FD1C7CEC2}" name="%Vida vs Meta9" dataDxfId="19" dataCellStyle="Porcentaje"/>
+    <tableColumn id="30" xr3:uid="{E7FB912B-27FD-1345-845F-E51E648031F5}" name="GMM Individual10" dataDxfId="18" dataCellStyle="Millares"/>
+    <tableColumn id="31" xr3:uid="{D5FF299C-A405-CE44-B4CD-CED400EFE81F}" name="GMM G&amp;C11" dataDxfId="17" dataCellStyle="Millares"/>
+    <tableColumn id="32" xr3:uid="{D7EFF89B-8E34-EA46-B72C-61EE3166E416}" name="Cancelacion de Pólizas12" dataDxfId="16" dataCellStyle="Millares"/>
+    <tableColumn id="33" xr3:uid="{81E1798B-3D20-E748-BDAB-7A2A6F5BF33B}" name="Total Productos Limitados13" dataDxfId="15" dataCellStyle="Millares"/>
+    <tableColumn id="34" xr3:uid="{7A820362-E31F-4D41-B400-9AD11AE00577}" name="Tope personales14" dataDxfId="14" dataCellStyle="Millares"/>
+    <tableColumn id="35" xr3:uid="{09E5F95B-08D0-B946-B14E-3F06BC9C57F0}" name="Total Comisión" dataDxfId="13" dataCellStyle="Millares"/>
+    <tableColumn id="36" xr3:uid="{523C81DC-6FA9-A24D-AF9B-9D74B552A8BA}" name="Columna15" dataDxfId="12" dataCellStyle="Millares"/>
+    <tableColumn id="37" xr3:uid="{ACF68D6F-CC4F-F94A-A3AE-C7407A1AC3DE}" name="Camino Prima" dataDxfId="11" dataCellStyle="Millares"/>
+    <tableColumn id="38" xr3:uid="{39FE9301-7AE9-0A42-B79D-CA4998AB76AE}" name="OBSERVACIÓN" dataDxfId="10" dataCellStyle="Millares"/>
+    <tableColumn id="39" xr3:uid="{99E25200-803C-E54D-88BD-27CB86CAED40}" name="Camino  Comisión" dataDxfId="9" dataCellStyle="Millares"/>
+    <tableColumn id="40" xr3:uid="{45B29C50-720D-8F4E-9803-310BA4AC814E}" name="NIVEL_x000a_" dataDxfId="8" dataCellStyle="Millares"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7885,24 +7954,44 @@
       <c r="AN53" s="35"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A6:AI53 AM6:AN53 AK6:AK53">
+  <conditionalFormatting sqref="A53:AI53 AM53:AN53 AK53">
+    <cfRule type="expression" dxfId="7" priority="8" stopIfTrue="1">
+      <formula>$B53&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK53:AN53">
+    <cfRule type="expression" dxfId="6" priority="5" stopIfTrue="1">
+      <formula>$B53&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL53">
+    <cfRule type="expression" dxfId="5" priority="6" stopIfTrue="1">
+      <formula>$B53&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN53 V53 AI53">
+    <cfRule type="expression" dxfId="4" priority="7" stopIfTrue="1">
+      <formula>$B53&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A6:AI52 AK6:AK52 AM6:AN52">
     <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK42:AN53">
-    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
-      <formula>$B42&lt;&gt;""</formula>
+  <conditionalFormatting sqref="V6:V52 AI6:AI52 AN6:AN52">
+    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
+      <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL6:AL53">
+  <conditionalFormatting sqref="AL6:AL52">
     <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AN6:AN53 V6:V53 AI6:AI53">
-    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
-      <formula>$B6&lt;&gt;""</formula>
+  <conditionalFormatting sqref="AK42:AN52">
+    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
+      <formula>$B42&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/mdrt/MDRT.xlsx
+++ b/mdrt/MDRT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/mdrt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D653B46D-4888-A746-A9F3-5C925BE67C1D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456CB1C1-BE89-BF47-BC6E-CB439D67A180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{263D14F0-BAEF-1E4F-83AF-E2F80B31AC70}"/>
   </bookViews>
@@ -782,76 +782,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="49">
-    <dxf>
-      <border>
-        <left style="hair">
-          <color rgb="FF002060"/>
-        </left>
-        <right style="hair">
-          <color rgb="FF002060"/>
-        </right>
-        <top style="hair">
-          <color rgb="FF002060"/>
-        </top>
-        <bottom style="hair">
-          <color rgb="FF002060"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color rgb="FF002060"/>
-        </left>
-        <right style="hair">
-          <color rgb="FF002060"/>
-        </right>
-        <top style="hair">
-          <color rgb="FF002060"/>
-        </top>
-        <bottom style="hair">
-          <color rgb="FF002060"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="45">
     <dxf>
       <fill>
         <patternFill>
@@ -1973,49 +1904,49 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}" name="Tabla1" displayName="Tabla1" ref="A4:AN53" totalsRowShown="0" dataDxfId="48" dataCellStyle="Millares">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}" name="Tabla1" displayName="Tabla1" ref="A4:AN53" totalsRowShown="0" dataDxfId="44" dataCellStyle="Millares">
   <autoFilter ref="A4:AN53" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}"/>
   <tableColumns count="40">
-    <tableColumn id="1" xr3:uid="{1B45D68F-9E92-9A48-B147-43382D17EADB}" name="Dir / Zona" dataDxfId="47"/>
-    <tableColumn id="2" xr3:uid="{8141432D-DFE6-034B-8474-F9783519965C}" name="Oficina" dataDxfId="46"/>
-    <tableColumn id="3" xr3:uid="{3026117E-099F-6549-A16F-3CA4F85DA282}" name="Mat" dataDxfId="45"/>
-    <tableColumn id="4" xr3:uid="{80621F5B-C573-8944-AF37-DC364F1BE0A9}" name="Suc" dataDxfId="44"/>
-    <tableColumn id="5" xr3:uid="{9D7D11D1-2D98-5646-92D8-F8703E85240A}" name="Promotor / Partner" dataDxfId="43"/>
-    <tableColumn id="6" xr3:uid="{870F3B42-A14B-1947-827D-9A6082152D25}" name="Asesor" dataDxfId="42"/>
-    <tableColumn id="7" xr3:uid="{CA38BEAA-FBC9-474E-8C66-960105DEBCF2}" name="Nombre del Asesor" dataDxfId="41"/>
-    <tableColumn id="8" xr3:uid="{8B8898BF-4E49-0543-9598-18FF2D3F6340}" name="Conexión" dataDxfId="40"/>
-    <tableColumn id="9" xr3:uid="{49ED1251-337D-EC49-A858-207AB60B673C}" name="Grupo" dataDxfId="39" dataCellStyle="Millares"/>
-    <tableColumn id="10" xr3:uid="{26692A66-EA2C-DD40-AAC8-07A5FE32BC7D}" name="Vida Individual" dataDxfId="38" dataCellStyle="Millares"/>
-    <tableColumn id="11" xr3:uid="{45DC445E-D43B-394B-91CD-B3001CC307CC}" name="Vida G&amp;C" dataDxfId="37" dataCellStyle="Millares"/>
-    <tableColumn id="12" xr3:uid="{953B1F2A-AB88-8A40-B82F-B5DBE8FAEA70}" name="Segudescuento" dataDxfId="36" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{27E03CF4-3925-2045-BF66-C5BB1ECC7061}" name="Aportaciones Adicionales (AVEs)" dataDxfId="35" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{7375183C-90AB-0B47-A516-65079E7802F1}" name="Cancelacion de Pólizas" dataDxfId="34" dataCellStyle="Millares"/>
-    <tableColumn id="15" xr3:uid="{B0F3DBFB-9B00-894E-8929-BF5CA63336C6}" name="Total de Productos Ilimitados" dataDxfId="33" dataCellStyle="Millares"/>
-    <tableColumn id="16" xr3:uid="{3C9D5C71-B64C-434C-8D65-968245DAE09C}" name="%Vida vs Meta" dataDxfId="32" dataCellStyle="Porcentaje"/>
-    <tableColumn id="17" xr3:uid="{088A86A3-8B28-DE4E-A384-CA0EA913DA34}" name="GMM Individual" dataDxfId="31" dataCellStyle="Millares"/>
-    <tableColumn id="18" xr3:uid="{A8791E9D-69D9-C844-AE4C-8AEEFA976B8B}" name="GMM G&amp;C" dataDxfId="30" dataCellStyle="Millares"/>
-    <tableColumn id="19" xr3:uid="{0FFCB5A1-F8D9-2344-9DC7-667454959C98}" name="Cancelacion de Pólizas2" dataDxfId="29" dataCellStyle="Millares"/>
-    <tableColumn id="20" xr3:uid="{FDCA43A0-92B9-954B-B283-ABAD7C194405}" name="Total Productos Limitados" dataDxfId="28" dataCellStyle="Millares"/>
-    <tableColumn id="21" xr3:uid="{7C93BB8B-9213-EA49-A648-EF5192999BF7}" name="Tope personales" dataDxfId="27" dataCellStyle="Millares"/>
-    <tableColumn id="22" xr3:uid="{70D3FAB6-79FB-994B-AB69-F0BBB15C6AFD}" name="Total Prima" dataDxfId="26" dataCellStyle="Millares"/>
-    <tableColumn id="23" xr3:uid="{0E0D17EB-06B5-AF45-9773-7D3921FC5B9C}" name="Vida Individual3" dataDxfId="25" dataCellStyle="Millares"/>
-    <tableColumn id="24" xr3:uid="{2A25EC7F-F387-9948-8D9A-38BFD2316AB4}" name="Vida G&amp;C4" dataDxfId="24" dataCellStyle="Millares"/>
-    <tableColumn id="25" xr3:uid="{F7E8005C-762C-7146-A541-3589C41B3DA2}" name="Segudescuento5" dataDxfId="23" dataCellStyle="Millares"/>
-    <tableColumn id="26" xr3:uid="{278BB65E-357A-1D4C-B1D0-5880BBD354CD}" name="Aportaciones Adicionales (AVEs)6" dataDxfId="22" dataCellStyle="Millares"/>
-    <tableColumn id="27" xr3:uid="{0490A388-0C84-C043-A7E8-E5DC8A03AF3F}" name="Cancelacion de Pólizas7" dataDxfId="21" dataCellStyle="Millares"/>
-    <tableColumn id="28" xr3:uid="{C06E1BE2-8968-A045-B8AB-E420B9B469A1}" name="Total de Productos Ilimitados8" dataDxfId="20" dataCellStyle="Millares"/>
-    <tableColumn id="29" xr3:uid="{BEBE08BA-F641-3141-BCA9-713FD1C7CEC2}" name="%Vida vs Meta9" dataDxfId="19" dataCellStyle="Porcentaje"/>
-    <tableColumn id="30" xr3:uid="{E7FB912B-27FD-1345-845F-E51E648031F5}" name="GMM Individual10" dataDxfId="18" dataCellStyle="Millares"/>
-    <tableColumn id="31" xr3:uid="{D5FF299C-A405-CE44-B4CD-CED400EFE81F}" name="GMM G&amp;C11" dataDxfId="17" dataCellStyle="Millares"/>
-    <tableColumn id="32" xr3:uid="{D7EFF89B-8E34-EA46-B72C-61EE3166E416}" name="Cancelacion de Pólizas12" dataDxfId="16" dataCellStyle="Millares"/>
-    <tableColumn id="33" xr3:uid="{81E1798B-3D20-E748-BDAB-7A2A6F5BF33B}" name="Total Productos Limitados13" dataDxfId="15" dataCellStyle="Millares"/>
-    <tableColumn id="34" xr3:uid="{7A820362-E31F-4D41-B400-9AD11AE00577}" name="Tope personales14" dataDxfId="14" dataCellStyle="Millares"/>
-    <tableColumn id="35" xr3:uid="{09E5F95B-08D0-B946-B14E-3F06BC9C57F0}" name="Total Comisión" dataDxfId="13" dataCellStyle="Millares"/>
-    <tableColumn id="36" xr3:uid="{523C81DC-6FA9-A24D-AF9B-9D74B552A8BA}" name="Columna15" dataDxfId="12" dataCellStyle="Millares"/>
-    <tableColumn id="37" xr3:uid="{ACF68D6F-CC4F-F94A-A3AE-C7407A1AC3DE}" name="Camino Prima" dataDxfId="11" dataCellStyle="Millares"/>
-    <tableColumn id="38" xr3:uid="{39FE9301-7AE9-0A42-B79D-CA4998AB76AE}" name="OBSERVACIÓN" dataDxfId="10" dataCellStyle="Millares"/>
-    <tableColumn id="39" xr3:uid="{99E25200-803C-E54D-88BD-27CB86CAED40}" name="Camino  Comisión" dataDxfId="9" dataCellStyle="Millares"/>
-    <tableColumn id="40" xr3:uid="{45B29C50-720D-8F4E-9803-310BA4AC814E}" name="NIVEL_x000a_" dataDxfId="8" dataCellStyle="Millares"/>
+    <tableColumn id="1" xr3:uid="{1B45D68F-9E92-9A48-B147-43382D17EADB}" name="Dir / Zona" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{8141432D-DFE6-034B-8474-F9783519965C}" name="Oficina" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{3026117E-099F-6549-A16F-3CA4F85DA282}" name="Mat" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{80621F5B-C573-8944-AF37-DC364F1BE0A9}" name="Suc" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{9D7D11D1-2D98-5646-92D8-F8703E85240A}" name="Promotor / Partner" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{870F3B42-A14B-1947-827D-9A6082152D25}" name="Asesor" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{CA38BEAA-FBC9-474E-8C66-960105DEBCF2}" name="Nombre del Asesor" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{8B8898BF-4E49-0543-9598-18FF2D3F6340}" name="Conexión" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{49ED1251-337D-EC49-A858-207AB60B673C}" name="Grupo" dataDxfId="35" dataCellStyle="Millares"/>
+    <tableColumn id="10" xr3:uid="{26692A66-EA2C-DD40-AAC8-07A5FE32BC7D}" name="Vida Individual" dataDxfId="34" dataCellStyle="Millares"/>
+    <tableColumn id="11" xr3:uid="{45DC445E-D43B-394B-91CD-B3001CC307CC}" name="Vida G&amp;C" dataDxfId="33" dataCellStyle="Millares"/>
+    <tableColumn id="12" xr3:uid="{953B1F2A-AB88-8A40-B82F-B5DBE8FAEA70}" name="Segudescuento" dataDxfId="32" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{27E03CF4-3925-2045-BF66-C5BB1ECC7061}" name="Aportaciones Adicionales (AVEs)" dataDxfId="31" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{7375183C-90AB-0B47-A516-65079E7802F1}" name="Cancelacion de Pólizas" dataDxfId="30" dataCellStyle="Millares"/>
+    <tableColumn id="15" xr3:uid="{B0F3DBFB-9B00-894E-8929-BF5CA63336C6}" name="Total de Productos Ilimitados" dataDxfId="29" dataCellStyle="Millares"/>
+    <tableColumn id="16" xr3:uid="{3C9D5C71-B64C-434C-8D65-968245DAE09C}" name="%Vida vs Meta" dataDxfId="28" dataCellStyle="Porcentaje"/>
+    <tableColumn id="17" xr3:uid="{088A86A3-8B28-DE4E-A384-CA0EA913DA34}" name="GMM Individual" dataDxfId="27" dataCellStyle="Millares"/>
+    <tableColumn id="18" xr3:uid="{A8791E9D-69D9-C844-AE4C-8AEEFA976B8B}" name="GMM G&amp;C" dataDxfId="26" dataCellStyle="Millares"/>
+    <tableColumn id="19" xr3:uid="{0FFCB5A1-F8D9-2344-9DC7-667454959C98}" name="Cancelacion de Pólizas2" dataDxfId="25" dataCellStyle="Millares"/>
+    <tableColumn id="20" xr3:uid="{FDCA43A0-92B9-954B-B283-ABAD7C194405}" name="Total Productos Limitados" dataDxfId="24" dataCellStyle="Millares"/>
+    <tableColumn id="21" xr3:uid="{7C93BB8B-9213-EA49-A648-EF5192999BF7}" name="Tope personales" dataDxfId="23" dataCellStyle="Millares"/>
+    <tableColumn id="22" xr3:uid="{70D3FAB6-79FB-994B-AB69-F0BBB15C6AFD}" name="Total Prima" dataDxfId="22" dataCellStyle="Millares"/>
+    <tableColumn id="23" xr3:uid="{0E0D17EB-06B5-AF45-9773-7D3921FC5B9C}" name="Vida Individual3" dataDxfId="21" dataCellStyle="Millares"/>
+    <tableColumn id="24" xr3:uid="{2A25EC7F-F387-9948-8D9A-38BFD2316AB4}" name="Vida G&amp;C4" dataDxfId="20" dataCellStyle="Millares"/>
+    <tableColumn id="25" xr3:uid="{F7E8005C-762C-7146-A541-3589C41B3DA2}" name="Segudescuento5" dataDxfId="19" dataCellStyle="Millares"/>
+    <tableColumn id="26" xr3:uid="{278BB65E-357A-1D4C-B1D0-5880BBD354CD}" name="Aportaciones Adicionales (AVEs)6" dataDxfId="18" dataCellStyle="Millares"/>
+    <tableColumn id="27" xr3:uid="{0490A388-0C84-C043-A7E8-E5DC8A03AF3F}" name="Cancelacion de Pólizas7" dataDxfId="17" dataCellStyle="Millares"/>
+    <tableColumn id="28" xr3:uid="{C06E1BE2-8968-A045-B8AB-E420B9B469A1}" name="Total de Productos Ilimitados8" dataDxfId="16" dataCellStyle="Millares"/>
+    <tableColumn id="29" xr3:uid="{BEBE08BA-F641-3141-BCA9-713FD1C7CEC2}" name="%Vida vs Meta9" dataDxfId="15" dataCellStyle="Porcentaje"/>
+    <tableColumn id="30" xr3:uid="{E7FB912B-27FD-1345-845F-E51E648031F5}" name="GMM Individual10" dataDxfId="14" dataCellStyle="Millares"/>
+    <tableColumn id="31" xr3:uid="{D5FF299C-A405-CE44-B4CD-CED400EFE81F}" name="GMM G&amp;C11" dataDxfId="13" dataCellStyle="Millares"/>
+    <tableColumn id="32" xr3:uid="{D7EFF89B-8E34-EA46-B72C-61EE3166E416}" name="Cancelacion de Pólizas12" dataDxfId="12" dataCellStyle="Millares"/>
+    <tableColumn id="33" xr3:uid="{81E1798B-3D20-E748-BDAB-7A2A6F5BF33B}" name="Total Productos Limitados13" dataDxfId="11" dataCellStyle="Millares"/>
+    <tableColumn id="34" xr3:uid="{7A820362-E31F-4D41-B400-9AD11AE00577}" name="Tope personales14" dataDxfId="10" dataCellStyle="Millares"/>
+    <tableColumn id="35" xr3:uid="{09E5F95B-08D0-B946-B14E-3F06BC9C57F0}" name="Total Comisión" dataDxfId="9" dataCellStyle="Millares"/>
+    <tableColumn id="36" xr3:uid="{523C81DC-6FA9-A24D-AF9B-9D74B552A8BA}" name="Columna15" dataDxfId="8" dataCellStyle="Millares"/>
+    <tableColumn id="37" xr3:uid="{ACF68D6F-CC4F-F94A-A3AE-C7407A1AC3DE}" name="Camino Prima" dataDxfId="7" dataCellStyle="Millares"/>
+    <tableColumn id="38" xr3:uid="{39FE9301-7AE9-0A42-B79D-CA4998AB76AE}" name="OBSERVACIÓN" dataDxfId="6" dataCellStyle="Millares"/>
+    <tableColumn id="39" xr3:uid="{99E25200-803C-E54D-88BD-27CB86CAED40}" name="Camino  Comisión" dataDxfId="5" dataCellStyle="Millares"/>
+    <tableColumn id="40" xr3:uid="{45B29C50-720D-8F4E-9803-310BA4AC814E}" name="NIVEL_x000a_" dataDxfId="4" dataCellStyle="Millares"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7954,44 +7885,24 @@
       <c r="AN53" s="35"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A53:AI53 AM53:AN53 AK53">
-    <cfRule type="expression" dxfId="7" priority="8" stopIfTrue="1">
-      <formula>$B53&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK53:AN53">
-    <cfRule type="expression" dxfId="6" priority="5" stopIfTrue="1">
-      <formula>$B53&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL53">
-    <cfRule type="expression" dxfId="5" priority="6" stopIfTrue="1">
-      <formula>$B53&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN53 V53 AI53">
-    <cfRule type="expression" dxfId="4" priority="7" stopIfTrue="1">
-      <formula>$B53&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A6:AI52 AK6:AK52 AM6:AN52">
+  <conditionalFormatting sqref="A6:AI53 AM6:AN53 AK6:AK53">
     <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V6:V52 AI6:AI52 AN6:AN52">
-    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
-      <formula>$B6&lt;&gt;""</formula>
+  <conditionalFormatting sqref="AK42:AN53">
+    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
+      <formula>$B42&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL6:AL52">
+  <conditionalFormatting sqref="AL6:AL53">
     <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK42:AN52">
-    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
-      <formula>$B42&lt;&gt;""</formula>
+  <conditionalFormatting sqref="AN6:AN53 V6:V53 AI6:AI53">
+    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
+      <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/mdrt/MDRT.xlsx
+++ b/mdrt/MDRT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/mdrt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{456CB1C1-BE89-BF47-BC6E-CB439D67A180}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3C6504-6A0D-AD49-9B15-52845735A4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{263D14F0-BAEF-1E4F-83AF-E2F80B31AC70}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="327" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="145">
   <si>
     <t>Dir / Zona</t>
   </si>
@@ -460,6 +460,18 @@
   </si>
   <si>
     <t>Avance del 1 de enero al 31 de marzo de 2026.</t>
+  </si>
+  <si>
+    <t>PAULA ANGELICA LOMELI CAZARES</t>
+  </si>
+  <si>
+    <t>LOCP911015T44</t>
+  </si>
+  <si>
+    <t>LUIS GUILLERMO OLGUIN FERNANDEZ</t>
+  </si>
+  <si>
+    <t>OUFL8603105M2</t>
   </si>
 </sst>
 </file>
@@ -782,7 +794,92 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="45">
+  <dxfs count="50">
+    <dxf>
+      <border>
+        <left style="hair">
+          <color rgb="FF002060"/>
+        </left>
+        <right style="hair">
+          <color rgb="FF002060"/>
+        </right>
+        <top style="hair">
+          <color rgb="FF002060"/>
+        </top>
+        <bottom style="hair">
+          <color rgb="FF002060"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="hair">
+          <color rgb="FF002060"/>
+        </left>
+        <right style="hair">
+          <color rgb="FF002060"/>
+        </right>
+        <top style="hair">
+          <color rgb="FF002060"/>
+        </top>
+        <bottom style="hair">
+          <color rgb="FF002060"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="9" tint="0.79998168889431442"/>
+        </patternFill>
+      </fill>
+      <border>
+        <left style="hair">
+          <color rgb="FF002060"/>
+        </left>
+        <right style="hair">
+          <color rgb="FF002060"/>
+        </right>
+        <top style="hair">
+          <color rgb="FF002060"/>
+        </top>
+        <bottom style="hair">
+          <color rgb="FF002060"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </left>
+        <right style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </right>
+        <top style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0" tint="-0.14996795556505021"/>
+        </bottom>
+      </border>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1904,49 +2001,49 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}" name="Tabla1" displayName="Tabla1" ref="A4:AN53" totalsRowShown="0" dataDxfId="44" dataCellStyle="Millares">
-  <autoFilter ref="A4:AN53" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}" name="Tabla1" displayName="Tabla1" ref="A4:AN54" totalsRowShown="0" dataDxfId="49" dataCellStyle="Millares">
+  <autoFilter ref="A4:AN54" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}"/>
   <tableColumns count="40">
-    <tableColumn id="1" xr3:uid="{1B45D68F-9E92-9A48-B147-43382D17EADB}" name="Dir / Zona" dataDxfId="43"/>
-    <tableColumn id="2" xr3:uid="{8141432D-DFE6-034B-8474-F9783519965C}" name="Oficina" dataDxfId="42"/>
-    <tableColumn id="3" xr3:uid="{3026117E-099F-6549-A16F-3CA4F85DA282}" name="Mat" dataDxfId="41"/>
-    <tableColumn id="4" xr3:uid="{80621F5B-C573-8944-AF37-DC364F1BE0A9}" name="Suc" dataDxfId="40"/>
-    <tableColumn id="5" xr3:uid="{9D7D11D1-2D98-5646-92D8-F8703E85240A}" name="Promotor / Partner" dataDxfId="39"/>
-    <tableColumn id="6" xr3:uid="{870F3B42-A14B-1947-827D-9A6082152D25}" name="Asesor" dataDxfId="38"/>
-    <tableColumn id="7" xr3:uid="{CA38BEAA-FBC9-474E-8C66-960105DEBCF2}" name="Nombre del Asesor" dataDxfId="37"/>
-    <tableColumn id="8" xr3:uid="{8B8898BF-4E49-0543-9598-18FF2D3F6340}" name="Conexión" dataDxfId="36"/>
-    <tableColumn id="9" xr3:uid="{49ED1251-337D-EC49-A858-207AB60B673C}" name="Grupo" dataDxfId="35" dataCellStyle="Millares"/>
-    <tableColumn id="10" xr3:uid="{26692A66-EA2C-DD40-AAC8-07A5FE32BC7D}" name="Vida Individual" dataDxfId="34" dataCellStyle="Millares"/>
-    <tableColumn id="11" xr3:uid="{45DC445E-D43B-394B-91CD-B3001CC307CC}" name="Vida G&amp;C" dataDxfId="33" dataCellStyle="Millares"/>
-    <tableColumn id="12" xr3:uid="{953B1F2A-AB88-8A40-B82F-B5DBE8FAEA70}" name="Segudescuento" dataDxfId="32" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{27E03CF4-3925-2045-BF66-C5BB1ECC7061}" name="Aportaciones Adicionales (AVEs)" dataDxfId="31" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{7375183C-90AB-0B47-A516-65079E7802F1}" name="Cancelacion de Pólizas" dataDxfId="30" dataCellStyle="Millares"/>
-    <tableColumn id="15" xr3:uid="{B0F3DBFB-9B00-894E-8929-BF5CA63336C6}" name="Total de Productos Ilimitados" dataDxfId="29" dataCellStyle="Millares"/>
-    <tableColumn id="16" xr3:uid="{3C9D5C71-B64C-434C-8D65-968245DAE09C}" name="%Vida vs Meta" dataDxfId="28" dataCellStyle="Porcentaje"/>
-    <tableColumn id="17" xr3:uid="{088A86A3-8B28-DE4E-A384-CA0EA913DA34}" name="GMM Individual" dataDxfId="27" dataCellStyle="Millares"/>
-    <tableColumn id="18" xr3:uid="{A8791E9D-69D9-C844-AE4C-8AEEFA976B8B}" name="GMM G&amp;C" dataDxfId="26" dataCellStyle="Millares"/>
-    <tableColumn id="19" xr3:uid="{0FFCB5A1-F8D9-2344-9DC7-667454959C98}" name="Cancelacion de Pólizas2" dataDxfId="25" dataCellStyle="Millares"/>
-    <tableColumn id="20" xr3:uid="{FDCA43A0-92B9-954B-B283-ABAD7C194405}" name="Total Productos Limitados" dataDxfId="24" dataCellStyle="Millares"/>
-    <tableColumn id="21" xr3:uid="{7C93BB8B-9213-EA49-A648-EF5192999BF7}" name="Tope personales" dataDxfId="23" dataCellStyle="Millares"/>
-    <tableColumn id="22" xr3:uid="{70D3FAB6-79FB-994B-AB69-F0BBB15C6AFD}" name="Total Prima" dataDxfId="22" dataCellStyle="Millares"/>
-    <tableColumn id="23" xr3:uid="{0E0D17EB-06B5-AF45-9773-7D3921FC5B9C}" name="Vida Individual3" dataDxfId="21" dataCellStyle="Millares"/>
-    <tableColumn id="24" xr3:uid="{2A25EC7F-F387-9948-8D9A-38BFD2316AB4}" name="Vida G&amp;C4" dataDxfId="20" dataCellStyle="Millares"/>
-    <tableColumn id="25" xr3:uid="{F7E8005C-762C-7146-A541-3589C41B3DA2}" name="Segudescuento5" dataDxfId="19" dataCellStyle="Millares"/>
-    <tableColumn id="26" xr3:uid="{278BB65E-357A-1D4C-B1D0-5880BBD354CD}" name="Aportaciones Adicionales (AVEs)6" dataDxfId="18" dataCellStyle="Millares"/>
-    <tableColumn id="27" xr3:uid="{0490A388-0C84-C043-A7E8-E5DC8A03AF3F}" name="Cancelacion de Pólizas7" dataDxfId="17" dataCellStyle="Millares"/>
-    <tableColumn id="28" xr3:uid="{C06E1BE2-8968-A045-B8AB-E420B9B469A1}" name="Total de Productos Ilimitados8" dataDxfId="16" dataCellStyle="Millares"/>
-    <tableColumn id="29" xr3:uid="{BEBE08BA-F641-3141-BCA9-713FD1C7CEC2}" name="%Vida vs Meta9" dataDxfId="15" dataCellStyle="Porcentaje"/>
-    <tableColumn id="30" xr3:uid="{E7FB912B-27FD-1345-845F-E51E648031F5}" name="GMM Individual10" dataDxfId="14" dataCellStyle="Millares"/>
-    <tableColumn id="31" xr3:uid="{D5FF299C-A405-CE44-B4CD-CED400EFE81F}" name="GMM G&amp;C11" dataDxfId="13" dataCellStyle="Millares"/>
-    <tableColumn id="32" xr3:uid="{D7EFF89B-8E34-EA46-B72C-61EE3166E416}" name="Cancelacion de Pólizas12" dataDxfId="12" dataCellStyle="Millares"/>
-    <tableColumn id="33" xr3:uid="{81E1798B-3D20-E748-BDAB-7A2A6F5BF33B}" name="Total Productos Limitados13" dataDxfId="11" dataCellStyle="Millares"/>
-    <tableColumn id="34" xr3:uid="{7A820362-E31F-4D41-B400-9AD11AE00577}" name="Tope personales14" dataDxfId="10" dataCellStyle="Millares"/>
-    <tableColumn id="35" xr3:uid="{09E5F95B-08D0-B946-B14E-3F06BC9C57F0}" name="Total Comisión" dataDxfId="9" dataCellStyle="Millares"/>
-    <tableColumn id="36" xr3:uid="{523C81DC-6FA9-A24D-AF9B-9D74B552A8BA}" name="Columna15" dataDxfId="8" dataCellStyle="Millares"/>
-    <tableColumn id="37" xr3:uid="{ACF68D6F-CC4F-F94A-A3AE-C7407A1AC3DE}" name="Camino Prima" dataDxfId="7" dataCellStyle="Millares"/>
-    <tableColumn id="38" xr3:uid="{39FE9301-7AE9-0A42-B79D-CA4998AB76AE}" name="OBSERVACIÓN" dataDxfId="6" dataCellStyle="Millares"/>
-    <tableColumn id="39" xr3:uid="{99E25200-803C-E54D-88BD-27CB86CAED40}" name="Camino  Comisión" dataDxfId="5" dataCellStyle="Millares"/>
-    <tableColumn id="40" xr3:uid="{45B29C50-720D-8F4E-9803-310BA4AC814E}" name="NIVEL_x000a_" dataDxfId="4" dataCellStyle="Millares"/>
+    <tableColumn id="1" xr3:uid="{1B45D68F-9E92-9A48-B147-43382D17EADB}" name="Dir / Zona" dataDxfId="48"/>
+    <tableColumn id="2" xr3:uid="{8141432D-DFE6-034B-8474-F9783519965C}" name="Oficina" dataDxfId="47"/>
+    <tableColumn id="3" xr3:uid="{3026117E-099F-6549-A16F-3CA4F85DA282}" name="Mat" dataDxfId="46"/>
+    <tableColumn id="4" xr3:uid="{80621F5B-C573-8944-AF37-DC364F1BE0A9}" name="Suc" dataDxfId="45"/>
+    <tableColumn id="5" xr3:uid="{9D7D11D1-2D98-5646-92D8-F8703E85240A}" name="Promotor / Partner" dataDxfId="44"/>
+    <tableColumn id="6" xr3:uid="{870F3B42-A14B-1947-827D-9A6082152D25}" name="Asesor" dataDxfId="43"/>
+    <tableColumn id="7" xr3:uid="{CA38BEAA-FBC9-474E-8C66-960105DEBCF2}" name="Nombre del Asesor" dataDxfId="42"/>
+    <tableColumn id="8" xr3:uid="{8B8898BF-4E49-0543-9598-18FF2D3F6340}" name="Conexión" dataDxfId="41"/>
+    <tableColumn id="9" xr3:uid="{49ED1251-337D-EC49-A858-207AB60B673C}" name="Grupo" dataDxfId="40" dataCellStyle="Millares"/>
+    <tableColumn id="10" xr3:uid="{26692A66-EA2C-DD40-AAC8-07A5FE32BC7D}" name="Vida Individual" dataDxfId="39" dataCellStyle="Millares"/>
+    <tableColumn id="11" xr3:uid="{45DC445E-D43B-394B-91CD-B3001CC307CC}" name="Vida G&amp;C" dataDxfId="38" dataCellStyle="Millares"/>
+    <tableColumn id="12" xr3:uid="{953B1F2A-AB88-8A40-B82F-B5DBE8FAEA70}" name="Segudescuento" dataDxfId="37" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{27E03CF4-3925-2045-BF66-C5BB1ECC7061}" name="Aportaciones Adicionales (AVEs)" dataDxfId="36" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{7375183C-90AB-0B47-A516-65079E7802F1}" name="Cancelacion de Pólizas" dataDxfId="35" dataCellStyle="Millares"/>
+    <tableColumn id="15" xr3:uid="{B0F3DBFB-9B00-894E-8929-BF5CA63336C6}" name="Total de Productos Ilimitados" dataDxfId="34" dataCellStyle="Millares"/>
+    <tableColumn id="16" xr3:uid="{3C9D5C71-B64C-434C-8D65-968245DAE09C}" name="%Vida vs Meta" dataDxfId="33" dataCellStyle="Porcentaje"/>
+    <tableColumn id="17" xr3:uid="{088A86A3-8B28-DE4E-A384-CA0EA913DA34}" name="GMM Individual" dataDxfId="32" dataCellStyle="Millares"/>
+    <tableColumn id="18" xr3:uid="{A8791E9D-69D9-C844-AE4C-8AEEFA976B8B}" name="GMM G&amp;C" dataDxfId="31" dataCellStyle="Millares"/>
+    <tableColumn id="19" xr3:uid="{0FFCB5A1-F8D9-2344-9DC7-667454959C98}" name="Cancelacion de Pólizas2" dataDxfId="30" dataCellStyle="Millares"/>
+    <tableColumn id="20" xr3:uid="{FDCA43A0-92B9-954B-B283-ABAD7C194405}" name="Total Productos Limitados" dataDxfId="29" dataCellStyle="Millares"/>
+    <tableColumn id="21" xr3:uid="{7C93BB8B-9213-EA49-A648-EF5192999BF7}" name="Tope personales" dataDxfId="28" dataCellStyle="Millares"/>
+    <tableColumn id="22" xr3:uid="{70D3FAB6-79FB-994B-AB69-F0BBB15C6AFD}" name="Total Prima" dataDxfId="27" dataCellStyle="Millares"/>
+    <tableColumn id="23" xr3:uid="{0E0D17EB-06B5-AF45-9773-7D3921FC5B9C}" name="Vida Individual3" dataDxfId="26" dataCellStyle="Millares"/>
+    <tableColumn id="24" xr3:uid="{2A25EC7F-F387-9948-8D9A-38BFD2316AB4}" name="Vida G&amp;C4" dataDxfId="25" dataCellStyle="Millares"/>
+    <tableColumn id="25" xr3:uid="{F7E8005C-762C-7146-A541-3589C41B3DA2}" name="Segudescuento5" dataDxfId="24" dataCellStyle="Millares"/>
+    <tableColumn id="26" xr3:uid="{278BB65E-357A-1D4C-B1D0-5880BBD354CD}" name="Aportaciones Adicionales (AVEs)6" dataDxfId="23" dataCellStyle="Millares"/>
+    <tableColumn id="27" xr3:uid="{0490A388-0C84-C043-A7E8-E5DC8A03AF3F}" name="Cancelacion de Pólizas7" dataDxfId="22" dataCellStyle="Millares"/>
+    <tableColumn id="28" xr3:uid="{C06E1BE2-8968-A045-B8AB-E420B9B469A1}" name="Total de Productos Ilimitados8" dataDxfId="21" dataCellStyle="Millares"/>
+    <tableColumn id="29" xr3:uid="{BEBE08BA-F641-3141-BCA9-713FD1C7CEC2}" name="%Vida vs Meta9" dataDxfId="20" dataCellStyle="Porcentaje"/>
+    <tableColumn id="30" xr3:uid="{E7FB912B-27FD-1345-845F-E51E648031F5}" name="GMM Individual10" dataDxfId="19" dataCellStyle="Millares"/>
+    <tableColumn id="31" xr3:uid="{D5FF299C-A405-CE44-B4CD-CED400EFE81F}" name="GMM G&amp;C11" dataDxfId="18" dataCellStyle="Millares"/>
+    <tableColumn id="32" xr3:uid="{D7EFF89B-8E34-EA46-B72C-61EE3166E416}" name="Cancelacion de Pólizas12" dataDxfId="17" dataCellStyle="Millares"/>
+    <tableColumn id="33" xr3:uid="{81E1798B-3D20-E748-BDAB-7A2A6F5BF33B}" name="Total Productos Limitados13" dataDxfId="16" dataCellStyle="Millares"/>
+    <tableColumn id="34" xr3:uid="{7A820362-E31F-4D41-B400-9AD11AE00577}" name="Tope personales14" dataDxfId="15" dataCellStyle="Millares"/>
+    <tableColumn id="35" xr3:uid="{09E5F95B-08D0-B946-B14E-3F06BC9C57F0}" name="Total Comisión" dataDxfId="14" dataCellStyle="Millares"/>
+    <tableColumn id="36" xr3:uid="{523C81DC-6FA9-A24D-AF9B-9D74B552A8BA}" name="Columna15" dataDxfId="13" dataCellStyle="Millares"/>
+    <tableColumn id="37" xr3:uid="{ACF68D6F-CC4F-F94A-A3AE-C7407A1AC3DE}" name="Camino Prima" dataDxfId="12" dataCellStyle="Millares"/>
+    <tableColumn id="38" xr3:uid="{39FE9301-7AE9-0A42-B79D-CA4998AB76AE}" name="OBSERVACIÓN" dataDxfId="11" dataCellStyle="Millares"/>
+    <tableColumn id="39" xr3:uid="{99E25200-803C-E54D-88BD-27CB86CAED40}" name="Camino  Comisión" dataDxfId="10" dataCellStyle="Millares"/>
+    <tableColumn id="40" xr3:uid="{45B29C50-720D-8F4E-9803-310BA4AC814E}" name="NIVEL_x000a_" dataDxfId="9" dataCellStyle="Millares"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2269,7 +2366,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{19EA010B-EC8A-2245-B887-9FC4562CE2C9}">
-  <dimension ref="A1:AN53"/>
+  <dimension ref="A1:AN54"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.33203125" customWidth="1"/>
@@ -2505,7 +2602,7 @@
         <v>30</v>
       </c>
       <c r="J6" s="30">
-        <v>550040.93999999994</v>
+        <v>657188.18000000005</v>
       </c>
       <c r="K6" s="30">
         <v>0</v>
@@ -2514,19 +2611,19 @@
         <v>0</v>
       </c>
       <c r="M6" s="31">
-        <v>113328.4</v>
+        <v>113674.97</v>
       </c>
       <c r="N6" s="31">
         <v>0</v>
       </c>
       <c r="O6" s="29">
-        <v>663369.34</v>
+        <v>770863.15</v>
       </c>
       <c r="P6" s="32">
-        <v>0.3664</v>
+        <v>0.42580000000000001</v>
       </c>
       <c r="Q6" s="30">
-        <v>338670.94</v>
+        <v>376735.9</v>
       </c>
       <c r="R6" s="30">
         <v>0</v>
@@ -2535,16 +2632,16 @@
         <v>13875</v>
       </c>
       <c r="T6" s="29">
-        <v>324795.94</v>
+        <v>362860.9</v>
       </c>
       <c r="U6" s="29">
         <v>0</v>
       </c>
       <c r="V6" s="29">
-        <v>988165.28</v>
+        <v>1133724.05</v>
       </c>
       <c r="W6" s="29">
-        <v>192846.25</v>
+        <v>233809.61</v>
       </c>
       <c r="X6" s="29">
         <v>0</v>
@@ -2553,19 +2650,19 @@
         <v>0</v>
       </c>
       <c r="Z6" s="31">
-        <v>6414.89</v>
+        <v>6440.93</v>
       </c>
       <c r="AA6" s="31">
         <v>0</v>
       </c>
       <c r="AB6" s="29">
-        <v>199261.14</v>
+        <v>240250.54</v>
       </c>
       <c r="AC6" s="32">
-        <v>0.22009999999999999</v>
+        <v>0.26540000000000002</v>
       </c>
       <c r="AD6" s="29">
-        <v>73124.62</v>
+        <v>79391.66</v>
       </c>
       <c r="AE6" s="29">
         <v>0</v>
@@ -2574,13 +2671,13 @@
         <v>2848</v>
       </c>
       <c r="AG6" s="29">
-        <v>70276.62</v>
+        <v>76543.66</v>
       </c>
       <c r="AH6" s="29">
         <v>0</v>
       </c>
       <c r="AI6" s="29">
-        <v>269537.76</v>
+        <v>316794.2</v>
       </c>
       <c r="AJ6" s="33" t="s">
         <v>31</v>
@@ -2627,7 +2724,7 @@
         <v>30</v>
       </c>
       <c r="J7" s="30">
-        <v>200525.76</v>
+        <v>268554.28999999998</v>
       </c>
       <c r="K7" s="30">
         <v>0</v>
@@ -2636,16 +2733,16 @@
         <v>0</v>
       </c>
       <c r="M7" s="31">
-        <v>88228.15</v>
+        <v>88915.68</v>
       </c>
       <c r="N7" s="31">
         <v>0</v>
       </c>
       <c r="O7" s="29">
-        <v>288753.90999999997</v>
+        <v>357469.97</v>
       </c>
       <c r="P7" s="32">
-        <v>0.1595</v>
+        <v>0.19750000000000001</v>
       </c>
       <c r="Q7" s="30">
         <v>0</v>
@@ -2663,10 +2760,10 @@
         <v>0</v>
       </c>
       <c r="V7" s="29">
-        <v>288753.90999999997</v>
+        <v>357469.97</v>
       </c>
       <c r="W7" s="29">
-        <v>53337.3</v>
+        <v>78904.41</v>
       </c>
       <c r="X7" s="29">
         <v>0</v>
@@ -2675,16 +2772,16 @@
         <v>0</v>
       </c>
       <c r="Z7" s="31">
-        <v>5364.22</v>
+        <v>5426.88</v>
       </c>
       <c r="AA7" s="31">
         <v>0</v>
       </c>
       <c r="AB7" s="29">
-        <v>58701.52</v>
+        <v>84331.29</v>
       </c>
       <c r="AC7" s="32">
-        <v>6.4799999999999996E-2</v>
+        <v>9.3200000000000005E-2</v>
       </c>
       <c r="AD7" s="29">
         <v>0</v>
@@ -2702,7 +2799,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="29">
-        <v>58701.52</v>
+        <v>84331.29</v>
       </c>
       <c r="AJ7" s="33" t="s">
         <v>47</v>
@@ -2741,7 +2838,7 @@
         <v>30</v>
       </c>
       <c r="J8" s="30">
-        <v>127806.03</v>
+        <v>150082.06</v>
       </c>
       <c r="K8" s="30">
         <v>0</v>
@@ -2750,16 +2847,16 @@
         <v>0</v>
       </c>
       <c r="M8" s="31">
-        <v>1020.54</v>
+        <v>1265.23</v>
       </c>
       <c r="N8" s="31">
         <v>0</v>
       </c>
       <c r="O8" s="29">
-        <v>128826.57</v>
+        <v>151347.29</v>
       </c>
       <c r="P8" s="32">
-        <v>7.1199999999999999E-2</v>
+        <v>8.3599999999999994E-2</v>
       </c>
       <c r="Q8" s="30">
         <v>145683.81</v>
@@ -2777,10 +2874,10 @@
         <v>0</v>
       </c>
       <c r="V8" s="29">
-        <v>274510.38</v>
+        <v>297031.09999999998</v>
       </c>
       <c r="W8" s="29">
-        <v>45752.84</v>
+        <v>52498.91</v>
       </c>
       <c r="X8" s="29">
         <v>0</v>
@@ -2789,16 +2886,16 @@
         <v>0</v>
       </c>
       <c r="Z8" s="31">
-        <v>122.99</v>
+        <v>155.62</v>
       </c>
       <c r="AA8" s="31">
         <v>0</v>
       </c>
       <c r="AB8" s="29">
-        <v>45875.83</v>
+        <v>52654.53</v>
       </c>
       <c r="AC8" s="32">
-        <v>5.0700000000000002E-2</v>
+        <v>5.8200000000000002E-2</v>
       </c>
       <c r="AD8" s="29">
         <v>21216.080000000002</v>
@@ -2816,7 +2913,7 @@
         <v>0</v>
       </c>
       <c r="AI8" s="29">
-        <v>67091.91</v>
+        <v>73870.61</v>
       </c>
       <c r="AJ8" s="33" t="s">
         <v>63</v>
@@ -3083,7 +3180,7 @@
         <v>30</v>
       </c>
       <c r="J11" s="30">
-        <v>111482.82</v>
+        <v>139052.07</v>
       </c>
       <c r="K11" s="30">
         <v>0</v>
@@ -3098,10 +3195,10 @@
         <v>0</v>
       </c>
       <c r="O11" s="29">
-        <v>113774.64</v>
+        <v>141343.89000000001</v>
       </c>
       <c r="P11" s="32">
-        <v>6.2799999999999995E-2</v>
+        <v>7.8100000000000003E-2</v>
       </c>
       <c r="Q11" s="30">
         <v>64612.59</v>
@@ -3119,10 +3216,10 @@
         <v>0</v>
       </c>
       <c r="V11" s="29">
-        <v>178387.23</v>
+        <v>205956.48000000001</v>
       </c>
       <c r="W11" s="29">
-        <v>30100.36</v>
+        <v>38371.129999999997</v>
       </c>
       <c r="X11" s="29">
         <v>0</v>
@@ -3131,16 +3228,16 @@
         <v>0</v>
       </c>
       <c r="Z11" s="31">
-        <v>569.19000000000005</v>
+        <v>592.97</v>
       </c>
       <c r="AA11" s="31">
         <v>0</v>
       </c>
       <c r="AB11" s="29">
-        <v>30669.55</v>
+        <v>38964.1</v>
       </c>
       <c r="AC11" s="32">
-        <v>3.39E-2</v>
+        <v>4.2999999999999997E-2</v>
       </c>
       <c r="AD11" s="29">
         <v>11978.48</v>
@@ -3158,7 +3255,7 @@
         <v>0</v>
       </c>
       <c r="AI11" s="29">
-        <v>42648.03</v>
+        <v>50942.58</v>
       </c>
       <c r="AJ11" s="33" t="s">
         <v>37</v>
@@ -3185,19 +3282,19 @@
         <v>28</v>
       </c>
       <c r="F12" s="27">
-        <v>90355</v>
+        <v>47116</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>38</v>
+        <v>50</v>
       </c>
       <c r="H12" s="28">
-        <v>43949</v>
+        <v>44616</v>
       </c>
       <c r="I12" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J12" s="30">
-        <v>126885.75999999999</v>
+        <v>97248.639999999999</v>
       </c>
       <c r="K12" s="30">
         <v>0</v>
@@ -3206,19 +3303,19 @@
         <v>0</v>
       </c>
       <c r="M12" s="31">
-        <v>22390.68</v>
+        <v>5898.33</v>
       </c>
       <c r="N12" s="31">
         <v>0</v>
       </c>
       <c r="O12" s="29">
-        <v>149276.44</v>
+        <v>103146.97</v>
       </c>
       <c r="P12" s="32">
-        <v>8.2500000000000004E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="Q12" s="30">
-        <v>0</v>
+        <v>50792.35</v>
       </c>
       <c r="R12" s="30">
         <v>0</v>
@@ -3227,16 +3324,16 @@
         <v>0</v>
       </c>
       <c r="T12" s="29">
-        <v>0</v>
+        <v>50792.35</v>
       </c>
       <c r="U12" s="29">
         <v>0</v>
       </c>
       <c r="V12" s="29">
-        <v>149276.44</v>
+        <v>153939.32</v>
       </c>
       <c r="W12" s="29">
-        <v>50742.080000000002</v>
+        <v>30947.200000000001</v>
       </c>
       <c r="X12" s="29">
         <v>0</v>
@@ -3245,19 +3342,19 @@
         <v>0</v>
       </c>
       <c r="Z12" s="31">
-        <v>1235</v>
+        <v>948.02</v>
       </c>
       <c r="AA12" s="31">
         <v>0</v>
       </c>
       <c r="AB12" s="29">
-        <v>51977.08</v>
+        <v>31895.22</v>
       </c>
       <c r="AC12" s="32">
-        <v>5.74E-2</v>
+        <v>3.5200000000000002E-2</v>
       </c>
       <c r="AD12" s="29">
-        <v>0</v>
+        <v>9868.51</v>
       </c>
       <c r="AE12" s="29">
         <v>0</v>
@@ -3266,16 +3363,16 @@
         <v>0</v>
       </c>
       <c r="AG12" s="29">
-        <v>0</v>
+        <v>9868.51</v>
       </c>
       <c r="AH12" s="29">
         <v>0</v>
       </c>
       <c r="AI12" s="29">
-        <v>51977.08</v>
+        <v>41763.730000000003</v>
       </c>
       <c r="AJ12" s="33" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="AK12" s="34"/>
       <c r="AL12" s="34"/>
@@ -3293,25 +3390,25 @@
         <v>2043</v>
       </c>
       <c r="D13" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F13" s="27">
-        <v>104718</v>
+        <v>90355</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="H13" s="28">
-        <v>45264</v>
+        <v>43949</v>
       </c>
       <c r="I13" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J13" s="30">
-        <v>112348.82</v>
+        <v>126885.75999999999</v>
       </c>
       <c r="K13" s="30">
         <v>0</v>
@@ -3320,19 +3417,19 @@
         <v>0</v>
       </c>
       <c r="M13" s="31">
-        <v>2640.94</v>
+        <v>22390.68</v>
       </c>
       <c r="N13" s="31">
         <v>0</v>
       </c>
       <c r="O13" s="29">
-        <v>114989.75999999999</v>
+        <v>149276.44</v>
       </c>
       <c r="P13" s="32">
-        <v>6.3500000000000001E-2</v>
+        <v>8.2500000000000004E-2</v>
       </c>
       <c r="Q13" s="30">
-        <v>31773.599999999999</v>
+        <v>0</v>
       </c>
       <c r="R13" s="30">
         <v>0</v>
@@ -3341,16 +3438,16 @@
         <v>0</v>
       </c>
       <c r="T13" s="29">
-        <v>31773.599999999999</v>
+        <v>0</v>
       </c>
       <c r="U13" s="29">
         <v>0</v>
       </c>
       <c r="V13" s="29">
-        <v>146763.35999999999</v>
+        <v>149276.44</v>
       </c>
       <c r="W13" s="29">
-        <v>34992.42</v>
+        <v>50742.080000000002</v>
       </c>
       <c r="X13" s="29">
         <v>0</v>
@@ -3359,19 +3456,19 @@
         <v>0</v>
       </c>
       <c r="Z13" s="31">
-        <v>275.58</v>
+        <v>1235</v>
       </c>
       <c r="AA13" s="31">
         <v>0</v>
       </c>
       <c r="AB13" s="29">
-        <v>35268</v>
+        <v>51977.08</v>
       </c>
       <c r="AC13" s="32">
-        <v>3.9E-2</v>
+        <v>5.74E-2</v>
       </c>
       <c r="AD13" s="29">
-        <v>6601.68</v>
+        <v>0</v>
       </c>
       <c r="AE13" s="29">
         <v>0</v>
@@ -3380,16 +3477,16 @@
         <v>0</v>
       </c>
       <c r="AG13" s="29">
-        <v>6601.68</v>
+        <v>0</v>
       </c>
       <c r="AH13" s="29">
         <v>0</v>
       </c>
       <c r="AI13" s="29">
-        <v>41869.68</v>
+        <v>51977.08</v>
       </c>
       <c r="AJ13" s="33" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="AK13" s="34"/>
       <c r="AL13" s="34"/>
@@ -3407,25 +3504,25 @@
         <v>2043</v>
       </c>
       <c r="D14" s="26">
-        <v>2856</v>
+        <v>2692</v>
       </c>
       <c r="E14" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F14" s="27">
-        <v>115047</v>
+        <v>104718</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="H14" s="28">
-        <v>45944</v>
+        <v>45264</v>
       </c>
       <c r="I14" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J14" s="30">
-        <v>24598.61</v>
+        <v>112348.82</v>
       </c>
       <c r="K14" s="30">
         <v>0</v>
@@ -3434,19 +3531,19 @@
         <v>0</v>
       </c>
       <c r="M14" s="31">
-        <v>701.1</v>
+        <v>2640.94</v>
       </c>
       <c r="N14" s="31">
         <v>0</v>
       </c>
       <c r="O14" s="29">
-        <v>76619.839999999997</v>
+        <v>114989.75999999999</v>
       </c>
       <c r="P14" s="32">
-        <v>4.2299999999999997E-2</v>
+        <v>6.3500000000000001E-2</v>
       </c>
       <c r="Q14" s="30">
-        <v>40110.959999999999</v>
+        <v>31773.599999999999</v>
       </c>
       <c r="R14" s="30">
         <v>0</v>
@@ -3455,16 +3552,16 @@
         <v>0</v>
       </c>
       <c r="T14" s="29">
-        <v>49236.79</v>
+        <v>31773.599999999999</v>
       </c>
       <c r="U14" s="29">
-        <v>60445.96</v>
+        <v>0</v>
       </c>
       <c r="V14" s="29">
-        <v>125856.63</v>
+        <v>146763.35999999999</v>
       </c>
       <c r="W14" s="29">
-        <v>7564.38</v>
+        <v>34992.42</v>
       </c>
       <c r="X14" s="29">
         <v>0</v>
@@ -3473,19 +3570,19 @@
         <v>0</v>
       </c>
       <c r="Z14" s="31">
-        <v>93.49</v>
+        <v>275.58</v>
       </c>
       <c r="AA14" s="31">
         <v>0</v>
       </c>
       <c r="AB14" s="29">
-        <v>23053.91</v>
+        <v>35268</v>
       </c>
       <c r="AC14" s="32">
-        <v>2.5499999999999998E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="AD14" s="29">
-        <v>8472.36</v>
+        <v>6601.68</v>
       </c>
       <c r="AE14" s="29">
         <v>0</v>
@@ -3494,16 +3591,16 @@
         <v>0</v>
       </c>
       <c r="AG14" s="29">
-        <v>10021.94</v>
+        <v>6601.68</v>
       </c>
       <c r="AH14" s="29">
-        <v>16945.62</v>
+        <v>0</v>
       </c>
       <c r="AI14" s="29">
-        <v>33075.85</v>
+        <v>41869.68</v>
       </c>
       <c r="AJ14" s="33" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="AK14" s="34"/>
       <c r="AL14" s="34"/>
@@ -3521,25 +3618,25 @@
         <v>2043</v>
       </c>
       <c r="D15" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E15" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F15" s="27">
-        <v>47116</v>
+        <v>115047</v>
       </c>
       <c r="G15" s="25" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="H15" s="28">
-        <v>44616</v>
+        <v>45944</v>
       </c>
       <c r="I15" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J15" s="30">
-        <v>61796.57</v>
+        <v>24598.61</v>
       </c>
       <c r="K15" s="30">
         <v>0</v>
@@ -3548,19 +3645,19 @@
         <v>0</v>
       </c>
       <c r="M15" s="31">
-        <v>5030</v>
+        <v>841.61</v>
       </c>
       <c r="N15" s="31">
         <v>0</v>
       </c>
       <c r="O15" s="29">
-        <v>66826.570000000007</v>
+        <v>76760.350000000006</v>
       </c>
       <c r="P15" s="32">
-        <v>3.6900000000000002E-2</v>
+        <v>4.24E-2</v>
       </c>
       <c r="Q15" s="30">
-        <v>50792.35</v>
+        <v>40110.959999999999</v>
       </c>
       <c r="R15" s="30">
         <v>0</v>
@@ -3569,16 +3666,16 @@
         <v>0</v>
       </c>
       <c r="T15" s="29">
-        <v>50792.35</v>
+        <v>49236.79</v>
       </c>
       <c r="U15" s="29">
-        <v>0</v>
+        <v>60445.96</v>
       </c>
       <c r="V15" s="29">
-        <v>117618.92</v>
+        <v>125997.14</v>
       </c>
       <c r="W15" s="29">
-        <v>18538.98</v>
+        <v>7564.38</v>
       </c>
       <c r="X15" s="29">
         <v>0</v>
@@ -3587,19 +3684,19 @@
         <v>0</v>
       </c>
       <c r="Z15" s="31">
-        <v>796.1</v>
+        <v>112.23</v>
       </c>
       <c r="AA15" s="31">
         <v>0</v>
       </c>
       <c r="AB15" s="29">
-        <v>19335.080000000002</v>
+        <v>23072.65</v>
       </c>
       <c r="AC15" s="32">
-        <v>2.1399999999999999E-2</v>
+        <v>2.5499999999999998E-2</v>
       </c>
       <c r="AD15" s="29">
-        <v>9868.51</v>
+        <v>8472.36</v>
       </c>
       <c r="AE15" s="29">
         <v>0</v>
@@ -3608,16 +3705,16 @@
         <v>0</v>
       </c>
       <c r="AG15" s="29">
-        <v>9868.51</v>
+        <v>10021.94</v>
       </c>
       <c r="AH15" s="29">
-        <v>0</v>
+        <v>16945.62</v>
       </c>
       <c r="AI15" s="29">
-        <v>29203.59</v>
+        <v>33094.589999999997</v>
       </c>
       <c r="AJ15" s="33" t="s">
-        <v>51</v>
+        <v>45</v>
       </c>
       <c r="AK15" s="34"/>
       <c r="AL15" s="34"/>
@@ -3635,25 +3732,25 @@
         <v>2043</v>
       </c>
       <c r="D16" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E16" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F16" s="27">
-        <v>115404</v>
+        <v>116876</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>60</v>
+        <v>141</v>
       </c>
       <c r="H16" s="28">
-        <v>45986</v>
+        <v>46111</v>
       </c>
       <c r="I16" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J16" s="30">
-        <v>29852.74</v>
+        <v>118805.62</v>
       </c>
       <c r="K16" s="30">
         <v>0</v>
@@ -3668,13 +3765,13 @@
         <v>0</v>
       </c>
       <c r="O16" s="29">
-        <v>29852.74</v>
+        <v>118805.62</v>
       </c>
       <c r="P16" s="32">
-        <v>1.6500000000000001E-2</v>
+        <v>6.5600000000000006E-2</v>
       </c>
       <c r="Q16" s="30">
-        <v>79361.350000000006</v>
+        <v>5150.32</v>
       </c>
       <c r="R16" s="30">
         <v>0</v>
@@ -3683,16 +3780,16 @@
         <v>0</v>
       </c>
       <c r="T16" s="29">
-        <v>79361.350000000006</v>
+        <v>5150.32</v>
       </c>
       <c r="U16" s="29">
         <v>0</v>
       </c>
       <c r="V16" s="29">
-        <v>109214.09</v>
+        <v>123955.94</v>
       </c>
       <c r="W16" s="29">
-        <v>10448.459999999999</v>
+        <v>33860.04</v>
       </c>
       <c r="X16" s="29">
         <v>0</v>
@@ -3707,13 +3804,13 @@
         <v>0</v>
       </c>
       <c r="AB16" s="29">
-        <v>10448.459999999999</v>
+        <v>33860.04</v>
       </c>
       <c r="AC16" s="32">
-        <v>1.15E-2</v>
+        <v>3.7400000000000003E-2</v>
       </c>
       <c r="AD16" s="29">
-        <v>16033.12</v>
+        <v>752.44</v>
       </c>
       <c r="AE16" s="29">
         <v>0</v>
@@ -3722,16 +3819,16 @@
         <v>0</v>
       </c>
       <c r="AG16" s="29">
-        <v>16033.12</v>
+        <v>752.44</v>
       </c>
       <c r="AH16" s="29">
         <v>0</v>
       </c>
       <c r="AI16" s="29">
-        <v>26481.58</v>
+        <v>34612.480000000003</v>
       </c>
       <c r="AJ16" s="33" t="s">
-        <v>61</v>
+        <v>142</v>
       </c>
       <c r="AK16" s="34"/>
       <c r="AL16" s="34"/>
@@ -3755,19 +3852,19 @@
         <v>28</v>
       </c>
       <c r="F17" s="27">
-        <v>107488</v>
+        <v>115404</v>
       </c>
       <c r="G17" s="25" t="s">
-        <v>48</v>
+        <v>60</v>
       </c>
       <c r="H17" s="28">
-        <v>45440</v>
+        <v>45986</v>
       </c>
       <c r="I17" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J17" s="30">
-        <v>0</v>
+        <v>29852.74</v>
       </c>
       <c r="K17" s="30">
         <v>0</v>
@@ -3776,19 +3873,19 @@
         <v>0</v>
       </c>
       <c r="M17" s="31">
-        <v>157.72</v>
+        <v>0</v>
       </c>
       <c r="N17" s="31">
         <v>0</v>
       </c>
       <c r="O17" s="29">
-        <v>157.72</v>
+        <v>29852.74</v>
       </c>
       <c r="P17" s="32">
-        <v>1E-4</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="Q17" s="30">
-        <v>98471.17</v>
+        <v>79361.350000000006</v>
       </c>
       <c r="R17" s="30">
         <v>0</v>
@@ -3797,16 +3894,16 @@
         <v>0</v>
       </c>
       <c r="T17" s="29">
-        <v>98471.17</v>
+        <v>79361.350000000006</v>
       </c>
       <c r="U17" s="29">
         <v>0</v>
       </c>
       <c r="V17" s="29">
-        <v>98628.89</v>
+        <v>109214.09</v>
       </c>
       <c r="W17" s="29">
-        <v>0</v>
+        <v>10448.459999999999</v>
       </c>
       <c r="X17" s="29">
         <v>0</v>
@@ -3815,19 +3912,19 @@
         <v>0</v>
       </c>
       <c r="Z17" s="31">
-        <v>21.03</v>
+        <v>0</v>
       </c>
       <c r="AA17" s="31">
         <v>0</v>
       </c>
       <c r="AB17" s="29">
-        <v>21.03</v>
+        <v>10448.459999999999</v>
       </c>
       <c r="AC17" s="32">
-        <v>0</v>
+        <v>1.15E-2</v>
       </c>
       <c r="AD17" s="29">
-        <v>21311.65</v>
+        <v>16033.12</v>
       </c>
       <c r="AE17" s="29">
         <v>0</v>
@@ -3836,16 +3933,16 @@
         <v>0</v>
       </c>
       <c r="AG17" s="29">
-        <v>21311.65</v>
+        <v>16033.12</v>
       </c>
       <c r="AH17" s="29">
         <v>0</v>
       </c>
       <c r="AI17" s="29">
-        <v>21332.68</v>
+        <v>26481.58</v>
       </c>
       <c r="AJ17" s="33" t="s">
-        <v>49</v>
+        <v>61</v>
       </c>
       <c r="AK17" s="34"/>
       <c r="AL17" s="34"/>
@@ -3863,25 +3960,25 @@
         <v>2043</v>
       </c>
       <c r="D18" s="26">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E18" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F18" s="27">
-        <v>116060</v>
+        <v>107488</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="H18" s="28">
-        <v>46010</v>
+        <v>45440</v>
       </c>
       <c r="I18" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J18" s="30">
-        <v>21769.200000000001</v>
+        <v>0</v>
       </c>
       <c r="K18" s="30">
         <v>0</v>
@@ -3890,19 +3987,19 @@
         <v>0</v>
       </c>
       <c r="M18" s="31">
-        <v>0</v>
+        <v>157.72</v>
       </c>
       <c r="N18" s="31">
         <v>0</v>
       </c>
       <c r="O18" s="29">
-        <v>52038.66</v>
+        <v>157.72</v>
       </c>
       <c r="P18" s="32">
-        <v>2.87E-2</v>
+        <v>1E-4</v>
       </c>
       <c r="Q18" s="30">
-        <v>30604.240000000002</v>
+        <v>98471.17</v>
       </c>
       <c r="R18" s="30">
         <v>0</v>
@@ -3911,16 +4008,16 @@
         <v>0</v>
       </c>
       <c r="T18" s="29">
-        <v>30604.240000000002</v>
+        <v>98471.17</v>
       </c>
       <c r="U18" s="29">
-        <v>30269.46</v>
+        <v>0</v>
       </c>
       <c r="V18" s="29">
-        <v>82642.899999999994</v>
+        <v>98628.89</v>
       </c>
       <c r="W18" s="29">
-        <v>6774.12</v>
+        <v>0</v>
       </c>
       <c r="X18" s="29">
         <v>0</v>
@@ -3929,19 +4026,19 @@
         <v>0</v>
       </c>
       <c r="Z18" s="31">
-        <v>0</v>
+        <v>21.03</v>
       </c>
       <c r="AA18" s="31">
         <v>0</v>
       </c>
       <c r="AB18" s="29">
-        <v>16652.57</v>
+        <v>21.03</v>
       </c>
       <c r="AC18" s="32">
-        <v>1.84E-2</v>
+        <v>0</v>
       </c>
       <c r="AD18" s="29">
-        <v>6397.42</v>
+        <v>21311.65</v>
       </c>
       <c r="AE18" s="29">
         <v>0</v>
@@ -3950,16 +4047,16 @@
         <v>0</v>
       </c>
       <c r="AG18" s="29">
-        <v>6397.42</v>
+        <v>21311.65</v>
       </c>
       <c r="AH18" s="29">
-        <v>9878.4500000000007</v>
+        <v>0</v>
       </c>
       <c r="AI18" s="29">
-        <v>23049.99</v>
+        <v>21332.68</v>
       </c>
       <c r="AJ18" s="33" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="AK18" s="34"/>
       <c r="AL18" s="34"/>
@@ -3977,25 +4074,25 @@
         <v>2043</v>
       </c>
       <c r="D19" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E19" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F19" s="27">
-        <v>105696</v>
+        <v>116060</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H19" s="28">
-        <v>45279</v>
+        <v>46010</v>
       </c>
       <c r="I19" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J19" s="30">
-        <v>62837.82</v>
+        <v>21769.200000000001</v>
       </c>
       <c r="K19" s="30">
         <v>0</v>
@@ -4004,19 +4101,19 @@
         <v>0</v>
       </c>
       <c r="M19" s="31">
-        <v>1354.39</v>
+        <v>0</v>
       </c>
       <c r="N19" s="31">
         <v>0</v>
       </c>
       <c r="O19" s="29">
-        <v>64192.21</v>
+        <v>52038.66</v>
       </c>
       <c r="P19" s="32">
-        <v>3.5499999999999997E-2</v>
+        <v>2.87E-2</v>
       </c>
       <c r="Q19" s="30">
-        <v>16178.04</v>
+        <v>30604.240000000002</v>
       </c>
       <c r="R19" s="30">
         <v>0</v>
@@ -4025,16 +4122,16 @@
         <v>0</v>
       </c>
       <c r="T19" s="29">
-        <v>16178.04</v>
+        <v>30604.240000000002</v>
       </c>
       <c r="U19" s="29">
-        <v>0</v>
+        <v>30269.46</v>
       </c>
       <c r="V19" s="29">
-        <v>80370.25</v>
+        <v>82642.899999999994</v>
       </c>
       <c r="W19" s="29">
-        <v>20942.14</v>
+        <v>6774.12</v>
       </c>
       <c r="X19" s="29">
         <v>0</v>
@@ -4043,19 +4140,19 @@
         <v>0</v>
       </c>
       <c r="Z19" s="31">
-        <v>112.4</v>
+        <v>0</v>
       </c>
       <c r="AA19" s="31">
         <v>0</v>
       </c>
       <c r="AB19" s="29">
-        <v>21054.54</v>
+        <v>16652.57</v>
       </c>
       <c r="AC19" s="32">
-        <v>2.3300000000000001E-2</v>
+        <v>1.84E-2</v>
       </c>
       <c r="AD19" s="29">
-        <v>3240.17</v>
+        <v>6397.42</v>
       </c>
       <c r="AE19" s="29">
         <v>0</v>
@@ -4064,16 +4161,16 @@
         <v>0</v>
       </c>
       <c r="AG19" s="29">
-        <v>3240.17</v>
+        <v>6397.42</v>
       </c>
       <c r="AH19" s="29">
-        <v>0</v>
+        <v>9878.4500000000007</v>
       </c>
       <c r="AI19" s="29">
-        <v>24294.71</v>
+        <v>23049.99</v>
       </c>
       <c r="AJ19" s="33" t="s">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="AK19" s="34"/>
       <c r="AL19" s="34"/>
@@ -4091,25 +4188,25 @@
         <v>2043</v>
       </c>
       <c r="D20" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E20" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="27">
-        <v>108404</v>
+        <v>105696</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>56</v>
+        <v>68</v>
       </c>
       <c r="H20" s="28">
-        <v>45467</v>
+        <v>45279</v>
       </c>
       <c r="I20" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J20" s="30">
-        <v>36910.69</v>
+        <v>62837.82</v>
       </c>
       <c r="K20" s="30">
         <v>0</v>
@@ -4118,19 +4215,19 @@
         <v>0</v>
       </c>
       <c r="M20" s="31">
-        <v>7677.21</v>
+        <v>1354.39</v>
       </c>
       <c r="N20" s="31">
         <v>0</v>
       </c>
       <c r="O20" s="29">
-        <v>44587.9</v>
+        <v>64192.21</v>
       </c>
       <c r="P20" s="32">
-        <v>2.46E-2</v>
+        <v>3.5499999999999997E-2</v>
       </c>
       <c r="Q20" s="30">
-        <v>27059.39</v>
+        <v>16178.04</v>
       </c>
       <c r="R20" s="30">
         <v>0</v>
@@ -4139,16 +4236,16 @@
         <v>0</v>
       </c>
       <c r="T20" s="29">
-        <v>27059.39</v>
+        <v>16178.04</v>
       </c>
       <c r="U20" s="29">
         <v>0</v>
       </c>
       <c r="V20" s="29">
-        <v>71647.289999999994</v>
+        <v>80370.25</v>
       </c>
       <c r="W20" s="29">
-        <v>11073.21</v>
+        <v>20942.14</v>
       </c>
       <c r="X20" s="29">
         <v>0</v>
@@ -4157,19 +4254,19 @@
         <v>0</v>
       </c>
       <c r="Z20" s="31">
-        <v>773.62</v>
+        <v>112.4</v>
       </c>
       <c r="AA20" s="31">
         <v>0</v>
       </c>
       <c r="AB20" s="29">
-        <v>11846.83</v>
+        <v>21054.54</v>
       </c>
       <c r="AC20" s="32">
-        <v>1.3100000000000001E-2</v>
+        <v>2.3300000000000001E-2</v>
       </c>
       <c r="AD20" s="29">
-        <v>5601.07</v>
+        <v>3240.17</v>
       </c>
       <c r="AE20" s="29">
         <v>0</v>
@@ -4178,16 +4275,16 @@
         <v>0</v>
       </c>
       <c r="AG20" s="29">
-        <v>5601.07</v>
+        <v>3240.17</v>
       </c>
       <c r="AH20" s="29">
         <v>0</v>
       </c>
       <c r="AI20" s="29">
-        <v>17447.900000000001</v>
+        <v>24294.71</v>
       </c>
       <c r="AJ20" s="33" t="s">
-        <v>57</v>
+        <v>69</v>
       </c>
       <c r="AK20" s="34"/>
       <c r="AL20" s="34"/>
@@ -4211,19 +4308,19 @@
         <v>28</v>
       </c>
       <c r="F21" s="27">
-        <v>113450</v>
+        <v>108404</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="H21" s="28">
-        <v>45852</v>
+        <v>45467</v>
       </c>
       <c r="I21" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J21" s="30">
-        <v>58035.37</v>
+        <v>36910.69</v>
       </c>
       <c r="K21" s="30">
         <v>0</v>
@@ -4232,19 +4329,19 @@
         <v>0</v>
       </c>
       <c r="M21" s="31">
-        <v>540</v>
+        <v>8522.58</v>
       </c>
       <c r="N21" s="31">
-        <v>0</v>
+        <v>1952.51</v>
       </c>
       <c r="O21" s="29">
-        <v>58575.37</v>
+        <v>43480.76</v>
       </c>
       <c r="P21" s="32">
-        <v>3.2399999999999998E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="Q21" s="30">
-        <v>0</v>
+        <v>27059.39</v>
       </c>
       <c r="R21" s="30">
         <v>0</v>
@@ -4253,16 +4350,16 @@
         <v>0</v>
       </c>
       <c r="T21" s="29">
-        <v>0</v>
+        <v>27059.39</v>
       </c>
       <c r="U21" s="29">
         <v>0</v>
       </c>
       <c r="V21" s="29">
-        <v>58575.37</v>
+        <v>70540.149999999994</v>
       </c>
       <c r="W21" s="29">
-        <v>15669.55</v>
+        <v>11073.21</v>
       </c>
       <c r="X21" s="29">
         <v>0</v>
@@ -4271,19 +4368,19 @@
         <v>0</v>
       </c>
       <c r="Z21" s="31">
-        <v>42</v>
+        <v>886.33</v>
       </c>
       <c r="AA21" s="31">
-        <v>0</v>
+        <v>529.12</v>
       </c>
       <c r="AB21" s="29">
-        <v>15711.55</v>
+        <v>11430.42</v>
       </c>
       <c r="AC21" s="32">
-        <v>1.7399999999999999E-2</v>
+        <v>1.26E-2</v>
       </c>
       <c r="AD21" s="29">
-        <v>0</v>
+        <v>5601.07</v>
       </c>
       <c r="AE21" s="29">
         <v>0</v>
@@ -4292,16 +4389,16 @@
         <v>0</v>
       </c>
       <c r="AG21" s="29">
-        <v>0</v>
+        <v>5601.07</v>
       </c>
       <c r="AH21" s="29">
         <v>0</v>
       </c>
       <c r="AI21" s="29">
-        <v>15711.55</v>
+        <v>17031.490000000002</v>
       </c>
       <c r="AJ21" s="33" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="AK21" s="34"/>
       <c r="AL21" s="34"/>
@@ -4319,25 +4416,25 @@
         <v>2043</v>
       </c>
       <c r="D22" s="26">
-        <v>2043</v>
+        <v>2692</v>
       </c>
       <c r="E22" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F22" s="27">
-        <v>102825</v>
+        <v>113450</v>
       </c>
       <c r="G22" s="25" t="s">
-        <v>84</v>
+        <v>58</v>
       </c>
       <c r="H22" s="28">
-        <v>45117</v>
+        <v>45852</v>
       </c>
       <c r="I22" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J22" s="30">
-        <v>0</v>
+        <v>58035.37</v>
       </c>
       <c r="K22" s="30">
         <v>0</v>
@@ -4346,19 +4443,19 @@
         <v>0</v>
       </c>
       <c r="M22" s="31">
-        <v>455.37</v>
+        <v>540</v>
       </c>
       <c r="N22" s="31">
         <v>0</v>
       </c>
       <c r="O22" s="29">
-        <v>455.37</v>
+        <v>58575.37</v>
       </c>
       <c r="P22" s="32">
-        <v>2.9999999999999997E-4</v>
+        <v>3.2399999999999998E-2</v>
       </c>
       <c r="Q22" s="30">
-        <v>52510.1</v>
+        <v>0</v>
       </c>
       <c r="R22" s="30">
         <v>0</v>
@@ -4367,16 +4464,16 @@
         <v>0</v>
       </c>
       <c r="T22" s="29">
-        <v>52510.1</v>
+        <v>0</v>
       </c>
       <c r="U22" s="29">
         <v>0</v>
       </c>
       <c r="V22" s="29">
-        <v>52965.47</v>
+        <v>58575.37</v>
       </c>
       <c r="W22" s="29">
-        <v>0</v>
+        <v>15669.55</v>
       </c>
       <c r="X22" s="29">
         <v>0</v>
@@ -4385,19 +4482,19 @@
         <v>0</v>
       </c>
       <c r="Z22" s="31">
-        <v>151.79</v>
+        <v>42</v>
       </c>
       <c r="AA22" s="31">
         <v>0</v>
       </c>
       <c r="AB22" s="29">
-        <v>151.79</v>
+        <v>15711.55</v>
       </c>
       <c r="AC22" s="32">
-        <v>2.0000000000000001E-4</v>
+        <v>1.7399999999999999E-2</v>
       </c>
       <c r="AD22" s="29">
-        <v>10881.11</v>
+        <v>0</v>
       </c>
       <c r="AE22" s="29">
         <v>0</v>
@@ -4406,16 +4503,16 @@
         <v>0</v>
       </c>
       <c r="AG22" s="29">
-        <v>10881.11</v>
+        <v>0</v>
       </c>
       <c r="AH22" s="29">
         <v>0</v>
       </c>
       <c r="AI22" s="29">
-        <v>11032.9</v>
+        <v>15711.55</v>
       </c>
       <c r="AJ22" s="33" t="s">
-        <v>85</v>
+        <v>59</v>
       </c>
       <c r="AK22" s="34"/>
       <c r="AL22" s="34"/>
@@ -4439,13 +4536,13 @@
         <v>28</v>
       </c>
       <c r="F23" s="27">
-        <v>88234</v>
+        <v>102825</v>
       </c>
       <c r="G23" s="25" t="s">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="H23" s="28">
-        <v>43794</v>
+        <v>45117</v>
       </c>
       <c r="I23" s="29" t="s">
         <v>30</v>
@@ -4460,19 +4557,19 @@
         <v>0</v>
       </c>
       <c r="M23" s="31">
-        <v>879.63</v>
+        <v>685.23</v>
       </c>
       <c r="N23" s="31">
         <v>0</v>
       </c>
       <c r="O23" s="29">
-        <v>879.63</v>
+        <v>685.23</v>
       </c>
       <c r="P23" s="32">
-        <v>5.0000000000000001E-4</v>
+        <v>4.0000000000000002E-4</v>
       </c>
       <c r="Q23" s="30">
-        <v>40309.919999999998</v>
+        <v>52510.1</v>
       </c>
       <c r="R23" s="30">
         <v>0</v>
@@ -4481,13 +4578,13 @@
         <v>0</v>
       </c>
       <c r="T23" s="29">
-        <v>40309.919999999998</v>
+        <v>52510.1</v>
       </c>
       <c r="U23" s="29">
         <v>0</v>
       </c>
       <c r="V23" s="29">
-        <v>41189.550000000003</v>
+        <v>53195.33</v>
       </c>
       <c r="W23" s="29">
         <v>0</v>
@@ -4499,19 +4596,19 @@
         <v>0</v>
       </c>
       <c r="Z23" s="31">
-        <v>117.28</v>
+        <v>228.41</v>
       </c>
       <c r="AA23" s="31">
         <v>0</v>
       </c>
       <c r="AB23" s="29">
-        <v>117.28</v>
+        <v>228.41</v>
       </c>
       <c r="AC23" s="32">
-        <v>1E-4</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="AD23" s="29">
-        <v>8479.68</v>
+        <v>10881.11</v>
       </c>
       <c r="AE23" s="29">
         <v>0</v>
@@ -4520,16 +4617,16 @@
         <v>0</v>
       </c>
       <c r="AG23" s="29">
-        <v>8479.68</v>
+        <v>10881.11</v>
       </c>
       <c r="AH23" s="29">
         <v>0</v>
       </c>
       <c r="AI23" s="29">
-        <v>8596.9599999999991</v>
+        <v>11109.52</v>
       </c>
       <c r="AJ23" s="33" t="s">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AK23" s="34"/>
       <c r="AL23" s="34"/>
@@ -4547,25 +4644,25 @@
         <v>2043</v>
       </c>
       <c r="D24" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E24" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F24" s="27">
-        <v>108405</v>
+        <v>88234</v>
       </c>
       <c r="G24" s="25" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="H24" s="28">
-        <v>45471</v>
+        <v>43794</v>
       </c>
       <c r="I24" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J24" s="30">
-        <v>36157.08</v>
+        <v>0</v>
       </c>
       <c r="K24" s="30">
         <v>0</v>
@@ -4574,19 +4671,19 @@
         <v>0</v>
       </c>
       <c r="M24" s="31">
-        <v>0.6</v>
+        <v>879.63</v>
       </c>
       <c r="N24" s="31">
         <v>0</v>
       </c>
       <c r="O24" s="29">
-        <v>36157.68</v>
+        <v>879.63</v>
       </c>
       <c r="P24" s="32">
-        <v>0.02</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q24" s="30">
-        <v>0</v>
+        <v>40309.919999999998</v>
       </c>
       <c r="R24" s="30">
         <v>0</v>
@@ -4595,16 +4692,16 @@
         <v>0</v>
       </c>
       <c r="T24" s="29">
-        <v>0</v>
+        <v>40309.919999999998</v>
       </c>
       <c r="U24" s="29">
         <v>0</v>
       </c>
       <c r="V24" s="29">
-        <v>36157.68</v>
+        <v>41189.550000000003</v>
       </c>
       <c r="W24" s="29">
-        <v>10847.12</v>
+        <v>0</v>
       </c>
       <c r="X24" s="29">
         <v>0</v>
@@ -4613,19 +4710,19 @@
         <v>0</v>
       </c>
       <c r="Z24" s="31">
-        <v>0.08</v>
+        <v>117.28</v>
       </c>
       <c r="AA24" s="31">
         <v>0</v>
       </c>
       <c r="AB24" s="29">
-        <v>10847.2</v>
+        <v>117.28</v>
       </c>
       <c r="AC24" s="32">
-        <v>1.2E-2</v>
+        <v>1E-4</v>
       </c>
       <c r="AD24" s="29">
-        <v>0</v>
+        <v>8479.68</v>
       </c>
       <c r="AE24" s="29">
         <v>0</v>
@@ -4634,16 +4731,16 @@
         <v>0</v>
       </c>
       <c r="AG24" s="29">
-        <v>0</v>
+        <v>8479.68</v>
       </c>
       <c r="AH24" s="29">
         <v>0</v>
       </c>
       <c r="AI24" s="29">
-        <v>10847.2</v>
+        <v>8596.9599999999991</v>
       </c>
       <c r="AJ24" s="33" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="AK24" s="34"/>
       <c r="AL24" s="34"/>
@@ -4661,25 +4758,25 @@
         <v>2043</v>
       </c>
       <c r="D25" s="26">
-        <v>2043</v>
+        <v>2692</v>
       </c>
       <c r="E25" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F25" s="27">
-        <v>106018</v>
+        <v>108405</v>
       </c>
       <c r="G25" s="25" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="H25" s="28">
-        <v>45344</v>
+        <v>45471</v>
       </c>
       <c r="I25" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J25" s="30">
-        <v>34230.339999999997</v>
+        <v>36157.08</v>
       </c>
       <c r="K25" s="30">
         <v>0</v>
@@ -4688,16 +4785,16 @@
         <v>0</v>
       </c>
       <c r="M25" s="31">
-        <v>426.22</v>
+        <v>0.6</v>
       </c>
       <c r="N25" s="31">
         <v>0</v>
       </c>
       <c r="O25" s="29">
-        <v>34656.559999999998</v>
+        <v>36157.68</v>
       </c>
       <c r="P25" s="32">
-        <v>1.9099999999999999E-2</v>
+        <v>0.02</v>
       </c>
       <c r="Q25" s="30">
         <v>0</v>
@@ -4715,10 +4812,10 @@
         <v>0</v>
       </c>
       <c r="V25" s="29">
-        <v>34656.559999999998</v>
+        <v>36157.68</v>
       </c>
       <c r="W25" s="29">
-        <v>10269.11</v>
+        <v>10847.12</v>
       </c>
       <c r="X25" s="29">
         <v>0</v>
@@ -4727,16 +4824,16 @@
         <v>0</v>
       </c>
       <c r="Z25" s="31">
-        <v>56.83</v>
+        <v>0.08</v>
       </c>
       <c r="AA25" s="31">
         <v>0</v>
       </c>
       <c r="AB25" s="29">
-        <v>10325.94</v>
+        <v>10847.2</v>
       </c>
       <c r="AC25" s="32">
-        <v>1.14E-2</v>
+        <v>1.2E-2</v>
       </c>
       <c r="AD25" s="29">
         <v>0</v>
@@ -4754,10 +4851,10 @@
         <v>0</v>
       </c>
       <c r="AI25" s="29">
-        <v>10325.94</v>
+        <v>10847.2</v>
       </c>
       <c r="AJ25" s="33" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="AK25" s="34"/>
       <c r="AL25" s="34"/>
@@ -4781,19 +4878,19 @@
         <v>28</v>
       </c>
       <c r="F26" s="27">
-        <v>100677</v>
+        <v>106018</v>
       </c>
       <c r="G26" s="25" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="H26" s="28">
-        <v>44999</v>
+        <v>45344</v>
       </c>
       <c r="I26" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J26" s="30">
-        <v>0</v>
+        <v>34230.339999999997</v>
       </c>
       <c r="K26" s="30">
         <v>0</v>
@@ -4802,19 +4899,19 @@
         <v>0</v>
       </c>
       <c r="M26" s="31">
-        <v>1621.42</v>
+        <v>426.22</v>
       </c>
       <c r="N26" s="31">
         <v>0</v>
       </c>
       <c r="O26" s="29">
-        <v>1621.42</v>
+        <v>34656.559999999998</v>
       </c>
       <c r="P26" s="32">
-        <v>8.9999999999999998E-4</v>
+        <v>1.9099999999999999E-2</v>
       </c>
       <c r="Q26" s="30">
-        <v>29685.599999999999</v>
+        <v>0</v>
       </c>
       <c r="R26" s="30">
         <v>0</v>
@@ -4823,16 +4920,16 @@
         <v>0</v>
       </c>
       <c r="T26" s="29">
-        <v>29685.599999999999</v>
+        <v>0</v>
       </c>
       <c r="U26" s="29">
         <v>0</v>
       </c>
       <c r="V26" s="29">
-        <v>31307.02</v>
+        <v>34656.559999999998</v>
       </c>
       <c r="W26" s="29">
-        <v>0</v>
+        <v>10269.11</v>
       </c>
       <c r="X26" s="29">
         <v>0</v>
@@ -4841,19 +4938,19 @@
         <v>0</v>
       </c>
       <c r="Z26" s="31">
-        <v>102.91</v>
+        <v>56.83</v>
       </c>
       <c r="AA26" s="31">
         <v>0</v>
       </c>
       <c r="AB26" s="29">
-        <v>102.91</v>
+        <v>10325.94</v>
       </c>
       <c r="AC26" s="32">
-        <v>1E-4</v>
+        <v>1.14E-2</v>
       </c>
       <c r="AD26" s="29">
-        <v>6178.8</v>
+        <v>0</v>
       </c>
       <c r="AE26" s="29">
         <v>0</v>
@@ -4862,16 +4959,16 @@
         <v>0</v>
       </c>
       <c r="AG26" s="29">
-        <v>6178.8</v>
+        <v>0</v>
       </c>
       <c r="AH26" s="29">
         <v>0</v>
       </c>
       <c r="AI26" s="29">
-        <v>6281.71</v>
+        <v>10325.94</v>
       </c>
       <c r="AJ26" s="33" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="AK26" s="34"/>
       <c r="AL26" s="34"/>
@@ -4895,13 +4992,13 @@
         <v>28</v>
       </c>
       <c r="F27" s="27">
-        <v>80925</v>
+        <v>100677</v>
       </c>
       <c r="G27" s="25" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="H27" s="28">
-        <v>43439</v>
+        <v>44999</v>
       </c>
       <c r="I27" s="29" t="s">
         <v>30</v>
@@ -4916,19 +5013,19 @@
         <v>0</v>
       </c>
       <c r="M27" s="31">
-        <v>5216.63</v>
+        <v>1621.42</v>
       </c>
       <c r="N27" s="31">
         <v>0</v>
       </c>
       <c r="O27" s="29">
-        <v>5216.63</v>
+        <v>1621.42</v>
       </c>
       <c r="P27" s="32">
-        <v>2.8999999999999998E-3</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="Q27" s="30">
-        <v>23039.919999999998</v>
+        <v>29685.599999999999</v>
       </c>
       <c r="R27" s="30">
         <v>0</v>
@@ -4937,13 +5034,13 @@
         <v>0</v>
       </c>
       <c r="T27" s="29">
-        <v>23039.919999999998</v>
+        <v>29685.599999999999</v>
       </c>
       <c r="U27" s="29">
         <v>0</v>
       </c>
       <c r="V27" s="29">
-        <v>28256.55</v>
+        <v>31307.02</v>
       </c>
       <c r="W27" s="29">
         <v>0</v>
@@ -4955,19 +5052,19 @@
         <v>0</v>
       </c>
       <c r="Z27" s="31">
-        <v>570.55999999999995</v>
+        <v>102.91</v>
       </c>
       <c r="AA27" s="31">
         <v>0</v>
       </c>
       <c r="AB27" s="29">
-        <v>570.55999999999995</v>
+        <v>102.91</v>
       </c>
       <c r="AC27" s="32">
-        <v>5.9999999999999995E-4</v>
+        <v>1E-4</v>
       </c>
       <c r="AD27" s="29">
-        <v>4694.78</v>
+        <v>6178.8</v>
       </c>
       <c r="AE27" s="29">
         <v>0</v>
@@ -4976,16 +5073,16 @@
         <v>0</v>
       </c>
       <c r="AG27" s="29">
-        <v>4694.78</v>
+        <v>6178.8</v>
       </c>
       <c r="AH27" s="29">
         <v>0</v>
       </c>
       <c r="AI27" s="29">
-        <v>5265.34</v>
+        <v>6281.71</v>
       </c>
       <c r="AJ27" s="33" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="AK27" s="34"/>
       <c r="AL27" s="34"/>
@@ -5009,13 +5106,13 @@
         <v>28</v>
       </c>
       <c r="F28" s="27">
-        <v>110105</v>
+        <v>80925</v>
       </c>
       <c r="G28" s="25" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H28" s="28">
-        <v>45560</v>
+        <v>43439</v>
       </c>
       <c r="I28" s="29" t="s">
         <v>30</v>
@@ -5030,19 +5127,19 @@
         <v>0</v>
       </c>
       <c r="M28" s="31">
-        <v>960</v>
+        <v>5216.63</v>
       </c>
       <c r="N28" s="31">
         <v>0</v>
       </c>
       <c r="O28" s="29">
-        <v>960</v>
+        <v>5216.63</v>
       </c>
       <c r="P28" s="32">
-        <v>5.0000000000000001E-4</v>
+        <v>2.8999999999999998E-3</v>
       </c>
       <c r="Q28" s="30">
-        <v>25046.54</v>
+        <v>23039.919999999998</v>
       </c>
       <c r="R28" s="30">
         <v>0</v>
@@ -5051,13 +5148,13 @@
         <v>0</v>
       </c>
       <c r="T28" s="29">
-        <v>25046.54</v>
+        <v>23039.919999999998</v>
       </c>
       <c r="U28" s="29">
         <v>0</v>
       </c>
       <c r="V28" s="29">
-        <v>26006.54</v>
+        <v>28256.55</v>
       </c>
       <c r="W28" s="29">
         <v>0</v>
@@ -5069,19 +5166,19 @@
         <v>0</v>
       </c>
       <c r="Z28" s="31">
-        <v>48</v>
+        <v>570.55999999999995</v>
       </c>
       <c r="AA28" s="31">
         <v>0</v>
       </c>
       <c r="AB28" s="29">
-        <v>48</v>
+        <v>570.55999999999995</v>
       </c>
       <c r="AC28" s="32">
-        <v>1E-4</v>
+        <v>5.9999999999999995E-4</v>
       </c>
       <c r="AD28" s="29">
-        <v>5158.24</v>
+        <v>4694.78</v>
       </c>
       <c r="AE28" s="29">
         <v>0</v>
@@ -5090,16 +5187,16 @@
         <v>0</v>
       </c>
       <c r="AG28" s="29">
-        <v>5158.24</v>
+        <v>4694.78</v>
       </c>
       <c r="AH28" s="29">
         <v>0</v>
       </c>
       <c r="AI28" s="29">
-        <v>5206.24</v>
+        <v>5265.34</v>
       </c>
       <c r="AJ28" s="33" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="AK28" s="34"/>
       <c r="AL28" s="34"/>
@@ -5123,19 +5220,19 @@
         <v>28</v>
       </c>
       <c r="F29" s="27">
-        <v>65046</v>
+        <v>110105</v>
       </c>
       <c r="G29" s="25" t="s">
-        <v>86</v>
+        <v>72</v>
       </c>
       <c r="H29" s="28">
-        <v>44763</v>
+        <v>45560</v>
       </c>
       <c r="I29" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J29" s="30">
-        <v>25330.85</v>
+        <v>0</v>
       </c>
       <c r="K29" s="30">
         <v>0</v>
@@ -5144,19 +5241,19 @@
         <v>0</v>
       </c>
       <c r="M29" s="31">
-        <v>180</v>
+        <v>960</v>
       </c>
       <c r="N29" s="31">
         <v>0</v>
       </c>
       <c r="O29" s="29">
-        <v>25510.85</v>
+        <v>960</v>
       </c>
       <c r="P29" s="32">
-        <v>1.41E-2</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q29" s="30">
-        <v>0</v>
+        <v>25046.54</v>
       </c>
       <c r="R29" s="30">
         <v>0</v>
@@ -5165,16 +5262,16 @@
         <v>0</v>
       </c>
       <c r="T29" s="29">
-        <v>0</v>
+        <v>25046.54</v>
       </c>
       <c r="U29" s="29">
         <v>0</v>
       </c>
       <c r="V29" s="29">
-        <v>25510.85</v>
+        <v>26006.54</v>
       </c>
       <c r="W29" s="29">
-        <v>7651.85</v>
+        <v>0</v>
       </c>
       <c r="X29" s="29">
         <v>0</v>
@@ -5183,19 +5280,19 @@
         <v>0</v>
       </c>
       <c r="Z29" s="31">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="AA29" s="31">
         <v>0</v>
       </c>
       <c r="AB29" s="29">
-        <v>7660.85</v>
+        <v>48</v>
       </c>
       <c r="AC29" s="32">
-        <v>8.5000000000000006E-3</v>
+        <v>1E-4</v>
       </c>
       <c r="AD29" s="29">
-        <v>0</v>
+        <v>5158.24</v>
       </c>
       <c r="AE29" s="29">
         <v>0</v>
@@ -5204,16 +5301,16 @@
         <v>0</v>
       </c>
       <c r="AG29" s="29">
-        <v>0</v>
+        <v>5158.24</v>
       </c>
       <c r="AH29" s="29">
         <v>0</v>
       </c>
       <c r="AI29" s="29">
-        <v>7660.85</v>
+        <v>5206.24</v>
       </c>
       <c r="AJ29" s="33" t="s">
-        <v>87</v>
+        <v>73</v>
       </c>
       <c r="AK29" s="34"/>
       <c r="AL29" s="34"/>
@@ -5231,25 +5328,25 @@
         <v>2043</v>
       </c>
       <c r="D30" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E30" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F30" s="27">
-        <v>114157</v>
+        <v>65046</v>
       </c>
       <c r="G30" s="25" t="s">
-        <v>120</v>
+        <v>86</v>
       </c>
       <c r="H30" s="28">
-        <v>45904</v>
+        <v>44763</v>
       </c>
       <c r="I30" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J30" s="30">
-        <v>20303.28</v>
+        <v>25330.85</v>
       </c>
       <c r="K30" s="30">
         <v>0</v>
@@ -5258,16 +5355,16 @@
         <v>0</v>
       </c>
       <c r="M30" s="31">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="N30" s="31">
         <v>0</v>
       </c>
       <c r="O30" s="29">
-        <v>20303.28</v>
+        <v>25510.85</v>
       </c>
       <c r="P30" s="32">
-        <v>1.12E-2</v>
+        <v>1.41E-2</v>
       </c>
       <c r="Q30" s="30">
         <v>0</v>
@@ -5285,10 +5382,10 @@
         <v>0</v>
       </c>
       <c r="V30" s="29">
-        <v>20303.28</v>
+        <v>25510.85</v>
       </c>
       <c r="W30" s="29">
-        <v>5307.72</v>
+        <v>7651.85</v>
       </c>
       <c r="X30" s="29">
         <v>0</v>
@@ -5297,16 +5394,16 @@
         <v>0</v>
       </c>
       <c r="Z30" s="31">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AA30" s="31">
         <v>0</v>
       </c>
       <c r="AB30" s="29">
-        <v>5307.72</v>
+        <v>7660.85</v>
       </c>
       <c r="AC30" s="32">
-        <v>5.8999999999999999E-3</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="AD30" s="29">
         <v>0</v>
@@ -5324,10 +5421,10 @@
         <v>0</v>
       </c>
       <c r="AI30" s="29">
-        <v>5307.72</v>
+        <v>7660.85</v>
       </c>
       <c r="AJ30" s="33" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="AK30" s="34"/>
       <c r="AL30" s="34"/>
@@ -5351,19 +5448,19 @@
         <v>28</v>
       </c>
       <c r="F31" s="27">
-        <v>98797</v>
+        <v>104343</v>
       </c>
       <c r="G31" s="25" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H31" s="28">
-        <v>44342</v>
+        <v>45201</v>
       </c>
       <c r="I31" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J31" s="30">
-        <v>0</v>
+        <v>20601.72</v>
       </c>
       <c r="K31" s="30">
         <v>0</v>
@@ -5372,16 +5469,16 @@
         <v>0</v>
       </c>
       <c r="M31" s="31">
-        <v>18002.650000000001</v>
+        <v>3182.67</v>
       </c>
       <c r="N31" s="31">
         <v>0</v>
       </c>
       <c r="O31" s="29">
-        <v>18002.650000000001</v>
+        <v>23784.39</v>
       </c>
       <c r="P31" s="32">
-        <v>9.9000000000000008E-3</v>
+        <v>1.3100000000000001E-2</v>
       </c>
       <c r="Q31" s="30">
         <v>0</v>
@@ -5399,10 +5496,10 @@
         <v>0</v>
       </c>
       <c r="V31" s="29">
-        <v>18002.650000000001</v>
+        <v>23784.39</v>
       </c>
       <c r="W31" s="29">
-        <v>0</v>
+        <v>7084.66</v>
       </c>
       <c r="X31" s="29">
         <v>0</v>
@@ -5411,16 +5508,16 @@
         <v>0</v>
       </c>
       <c r="Z31" s="31">
-        <v>900.13</v>
+        <v>374.33</v>
       </c>
       <c r="AA31" s="31">
         <v>0</v>
       </c>
       <c r="AB31" s="29">
-        <v>900.13</v>
+        <v>7458.99</v>
       </c>
       <c r="AC31" s="32">
-        <v>1E-3</v>
+        <v>8.2000000000000007E-3</v>
       </c>
       <c r="AD31" s="29">
         <v>0</v>
@@ -5438,10 +5535,10 @@
         <v>0</v>
       </c>
       <c r="AI31" s="29">
-        <v>900.13</v>
+        <v>7458.99</v>
       </c>
       <c r="AJ31" s="33" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="AK31" s="34"/>
       <c r="AL31" s="34"/>
@@ -5459,25 +5556,25 @@
         <v>2043</v>
       </c>
       <c r="D32" s="26">
-        <v>2043</v>
+        <v>2692</v>
       </c>
       <c r="E32" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F32" s="27">
-        <v>104343</v>
+        <v>114157</v>
       </c>
       <c r="G32" s="25" t="s">
-        <v>78</v>
+        <v>120</v>
       </c>
       <c r="H32" s="28">
-        <v>45201</v>
+        <v>45904</v>
       </c>
       <c r="I32" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J32" s="30">
-        <v>0</v>
+        <v>20303.28</v>
       </c>
       <c r="K32" s="30">
         <v>0</v>
@@ -5486,16 +5583,16 @@
         <v>0</v>
       </c>
       <c r="M32" s="31">
-        <v>2480.0300000000002</v>
+        <v>0</v>
       </c>
       <c r="N32" s="31">
         <v>0</v>
       </c>
       <c r="O32" s="29">
-        <v>2480.0300000000002</v>
+        <v>20303.28</v>
       </c>
       <c r="P32" s="32">
-        <v>1.4E-3</v>
+        <v>1.12E-2</v>
       </c>
       <c r="Q32" s="30">
         <v>0</v>
@@ -5513,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="V32" s="29">
-        <v>2480.0300000000002</v>
+        <v>20303.28</v>
       </c>
       <c r="W32" s="29">
-        <v>0</v>
+        <v>5307.72</v>
       </c>
       <c r="X32" s="29">
         <v>0</v>
@@ -5525,16 +5622,16 @@
         <v>0</v>
       </c>
       <c r="Z32" s="31">
-        <v>280.64</v>
+        <v>0</v>
       </c>
       <c r="AA32" s="31">
         <v>0</v>
       </c>
       <c r="AB32" s="29">
-        <v>280.64</v>
+        <v>5307.72</v>
       </c>
       <c r="AC32" s="32">
-        <v>2.9999999999999997E-4</v>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="AD32" s="29">
         <v>0</v>
@@ -5552,10 +5649,10 @@
         <v>0</v>
       </c>
       <c r="AI32" s="29">
-        <v>280.64</v>
+        <v>5307.72</v>
       </c>
       <c r="AJ32" s="33" t="s">
-        <v>79</v>
+        <v>121</v>
       </c>
       <c r="AK32" s="34"/>
       <c r="AL32" s="34"/>
@@ -5573,19 +5670,19 @@
         <v>2043</v>
       </c>
       <c r="D33" s="26">
-        <v>2511</v>
+        <v>2043</v>
       </c>
       <c r="E33" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F33" s="27">
-        <v>63441</v>
+        <v>98797</v>
       </c>
       <c r="G33" s="25" t="s">
-        <v>82</v>
+        <v>76</v>
       </c>
       <c r="H33" s="28">
-        <v>44733</v>
+        <v>44342</v>
       </c>
       <c r="I33" s="29" t="s">
         <v>30</v>
@@ -5600,16 +5697,16 @@
         <v>0</v>
       </c>
       <c r="M33" s="31">
-        <v>300.06</v>
+        <v>18002.650000000001</v>
       </c>
       <c r="N33" s="31">
         <v>0</v>
       </c>
       <c r="O33" s="29">
-        <v>300.06</v>
+        <v>18002.650000000001</v>
       </c>
       <c r="P33" s="32">
-        <v>2.0000000000000001E-4</v>
+        <v>9.9000000000000008E-3</v>
       </c>
       <c r="Q33" s="30">
         <v>0</v>
@@ -5627,7 +5724,7 @@
         <v>0</v>
       </c>
       <c r="V33" s="29">
-        <v>300.06</v>
+        <v>18002.650000000001</v>
       </c>
       <c r="W33" s="29">
         <v>0</v>
@@ -5639,16 +5736,16 @@
         <v>0</v>
       </c>
       <c r="Z33" s="31">
-        <v>15</v>
+        <v>900.13</v>
       </c>
       <c r="AA33" s="31">
         <v>0</v>
       </c>
       <c r="AB33" s="29">
-        <v>15</v>
+        <v>900.13</v>
       </c>
       <c r="AC33" s="32">
-        <v>0</v>
+        <v>1E-3</v>
       </c>
       <c r="AD33" s="29">
         <v>0</v>
@@ -5666,10 +5763,10 @@
         <v>0</v>
       </c>
       <c r="AI33" s="29">
-        <v>15</v>
+        <v>900.13</v>
       </c>
       <c r="AJ33" s="33" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AK33" s="34"/>
       <c r="AL33" s="34"/>
@@ -5687,19 +5784,19 @@
         <v>2043</v>
       </c>
       <c r="D34" s="26">
-        <v>2043</v>
+        <v>2511</v>
       </c>
       <c r="E34" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F34" s="27">
-        <v>108658</v>
+        <v>63441</v>
       </c>
       <c r="G34" s="25" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
       <c r="H34" s="28">
-        <v>45497</v>
+        <v>44733</v>
       </c>
       <c r="I34" s="29" t="s">
         <v>30</v>
@@ -5714,16 +5811,16 @@
         <v>0</v>
       </c>
       <c r="M34" s="31">
-        <v>180.03</v>
+        <v>300.06</v>
       </c>
       <c r="N34" s="31">
         <v>0</v>
       </c>
       <c r="O34" s="29">
-        <v>180.03</v>
+        <v>300.06</v>
       </c>
       <c r="P34" s="32">
-        <v>1E-4</v>
+        <v>2.0000000000000001E-4</v>
       </c>
       <c r="Q34" s="30">
         <v>0</v>
@@ -5741,7 +5838,7 @@
         <v>0</v>
       </c>
       <c r="V34" s="29">
-        <v>180.03</v>
+        <v>300.06</v>
       </c>
       <c r="W34" s="29">
         <v>0</v>
@@ -5753,13 +5850,13 @@
         <v>0</v>
       </c>
       <c r="Z34" s="31">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AA34" s="31">
         <v>0</v>
       </c>
       <c r="AB34" s="29">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AC34" s="32">
         <v>0</v>
@@ -5780,10 +5877,10 @@
         <v>0</v>
       </c>
       <c r="AI34" s="29">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AJ34" s="33" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="AK34" s="34"/>
       <c r="AL34" s="34"/>
@@ -5807,13 +5904,13 @@
         <v>28</v>
       </c>
       <c r="F35" s="27">
-        <v>109998</v>
+        <v>108658</v>
       </c>
       <c r="G35" s="25" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="H35" s="28">
-        <v>45596</v>
+        <v>45497</v>
       </c>
       <c r="I35" s="29" t="s">
         <v>30</v>
@@ -5828,13 +5925,13 @@
         <v>0</v>
       </c>
       <c r="M35" s="31">
-        <v>162.5</v>
+        <v>180.03</v>
       </c>
       <c r="N35" s="31">
         <v>0</v>
       </c>
       <c r="O35" s="29">
-        <v>162.5</v>
+        <v>180.03</v>
       </c>
       <c r="P35" s="32">
         <v>1E-4</v>
@@ -5855,7 +5952,7 @@
         <v>0</v>
       </c>
       <c r="V35" s="29">
-        <v>162.5</v>
+        <v>180.03</v>
       </c>
       <c r="W35" s="29">
         <v>0</v>
@@ -5867,13 +5964,13 @@
         <v>0</v>
       </c>
       <c r="Z35" s="31">
-        <v>21.66</v>
+        <v>9</v>
       </c>
       <c r="AA35" s="31">
         <v>0</v>
       </c>
       <c r="AB35" s="29">
-        <v>21.66</v>
+        <v>9</v>
       </c>
       <c r="AC35" s="32">
         <v>0</v>
@@ -5894,10 +5991,10 @@
         <v>0</v>
       </c>
       <c r="AI35" s="29">
-        <v>21.66</v>
+        <v>9</v>
       </c>
       <c r="AJ35" s="33" t="s">
-        <v>91</v>
+        <v>105</v>
       </c>
       <c r="AK35" s="34"/>
       <c r="AL35" s="34"/>
@@ -5915,19 +6012,19 @@
         <v>2043</v>
       </c>
       <c r="D36" s="26">
-        <v>2511</v>
+        <v>2043</v>
       </c>
       <c r="E36" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F36" s="27">
-        <v>69684</v>
+        <v>109998</v>
       </c>
       <c r="G36" s="25" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H36" s="28">
-        <v>44771</v>
+        <v>45596</v>
       </c>
       <c r="I36" s="29" t="s">
         <v>30</v>
@@ -5942,13 +6039,13 @@
         <v>0</v>
       </c>
       <c r="M36" s="31">
-        <v>142.55000000000001</v>
+        <v>162.5</v>
       </c>
       <c r="N36" s="31">
         <v>0</v>
       </c>
       <c r="O36" s="29">
-        <v>142.55000000000001</v>
+        <v>162.5</v>
       </c>
       <c r="P36" s="32">
         <v>1E-4</v>
@@ -5969,7 +6066,7 @@
         <v>0</v>
       </c>
       <c r="V36" s="29">
-        <v>142.55000000000001</v>
+        <v>162.5</v>
       </c>
       <c r="W36" s="29">
         <v>0</v>
@@ -5981,13 +6078,13 @@
         <v>0</v>
       </c>
       <c r="Z36" s="31">
-        <v>19.010000000000002</v>
+        <v>21.66</v>
       </c>
       <c r="AA36" s="31">
         <v>0</v>
       </c>
       <c r="AB36" s="29">
-        <v>19.010000000000002</v>
+        <v>21.66</v>
       </c>
       <c r="AC36" s="32">
         <v>0</v>
@@ -6008,10 +6105,10 @@
         <v>0</v>
       </c>
       <c r="AI36" s="29">
-        <v>19.010000000000002</v>
+        <v>21.66</v>
       </c>
       <c r="AJ36" s="33" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="AK36" s="34"/>
       <c r="AL36" s="34"/>
@@ -6035,13 +6132,13 @@
         <v>28</v>
       </c>
       <c r="F37" s="27">
-        <v>59120</v>
+        <v>69684</v>
       </c>
       <c r="G37" s="25" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="H37" s="28">
-        <v>44708</v>
+        <v>44771</v>
       </c>
       <c r="I37" s="29" t="s">
         <v>30</v>
@@ -6056,16 +6153,16 @@
         <v>0</v>
       </c>
       <c r="M37" s="31">
-        <v>0</v>
+        <v>142.55000000000001</v>
       </c>
       <c r="N37" s="31">
         <v>0</v>
       </c>
       <c r="O37" s="29">
-        <v>0</v>
+        <v>142.55000000000001</v>
       </c>
       <c r="P37" s="32">
-        <v>0</v>
+        <v>1E-4</v>
       </c>
       <c r="Q37" s="30">
         <v>0</v>
@@ -6083,7 +6180,7 @@
         <v>0</v>
       </c>
       <c r="V37" s="29">
-        <v>0</v>
+        <v>142.55000000000001</v>
       </c>
       <c r="W37" s="29">
         <v>0</v>
@@ -6095,13 +6192,13 @@
         <v>0</v>
       </c>
       <c r="Z37" s="31">
-        <v>0</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="AA37" s="31">
         <v>0</v>
       </c>
       <c r="AB37" s="29">
-        <v>0</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="AC37" s="32">
         <v>0</v>
@@ -6122,10 +6219,10 @@
         <v>0</v>
       </c>
       <c r="AI37" s="29">
-        <v>0</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="AJ37" s="33" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="AK37" s="34"/>
       <c r="AL37" s="34"/>
@@ -6143,22 +6240,22 @@
         <v>2043</v>
       </c>
       <c r="D38" s="26">
-        <v>2043</v>
+        <v>2511</v>
       </c>
       <c r="E38" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F38" s="27">
-        <v>64502</v>
+        <v>59120</v>
       </c>
       <c r="G38" s="25" t="s">
-        <v>28</v>
+        <v>92</v>
       </c>
       <c r="H38" s="28">
-        <v>42173</v>
+        <v>44708</v>
       </c>
       <c r="I38" s="29" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="J38" s="30">
         <v>0</v>
@@ -6239,7 +6336,7 @@
         <v>0</v>
       </c>
       <c r="AJ38" s="33" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="AK38" s="34"/>
       <c r="AL38" s="34"/>
@@ -6257,22 +6354,22 @@
         <v>2043</v>
       </c>
       <c r="D39" s="26">
-        <v>2511</v>
+        <v>2043</v>
       </c>
       <c r="E39" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F39" s="27">
-        <v>81044</v>
+        <v>64502</v>
       </c>
       <c r="G39" s="25" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="H39" s="28">
-        <v>44872</v>
+        <v>42173</v>
       </c>
       <c r="I39" s="29" t="s">
-        <v>30</v>
+        <v>94</v>
       </c>
       <c r="J39" s="30">
         <v>0</v>
@@ -6353,7 +6450,7 @@
         <v>0</v>
       </c>
       <c r="AJ39" s="33" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="AK39" s="34"/>
       <c r="AL39" s="34"/>
@@ -6371,19 +6468,19 @@
         <v>2043</v>
       </c>
       <c r="D40" s="26">
-        <v>2043</v>
+        <v>2511</v>
       </c>
       <c r="E40" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F40" s="27">
-        <v>90177</v>
+        <v>81044</v>
       </c>
       <c r="G40" s="25" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="H40" s="28">
-        <v>43949</v>
+        <v>44872</v>
       </c>
       <c r="I40" s="29" t="s">
         <v>30</v>
@@ -6467,7 +6564,7 @@
         <v>0</v>
       </c>
       <c r="AJ40" s="33" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="AK40" s="34"/>
       <c r="AL40" s="34"/>
@@ -6491,13 +6588,13 @@
         <v>28</v>
       </c>
       <c r="F41" s="27">
-        <v>94205</v>
+        <v>90177</v>
       </c>
       <c r="G41" s="25" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="H41" s="28">
-        <v>44116</v>
+        <v>43949</v>
       </c>
       <c r="I41" s="29" t="s">
         <v>30</v>
@@ -6581,7 +6678,7 @@
         <v>0</v>
       </c>
       <c r="AJ41" s="33" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="AK41" s="34"/>
       <c r="AL41" s="34"/>
@@ -6605,13 +6702,13 @@
         <v>28</v>
       </c>
       <c r="F42" s="27">
-        <v>101640</v>
+        <v>94205</v>
       </c>
       <c r="G42" s="25" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="H42" s="28">
-        <v>45104</v>
+        <v>44116</v>
       </c>
       <c r="I42" s="29" t="s">
         <v>30</v>
@@ -6695,7 +6792,7 @@
         <v>0</v>
       </c>
       <c r="AJ42" s="33" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="AK42" s="34"/>
       <c r="AL42" s="34"/>
@@ -6719,13 +6816,13 @@
         <v>28</v>
       </c>
       <c r="F43" s="27">
-        <v>103982</v>
+        <v>101640</v>
       </c>
       <c r="G43" s="25" t="s">
-        <v>138</v>
+        <v>102</v>
       </c>
       <c r="H43" s="28">
-        <v>45216</v>
+        <v>45104</v>
       </c>
       <c r="I43" s="29" t="s">
         <v>30</v>
@@ -6809,7 +6906,7 @@
         <v>0</v>
       </c>
       <c r="AJ43" s="33" t="s">
-        <v>139</v>
+        <v>103</v>
       </c>
       <c r="AK43" s="34"/>
       <c r="AL43" s="34"/>
@@ -6833,13 +6930,13 @@
         <v>28</v>
       </c>
       <c r="F44" s="27">
-        <v>109007</v>
+        <v>103982</v>
       </c>
       <c r="G44" s="25" t="s">
-        <v>106</v>
+        <v>138</v>
       </c>
       <c r="H44" s="28">
-        <v>45525</v>
+        <v>45216</v>
       </c>
       <c r="I44" s="29" t="s">
         <v>30</v>
@@ -6923,7 +7020,7 @@
         <v>0</v>
       </c>
       <c r="AJ44" s="33" t="s">
-        <v>107</v>
+        <v>139</v>
       </c>
       <c r="AK44" s="34"/>
       <c r="AL44" s="34"/>
@@ -6941,19 +7038,19 @@
         <v>2043</v>
       </c>
       <c r="D45" s="26">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E45" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F45" s="27">
-        <v>109819</v>
+        <v>109007</v>
       </c>
       <c r="G45" s="25" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="H45" s="28">
-        <v>45562</v>
+        <v>45525</v>
       </c>
       <c r="I45" s="29" t="s">
         <v>30</v>
@@ -7037,7 +7134,7 @@
         <v>0</v>
       </c>
       <c r="AJ45" s="33" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="AK45" s="34"/>
       <c r="AL45" s="34"/>
@@ -7055,19 +7152,19 @@
         <v>2043</v>
       </c>
       <c r="D46" s="26">
-        <v>2692</v>
+        <v>2856</v>
       </c>
       <c r="E46" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="27">
-        <v>110575</v>
+        <v>109819</v>
       </c>
       <c r="G46" s="25" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H46" s="28">
-        <v>45583</v>
+        <v>45562</v>
       </c>
       <c r="I46" s="29" t="s">
         <v>30</v>
@@ -7151,7 +7248,7 @@
         <v>0</v>
       </c>
       <c r="AJ46" s="33" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AK46" s="34"/>
       <c r="AL46" s="34"/>
@@ -7169,19 +7266,19 @@
         <v>2043</v>
       </c>
       <c r="D47" s="26">
-        <v>2856</v>
+        <v>2692</v>
       </c>
       <c r="E47" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F47" s="27">
-        <v>111960</v>
+        <v>110575</v>
       </c>
       <c r="G47" s="25" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="H47" s="28">
-        <v>45707</v>
+        <v>45583</v>
       </c>
       <c r="I47" s="29" t="s">
         <v>30</v>
@@ -7265,7 +7362,7 @@
         <v>0</v>
       </c>
       <c r="AJ47" s="33" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="AK47" s="34"/>
       <c r="AL47" s="34"/>
@@ -7289,13 +7386,13 @@
         <v>28</v>
       </c>
       <c r="F48" s="27">
-        <v>112522</v>
+        <v>111960</v>
       </c>
       <c r="G48" s="25" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H48" s="28">
-        <v>45776</v>
+        <v>45707</v>
       </c>
       <c r="I48" s="29" t="s">
         <v>30</v>
@@ -7379,7 +7476,7 @@
         <v>0</v>
       </c>
       <c r="AJ48" s="33" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="AK48" s="34"/>
       <c r="AL48" s="34"/>
@@ -7403,13 +7500,13 @@
         <v>28</v>
       </c>
       <c r="F49" s="27">
-        <v>113076</v>
+        <v>112083</v>
       </c>
       <c r="G49" s="25" t="s">
-        <v>116</v>
+        <v>143</v>
       </c>
       <c r="H49" s="28">
-        <v>45806</v>
+        <v>45736</v>
       </c>
       <c r="I49" s="29" t="s">
         <v>30</v>
@@ -7493,7 +7590,7 @@
         <v>0</v>
       </c>
       <c r="AJ49" s="33" t="s">
-        <v>117</v>
+        <v>144</v>
       </c>
       <c r="AK49" s="34"/>
       <c r="AL49" s="34"/>
@@ -7517,13 +7614,13 @@
         <v>28</v>
       </c>
       <c r="F50" s="27">
-        <v>114100</v>
+        <v>112522</v>
       </c>
       <c r="G50" s="25" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H50" s="28">
-        <v>45863</v>
+        <v>45776</v>
       </c>
       <c r="I50" s="29" t="s">
         <v>30</v>
@@ -7607,7 +7704,7 @@
         <v>0</v>
       </c>
       <c r="AJ50" s="33" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="AK50" s="34"/>
       <c r="AL50" s="34"/>
@@ -7631,19 +7728,19 @@
         <v>28</v>
       </c>
       <c r="F51" s="27">
-        <v>95148</v>
+        <v>113076</v>
       </c>
       <c r="G51" s="25" t="s">
-        <v>54</v>
+        <v>116</v>
       </c>
       <c r="H51" s="28">
-        <v>44916</v>
+        <v>45806</v>
       </c>
       <c r="I51" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J51" s="30">
-        <v>46057.760000000002</v>
+        <v>0</v>
       </c>
       <c r="K51" s="30">
         <v>0</v>
@@ -7658,31 +7755,31 @@
         <v>0</v>
       </c>
       <c r="O51" s="29">
-        <v>46057.760000000002</v>
+        <v>0</v>
       </c>
       <c r="P51" s="32">
-        <v>2.5399999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="Q51" s="30">
-        <v>23133.08</v>
+        <v>0</v>
       </c>
       <c r="R51" s="30">
         <v>0</v>
       </c>
       <c r="S51" s="30">
-        <v>69825</v>
+        <v>0</v>
       </c>
       <c r="T51" s="29">
-        <v>-46691.92</v>
+        <v>0</v>
       </c>
       <c r="U51" s="29">
         <v>0</v>
       </c>
       <c r="V51" s="29">
-        <v>-634.16</v>
+        <v>0</v>
       </c>
       <c r="W51" s="29">
-        <v>13817.33</v>
+        <v>0</v>
       </c>
       <c r="X51" s="29">
         <v>0</v>
@@ -7697,31 +7794,31 @@
         <v>0</v>
       </c>
       <c r="AB51" s="29">
-        <v>13817.33</v>
+        <v>0</v>
       </c>
       <c r="AC51" s="32">
-        <v>1.5299999999999999E-2</v>
+        <v>0</v>
       </c>
       <c r="AD51" s="29">
-        <v>4744.3599999999997</v>
+        <v>0</v>
       </c>
       <c r="AE51" s="29">
         <v>0</v>
       </c>
       <c r="AF51" s="29">
-        <v>15103</v>
+        <v>0</v>
       </c>
       <c r="AG51" s="29">
-        <v>-10358.64</v>
+        <v>0</v>
       </c>
       <c r="AH51" s="29">
         <v>0</v>
       </c>
       <c r="AI51" s="29">
-        <v>3458.69</v>
+        <v>0</v>
       </c>
       <c r="AJ51" s="33" t="s">
-        <v>55</v>
+        <v>117</v>
       </c>
       <c r="AK51" s="34"/>
       <c r="AL51" s="34"/>
@@ -7739,19 +7836,19 @@
         <v>2043</v>
       </c>
       <c r="D52" s="26">
-        <v>2692</v>
+        <v>2856</v>
       </c>
       <c r="E52" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F52" s="27">
-        <v>114431</v>
+        <v>114100</v>
       </c>
       <c r="G52" s="25" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H52" s="28">
-        <v>45930</v>
+        <v>45863</v>
       </c>
       <c r="I52" s="29" t="s">
         <v>30</v>
@@ -7769,13 +7866,13 @@
         <v>0</v>
       </c>
       <c r="N52" s="31">
-        <v>17664.759999999998</v>
+        <v>0</v>
       </c>
       <c r="O52" s="29">
-        <v>-17664.759999999998</v>
+        <v>0</v>
       </c>
       <c r="P52" s="32">
-        <v>-9.7999999999999997E-3</v>
+        <v>0</v>
       </c>
       <c r="Q52" s="30">
         <v>0</v>
@@ -7793,7 +7890,7 @@
         <v>0</v>
       </c>
       <c r="V52" s="29">
-        <v>-17664.759999999998</v>
+        <v>0</v>
       </c>
       <c r="W52" s="29">
         <v>0</v>
@@ -7808,13 +7905,13 @@
         <v>0</v>
       </c>
       <c r="AA52" s="31">
-        <v>5504.42</v>
+        <v>0</v>
       </c>
       <c r="AB52" s="29">
-        <v>-5504.42</v>
+        <v>0</v>
       </c>
       <c r="AC52" s="32">
-        <v>-6.1000000000000004E-3</v>
+        <v>0</v>
       </c>
       <c r="AD52" s="29">
         <v>0</v>
@@ -7832,10 +7929,10 @@
         <v>0</v>
       </c>
       <c r="AI52" s="29">
-        <v>-5504.42</v>
+        <v>0</v>
       </c>
       <c r="AJ52" s="33" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="AK52" s="34"/>
       <c r="AL52" s="34"/>
@@ -7843,66 +7940,257 @@
       <c r="AN52" s="35"/>
     </row>
     <row r="53" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A53" s="25"/>
-      <c r="B53" s="25"/>
-      <c r="C53" s="26"/>
-      <c r="D53" s="26"/>
-      <c r="E53" s="25"/>
-      <c r="F53" s="27"/>
-      <c r="G53" s="25"/>
-      <c r="H53" s="28"/>
-      <c r="I53" s="29"/>
-      <c r="J53" s="30"/>
-      <c r="K53" s="30"/>
-      <c r="L53" s="29"/>
-      <c r="M53" s="31"/>
-      <c r="N53" s="31"/>
-      <c r="O53" s="29"/>
-      <c r="P53" s="32"/>
-      <c r="Q53" s="30"/>
-      <c r="R53" s="30"/>
-      <c r="S53" s="30"/>
-      <c r="T53" s="29"/>
-      <c r="U53" s="29"/>
-      <c r="V53" s="29"/>
-      <c r="W53" s="29"/>
-      <c r="X53" s="29"/>
-      <c r="Y53" s="29"/>
-      <c r="Z53" s="31"/>
-      <c r="AA53" s="31"/>
-      <c r="AB53" s="29"/>
-      <c r="AC53" s="32"/>
-      <c r="AD53" s="29"/>
-      <c r="AE53" s="29"/>
-      <c r="AF53" s="29"/>
-      <c r="AG53" s="29"/>
-      <c r="AH53" s="29"/>
-      <c r="AI53" s="29"/>
-      <c r="AJ53" s="33"/>
+      <c r="A53" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B53" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C53" s="26">
+        <v>2043</v>
+      </c>
+      <c r="D53" s="26">
+        <v>2043</v>
+      </c>
+      <c r="E53" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="F53" s="27">
+        <v>95148</v>
+      </c>
+      <c r="G53" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="H53" s="28">
+        <v>44916</v>
+      </c>
+      <c r="I53" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="J53" s="30">
+        <v>46057.760000000002</v>
+      </c>
+      <c r="K53" s="30">
+        <v>0</v>
+      </c>
+      <c r="L53" s="29">
+        <v>0</v>
+      </c>
+      <c r="M53" s="31">
+        <v>0</v>
+      </c>
+      <c r="N53" s="31">
+        <v>0</v>
+      </c>
+      <c r="O53" s="29">
+        <v>46057.760000000002</v>
+      </c>
+      <c r="P53" s="32">
+        <v>2.5399999999999999E-2</v>
+      </c>
+      <c r="Q53" s="30">
+        <v>23133.08</v>
+      </c>
+      <c r="R53" s="30">
+        <v>0</v>
+      </c>
+      <c r="S53" s="30">
+        <v>69825</v>
+      </c>
+      <c r="T53" s="29">
+        <v>-46691.92</v>
+      </c>
+      <c r="U53" s="29">
+        <v>0</v>
+      </c>
+      <c r="V53" s="29">
+        <v>-634.16</v>
+      </c>
+      <c r="W53" s="29">
+        <v>13817.33</v>
+      </c>
+      <c r="X53" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="29">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="31">
+        <v>0</v>
+      </c>
+      <c r="AA53" s="31">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="29">
+        <v>13817.33</v>
+      </c>
+      <c r="AC53" s="32">
+        <v>1.5299999999999999E-2</v>
+      </c>
+      <c r="AD53" s="29">
+        <v>4744.3599999999997</v>
+      </c>
+      <c r="AE53" s="29">
+        <v>0</v>
+      </c>
+      <c r="AF53" s="29">
+        <v>15103</v>
+      </c>
+      <c r="AG53" s="29">
+        <v>-10358.64</v>
+      </c>
+      <c r="AH53" s="29">
+        <v>0</v>
+      </c>
+      <c r="AI53" s="29">
+        <v>3458.69</v>
+      </c>
+      <c r="AJ53" s="33" t="s">
+        <v>55</v>
+      </c>
       <c r="AK53" s="34"/>
       <c r="AL53" s="34"/>
       <c r="AM53" s="34"/>
       <c r="AN53" s="35"/>
     </row>
+    <row r="54" spans="1:40" x14ac:dyDescent="0.2">
+      <c r="A54" s="25" t="s">
+        <v>26</v>
+      </c>
+      <c r="B54" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="C54" s="26">
+        <v>2043</v>
+      </c>
+      <c r="D54" s="26">
+        <v>2692</v>
+      </c>
+      <c r="E54" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="F54" s="27">
+        <v>114431</v>
+      </c>
+      <c r="G54" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="H54" s="28">
+        <v>45930</v>
+      </c>
+      <c r="I54" s="29" t="s">
+        <v>30</v>
+      </c>
+      <c r="J54" s="30">
+        <v>0</v>
+      </c>
+      <c r="K54" s="30">
+        <v>0</v>
+      </c>
+      <c r="L54" s="29">
+        <v>0</v>
+      </c>
+      <c r="M54" s="31">
+        <v>0</v>
+      </c>
+      <c r="N54" s="31">
+        <v>17664.759999999998</v>
+      </c>
+      <c r="O54" s="29">
+        <v>-17664.759999999998</v>
+      </c>
+      <c r="P54" s="32">
+        <v>-9.7999999999999997E-3</v>
+      </c>
+      <c r="Q54" s="30">
+        <v>0</v>
+      </c>
+      <c r="R54" s="30">
+        <v>0</v>
+      </c>
+      <c r="S54" s="30">
+        <v>0</v>
+      </c>
+      <c r="T54" s="29">
+        <v>0</v>
+      </c>
+      <c r="U54" s="29">
+        <v>0</v>
+      </c>
+      <c r="V54" s="29">
+        <v>-17664.759999999998</v>
+      </c>
+      <c r="W54" s="29">
+        <v>0</v>
+      </c>
+      <c r="X54" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="29">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="31">
+        <v>0</v>
+      </c>
+      <c r="AA54" s="31">
+        <v>5504.42</v>
+      </c>
+      <c r="AB54" s="29">
+        <v>-5504.42</v>
+      </c>
+      <c r="AC54" s="32">
+        <v>-6.1000000000000004E-3</v>
+      </c>
+      <c r="AD54" s="29">
+        <v>0</v>
+      </c>
+      <c r="AE54" s="29">
+        <v>0</v>
+      </c>
+      <c r="AF54" s="29">
+        <v>0</v>
+      </c>
+      <c r="AG54" s="29">
+        <v>0</v>
+      </c>
+      <c r="AH54" s="29">
+        <v>0</v>
+      </c>
+      <c r="AI54" s="29">
+        <v>-5504.42</v>
+      </c>
+      <c r="AJ54" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="AK54" s="34"/>
+      <c r="AL54" s="34"/>
+      <c r="AM54" s="34"/>
+      <c r="AN54" s="35"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="A6:AI53 AM6:AN53 AK6:AK53">
+  <conditionalFormatting sqref="A6:AI54 AK6:AK54 AM6:AN54">
+    <cfRule type="expression" dxfId="4" priority="5" stopIfTrue="1">
+      <formula>$B6&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="V6:V54 AI6:AI54 AN6:AN54">
     <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK42:AN53">
-    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
+  <conditionalFormatting sqref="AL6:AL54">
+    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
+      <formula>$B6&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK42:AN42">
+    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
       <formula>$B42&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL6:AL53">
-    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
-      <formula>$B6&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN6:AN53 V6:V53 AI6:AI53">
-    <cfRule type="expression" dxfId="0" priority="3" stopIfTrue="1">
-      <formula>$B6&lt;&gt;""</formula>
+  <conditionalFormatting sqref="AK43:AN54">
+    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
+      <formula>$B43&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/mdrt/MDRT.xlsx
+++ b/mdrt/MDRT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/mdrt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E3C6504-6A0D-AD49-9B15-52845735A4C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFE5E8F-1F47-2343-973D-98C2FD681F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{263D14F0-BAEF-1E4F-83AF-E2F80B31AC70}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="139">
   <si>
     <t>Dir / Zona</t>
   </si>
@@ -201,12 +201,6 @@
     <t>FICL911028663</t>
   </si>
   <si>
-    <t>ENRIQUE ADRIAN GUTIERREZ JIMENEZ</t>
-  </si>
-  <si>
-    <t>GUJE850701PM1</t>
-  </si>
-  <si>
     <t>LILIANA IVETTE CASTILLO SANCHEZ</t>
   </si>
   <si>
@@ -351,12 +345,6 @@
     <t>NURS9407304CA</t>
   </si>
   <si>
-    <t>ROCIO IVON RUIZ GARCIA</t>
-  </si>
-  <si>
-    <t>RUGR990605QA5</t>
-  </si>
-  <si>
     <t>ISAI ANTONIO ROJAS MARTINEZ</t>
   </si>
   <si>
@@ -375,24 +363,12 @@
     <t>AAMR810909U34</t>
   </si>
   <si>
-    <t>CLAUDIA VALERIA HERNANDEZ MACIAS</t>
-  </si>
-  <si>
-    <t>HEMC050122FT4</t>
-  </si>
-  <si>
     <t>LAURA DOLORES MONTAÐO MONTAÐO</t>
   </si>
   <si>
     <t>MOML870409DP3</t>
   </si>
   <si>
-    <t>BRUNO BRAULIO MACIAS ALVAREZ</t>
-  </si>
-  <si>
-    <t>MAAB830815GI1</t>
-  </si>
-  <si>
     <t>ADRIANA ALEJANDRA JOYA MARTINEZ</t>
   </si>
   <si>
@@ -405,12 +381,6 @@
     <t>LOQH990117M78</t>
   </si>
   <si>
-    <t>MARIA JOSE GUZMAN ZAMORA</t>
-  </si>
-  <si>
-    <t>GUZJ9701303Y5</t>
-  </si>
-  <si>
     <t>Cancelacion de Pólizas2</t>
   </si>
   <si>
@@ -459,9 +429,6 @@
     <t>RIBF8912215D9</t>
   </si>
   <si>
-    <t>Avance del 1 de enero al 31 de marzo de 2026.</t>
-  </si>
-  <si>
     <t>PAULA ANGELICA LOMELI CAZARES</t>
   </si>
   <si>
@@ -472,6 +439,21 @@
   </si>
   <si>
     <t>OUFL8603105M2</t>
+  </si>
+  <si>
+    <t>SOFIA CAMPILLO VASCONCELOS</t>
+  </si>
+  <si>
+    <t>CAVS990527PR3</t>
+  </si>
+  <si>
+    <t>MONSERRAT VELASCO SANTOS</t>
+  </si>
+  <si>
+    <t>VESM870518R22</t>
+  </si>
+  <si>
+    <t>Avance del 1 de enero al 08 de mayo de 2026.</t>
   </si>
 </sst>
 </file>
@@ -2406,7 +2388,7 @@
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.2">
       <c r="A1" s="36" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="4" spans="1:40" ht="28" x14ac:dyDescent="0.2">
@@ -2465,7 +2447,7 @@
         <v>17</v>
       </c>
       <c r="S4" s="4" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="T4" s="4" t="s">
         <v>18</v>
@@ -2477,46 +2459,46 @@
         <v>20</v>
       </c>
       <c r="W4" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="X4" s="6" t="s">
+        <v>116</v>
+      </c>
+      <c r="Y4" s="6" t="s">
+        <v>117</v>
+      </c>
+      <c r="Z4" s="6" t="s">
+        <v>118</v>
+      </c>
+      <c r="AA4" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB4" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC4" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD4" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE4" s="6" t="s">
+        <v>123</v>
+      </c>
+      <c r="AF4" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="AG4" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="X4" s="6" t="s">
+      <c r="AH4" s="6" t="s">
         <v>126</v>
-      </c>
-      <c r="Y4" s="6" t="s">
-        <v>127</v>
-      </c>
-      <c r="Z4" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="AA4" s="6" t="s">
-        <v>129</v>
-      </c>
-      <c r="AB4" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="AC4" s="8" t="s">
-        <v>131</v>
-      </c>
-      <c r="AD4" s="6" t="s">
-        <v>132</v>
-      </c>
-      <c r="AE4" s="6" t="s">
-        <v>133</v>
-      </c>
-      <c r="AF4" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="AG4" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="AH4" s="6" t="s">
-        <v>136</v>
       </c>
       <c r="AI4" s="9" t="s">
         <v>21</v>
       </c>
       <c r="AJ4" s="10" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="AK4" s="11" t="s">
         <v>22</v>
@@ -2602,7 +2584,7 @@
         <v>30</v>
       </c>
       <c r="J6" s="30">
-        <v>657188.18000000005</v>
+        <v>849751.51</v>
       </c>
       <c r="K6" s="30">
         <v>0</v>
@@ -2611,37 +2593,37 @@
         <v>0</v>
       </c>
       <c r="M6" s="31">
-        <v>113674.97</v>
+        <v>271976.46000000002</v>
       </c>
       <c r="N6" s="31">
         <v>0</v>
       </c>
       <c r="O6" s="29">
-        <v>770863.15</v>
+        <v>1121727.97</v>
       </c>
       <c r="P6" s="32">
-        <v>0.42580000000000001</v>
+        <v>0.61960000000000004</v>
       </c>
       <c r="Q6" s="30">
-        <v>376735.9</v>
+        <v>425395.99</v>
       </c>
       <c r="R6" s="30">
         <v>0</v>
       </c>
       <c r="S6" s="30">
-        <v>13875</v>
+        <v>18537</v>
       </c>
       <c r="T6" s="29">
-        <v>362860.9</v>
+        <v>406858.99</v>
       </c>
       <c r="U6" s="29">
         <v>0</v>
       </c>
       <c r="V6" s="29">
-        <v>1133724.05</v>
+        <v>1528586.96</v>
       </c>
       <c r="W6" s="29">
-        <v>233809.61</v>
+        <v>299713.59000000003</v>
       </c>
       <c r="X6" s="29">
         <v>0</v>
@@ -2650,34 +2632,34 @@
         <v>0</v>
       </c>
       <c r="Z6" s="31">
-        <v>6440.93</v>
+        <v>14981.03</v>
       </c>
       <c r="AA6" s="31">
         <v>0</v>
       </c>
       <c r="AB6" s="29">
-        <v>240250.54</v>
+        <v>314694.62</v>
       </c>
       <c r="AC6" s="32">
-        <v>0.26540000000000002</v>
+        <v>0.34770000000000001</v>
       </c>
       <c r="AD6" s="29">
-        <v>79391.66</v>
+        <v>89092.65</v>
       </c>
       <c r="AE6" s="29">
         <v>0</v>
       </c>
       <c r="AF6" s="29">
-        <v>2848</v>
+        <v>3811</v>
       </c>
       <c r="AG6" s="29">
-        <v>76543.66</v>
+        <v>85281.65</v>
       </c>
       <c r="AH6" s="29">
         <v>0</v>
       </c>
       <c r="AI6" s="29">
-        <v>316794.2</v>
+        <v>399976.27</v>
       </c>
       <c r="AJ6" s="33" t="s">
         <v>31</v>
@@ -2724,7 +2706,7 @@
         <v>30</v>
       </c>
       <c r="J7" s="30">
-        <v>268554.28999999998</v>
+        <v>612035.1</v>
       </c>
       <c r="K7" s="30">
         <v>0</v>
@@ -2733,16 +2715,16 @@
         <v>0</v>
       </c>
       <c r="M7" s="31">
-        <v>88915.68</v>
+        <v>93644.11</v>
       </c>
       <c r="N7" s="31">
         <v>0</v>
       </c>
       <c r="O7" s="29">
-        <v>357469.97</v>
+        <v>705679.21</v>
       </c>
       <c r="P7" s="32">
-        <v>0.19750000000000001</v>
+        <v>0.38979999999999998</v>
       </c>
       <c r="Q7" s="30">
         <v>0</v>
@@ -2760,10 +2742,10 @@
         <v>0</v>
       </c>
       <c r="V7" s="29">
-        <v>357469.97</v>
+        <v>705679.21</v>
       </c>
       <c r="W7" s="29">
-        <v>78904.41</v>
+        <v>194080.92</v>
       </c>
       <c r="X7" s="29">
         <v>0</v>
@@ -2772,16 +2754,16 @@
         <v>0</v>
       </c>
       <c r="Z7" s="31">
-        <v>5426.88</v>
+        <v>5739.81</v>
       </c>
       <c r="AA7" s="31">
         <v>0</v>
       </c>
       <c r="AB7" s="29">
-        <v>84331.29</v>
+        <v>199820.73</v>
       </c>
       <c r="AC7" s="32">
-        <v>9.3200000000000005E-2</v>
+        <v>0.22070000000000001</v>
       </c>
       <c r="AD7" s="29">
         <v>0</v>
@@ -2799,7 +2781,7 @@
         <v>0</v>
       </c>
       <c r="AI7" s="29">
-        <v>84331.29</v>
+        <v>199820.73</v>
       </c>
       <c r="AJ7" s="33" t="s">
         <v>47</v>
@@ -2820,25 +2802,25 @@
         <v>2043</v>
       </c>
       <c r="D8" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E8" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F8" s="27">
-        <v>104750</v>
+        <v>90355</v>
       </c>
       <c r="G8" s="25" t="s">
-        <v>62</v>
+        <v>38</v>
       </c>
       <c r="H8" s="28">
-        <v>45236</v>
+        <v>43949</v>
       </c>
       <c r="I8" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J8" s="30">
-        <v>150082.06</v>
+        <v>506776.96</v>
       </c>
       <c r="K8" s="30">
         <v>0</v>
@@ -2847,19 +2829,19 @@
         <v>0</v>
       </c>
       <c r="M8" s="31">
-        <v>1265.23</v>
+        <v>27307.81</v>
       </c>
       <c r="N8" s="31">
         <v>0</v>
       </c>
       <c r="O8" s="29">
-        <v>151347.29</v>
+        <v>534084.77</v>
       </c>
       <c r="P8" s="32">
-        <v>8.3599999999999994E-2</v>
+        <v>0.29499999999999998</v>
       </c>
       <c r="Q8" s="30">
-        <v>145683.81</v>
+        <v>24204.720000000001</v>
       </c>
       <c r="R8" s="30">
         <v>0</v>
@@ -2868,16 +2850,16 @@
         <v>0</v>
       </c>
       <c r="T8" s="29">
-        <v>145683.81</v>
+        <v>24204.720000000001</v>
       </c>
       <c r="U8" s="29">
         <v>0</v>
       </c>
       <c r="V8" s="29">
-        <v>297031.09999999998</v>
+        <v>558289.49</v>
       </c>
       <c r="W8" s="29">
-        <v>52498.91</v>
+        <v>180666.71</v>
       </c>
       <c r="X8" s="29">
         <v>0</v>
@@ -2886,19 +2868,19 @@
         <v>0</v>
       </c>
       <c r="Z8" s="31">
-        <v>155.62</v>
+        <v>1539.81</v>
       </c>
       <c r="AA8" s="31">
         <v>0</v>
       </c>
       <c r="AB8" s="29">
-        <v>52654.53</v>
+        <v>182206.52</v>
       </c>
       <c r="AC8" s="32">
-        <v>5.8200000000000002E-2</v>
+        <v>0.20130000000000001</v>
       </c>
       <c r="AD8" s="29">
-        <v>21216.080000000002</v>
+        <v>4936.5600000000004</v>
       </c>
       <c r="AE8" s="29">
         <v>0</v>
@@ -2907,16 +2889,16 @@
         <v>0</v>
       </c>
       <c r="AG8" s="29">
-        <v>21216.080000000002</v>
+        <v>4936.5600000000004</v>
       </c>
       <c r="AH8" s="29">
         <v>0</v>
       </c>
       <c r="AI8" s="29">
-        <v>73870.61</v>
+        <v>187143.08</v>
       </c>
       <c r="AJ8" s="33" t="s">
-        <v>63</v>
+        <v>39</v>
       </c>
       <c r="AK8" s="34"/>
       <c r="AL8" s="34"/>
@@ -2934,25 +2916,25 @@
         <v>2043</v>
       </c>
       <c r="D9" s="26">
-        <v>2692</v>
+        <v>2856</v>
       </c>
       <c r="E9" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F9" s="27">
-        <v>111056</v>
+        <v>110453</v>
       </c>
       <c r="G9" s="25" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="H9" s="28">
-        <v>45639</v>
+        <v>45600</v>
       </c>
       <c r="I9" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J9" s="30">
-        <v>0</v>
+        <v>335822.26</v>
       </c>
       <c r="K9" s="30">
         <v>0</v>
@@ -2961,19 +2943,19 @@
         <v>0</v>
       </c>
       <c r="M9" s="31">
-        <v>0</v>
+        <v>725.36</v>
       </c>
       <c r="N9" s="31">
         <v>0</v>
       </c>
       <c r="O9" s="29">
-        <v>0</v>
+        <v>336547.62</v>
       </c>
       <c r="P9" s="32">
-        <v>0</v>
+        <v>0.18590000000000001</v>
       </c>
       <c r="Q9" s="30">
-        <v>235038.77</v>
+        <v>46840.959999999999</v>
       </c>
       <c r="R9" s="30">
         <v>0</v>
@@ -2982,16 +2964,16 @@
         <v>0</v>
       </c>
       <c r="T9" s="29">
-        <v>235038.77</v>
+        <v>46840.959999999999</v>
       </c>
       <c r="U9" s="29">
         <v>0</v>
       </c>
       <c r="V9" s="29">
-        <v>235038.77</v>
+        <v>383388.58</v>
       </c>
       <c r="W9" s="29">
-        <v>0</v>
+        <v>106014.82</v>
       </c>
       <c r="X9" s="29">
         <v>0</v>
@@ -3000,19 +2982,19 @@
         <v>0</v>
       </c>
       <c r="Z9" s="31">
-        <v>0</v>
+        <v>96.72</v>
       </c>
       <c r="AA9" s="31">
         <v>0</v>
       </c>
       <c r="AB9" s="29">
-        <v>0</v>
+        <v>106111.54</v>
       </c>
       <c r="AC9" s="32">
-        <v>0</v>
+        <v>0.1172</v>
       </c>
       <c r="AD9" s="29">
-        <v>37294.720000000001</v>
+        <v>9367.49</v>
       </c>
       <c r="AE9" s="29">
         <v>0</v>
@@ -3021,16 +3003,16 @@
         <v>0</v>
       </c>
       <c r="AG9" s="29">
-        <v>37294.720000000001</v>
+        <v>9367.49</v>
       </c>
       <c r="AH9" s="29">
         <v>0</v>
       </c>
       <c r="AI9" s="29">
-        <v>37294.720000000001</v>
+        <v>115479.03</v>
       </c>
       <c r="AJ9" s="33" t="s">
-        <v>35</v>
+        <v>41</v>
       </c>
       <c r="AK9" s="34"/>
       <c r="AL9" s="34"/>
@@ -3048,25 +3030,25 @@
         <v>2043</v>
       </c>
       <c r="D10" s="26">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E10" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F10" s="27">
-        <v>110453</v>
+        <v>104750</v>
       </c>
       <c r="G10" s="25" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="H10" s="28">
-        <v>45600</v>
+        <v>45236</v>
       </c>
       <c r="I10" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J10" s="30">
-        <v>206465.86</v>
+        <v>179777.43</v>
       </c>
       <c r="K10" s="30">
         <v>0</v>
@@ -3075,19 +3057,19 @@
         <v>0</v>
       </c>
       <c r="M10" s="31">
-        <v>261.77</v>
+        <v>1857.77</v>
       </c>
       <c r="N10" s="31">
         <v>0</v>
       </c>
       <c r="O10" s="29">
-        <v>206727.63</v>
+        <v>181635.20000000001</v>
       </c>
       <c r="P10" s="32">
-        <v>0.1142</v>
+        <v>0.1003</v>
       </c>
       <c r="Q10" s="30">
-        <v>0</v>
+        <v>194243.11</v>
       </c>
       <c r="R10" s="30">
         <v>0</v>
@@ -3096,16 +3078,16 @@
         <v>0</v>
       </c>
       <c r="T10" s="29">
-        <v>0</v>
+        <v>194243.11</v>
       </c>
       <c r="U10" s="29">
         <v>0</v>
       </c>
       <c r="V10" s="29">
-        <v>206727.63</v>
+        <v>375878.31</v>
       </c>
       <c r="W10" s="29">
-        <v>66502.47</v>
+        <v>61630.61</v>
       </c>
       <c r="X10" s="29">
         <v>0</v>
@@ -3114,19 +3096,19 @@
         <v>0</v>
       </c>
       <c r="Z10" s="31">
-        <v>34.9</v>
+        <v>234.63</v>
       </c>
       <c r="AA10" s="31">
         <v>0</v>
       </c>
       <c r="AB10" s="29">
-        <v>66537.37</v>
+        <v>61865.24</v>
       </c>
       <c r="AC10" s="32">
-        <v>7.3499999999999996E-2</v>
+        <v>6.83E-2</v>
       </c>
       <c r="AD10" s="29">
-        <v>0</v>
+        <v>31580.12</v>
       </c>
       <c r="AE10" s="29">
         <v>0</v>
@@ -3135,16 +3117,16 @@
         <v>0</v>
       </c>
       <c r="AG10" s="29">
-        <v>0</v>
+        <v>31580.12</v>
       </c>
       <c r="AH10" s="29">
         <v>0</v>
       </c>
       <c r="AI10" s="29">
-        <v>66537.37</v>
+        <v>93445.36</v>
       </c>
       <c r="AJ10" s="33" t="s">
-        <v>41</v>
+        <v>61</v>
       </c>
       <c r="AK10" s="34"/>
       <c r="AL10" s="34"/>
@@ -3168,19 +3150,19 @@
         <v>28</v>
       </c>
       <c r="F11" s="27">
-        <v>94156</v>
+        <v>111056</v>
       </c>
       <c r="G11" s="25" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="H11" s="28">
-        <v>44159</v>
+        <v>45639</v>
       </c>
       <c r="I11" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J11" s="30">
-        <v>139052.07</v>
+        <v>62069.26</v>
       </c>
       <c r="K11" s="30">
         <v>0</v>
@@ -3189,19 +3171,19 @@
         <v>0</v>
       </c>
       <c r="M11" s="31">
-        <v>2291.8200000000002</v>
+        <v>0</v>
       </c>
       <c r="N11" s="31">
-        <v>0</v>
+        <v>2343.41</v>
       </c>
       <c r="O11" s="29">
-        <v>141343.89000000001</v>
+        <v>59725.85</v>
       </c>
       <c r="P11" s="32">
-        <v>7.8100000000000003E-2</v>
+        <v>3.3000000000000002E-2</v>
       </c>
       <c r="Q11" s="30">
-        <v>64612.59</v>
+        <v>278827.84000000003</v>
       </c>
       <c r="R11" s="30">
         <v>0</v>
@@ -3210,16 +3192,16 @@
         <v>0</v>
       </c>
       <c r="T11" s="29">
-        <v>64612.59</v>
+        <v>278827.84000000003</v>
       </c>
       <c r="U11" s="29">
         <v>0</v>
       </c>
       <c r="V11" s="29">
-        <v>205956.48000000001</v>
+        <v>338553.69</v>
       </c>
       <c r="W11" s="29">
-        <v>38371.129999999997</v>
+        <v>18620.77</v>
       </c>
       <c r="X11" s="29">
         <v>0</v>
@@ -3228,19 +3210,19 @@
         <v>0</v>
       </c>
       <c r="Z11" s="31">
-        <v>592.97</v>
+        <v>0</v>
       </c>
       <c r="AA11" s="31">
-        <v>0</v>
+        <v>9987.06</v>
       </c>
       <c r="AB11" s="29">
-        <v>38964.1</v>
+        <v>8633.7099999999991</v>
       </c>
       <c r="AC11" s="32">
-        <v>4.2999999999999997E-2</v>
+        <v>9.4999999999999998E-3</v>
       </c>
       <c r="AD11" s="29">
-        <v>11978.48</v>
+        <v>46576.31</v>
       </c>
       <c r="AE11" s="29">
         <v>0</v>
@@ -3249,16 +3231,16 @@
         <v>0</v>
       </c>
       <c r="AG11" s="29">
-        <v>11978.48</v>
+        <v>46576.31</v>
       </c>
       <c r="AH11" s="29">
         <v>0</v>
       </c>
       <c r="AI11" s="29">
-        <v>50942.58</v>
+        <v>55210.02</v>
       </c>
       <c r="AJ11" s="33" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="AK11" s="34"/>
       <c r="AL11" s="34"/>
@@ -3282,19 +3264,19 @@
         <v>28</v>
       </c>
       <c r="F12" s="27">
-        <v>47116</v>
+        <v>94156</v>
       </c>
       <c r="G12" s="25" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="H12" s="28">
-        <v>44616</v>
+        <v>44159</v>
       </c>
       <c r="I12" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J12" s="30">
-        <v>97248.639999999999</v>
+        <v>139052.07</v>
       </c>
       <c r="K12" s="30">
         <v>0</v>
@@ -3303,19 +3285,19 @@
         <v>0</v>
       </c>
       <c r="M12" s="31">
-        <v>5898.33</v>
+        <v>4843.2</v>
       </c>
       <c r="N12" s="31">
         <v>0</v>
       </c>
       <c r="O12" s="29">
-        <v>103146.97</v>
+        <v>143895.26999999999</v>
       </c>
       <c r="P12" s="32">
-        <v>5.7000000000000002E-2</v>
+        <v>7.9500000000000001E-2</v>
       </c>
       <c r="Q12" s="30">
-        <v>50792.35</v>
+        <v>113501.57</v>
       </c>
       <c r="R12" s="30">
         <v>0</v>
@@ -3324,16 +3306,16 @@
         <v>0</v>
       </c>
       <c r="T12" s="29">
-        <v>50792.35</v>
+        <v>113501.57</v>
       </c>
       <c r="U12" s="29">
         <v>0</v>
       </c>
       <c r="V12" s="29">
-        <v>153939.32</v>
+        <v>257396.84</v>
       </c>
       <c r="W12" s="29">
-        <v>30947.200000000001</v>
+        <v>38371.129999999997</v>
       </c>
       <c r="X12" s="29">
         <v>0</v>
@@ -3342,19 +3324,19 @@
         <v>0</v>
       </c>
       <c r="Z12" s="31">
-        <v>948.02</v>
+        <v>984.91</v>
       </c>
       <c r="AA12" s="31">
         <v>0</v>
       </c>
       <c r="AB12" s="29">
-        <v>31895.22</v>
+        <v>39356.04</v>
       </c>
       <c r="AC12" s="32">
-        <v>3.5200000000000002E-2</v>
+        <v>4.3499999999999997E-2</v>
       </c>
       <c r="AD12" s="29">
-        <v>9868.51</v>
+        <v>21993.599999999999</v>
       </c>
       <c r="AE12" s="29">
         <v>0</v>
@@ -3363,16 +3345,16 @@
         <v>0</v>
       </c>
       <c r="AG12" s="29">
-        <v>9868.51</v>
+        <v>21993.599999999999</v>
       </c>
       <c r="AH12" s="29">
         <v>0</v>
       </c>
       <c r="AI12" s="29">
-        <v>41763.730000000003</v>
+        <v>61349.64</v>
       </c>
       <c r="AJ12" s="33" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="AK12" s="34"/>
       <c r="AL12" s="34"/>
@@ -3390,25 +3372,25 @@
         <v>2043</v>
       </c>
       <c r="D13" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E13" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F13" s="27">
-        <v>90355</v>
+        <v>116883</v>
       </c>
       <c r="G13" s="25" t="s">
-        <v>38</v>
+        <v>134</v>
       </c>
       <c r="H13" s="28">
-        <v>43949</v>
+        <v>46126</v>
       </c>
       <c r="I13" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J13" s="30">
-        <v>126885.75999999999</v>
+        <v>193577.42</v>
       </c>
       <c r="K13" s="30">
         <v>0</v>
@@ -3417,19 +3399,19 @@
         <v>0</v>
       </c>
       <c r="M13" s="31">
-        <v>22390.68</v>
+        <v>0</v>
       </c>
       <c r="N13" s="31">
         <v>0</v>
       </c>
       <c r="O13" s="29">
-        <v>149276.44</v>
+        <v>193577.42</v>
       </c>
       <c r="P13" s="32">
-        <v>8.2500000000000004E-2</v>
+        <v>0.1069</v>
       </c>
       <c r="Q13" s="30">
-        <v>0</v>
+        <v>19404.849999999999</v>
       </c>
       <c r="R13" s="30">
         <v>0</v>
@@ -3438,16 +3420,16 @@
         <v>0</v>
       </c>
       <c r="T13" s="29">
-        <v>0</v>
+        <v>41282.410000000003</v>
       </c>
       <c r="U13" s="29">
-        <v>0</v>
+        <v>21877.56</v>
       </c>
       <c r="V13" s="29">
-        <v>149276.44</v>
+        <v>234859.83</v>
       </c>
       <c r="W13" s="29">
-        <v>50742.080000000002</v>
+        <v>59549.73</v>
       </c>
       <c r="X13" s="29">
         <v>0</v>
@@ -3456,19 +3438,19 @@
         <v>0</v>
       </c>
       <c r="Z13" s="31">
-        <v>1235</v>
+        <v>0</v>
       </c>
       <c r="AA13" s="31">
         <v>0</v>
       </c>
       <c r="AB13" s="29">
-        <v>51977.08</v>
+        <v>59549.73</v>
       </c>
       <c r="AC13" s="32">
-        <v>5.74E-2</v>
+        <v>6.5799999999999997E-2</v>
       </c>
       <c r="AD13" s="29">
-        <v>0</v>
+        <v>3895.07</v>
       </c>
       <c r="AE13" s="29">
         <v>0</v>
@@ -3477,16 +3459,16 @@
         <v>0</v>
       </c>
       <c r="AG13" s="29">
-        <v>0</v>
+        <v>8356.14</v>
       </c>
       <c r="AH13" s="29">
-        <v>0</v>
+        <v>4461.07</v>
       </c>
       <c r="AI13" s="29">
-        <v>51977.08</v>
+        <v>67905.87</v>
       </c>
       <c r="AJ13" s="33" t="s">
-        <v>39</v>
+        <v>135</v>
       </c>
       <c r="AK13" s="34"/>
       <c r="AL13" s="34"/>
@@ -3504,25 +3486,25 @@
         <v>2043</v>
       </c>
       <c r="D14" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E14" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F14" s="27">
-        <v>104718</v>
+        <v>117440</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>42</v>
+        <v>136</v>
       </c>
       <c r="H14" s="28">
-        <v>45264</v>
+        <v>46149</v>
       </c>
       <c r="I14" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J14" s="30">
-        <v>112348.82</v>
+        <v>220167.32</v>
       </c>
       <c r="K14" s="30">
         <v>0</v>
@@ -3531,19 +3513,19 @@
         <v>0</v>
       </c>
       <c r="M14" s="31">
-        <v>2640.94</v>
+        <v>0</v>
       </c>
       <c r="N14" s="31">
         <v>0</v>
       </c>
       <c r="O14" s="29">
-        <v>114989.75999999999</v>
+        <v>220167.32</v>
       </c>
       <c r="P14" s="32">
-        <v>6.3500000000000001E-2</v>
+        <v>0.1216</v>
       </c>
       <c r="Q14" s="30">
-        <v>31773.599999999999</v>
+        <v>0</v>
       </c>
       <c r="R14" s="30">
         <v>0</v>
@@ -3552,16 +3534,16 @@
         <v>0</v>
       </c>
       <c r="T14" s="29">
-        <v>31773.599999999999</v>
+        <v>0</v>
       </c>
       <c r="U14" s="29">
         <v>0</v>
       </c>
       <c r="V14" s="29">
-        <v>146763.35999999999</v>
+        <v>220167.32</v>
       </c>
       <c r="W14" s="29">
-        <v>34992.42</v>
+        <v>66398.399999999994</v>
       </c>
       <c r="X14" s="29">
         <v>0</v>
@@ -3570,19 +3552,19 @@
         <v>0</v>
       </c>
       <c r="Z14" s="31">
-        <v>275.58</v>
+        <v>0</v>
       </c>
       <c r="AA14" s="31">
         <v>0</v>
       </c>
       <c r="AB14" s="29">
-        <v>35268</v>
+        <v>66398.399999999994</v>
       </c>
       <c r="AC14" s="32">
-        <v>3.9E-2</v>
+        <v>7.3400000000000007E-2</v>
       </c>
       <c r="AD14" s="29">
-        <v>6601.68</v>
+        <v>0</v>
       </c>
       <c r="AE14" s="29">
         <v>0</v>
@@ -3591,16 +3573,16 @@
         <v>0</v>
       </c>
       <c r="AG14" s="29">
-        <v>6601.68</v>
+        <v>0</v>
       </c>
       <c r="AH14" s="29">
         <v>0</v>
       </c>
       <c r="AI14" s="29">
-        <v>41869.68</v>
+        <v>66398.399999999994</v>
       </c>
       <c r="AJ14" s="33" t="s">
-        <v>43</v>
+        <v>137</v>
       </c>
       <c r="AK14" s="34"/>
       <c r="AL14" s="34"/>
@@ -3618,25 +3600,25 @@
         <v>2043</v>
       </c>
       <c r="D15" s="26">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E15" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F15" s="27">
-        <v>115047</v>
+        <v>47116</v>
       </c>
       <c r="G15" s="25" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H15" s="28">
-        <v>45944</v>
+        <v>44616</v>
       </c>
       <c r="I15" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J15" s="30">
-        <v>24598.61</v>
+        <v>149780.22</v>
       </c>
       <c r="K15" s="30">
         <v>0</v>
@@ -3645,19 +3627,19 @@
         <v>0</v>
       </c>
       <c r="M15" s="31">
-        <v>841.61</v>
+        <v>11898.32</v>
       </c>
       <c r="N15" s="31">
         <v>0</v>
       </c>
       <c r="O15" s="29">
-        <v>76760.350000000006</v>
+        <v>161678.54</v>
       </c>
       <c r="P15" s="32">
-        <v>4.24E-2</v>
+        <v>8.9300000000000004E-2</v>
       </c>
       <c r="Q15" s="30">
-        <v>40110.959999999999</v>
+        <v>50792.35</v>
       </c>
       <c r="R15" s="30">
         <v>0</v>
@@ -3666,16 +3648,16 @@
         <v>0</v>
       </c>
       <c r="T15" s="29">
-        <v>49236.79</v>
+        <v>50792.35</v>
       </c>
       <c r="U15" s="29">
-        <v>60445.96</v>
+        <v>0</v>
       </c>
       <c r="V15" s="29">
-        <v>125997.14</v>
+        <v>212470.89</v>
       </c>
       <c r="W15" s="29">
-        <v>7564.38</v>
+        <v>49202.239999999998</v>
       </c>
       <c r="X15" s="29">
         <v>0</v>
@@ -3684,19 +3666,19 @@
         <v>0</v>
       </c>
       <c r="Z15" s="31">
-        <v>112.23</v>
+        <v>1754.25</v>
       </c>
       <c r="AA15" s="31">
         <v>0</v>
       </c>
       <c r="AB15" s="29">
-        <v>23072.65</v>
+        <v>50956.49</v>
       </c>
       <c r="AC15" s="32">
-        <v>2.5499999999999998E-2</v>
+        <v>5.6300000000000003E-2</v>
       </c>
       <c r="AD15" s="29">
-        <v>8472.36</v>
+        <v>9868.51</v>
       </c>
       <c r="AE15" s="29">
         <v>0</v>
@@ -3705,16 +3687,16 @@
         <v>0</v>
       </c>
       <c r="AG15" s="29">
-        <v>10021.94</v>
+        <v>9868.51</v>
       </c>
       <c r="AH15" s="29">
-        <v>16945.62</v>
+        <v>0</v>
       </c>
       <c r="AI15" s="29">
-        <v>33094.589999999997</v>
+        <v>60825</v>
       </c>
       <c r="AJ15" s="33" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="AK15" s="34"/>
       <c r="AL15" s="34"/>
@@ -3732,25 +3714,25 @@
         <v>2043</v>
       </c>
       <c r="D16" s="26">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E16" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F16" s="27">
-        <v>116876</v>
+        <v>105696</v>
       </c>
       <c r="G16" s="25" t="s">
-        <v>141</v>
+        <v>66</v>
       </c>
       <c r="H16" s="28">
-        <v>46111</v>
+        <v>45279</v>
       </c>
       <c r="I16" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J16" s="30">
-        <v>118805.62</v>
+        <v>174724.84</v>
       </c>
       <c r="K16" s="30">
         <v>0</v>
@@ -3759,19 +3741,19 @@
         <v>0</v>
       </c>
       <c r="M16" s="31">
-        <v>0</v>
+        <v>2444.4699999999998</v>
       </c>
       <c r="N16" s="31">
         <v>0</v>
       </c>
       <c r="O16" s="29">
-        <v>118805.62</v>
+        <v>177169.31</v>
       </c>
       <c r="P16" s="32">
-        <v>6.5600000000000006E-2</v>
+        <v>9.7900000000000001E-2</v>
       </c>
       <c r="Q16" s="30">
-        <v>5150.32</v>
+        <v>16178.04</v>
       </c>
       <c r="R16" s="30">
         <v>0</v>
@@ -3780,16 +3762,16 @@
         <v>0</v>
       </c>
       <c r="T16" s="29">
-        <v>5150.32</v>
+        <v>16178.04</v>
       </c>
       <c r="U16" s="29">
         <v>0</v>
       </c>
       <c r="V16" s="29">
-        <v>123955.94</v>
+        <v>193347.35</v>
       </c>
       <c r="W16" s="29">
-        <v>33860.04</v>
+        <v>59872.92</v>
       </c>
       <c r="X16" s="29">
         <v>0</v>
@@ -3798,19 +3780,19 @@
         <v>0</v>
       </c>
       <c r="Z16" s="31">
-        <v>0</v>
+        <v>182.74</v>
       </c>
       <c r="AA16" s="31">
         <v>0</v>
       </c>
       <c r="AB16" s="29">
-        <v>33860.04</v>
+        <v>60055.66</v>
       </c>
       <c r="AC16" s="32">
-        <v>3.7400000000000003E-2</v>
+        <v>6.6299999999999998E-2</v>
       </c>
       <c r="AD16" s="29">
-        <v>752.44</v>
+        <v>3240.17</v>
       </c>
       <c r="AE16" s="29">
         <v>0</v>
@@ -3819,16 +3801,16 @@
         <v>0</v>
       </c>
       <c r="AG16" s="29">
-        <v>752.44</v>
+        <v>3240.17</v>
       </c>
       <c r="AH16" s="29">
         <v>0</v>
       </c>
       <c r="AI16" s="29">
-        <v>34612.480000000003</v>
+        <v>63295.83</v>
       </c>
       <c r="AJ16" s="33" t="s">
-        <v>142</v>
+        <v>67</v>
       </c>
       <c r="AK16" s="34"/>
       <c r="AL16" s="34"/>
@@ -3852,19 +3834,19 @@
         <v>28</v>
       </c>
       <c r="F17" s="27">
-        <v>115404</v>
+        <v>104718</v>
       </c>
       <c r="G17" s="25" t="s">
-        <v>60</v>
+        <v>42</v>
       </c>
       <c r="H17" s="28">
-        <v>45986</v>
+        <v>45264</v>
       </c>
       <c r="I17" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J17" s="30">
-        <v>29852.74</v>
+        <v>112348.82</v>
       </c>
       <c r="K17" s="30">
         <v>0</v>
@@ -3873,19 +3855,19 @@
         <v>0</v>
       </c>
       <c r="M17" s="31">
-        <v>0</v>
+        <v>2772.46</v>
       </c>
       <c r="N17" s="31">
         <v>0</v>
       </c>
       <c r="O17" s="29">
-        <v>29852.74</v>
+        <v>115121.28</v>
       </c>
       <c r="P17" s="32">
-        <v>1.6500000000000001E-2</v>
+        <v>6.3600000000000004E-2</v>
       </c>
       <c r="Q17" s="30">
-        <v>79361.350000000006</v>
+        <v>31773.599999999999</v>
       </c>
       <c r="R17" s="30">
         <v>0</v>
@@ -3894,16 +3876,16 @@
         <v>0</v>
       </c>
       <c r="T17" s="29">
-        <v>79361.350000000006</v>
+        <v>31773.599999999999</v>
       </c>
       <c r="U17" s="29">
         <v>0</v>
       </c>
       <c r="V17" s="29">
-        <v>109214.09</v>
+        <v>146894.88</v>
       </c>
       <c r="W17" s="29">
-        <v>10448.459999999999</v>
+        <v>34992.42</v>
       </c>
       <c r="X17" s="29">
         <v>0</v>
@@ -3912,19 +3894,19 @@
         <v>0</v>
       </c>
       <c r="Z17" s="31">
-        <v>0</v>
+        <v>293.12</v>
       </c>
       <c r="AA17" s="31">
         <v>0</v>
       </c>
       <c r="AB17" s="29">
-        <v>10448.459999999999</v>
+        <v>35285.54</v>
       </c>
       <c r="AC17" s="32">
-        <v>1.15E-2</v>
+        <v>3.9E-2</v>
       </c>
       <c r="AD17" s="29">
-        <v>16033.12</v>
+        <v>6601.68</v>
       </c>
       <c r="AE17" s="29">
         <v>0</v>
@@ -3933,16 +3915,16 @@
         <v>0</v>
       </c>
       <c r="AG17" s="29">
-        <v>16033.12</v>
+        <v>6601.68</v>
       </c>
       <c r="AH17" s="29">
         <v>0</v>
       </c>
       <c r="AI17" s="29">
-        <v>26481.58</v>
+        <v>41887.22</v>
       </c>
       <c r="AJ17" s="33" t="s">
-        <v>61</v>
+        <v>43</v>
       </c>
       <c r="AK17" s="34"/>
       <c r="AL17" s="34"/>
@@ -3960,25 +3942,25 @@
         <v>2043</v>
       </c>
       <c r="D18" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E18" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F18" s="27">
-        <v>107488</v>
+        <v>115047</v>
       </c>
       <c r="G18" s="25" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="H18" s="28">
-        <v>45440</v>
+        <v>45944</v>
       </c>
       <c r="I18" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J18" s="30">
-        <v>0</v>
+        <v>24598.61</v>
       </c>
       <c r="K18" s="30">
         <v>0</v>
@@ -3987,19 +3969,19 @@
         <v>0</v>
       </c>
       <c r="M18" s="31">
-        <v>157.72</v>
+        <v>1532.6</v>
       </c>
       <c r="N18" s="31">
         <v>0</v>
       </c>
       <c r="O18" s="29">
-        <v>157.72</v>
+        <v>77451.34</v>
       </c>
       <c r="P18" s="32">
-        <v>1E-4</v>
+        <v>4.2799999999999998E-2</v>
       </c>
       <c r="Q18" s="30">
-        <v>98471.17</v>
+        <v>40110.959999999999</v>
       </c>
       <c r="R18" s="30">
         <v>0</v>
@@ -4008,16 +3990,16 @@
         <v>0</v>
       </c>
       <c r="T18" s="29">
-        <v>98471.17</v>
+        <v>49236.79</v>
       </c>
       <c r="U18" s="29">
-        <v>0</v>
+        <v>60445.96</v>
       </c>
       <c r="V18" s="29">
-        <v>98628.89</v>
+        <v>126688.13</v>
       </c>
       <c r="W18" s="29">
-        <v>0</v>
+        <v>7564.38</v>
       </c>
       <c r="X18" s="29">
         <v>0</v>
@@ -4026,19 +4008,19 @@
         <v>0</v>
       </c>
       <c r="Z18" s="31">
-        <v>21.03</v>
+        <v>204.36</v>
       </c>
       <c r="AA18" s="31">
         <v>0</v>
       </c>
       <c r="AB18" s="29">
-        <v>21.03</v>
+        <v>23164.78</v>
       </c>
       <c r="AC18" s="32">
-        <v>0</v>
+        <v>2.5600000000000001E-2</v>
       </c>
       <c r="AD18" s="29">
-        <v>21311.65</v>
+        <v>8472.36</v>
       </c>
       <c r="AE18" s="29">
         <v>0</v>
@@ -4047,16 +4029,16 @@
         <v>0</v>
       </c>
       <c r="AG18" s="29">
-        <v>21311.65</v>
+        <v>10021.94</v>
       </c>
       <c r="AH18" s="29">
-        <v>0</v>
+        <v>16945.62</v>
       </c>
       <c r="AI18" s="29">
-        <v>21332.68</v>
+        <v>33186.720000000001</v>
       </c>
       <c r="AJ18" s="33" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="AK18" s="34"/>
       <c r="AL18" s="34"/>
@@ -4080,19 +4062,19 @@
         <v>28</v>
       </c>
       <c r="F19" s="27">
-        <v>116060</v>
+        <v>116876</v>
       </c>
       <c r="G19" s="25" t="s">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="H19" s="28">
-        <v>46010</v>
+        <v>46111</v>
       </c>
       <c r="I19" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J19" s="30">
-        <v>21769.200000000001</v>
+        <v>118805.62</v>
       </c>
       <c r="K19" s="30">
         <v>0</v>
@@ -4107,13 +4089,13 @@
         <v>0</v>
       </c>
       <c r="O19" s="29">
-        <v>52038.66</v>
+        <v>118805.62</v>
       </c>
       <c r="P19" s="32">
-        <v>2.87E-2</v>
+        <v>6.5600000000000006E-2</v>
       </c>
       <c r="Q19" s="30">
-        <v>30604.240000000002</v>
+        <v>5150.32</v>
       </c>
       <c r="R19" s="30">
         <v>0</v>
@@ -4122,16 +4104,16 @@
         <v>0</v>
       </c>
       <c r="T19" s="29">
-        <v>30604.240000000002</v>
+        <v>5150.32</v>
       </c>
       <c r="U19" s="29">
-        <v>30269.46</v>
+        <v>0</v>
       </c>
       <c r="V19" s="29">
-        <v>82642.899999999994</v>
+        <v>123955.94</v>
       </c>
       <c r="W19" s="29">
-        <v>6774.12</v>
+        <v>33860.04</v>
       </c>
       <c r="X19" s="29">
         <v>0</v>
@@ -4146,13 +4128,13 @@
         <v>0</v>
       </c>
       <c r="AB19" s="29">
-        <v>16652.57</v>
+        <v>33860.04</v>
       </c>
       <c r="AC19" s="32">
-        <v>1.84E-2</v>
+        <v>3.7400000000000003E-2</v>
       </c>
       <c r="AD19" s="29">
-        <v>6397.42</v>
+        <v>752.44</v>
       </c>
       <c r="AE19" s="29">
         <v>0</v>
@@ -4161,16 +4143,16 @@
         <v>0</v>
       </c>
       <c r="AG19" s="29">
-        <v>6397.42</v>
+        <v>752.44</v>
       </c>
       <c r="AH19" s="29">
-        <v>9878.4500000000007</v>
+        <v>0</v>
       </c>
       <c r="AI19" s="29">
-        <v>23049.99</v>
+        <v>34612.480000000003</v>
       </c>
       <c r="AJ19" s="33" t="s">
-        <v>53</v>
+        <v>131</v>
       </c>
       <c r="AK19" s="34"/>
       <c r="AL19" s="34"/>
@@ -4194,19 +4176,19 @@
         <v>28</v>
       </c>
       <c r="F20" s="27">
-        <v>105696</v>
+        <v>115404</v>
       </c>
       <c r="G20" s="25" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="H20" s="28">
-        <v>45279</v>
+        <v>45986</v>
       </c>
       <c r="I20" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J20" s="30">
-        <v>62837.82</v>
+        <v>29852.74</v>
       </c>
       <c r="K20" s="30">
         <v>0</v>
@@ -4215,19 +4197,19 @@
         <v>0</v>
       </c>
       <c r="M20" s="31">
-        <v>1354.39</v>
+        <v>0</v>
       </c>
       <c r="N20" s="31">
         <v>0</v>
       </c>
       <c r="O20" s="29">
-        <v>64192.21</v>
+        <v>29852.74</v>
       </c>
       <c r="P20" s="32">
-        <v>3.5499999999999997E-2</v>
+        <v>1.6500000000000001E-2</v>
       </c>
       <c r="Q20" s="30">
-        <v>16178.04</v>
+        <v>79361.350000000006</v>
       </c>
       <c r="R20" s="30">
         <v>0</v>
@@ -4236,16 +4218,16 @@
         <v>0</v>
       </c>
       <c r="T20" s="29">
-        <v>16178.04</v>
+        <v>79361.350000000006</v>
       </c>
       <c r="U20" s="29">
         <v>0</v>
       </c>
       <c r="V20" s="29">
-        <v>80370.25</v>
+        <v>109214.09</v>
       </c>
       <c r="W20" s="29">
-        <v>20942.14</v>
+        <v>10448.459999999999</v>
       </c>
       <c r="X20" s="29">
         <v>0</v>
@@ -4254,19 +4236,19 @@
         <v>0</v>
       </c>
       <c r="Z20" s="31">
-        <v>112.4</v>
+        <v>0</v>
       </c>
       <c r="AA20" s="31">
         <v>0</v>
       </c>
       <c r="AB20" s="29">
-        <v>21054.54</v>
+        <v>10448.459999999999</v>
       </c>
       <c r="AC20" s="32">
-        <v>2.3300000000000001E-2</v>
+        <v>1.15E-2</v>
       </c>
       <c r="AD20" s="29">
-        <v>3240.17</v>
+        <v>16033.12</v>
       </c>
       <c r="AE20" s="29">
         <v>0</v>
@@ -4275,16 +4257,16 @@
         <v>0</v>
       </c>
       <c r="AG20" s="29">
-        <v>3240.17</v>
+        <v>16033.12</v>
       </c>
       <c r="AH20" s="29">
         <v>0</v>
       </c>
       <c r="AI20" s="29">
-        <v>24294.71</v>
+        <v>26481.58</v>
       </c>
       <c r="AJ20" s="33" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="AK20" s="34"/>
       <c r="AL20" s="34"/>
@@ -4302,25 +4284,25 @@
         <v>2043</v>
       </c>
       <c r="D21" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E21" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F21" s="27">
-        <v>108404</v>
+        <v>107488</v>
       </c>
       <c r="G21" s="25" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="H21" s="28">
-        <v>45467</v>
+        <v>45440</v>
       </c>
       <c r="I21" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J21" s="30">
-        <v>36910.69</v>
+        <v>0</v>
       </c>
       <c r="K21" s="30">
         <v>0</v>
@@ -4329,19 +4311,19 @@
         <v>0</v>
       </c>
       <c r="M21" s="31">
-        <v>8522.58</v>
+        <v>157.72</v>
       </c>
       <c r="N21" s="31">
-        <v>1952.51</v>
+        <v>0</v>
       </c>
       <c r="O21" s="29">
-        <v>43480.76</v>
+        <v>157.72</v>
       </c>
       <c r="P21" s="32">
-        <v>2.4E-2</v>
+        <v>1E-4</v>
       </c>
       <c r="Q21" s="30">
-        <v>27059.39</v>
+        <v>98471.17</v>
       </c>
       <c r="R21" s="30">
         <v>0</v>
@@ -4350,16 +4332,16 @@
         <v>0</v>
       </c>
       <c r="T21" s="29">
-        <v>27059.39</v>
+        <v>98471.17</v>
       </c>
       <c r="U21" s="29">
         <v>0</v>
       </c>
       <c r="V21" s="29">
-        <v>70540.149999999994</v>
+        <v>98628.89</v>
       </c>
       <c r="W21" s="29">
-        <v>11073.21</v>
+        <v>0</v>
       </c>
       <c r="X21" s="29">
         <v>0</v>
@@ -4368,19 +4350,19 @@
         <v>0</v>
       </c>
       <c r="Z21" s="31">
-        <v>886.33</v>
+        <v>21.03</v>
       </c>
       <c r="AA21" s="31">
-        <v>529.12</v>
+        <v>0</v>
       </c>
       <c r="AB21" s="29">
-        <v>11430.42</v>
+        <v>21.03</v>
       </c>
       <c r="AC21" s="32">
-        <v>1.26E-2</v>
+        <v>0</v>
       </c>
       <c r="AD21" s="29">
-        <v>5601.07</v>
+        <v>21311.65</v>
       </c>
       <c r="AE21" s="29">
         <v>0</v>
@@ -4389,16 +4371,16 @@
         <v>0</v>
       </c>
       <c r="AG21" s="29">
-        <v>5601.07</v>
+        <v>21311.65</v>
       </c>
       <c r="AH21" s="29">
         <v>0</v>
       </c>
       <c r="AI21" s="29">
-        <v>17031.490000000002</v>
+        <v>21332.68</v>
       </c>
       <c r="AJ21" s="33" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="AK21" s="34"/>
       <c r="AL21" s="34"/>
@@ -4416,25 +4398,25 @@
         <v>2043</v>
       </c>
       <c r="D22" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E22" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F22" s="27">
-        <v>113450</v>
+        <v>100677</v>
       </c>
       <c r="G22" s="25" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="H22" s="28">
-        <v>45852</v>
+        <v>44999</v>
       </c>
       <c r="I22" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J22" s="30">
-        <v>58035.37</v>
+        <v>65657.14</v>
       </c>
       <c r="K22" s="30">
         <v>0</v>
@@ -4443,19 +4425,19 @@
         <v>0</v>
       </c>
       <c r="M22" s="31">
-        <v>540</v>
+        <v>2064.3200000000002</v>
       </c>
       <c r="N22" s="31">
         <v>0</v>
       </c>
       <c r="O22" s="29">
-        <v>58575.37</v>
+        <v>67721.460000000006</v>
       </c>
       <c r="P22" s="32">
-        <v>3.2399999999999998E-2</v>
+        <v>3.7400000000000003E-2</v>
       </c>
       <c r="Q22" s="30">
-        <v>0</v>
+        <v>29685.599999999999</v>
       </c>
       <c r="R22" s="30">
         <v>0</v>
@@ -4464,16 +4446,16 @@
         <v>0</v>
       </c>
       <c r="T22" s="29">
-        <v>0</v>
+        <v>29685.599999999999</v>
       </c>
       <c r="U22" s="29">
         <v>0</v>
       </c>
       <c r="V22" s="29">
-        <v>58575.37</v>
+        <v>97407.06</v>
       </c>
       <c r="W22" s="29">
-        <v>15669.55</v>
+        <v>17727.419999999998</v>
       </c>
       <c r="X22" s="29">
         <v>0</v>
@@ -4482,19 +4464,19 @@
         <v>0</v>
       </c>
       <c r="Z22" s="31">
-        <v>42</v>
+        <v>161.96</v>
       </c>
       <c r="AA22" s="31">
         <v>0</v>
       </c>
       <c r="AB22" s="29">
-        <v>15711.55</v>
+        <v>17889.38</v>
       </c>
       <c r="AC22" s="32">
-        <v>1.7399999999999999E-2</v>
+        <v>1.9800000000000002E-2</v>
       </c>
       <c r="AD22" s="29">
-        <v>0</v>
+        <v>6178.8</v>
       </c>
       <c r="AE22" s="29">
         <v>0</v>
@@ -4503,16 +4485,16 @@
         <v>0</v>
       </c>
       <c r="AG22" s="29">
-        <v>0</v>
+        <v>6178.8</v>
       </c>
       <c r="AH22" s="29">
         <v>0</v>
       </c>
       <c r="AI22" s="29">
-        <v>15711.55</v>
+        <v>24068.18</v>
       </c>
       <c r="AJ22" s="33" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="AK22" s="34"/>
       <c r="AL22" s="34"/>
@@ -4539,7 +4521,7 @@
         <v>102825</v>
       </c>
       <c r="G23" s="25" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="H23" s="28">
         <v>45117</v>
@@ -4548,7 +4530,7 @@
         <v>30</v>
       </c>
       <c r="J23" s="30">
-        <v>0</v>
+        <v>30728.82</v>
       </c>
       <c r="K23" s="30">
         <v>0</v>
@@ -4563,10 +4545,10 @@
         <v>0</v>
       </c>
       <c r="O23" s="29">
-        <v>685.23</v>
+        <v>31414.05</v>
       </c>
       <c r="P23" s="32">
-        <v>4.0000000000000002E-4</v>
+        <v>1.7399999999999999E-2</v>
       </c>
       <c r="Q23" s="30">
         <v>52510.1</v>
@@ -4584,10 +4566,10 @@
         <v>0</v>
       </c>
       <c r="V23" s="29">
-        <v>53195.33</v>
+        <v>83924.15</v>
       </c>
       <c r="W23" s="29">
-        <v>0</v>
+        <v>9218.65</v>
       </c>
       <c r="X23" s="29">
         <v>0</v>
@@ -4602,10 +4584,10 @@
         <v>0</v>
       </c>
       <c r="AB23" s="29">
-        <v>228.41</v>
+        <v>9447.06</v>
       </c>
       <c r="AC23" s="32">
-        <v>2.9999999999999997E-4</v>
+        <v>1.04E-2</v>
       </c>
       <c r="AD23" s="29">
         <v>10881.11</v>
@@ -4623,10 +4605,10 @@
         <v>0</v>
       </c>
       <c r="AI23" s="29">
-        <v>11109.52</v>
+        <v>20328.169999999998</v>
       </c>
       <c r="AJ23" s="33" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="AK23" s="34"/>
       <c r="AL23" s="34"/>
@@ -4644,25 +4626,25 @@
         <v>2043</v>
       </c>
       <c r="D24" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E24" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F24" s="27">
-        <v>88234</v>
+        <v>116060</v>
       </c>
       <c r="G24" s="25" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="H24" s="28">
-        <v>43794</v>
+        <v>46010</v>
       </c>
       <c r="I24" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J24" s="30">
-        <v>0</v>
+        <v>21769.200000000001</v>
       </c>
       <c r="K24" s="30">
         <v>0</v>
@@ -4671,19 +4653,19 @@
         <v>0</v>
       </c>
       <c r="M24" s="31">
-        <v>879.63</v>
+        <v>0</v>
       </c>
       <c r="N24" s="31">
         <v>0</v>
       </c>
       <c r="O24" s="29">
-        <v>879.63</v>
+        <v>52038.66</v>
       </c>
       <c r="P24" s="32">
-        <v>5.0000000000000001E-4</v>
+        <v>2.87E-2</v>
       </c>
       <c r="Q24" s="30">
-        <v>40309.919999999998</v>
+        <v>30604.240000000002</v>
       </c>
       <c r="R24" s="30">
         <v>0</v>
@@ -4692,16 +4674,16 @@
         <v>0</v>
       </c>
       <c r="T24" s="29">
-        <v>40309.919999999998</v>
+        <v>30604.240000000002</v>
       </c>
       <c r="U24" s="29">
-        <v>0</v>
+        <v>30269.46</v>
       </c>
       <c r="V24" s="29">
-        <v>41189.550000000003</v>
+        <v>82642.899999999994</v>
       </c>
       <c r="W24" s="29">
-        <v>0</v>
+        <v>6774.12</v>
       </c>
       <c r="X24" s="29">
         <v>0</v>
@@ -4710,19 +4692,19 @@
         <v>0</v>
       </c>
       <c r="Z24" s="31">
-        <v>117.28</v>
+        <v>0</v>
       </c>
       <c r="AA24" s="31">
         <v>0</v>
       </c>
       <c r="AB24" s="29">
-        <v>117.28</v>
+        <v>16652.57</v>
       </c>
       <c r="AC24" s="32">
-        <v>1E-4</v>
+        <v>1.84E-2</v>
       </c>
       <c r="AD24" s="29">
-        <v>8479.68</v>
+        <v>6397.42</v>
       </c>
       <c r="AE24" s="29">
         <v>0</v>
@@ -4731,16 +4713,16 @@
         <v>0</v>
       </c>
       <c r="AG24" s="29">
-        <v>8479.68</v>
+        <v>6397.42</v>
       </c>
       <c r="AH24" s="29">
-        <v>0</v>
+        <v>9878.4500000000007</v>
       </c>
       <c r="AI24" s="29">
-        <v>8596.9599999999991</v>
+        <v>23049.99</v>
       </c>
       <c r="AJ24" s="33" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="AK24" s="34"/>
       <c r="AL24" s="34"/>
@@ -4758,25 +4740,25 @@
         <v>2043</v>
       </c>
       <c r="D25" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E25" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F25" s="27">
-        <v>108405</v>
+        <v>90177</v>
       </c>
       <c r="G25" s="25" t="s">
-        <v>66</v>
+        <v>96</v>
       </c>
       <c r="H25" s="28">
-        <v>45471</v>
+        <v>43949</v>
       </c>
       <c r="I25" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J25" s="30">
-        <v>36157.08</v>
+        <v>0</v>
       </c>
       <c r="K25" s="30">
         <v>0</v>
@@ -4785,19 +4767,19 @@
         <v>0</v>
       </c>
       <c r="M25" s="31">
-        <v>0.6</v>
+        <v>0</v>
       </c>
       <c r="N25" s="31">
         <v>0</v>
       </c>
       <c r="O25" s="29">
-        <v>36157.68</v>
+        <v>0</v>
       </c>
       <c r="P25" s="32">
-        <v>0.02</v>
+        <v>0</v>
       </c>
       <c r="Q25" s="30">
-        <v>0</v>
+        <v>65218.559999999998</v>
       </c>
       <c r="R25" s="30">
         <v>0</v>
@@ -4806,16 +4788,16 @@
         <v>0</v>
       </c>
       <c r="T25" s="29">
-        <v>0</v>
+        <v>65218.559999999998</v>
       </c>
       <c r="U25" s="29">
         <v>0</v>
       </c>
       <c r="V25" s="29">
-        <v>36157.68</v>
+        <v>65218.559999999998</v>
       </c>
       <c r="W25" s="29">
-        <v>10847.12</v>
+        <v>0</v>
       </c>
       <c r="X25" s="29">
         <v>0</v>
@@ -4824,19 +4806,19 @@
         <v>0</v>
       </c>
       <c r="Z25" s="31">
-        <v>0.08</v>
+        <v>0</v>
       </c>
       <c r="AA25" s="31">
         <v>0</v>
       </c>
       <c r="AB25" s="29">
-        <v>10847.2</v>
+        <v>0</v>
       </c>
       <c r="AC25" s="32">
-        <v>1.2E-2</v>
+        <v>0</v>
       </c>
       <c r="AD25" s="29">
-        <v>0</v>
+        <v>8248.92</v>
       </c>
       <c r="AE25" s="29">
         <v>0</v>
@@ -4845,16 +4827,16 @@
         <v>0</v>
       </c>
       <c r="AG25" s="29">
-        <v>0</v>
+        <v>8248.92</v>
       </c>
       <c r="AH25" s="29">
         <v>0</v>
       </c>
       <c r="AI25" s="29">
-        <v>10847.2</v>
+        <v>8248.92</v>
       </c>
       <c r="AJ25" s="33" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="AK25" s="34"/>
       <c r="AL25" s="34"/>
@@ -4878,19 +4860,19 @@
         <v>28</v>
       </c>
       <c r="F26" s="27">
-        <v>106018</v>
+        <v>108404</v>
       </c>
       <c r="G26" s="25" t="s">
-        <v>80</v>
+        <v>54</v>
       </c>
       <c r="H26" s="28">
-        <v>45344</v>
+        <v>45467</v>
       </c>
       <c r="I26" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J26" s="30">
-        <v>34230.339999999997</v>
+        <v>36910.69</v>
       </c>
       <c r="K26" s="30">
         <v>0</v>
@@ -4899,19 +4881,19 @@
         <v>0</v>
       </c>
       <c r="M26" s="31">
-        <v>426.22</v>
+        <v>9373.01</v>
       </c>
       <c r="N26" s="31">
-        <v>0</v>
+        <v>10569.73</v>
       </c>
       <c r="O26" s="29">
-        <v>34656.559999999998</v>
+        <v>35713.97</v>
       </c>
       <c r="P26" s="32">
-        <v>1.9099999999999999E-2</v>
+        <v>1.9699999999999999E-2</v>
       </c>
       <c r="Q26" s="30">
-        <v>0</v>
+        <v>27059.39</v>
       </c>
       <c r="R26" s="30">
         <v>0</v>
@@ -4920,16 +4902,16 @@
         <v>0</v>
       </c>
       <c r="T26" s="29">
-        <v>0</v>
+        <v>27059.39</v>
       </c>
       <c r="U26" s="29">
         <v>0</v>
       </c>
       <c r="V26" s="29">
-        <v>34656.559999999998</v>
+        <v>62773.36</v>
       </c>
       <c r="W26" s="29">
-        <v>10269.11</v>
+        <v>11073.21</v>
       </c>
       <c r="X26" s="29">
         <v>0</v>
@@ -4938,19 +4920,19 @@
         <v>0</v>
       </c>
       <c r="Z26" s="31">
-        <v>56.83</v>
+        <v>999.72</v>
       </c>
       <c r="AA26" s="31">
-        <v>0</v>
+        <v>3637.67</v>
       </c>
       <c r="AB26" s="29">
-        <v>10325.94</v>
+        <v>8435.26</v>
       </c>
       <c r="AC26" s="32">
-        <v>1.14E-2</v>
+        <v>9.2999999999999992E-3</v>
       </c>
       <c r="AD26" s="29">
-        <v>0</v>
+        <v>5601.07</v>
       </c>
       <c r="AE26" s="29">
         <v>0</v>
@@ -4959,16 +4941,16 @@
         <v>0</v>
       </c>
       <c r="AG26" s="29">
-        <v>0</v>
+        <v>5601.07</v>
       </c>
       <c r="AH26" s="29">
         <v>0</v>
       </c>
       <c r="AI26" s="29">
-        <v>10325.94</v>
+        <v>14036.33</v>
       </c>
       <c r="AJ26" s="33" t="s">
-        <v>81</v>
+        <v>55</v>
       </c>
       <c r="AK26" s="34"/>
       <c r="AL26" s="34"/>
@@ -4992,19 +4974,19 @@
         <v>28</v>
       </c>
       <c r="F27" s="27">
-        <v>100677</v>
+        <v>113450</v>
       </c>
       <c r="G27" s="25" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="H27" s="28">
-        <v>44999</v>
+        <v>45852</v>
       </c>
       <c r="I27" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J27" s="30">
-        <v>0</v>
+        <v>58035.37</v>
       </c>
       <c r="K27" s="30">
         <v>0</v>
@@ -5013,19 +4995,19 @@
         <v>0</v>
       </c>
       <c r="M27" s="31">
-        <v>1621.42</v>
+        <v>900</v>
       </c>
       <c r="N27" s="31">
         <v>0</v>
       </c>
       <c r="O27" s="29">
-        <v>1621.42</v>
+        <v>58935.37</v>
       </c>
       <c r="P27" s="32">
-        <v>8.9999999999999998E-4</v>
+        <v>3.2599999999999997E-2</v>
       </c>
       <c r="Q27" s="30">
-        <v>29685.599999999999</v>
+        <v>0</v>
       </c>
       <c r="R27" s="30">
         <v>0</v>
@@ -5034,16 +5016,16 @@
         <v>0</v>
       </c>
       <c r="T27" s="29">
-        <v>29685.599999999999</v>
+        <v>0</v>
       </c>
       <c r="U27" s="29">
         <v>0</v>
       </c>
       <c r="V27" s="29">
-        <v>31307.02</v>
+        <v>58935.37</v>
       </c>
       <c r="W27" s="29">
-        <v>0</v>
+        <v>15669.55</v>
       </c>
       <c r="X27" s="29">
         <v>0</v>
@@ -5052,19 +5034,19 @@
         <v>0</v>
       </c>
       <c r="Z27" s="31">
-        <v>102.91</v>
+        <v>60</v>
       </c>
       <c r="AA27" s="31">
         <v>0</v>
       </c>
       <c r="AB27" s="29">
-        <v>102.91</v>
+        <v>15729.55</v>
       </c>
       <c r="AC27" s="32">
-        <v>1E-4</v>
+        <v>1.7399999999999999E-2</v>
       </c>
       <c r="AD27" s="29">
-        <v>6178.8</v>
+        <v>0</v>
       </c>
       <c r="AE27" s="29">
         <v>0</v>
@@ -5073,16 +5055,16 @@
         <v>0</v>
       </c>
       <c r="AG27" s="29">
-        <v>6178.8</v>
+        <v>0</v>
       </c>
       <c r="AH27" s="29">
         <v>0</v>
       </c>
       <c r="AI27" s="29">
-        <v>6281.71</v>
+        <v>15729.55</v>
       </c>
       <c r="AJ27" s="33" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="AK27" s="34"/>
       <c r="AL27" s="34"/>
@@ -5106,19 +5088,19 @@
         <v>28</v>
       </c>
       <c r="F28" s="27">
-        <v>80925</v>
+        <v>104343</v>
       </c>
       <c r="G28" s="25" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="H28" s="28">
-        <v>43439</v>
+        <v>45201</v>
       </c>
       <c r="I28" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J28" s="30">
-        <v>0</v>
+        <v>50428.800000000003</v>
       </c>
       <c r="K28" s="30">
         <v>0</v>
@@ -5127,19 +5109,19 @@
         <v>0</v>
       </c>
       <c r="M28" s="31">
-        <v>5216.63</v>
+        <v>6622.88</v>
       </c>
       <c r="N28" s="31">
         <v>0</v>
       </c>
       <c r="O28" s="29">
-        <v>5216.63</v>
+        <v>57051.68</v>
       </c>
       <c r="P28" s="32">
-        <v>2.8999999999999998E-3</v>
+        <v>3.15E-2</v>
       </c>
       <c r="Q28" s="30">
-        <v>23039.919999999998</v>
+        <v>0</v>
       </c>
       <c r="R28" s="30">
         <v>0</v>
@@ -5148,16 +5130,16 @@
         <v>0</v>
       </c>
       <c r="T28" s="29">
-        <v>23039.919999999998</v>
+        <v>0</v>
       </c>
       <c r="U28" s="29">
         <v>0</v>
       </c>
       <c r="V28" s="29">
-        <v>28256.55</v>
+        <v>57051.68</v>
       </c>
       <c r="W28" s="29">
-        <v>0</v>
+        <v>16235.25</v>
       </c>
       <c r="X28" s="29">
         <v>0</v>
@@ -5166,19 +5148,19 @@
         <v>0</v>
       </c>
       <c r="Z28" s="31">
-        <v>570.55999999999995</v>
+        <v>683.03</v>
       </c>
       <c r="AA28" s="31">
         <v>0</v>
       </c>
       <c r="AB28" s="29">
-        <v>570.55999999999995</v>
+        <v>16918.28</v>
       </c>
       <c r="AC28" s="32">
-        <v>5.9999999999999995E-4</v>
+        <v>1.8700000000000001E-2</v>
       </c>
       <c r="AD28" s="29">
-        <v>4694.78</v>
+        <v>0</v>
       </c>
       <c r="AE28" s="29">
         <v>0</v>
@@ -5187,16 +5169,16 @@
         <v>0</v>
       </c>
       <c r="AG28" s="29">
-        <v>4694.78</v>
+        <v>0</v>
       </c>
       <c r="AH28" s="29">
         <v>0</v>
       </c>
       <c r="AI28" s="29">
-        <v>5265.34</v>
+        <v>16918.28</v>
       </c>
       <c r="AJ28" s="33" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="AK28" s="34"/>
       <c r="AL28" s="34"/>
@@ -5220,19 +5202,19 @@
         <v>28</v>
       </c>
       <c r="F29" s="27">
-        <v>110105</v>
+        <v>88234</v>
       </c>
       <c r="G29" s="25" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="H29" s="28">
-        <v>45560</v>
+        <v>43794</v>
       </c>
       <c r="I29" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J29" s="30">
-        <v>0</v>
+        <v>41678.550000000003</v>
       </c>
       <c r="K29" s="30">
         <v>0</v>
@@ -5241,37 +5223,37 @@
         <v>0</v>
       </c>
       <c r="M29" s="31">
-        <v>960</v>
+        <v>1258.42</v>
       </c>
       <c r="N29" s="31">
         <v>0</v>
       </c>
       <c r="O29" s="29">
-        <v>960</v>
+        <v>42936.97</v>
       </c>
       <c r="P29" s="32">
-        <v>5.0000000000000001E-4</v>
+        <v>2.3699999999999999E-2</v>
       </c>
       <c r="Q29" s="30">
-        <v>25046.54</v>
+        <v>40309.919999999998</v>
       </c>
       <c r="R29" s="30">
         <v>0</v>
       </c>
       <c r="S29" s="30">
-        <v>0</v>
+        <v>33794</v>
       </c>
       <c r="T29" s="29">
-        <v>25046.54</v>
+        <v>6515.92</v>
       </c>
       <c r="U29" s="29">
         <v>0</v>
       </c>
       <c r="V29" s="29">
-        <v>26006.54</v>
+        <v>49452.89</v>
       </c>
       <c r="W29" s="29">
-        <v>0</v>
+        <v>12503.56</v>
       </c>
       <c r="X29" s="29">
         <v>0</v>
@@ -5280,37 +5262,37 @@
         <v>0</v>
       </c>
       <c r="Z29" s="31">
-        <v>48</v>
+        <v>167.8</v>
       </c>
       <c r="AA29" s="31">
         <v>0</v>
       </c>
       <c r="AB29" s="29">
-        <v>48</v>
+        <v>12671.36</v>
       </c>
       <c r="AC29" s="32">
-        <v>1E-4</v>
+        <v>1.4E-2</v>
       </c>
       <c r="AD29" s="29">
-        <v>5158.24</v>
+        <v>8479.68</v>
       </c>
       <c r="AE29" s="29">
         <v>0</v>
       </c>
       <c r="AF29" s="29">
-        <v>0</v>
+        <v>7109</v>
       </c>
       <c r="AG29" s="29">
-        <v>5158.24</v>
+        <v>1370.68</v>
       </c>
       <c r="AH29" s="29">
         <v>0</v>
       </c>
       <c r="AI29" s="29">
-        <v>5206.24</v>
+        <v>14042.04</v>
       </c>
       <c r="AJ29" s="33" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="AK29" s="34"/>
       <c r="AL29" s="34"/>
@@ -5334,19 +5316,19 @@
         <v>28</v>
       </c>
       <c r="F30" s="27">
-        <v>65046</v>
+        <v>114157</v>
       </c>
       <c r="G30" s="25" t="s">
-        <v>86</v>
+        <v>112</v>
       </c>
       <c r="H30" s="28">
-        <v>44763</v>
+        <v>45904</v>
       </c>
       <c r="I30" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J30" s="30">
-        <v>25330.85</v>
+        <v>20303.28</v>
       </c>
       <c r="K30" s="30">
         <v>0</v>
@@ -5355,19 +5337,19 @@
         <v>0</v>
       </c>
       <c r="M30" s="31">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="N30" s="31">
         <v>0</v>
       </c>
       <c r="O30" s="29">
-        <v>25510.85</v>
+        <v>20303.28</v>
       </c>
       <c r="P30" s="32">
-        <v>1.41E-2</v>
+        <v>1.12E-2</v>
       </c>
       <c r="Q30" s="30">
-        <v>0</v>
+        <v>24156.67</v>
       </c>
       <c r="R30" s="30">
         <v>0</v>
@@ -5376,16 +5358,16 @@
         <v>0</v>
       </c>
       <c r="T30" s="29">
-        <v>0</v>
+        <v>24156.67</v>
       </c>
       <c r="U30" s="29">
         <v>0</v>
       </c>
       <c r="V30" s="29">
-        <v>25510.85</v>
+        <v>44459.95</v>
       </c>
       <c r="W30" s="29">
-        <v>7651.85</v>
+        <v>5307.72</v>
       </c>
       <c r="X30" s="29">
         <v>0</v>
@@ -5394,19 +5376,19 @@
         <v>0</v>
       </c>
       <c r="Z30" s="31">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="AA30" s="31">
         <v>0</v>
       </c>
       <c r="AB30" s="29">
-        <v>7660.85</v>
+        <v>5307.72</v>
       </c>
       <c r="AC30" s="32">
-        <v>8.5000000000000006E-3</v>
+        <v>5.8999999999999999E-3</v>
       </c>
       <c r="AD30" s="29">
-        <v>0</v>
+        <v>4962.47</v>
       </c>
       <c r="AE30" s="29">
         <v>0</v>
@@ -5415,16 +5397,16 @@
         <v>0</v>
       </c>
       <c r="AG30" s="29">
-        <v>0</v>
+        <v>4962.47</v>
       </c>
       <c r="AH30" s="29">
         <v>0</v>
       </c>
       <c r="AI30" s="29">
-        <v>7660.85</v>
+        <v>10270.19</v>
       </c>
       <c r="AJ30" s="33" t="s">
-        <v>87</v>
+        <v>113</v>
       </c>
       <c r="AK30" s="34"/>
       <c r="AL30" s="34"/>
@@ -5448,19 +5430,19 @@
         <v>28</v>
       </c>
       <c r="F31" s="27">
-        <v>104343</v>
+        <v>65046</v>
       </c>
       <c r="G31" s="25" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="H31" s="28">
-        <v>45201</v>
+        <v>44763</v>
       </c>
       <c r="I31" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J31" s="30">
-        <v>20601.72</v>
+        <v>25330.85</v>
       </c>
       <c r="K31" s="30">
         <v>0</v>
@@ -5469,19 +5451,19 @@
         <v>0</v>
       </c>
       <c r="M31" s="31">
-        <v>3182.67</v>
+        <v>308.64999999999998</v>
       </c>
       <c r="N31" s="31">
         <v>0</v>
       </c>
       <c r="O31" s="29">
-        <v>23784.39</v>
+        <v>25639.5</v>
       </c>
       <c r="P31" s="32">
-        <v>1.3100000000000001E-2</v>
+        <v>1.4200000000000001E-2</v>
       </c>
       <c r="Q31" s="30">
-        <v>0</v>
+        <v>17091.060000000001</v>
       </c>
       <c r="R31" s="30">
         <v>0</v>
@@ -5490,16 +5472,16 @@
         <v>0</v>
       </c>
       <c r="T31" s="29">
-        <v>0</v>
+        <v>17091.060000000001</v>
       </c>
       <c r="U31" s="29">
         <v>0</v>
       </c>
       <c r="V31" s="29">
-        <v>23784.39</v>
+        <v>42730.559999999998</v>
       </c>
       <c r="W31" s="29">
-        <v>7084.66</v>
+        <v>7651.85</v>
       </c>
       <c r="X31" s="29">
         <v>0</v>
@@ -5508,19 +5490,19 @@
         <v>0</v>
       </c>
       <c r="Z31" s="31">
-        <v>374.33</v>
+        <v>26.15</v>
       </c>
       <c r="AA31" s="31">
         <v>0</v>
       </c>
       <c r="AB31" s="29">
-        <v>7458.99</v>
+        <v>7678</v>
       </c>
       <c r="AC31" s="32">
-        <v>8.2000000000000007E-3</v>
+        <v>8.5000000000000006E-3</v>
       </c>
       <c r="AD31" s="29">
-        <v>0</v>
+        <v>2658.98</v>
       </c>
       <c r="AE31" s="29">
         <v>0</v>
@@ -5529,16 +5511,16 @@
         <v>0</v>
       </c>
       <c r="AG31" s="29">
-        <v>0</v>
+        <v>2658.98</v>
       </c>
       <c r="AH31" s="29">
         <v>0</v>
       </c>
       <c r="AI31" s="29">
-        <v>7458.99</v>
+        <v>10336.98</v>
       </c>
       <c r="AJ31" s="33" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="AK31" s="34"/>
       <c r="AL31" s="34"/>
@@ -5556,25 +5538,25 @@
         <v>2043</v>
       </c>
       <c r="D32" s="26">
-        <v>2692</v>
+        <v>2856</v>
       </c>
       <c r="E32" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F32" s="27">
-        <v>114157</v>
+        <v>114100</v>
       </c>
       <c r="G32" s="25" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="H32" s="28">
-        <v>45904</v>
+        <v>45863</v>
       </c>
       <c r="I32" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J32" s="30">
-        <v>20303.28</v>
+        <v>41068.42</v>
       </c>
       <c r="K32" s="30">
         <v>0</v>
@@ -5589,10 +5571,10 @@
         <v>0</v>
       </c>
       <c r="O32" s="29">
-        <v>20303.28</v>
+        <v>41068.42</v>
       </c>
       <c r="P32" s="32">
-        <v>1.12E-2</v>
+        <v>2.2700000000000001E-2</v>
       </c>
       <c r="Q32" s="30">
         <v>0</v>
@@ -5610,10 +5592,10 @@
         <v>0</v>
       </c>
       <c r="V32" s="29">
-        <v>20303.28</v>
+        <v>41068.42</v>
       </c>
       <c r="W32" s="29">
-        <v>5307.72</v>
+        <v>12640.99</v>
       </c>
       <c r="X32" s="29">
         <v>0</v>
@@ -5628,10 +5610,10 @@
         <v>0</v>
       </c>
       <c r="AB32" s="29">
-        <v>5307.72</v>
+        <v>12640.99</v>
       </c>
       <c r="AC32" s="32">
-        <v>5.8999999999999999E-3</v>
+        <v>1.4E-2</v>
       </c>
       <c r="AD32" s="29">
         <v>0</v>
@@ -5649,10 +5631,10 @@
         <v>0</v>
       </c>
       <c r="AI32" s="29">
-        <v>5307.72</v>
+        <v>12640.99</v>
       </c>
       <c r="AJ32" s="33" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="AK32" s="34"/>
       <c r="AL32" s="34"/>
@@ -5676,19 +5658,19 @@
         <v>28</v>
       </c>
       <c r="F33" s="27">
-        <v>98797</v>
+        <v>108405</v>
       </c>
       <c r="G33" s="25" t="s">
-        <v>76</v>
+        <v>64</v>
       </c>
       <c r="H33" s="28">
-        <v>44342</v>
+        <v>45471</v>
       </c>
       <c r="I33" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J33" s="30">
-        <v>0</v>
+        <v>36157.08</v>
       </c>
       <c r="K33" s="30">
         <v>0</v>
@@ -5697,16 +5679,16 @@
         <v>0</v>
       </c>
       <c r="M33" s="31">
-        <v>18002.650000000001</v>
+        <v>0.6</v>
       </c>
       <c r="N33" s="31">
         <v>0</v>
       </c>
       <c r="O33" s="29">
-        <v>18002.650000000001</v>
+        <v>36157.68</v>
       </c>
       <c r="P33" s="32">
-        <v>9.9000000000000008E-3</v>
+        <v>0.02</v>
       </c>
       <c r="Q33" s="30">
         <v>0</v>
@@ -5724,10 +5706,10 @@
         <v>0</v>
       </c>
       <c r="V33" s="29">
-        <v>18002.650000000001</v>
+        <v>36157.68</v>
       </c>
       <c r="W33" s="29">
-        <v>0</v>
+        <v>10847.12</v>
       </c>
       <c r="X33" s="29">
         <v>0</v>
@@ -5736,16 +5718,16 @@
         <v>0</v>
       </c>
       <c r="Z33" s="31">
-        <v>900.13</v>
+        <v>0.08</v>
       </c>
       <c r="AA33" s="31">
         <v>0</v>
       </c>
       <c r="AB33" s="29">
-        <v>900.13</v>
+        <v>10847.2</v>
       </c>
       <c r="AC33" s="32">
-        <v>1E-3</v>
+        <v>1.2E-2</v>
       </c>
       <c r="AD33" s="29">
         <v>0</v>
@@ -5763,10 +5745,10 @@
         <v>0</v>
       </c>
       <c r="AI33" s="29">
-        <v>900.13</v>
+        <v>10847.2</v>
       </c>
       <c r="AJ33" s="33" t="s">
-        <v>77</v>
+        <v>65</v>
       </c>
       <c r="AK33" s="34"/>
       <c r="AL33" s="34"/>
@@ -5784,25 +5766,25 @@
         <v>2043</v>
       </c>
       <c r="D34" s="26">
-        <v>2511</v>
+        <v>2043</v>
       </c>
       <c r="E34" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F34" s="27">
-        <v>63441</v>
+        <v>106018</v>
       </c>
       <c r="G34" s="25" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="H34" s="28">
-        <v>44733</v>
+        <v>45344</v>
       </c>
       <c r="I34" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J34" s="30">
-        <v>0</v>
+        <v>34230.339999999997</v>
       </c>
       <c r="K34" s="30">
         <v>0</v>
@@ -5811,16 +5793,16 @@
         <v>0</v>
       </c>
       <c r="M34" s="31">
-        <v>300.06</v>
+        <v>426.22</v>
       </c>
       <c r="N34" s="31">
         <v>0</v>
       </c>
       <c r="O34" s="29">
-        <v>300.06</v>
+        <v>34656.559999999998</v>
       </c>
       <c r="P34" s="32">
-        <v>2.0000000000000001E-4</v>
+        <v>1.9099999999999999E-2</v>
       </c>
       <c r="Q34" s="30">
         <v>0</v>
@@ -5838,10 +5820,10 @@
         <v>0</v>
       </c>
       <c r="V34" s="29">
-        <v>300.06</v>
+        <v>34656.559999999998</v>
       </c>
       <c r="W34" s="29">
-        <v>0</v>
+        <v>10269.11</v>
       </c>
       <c r="X34" s="29">
         <v>0</v>
@@ -5850,16 +5832,16 @@
         <v>0</v>
       </c>
       <c r="Z34" s="31">
-        <v>15</v>
+        <v>56.83</v>
       </c>
       <c r="AA34" s="31">
         <v>0</v>
       </c>
       <c r="AB34" s="29">
-        <v>15</v>
+        <v>10325.94</v>
       </c>
       <c r="AC34" s="32">
-        <v>0</v>
+        <v>1.14E-2</v>
       </c>
       <c r="AD34" s="29">
         <v>0</v>
@@ -5877,10 +5859,10 @@
         <v>0</v>
       </c>
       <c r="AI34" s="29">
-        <v>15</v>
+        <v>10325.94</v>
       </c>
       <c r="AJ34" s="33" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="AK34" s="34"/>
       <c r="AL34" s="34"/>
@@ -5904,13 +5886,13 @@
         <v>28</v>
       </c>
       <c r="F35" s="27">
-        <v>108658</v>
+        <v>80925</v>
       </c>
       <c r="G35" s="25" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="H35" s="28">
-        <v>45497</v>
+        <v>43439</v>
       </c>
       <c r="I35" s="29" t="s">
         <v>30</v>
@@ -5925,19 +5907,19 @@
         <v>0</v>
       </c>
       <c r="M35" s="31">
-        <v>180.03</v>
+        <v>6764.01</v>
       </c>
       <c r="N35" s="31">
         <v>0</v>
       </c>
       <c r="O35" s="29">
-        <v>180.03</v>
+        <v>6764.01</v>
       </c>
       <c r="P35" s="32">
-        <v>1E-4</v>
+        <v>3.7000000000000002E-3</v>
       </c>
       <c r="Q35" s="30">
-        <v>0</v>
+        <v>23039.919999999998</v>
       </c>
       <c r="R35" s="30">
         <v>0</v>
@@ -5946,13 +5928,13 @@
         <v>0</v>
       </c>
       <c r="T35" s="29">
-        <v>0</v>
+        <v>23039.919999999998</v>
       </c>
       <c r="U35" s="29">
         <v>0</v>
       </c>
       <c r="V35" s="29">
-        <v>180.03</v>
+        <v>29803.93</v>
       </c>
       <c r="W35" s="29">
         <v>0</v>
@@ -5964,19 +5946,19 @@
         <v>0</v>
       </c>
       <c r="Z35" s="31">
-        <v>9</v>
+        <v>776.88</v>
       </c>
       <c r="AA35" s="31">
         <v>0</v>
       </c>
       <c r="AB35" s="29">
-        <v>9</v>
+        <v>776.88</v>
       </c>
       <c r="AC35" s="32">
-        <v>0</v>
+        <v>8.9999999999999998E-4</v>
       </c>
       <c r="AD35" s="29">
-        <v>0</v>
+        <v>4694.78</v>
       </c>
       <c r="AE35" s="29">
         <v>0</v>
@@ -5985,16 +5967,16 @@
         <v>0</v>
       </c>
       <c r="AG35" s="29">
-        <v>0</v>
+        <v>4694.78</v>
       </c>
       <c r="AH35" s="29">
         <v>0</v>
       </c>
       <c r="AI35" s="29">
-        <v>9</v>
+        <v>5471.66</v>
       </c>
       <c r="AJ35" s="33" t="s">
-        <v>105</v>
+        <v>73</v>
       </c>
       <c r="AK35" s="34"/>
       <c r="AL35" s="34"/>
@@ -6018,13 +6000,13 @@
         <v>28</v>
       </c>
       <c r="F36" s="27">
-        <v>109998</v>
+        <v>110105</v>
       </c>
       <c r="G36" s="25" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="H36" s="28">
-        <v>45596</v>
+        <v>45560</v>
       </c>
       <c r="I36" s="29" t="s">
         <v>30</v>
@@ -6039,58 +6021,58 @@
         <v>0</v>
       </c>
       <c r="M36" s="31">
-        <v>162.5</v>
+        <v>1320</v>
       </c>
       <c r="N36" s="31">
         <v>0</v>
       </c>
       <c r="O36" s="29">
-        <v>162.5</v>
+        <v>1320</v>
       </c>
       <c r="P36" s="32">
+        <v>6.9999999999999999E-4</v>
+      </c>
+      <c r="Q36" s="30">
+        <v>25046.54</v>
+      </c>
+      <c r="R36" s="30">
+        <v>0</v>
+      </c>
+      <c r="S36" s="30">
+        <v>0</v>
+      </c>
+      <c r="T36" s="29">
+        <v>25046.54</v>
+      </c>
+      <c r="U36" s="29">
+        <v>0</v>
+      </c>
+      <c r="V36" s="29">
+        <v>26366.54</v>
+      </c>
+      <c r="W36" s="29">
+        <v>0</v>
+      </c>
+      <c r="X36" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="29">
+        <v>0</v>
+      </c>
+      <c r="Z36" s="31">
+        <v>66</v>
+      </c>
+      <c r="AA36" s="31">
+        <v>0</v>
+      </c>
+      <c r="AB36" s="29">
+        <v>66</v>
+      </c>
+      <c r="AC36" s="32">
         <v>1E-4</v>
       </c>
-      <c r="Q36" s="30">
-        <v>0</v>
-      </c>
-      <c r="R36" s="30">
-        <v>0</v>
-      </c>
-      <c r="S36" s="30">
-        <v>0</v>
-      </c>
-      <c r="T36" s="29">
-        <v>0</v>
-      </c>
-      <c r="U36" s="29">
-        <v>0</v>
-      </c>
-      <c r="V36" s="29">
-        <v>162.5</v>
-      </c>
-      <c r="W36" s="29">
-        <v>0</v>
-      </c>
-      <c r="X36" s="29">
-        <v>0</v>
-      </c>
-      <c r="Y36" s="29">
-        <v>0</v>
-      </c>
-      <c r="Z36" s="31">
-        <v>21.66</v>
-      </c>
-      <c r="AA36" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB36" s="29">
-        <v>21.66</v>
-      </c>
-      <c r="AC36" s="32">
-        <v>0</v>
-      </c>
       <c r="AD36" s="29">
-        <v>0</v>
+        <v>5158.24</v>
       </c>
       <c r="AE36" s="29">
         <v>0</v>
@@ -6099,16 +6081,16 @@
         <v>0</v>
       </c>
       <c r="AG36" s="29">
-        <v>0</v>
+        <v>5158.24</v>
       </c>
       <c r="AH36" s="29">
         <v>0</v>
       </c>
       <c r="AI36" s="29">
-        <v>21.66</v>
+        <v>5224.24</v>
       </c>
       <c r="AJ36" s="33" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="AK36" s="34"/>
       <c r="AL36" s="34"/>
@@ -6126,25 +6108,25 @@
         <v>2043</v>
       </c>
       <c r="D37" s="26">
-        <v>2511</v>
+        <v>2043</v>
       </c>
       <c r="E37" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F37" s="27">
-        <v>69684</v>
+        <v>112083</v>
       </c>
       <c r="G37" s="25" t="s">
-        <v>88</v>
+        <v>132</v>
       </c>
       <c r="H37" s="28">
-        <v>44771</v>
+        <v>45736</v>
       </c>
       <c r="I37" s="29" t="s">
         <v>30</v>
       </c>
       <c r="J37" s="30">
-        <v>0</v>
+        <v>21630.84</v>
       </c>
       <c r="K37" s="30">
         <v>0</v>
@@ -6153,16 +6135,16 @@
         <v>0</v>
       </c>
       <c r="M37" s="31">
-        <v>142.55000000000001</v>
+        <v>0</v>
       </c>
       <c r="N37" s="31">
         <v>0</v>
       </c>
       <c r="O37" s="29">
-        <v>142.55000000000001</v>
+        <v>21630.84</v>
       </c>
       <c r="P37" s="32">
-        <v>1E-4</v>
+        <v>1.1900000000000001E-2</v>
       </c>
       <c r="Q37" s="30">
         <v>0</v>
@@ -6180,10 +6162,10 @@
         <v>0</v>
       </c>
       <c r="V37" s="29">
-        <v>142.55000000000001</v>
+        <v>21630.84</v>
       </c>
       <c r="W37" s="29">
-        <v>0</v>
+        <v>7432.56</v>
       </c>
       <c r="X37" s="29">
         <v>0</v>
@@ -6192,16 +6174,16 @@
         <v>0</v>
       </c>
       <c r="Z37" s="31">
-        <v>19.010000000000002</v>
+        <v>0</v>
       </c>
       <c r="AA37" s="31">
         <v>0</v>
       </c>
       <c r="AB37" s="29">
-        <v>19.010000000000002</v>
+        <v>7432.56</v>
       </c>
       <c r="AC37" s="32">
-        <v>0</v>
+        <v>8.2000000000000007E-3</v>
       </c>
       <c r="AD37" s="29">
         <v>0</v>
@@ -6219,10 +6201,10 @@
         <v>0</v>
       </c>
       <c r="AI37" s="29">
-        <v>19.010000000000002</v>
+        <v>7432.56</v>
       </c>
       <c r="AJ37" s="33" t="s">
-        <v>89</v>
+        <v>133</v>
       </c>
       <c r="AK37" s="34"/>
       <c r="AL37" s="34"/>
@@ -6240,19 +6222,19 @@
         <v>2043</v>
       </c>
       <c r="D38" s="26">
-        <v>2511</v>
+        <v>2043</v>
       </c>
       <c r="E38" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F38" s="27">
-        <v>59120</v>
+        <v>98797</v>
       </c>
       <c r="G38" s="25" t="s">
-        <v>92</v>
+        <v>74</v>
       </c>
       <c r="H38" s="28">
-        <v>44708</v>
+        <v>44342</v>
       </c>
       <c r="I38" s="29" t="s">
         <v>30</v>
@@ -6267,16 +6249,16 @@
         <v>0</v>
       </c>
       <c r="M38" s="31">
-        <v>0</v>
+        <v>24003.19</v>
       </c>
       <c r="N38" s="31">
         <v>0</v>
       </c>
       <c r="O38" s="29">
-        <v>0</v>
+        <v>24003.19</v>
       </c>
       <c r="P38" s="32">
-        <v>0</v>
+        <v>1.3299999999999999E-2</v>
       </c>
       <c r="Q38" s="30">
         <v>0</v>
@@ -6285,16 +6267,16 @@
         <v>0</v>
       </c>
       <c r="S38" s="30">
-        <v>0</v>
+        <v>8154</v>
       </c>
       <c r="T38" s="29">
-        <v>0</v>
+        <v>-8154</v>
       </c>
       <c r="U38" s="29">
         <v>0</v>
       </c>
       <c r="V38" s="29">
-        <v>0</v>
+        <v>15849.19</v>
       </c>
       <c r="W38" s="29">
         <v>0</v>
@@ -6306,16 +6288,16 @@
         <v>0</v>
       </c>
       <c r="Z38" s="31">
-        <v>0</v>
+        <v>1200.1600000000001</v>
       </c>
       <c r="AA38" s="31">
         <v>0</v>
       </c>
       <c r="AB38" s="29">
-        <v>0</v>
+        <v>1200.1600000000001</v>
       </c>
       <c r="AC38" s="32">
-        <v>0</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="AD38" s="29">
         <v>0</v>
@@ -6324,19 +6306,19 @@
         <v>0</v>
       </c>
       <c r="AF38" s="29">
-        <v>0</v>
+        <v>1237</v>
       </c>
       <c r="AG38" s="29">
-        <v>0</v>
+        <v>-1237</v>
       </c>
       <c r="AH38" s="29">
         <v>0</v>
       </c>
       <c r="AI38" s="29">
-        <v>0</v>
+        <v>-36.840000000000003</v>
       </c>
       <c r="AJ38" s="33" t="s">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="AK38" s="34"/>
       <c r="AL38" s="34"/>
@@ -6360,16 +6342,16 @@
         <v>28</v>
       </c>
       <c r="F39" s="27">
-        <v>64502</v>
+        <v>101640</v>
       </c>
       <c r="G39" s="25" t="s">
-        <v>28</v>
+        <v>100</v>
       </c>
       <c r="H39" s="28">
-        <v>42173</v>
+        <v>45104</v>
       </c>
       <c r="I39" s="29" t="s">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="J39" s="30">
         <v>0</v>
@@ -6381,16 +6363,16 @@
         <v>0</v>
       </c>
       <c r="M39" s="31">
-        <v>0</v>
+        <v>9579.48</v>
       </c>
       <c r="N39" s="31">
         <v>0</v>
       </c>
       <c r="O39" s="29">
-        <v>0</v>
+        <v>9579.48</v>
       </c>
       <c r="P39" s="32">
-        <v>0</v>
+        <v>5.3E-3</v>
       </c>
       <c r="Q39" s="30">
         <v>0</v>
@@ -6408,7 +6390,7 @@
         <v>0</v>
       </c>
       <c r="V39" s="29">
-        <v>0</v>
+        <v>9579.48</v>
       </c>
       <c r="W39" s="29">
         <v>0</v>
@@ -6420,16 +6402,16 @@
         <v>0</v>
       </c>
       <c r="Z39" s="31">
-        <v>0</v>
+        <v>1277.26</v>
       </c>
       <c r="AA39" s="31">
         <v>0</v>
       </c>
       <c r="AB39" s="29">
-        <v>0</v>
+        <v>1277.26</v>
       </c>
       <c r="AC39" s="32">
-        <v>0</v>
+        <v>1.4E-3</v>
       </c>
       <c r="AD39" s="29">
         <v>0</v>
@@ -6447,10 +6429,10 @@
         <v>0</v>
       </c>
       <c r="AI39" s="29">
-        <v>0</v>
+        <v>1277.26</v>
       </c>
       <c r="AJ39" s="33" t="s">
-        <v>95</v>
+        <v>101</v>
       </c>
       <c r="AK39" s="34"/>
       <c r="AL39" s="34"/>
@@ -6468,22 +6450,22 @@
         <v>2043</v>
       </c>
       <c r="D40" s="26">
-        <v>2511</v>
+        <v>2043</v>
       </c>
       <c r="E40" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F40" s="27">
-        <v>81044</v>
+        <v>64502</v>
       </c>
       <c r="G40" s="25" t="s">
-        <v>96</v>
+        <v>28</v>
       </c>
       <c r="H40" s="28">
-        <v>44872</v>
+        <v>42173</v>
       </c>
       <c r="I40" s="29" t="s">
-        <v>30</v>
+        <v>92</v>
       </c>
       <c r="J40" s="30">
         <v>0</v>
@@ -6495,16 +6477,16 @@
         <v>0</v>
       </c>
       <c r="M40" s="31">
-        <v>0</v>
+        <v>8705.0400000000009</v>
       </c>
       <c r="N40" s="31">
         <v>0</v>
       </c>
       <c r="O40" s="29">
-        <v>0</v>
+        <v>8705.0400000000009</v>
       </c>
       <c r="P40" s="32">
-        <v>0</v>
+        <v>4.7999999999999996E-3</v>
       </c>
       <c r="Q40" s="30">
         <v>0</v>
@@ -6522,7 +6504,7 @@
         <v>0</v>
       </c>
       <c r="V40" s="29">
-        <v>0</v>
+        <v>8705.0400000000009</v>
       </c>
       <c r="W40" s="29">
         <v>0</v>
@@ -6534,16 +6516,16 @@
         <v>0</v>
       </c>
       <c r="Z40" s="31">
-        <v>0</v>
+        <v>435.25</v>
       </c>
       <c r="AA40" s="31">
         <v>0</v>
       </c>
       <c r="AB40" s="29">
-        <v>0</v>
+        <v>435.25</v>
       </c>
       <c r="AC40" s="32">
-        <v>0</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="AD40" s="29">
         <v>0</v>
@@ -6561,10 +6543,10 @@
         <v>0</v>
       </c>
       <c r="AI40" s="29">
-        <v>0</v>
+        <v>435.25</v>
       </c>
       <c r="AJ40" s="33" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="AK40" s="34"/>
       <c r="AL40" s="34"/>
@@ -6582,19 +6564,19 @@
         <v>2043</v>
       </c>
       <c r="D41" s="26">
-        <v>2043</v>
+        <v>2511</v>
       </c>
       <c r="E41" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F41" s="27">
-        <v>90177</v>
+        <v>81044</v>
       </c>
       <c r="G41" s="25" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="H41" s="28">
-        <v>43949</v>
+        <v>44872</v>
       </c>
       <c r="I41" s="29" t="s">
         <v>30</v>
@@ -6609,16 +6591,16 @@
         <v>0</v>
       </c>
       <c r="M41" s="31">
-        <v>0</v>
+        <v>2301.1799999999998</v>
       </c>
       <c r="N41" s="31">
         <v>0</v>
       </c>
       <c r="O41" s="29">
-        <v>0</v>
+        <v>2301.1799999999998</v>
       </c>
       <c r="P41" s="32">
-        <v>0</v>
+        <v>1.2999999999999999E-3</v>
       </c>
       <c r="Q41" s="30">
         <v>0</v>
@@ -6636,7 +6618,7 @@
         <v>0</v>
       </c>
       <c r="V41" s="29">
-        <v>0</v>
+        <v>2301.1799999999998</v>
       </c>
       <c r="W41" s="29">
         <v>0</v>
@@ -6648,16 +6630,16 @@
         <v>0</v>
       </c>
       <c r="Z41" s="31">
-        <v>0</v>
+        <v>306.82</v>
       </c>
       <c r="AA41" s="31">
         <v>0</v>
       </c>
       <c r="AB41" s="29">
-        <v>0</v>
+        <v>306.82</v>
       </c>
       <c r="AC41" s="32">
-        <v>0</v>
+        <v>2.9999999999999997E-4</v>
       </c>
       <c r="AD41" s="29">
         <v>0</v>
@@ -6675,10 +6657,10 @@
         <v>0</v>
       </c>
       <c r="AI41" s="29">
-        <v>0</v>
+        <v>306.82</v>
       </c>
       <c r="AJ41" s="33" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="AK41" s="34"/>
       <c r="AL41" s="34"/>
@@ -6696,19 +6678,19 @@
         <v>2043</v>
       </c>
       <c r="D42" s="26">
-        <v>2043</v>
+        <v>2511</v>
       </c>
       <c r="E42" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F42" s="27">
-        <v>94205</v>
+        <v>63441</v>
       </c>
       <c r="G42" s="25" t="s">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="H42" s="28">
-        <v>44116</v>
+        <v>44733</v>
       </c>
       <c r="I42" s="29" t="s">
         <v>30</v>
@@ -6723,16 +6705,16 @@
         <v>0</v>
       </c>
       <c r="M42" s="31">
-        <v>0</v>
+        <v>900.2</v>
       </c>
       <c r="N42" s="31">
         <v>0</v>
       </c>
       <c r="O42" s="29">
-        <v>0</v>
+        <v>900.2</v>
       </c>
       <c r="P42" s="32">
-        <v>0</v>
+        <v>5.0000000000000001E-4</v>
       </c>
       <c r="Q42" s="30">
         <v>0</v>
@@ -6750,7 +6732,7 @@
         <v>0</v>
       </c>
       <c r="V42" s="29">
-        <v>0</v>
+        <v>900.2</v>
       </c>
       <c r="W42" s="29">
         <v>0</v>
@@ -6762,13 +6744,13 @@
         <v>0</v>
       </c>
       <c r="Z42" s="31">
-        <v>0</v>
+        <v>45.01</v>
       </c>
       <c r="AA42" s="31">
         <v>0</v>
       </c>
       <c r="AB42" s="29">
-        <v>0</v>
+        <v>45.01</v>
       </c>
       <c r="AC42" s="32">
         <v>0</v>
@@ -6789,10 +6771,10 @@
         <v>0</v>
       </c>
       <c r="AI42" s="29">
-        <v>0</v>
+        <v>45.01</v>
       </c>
       <c r="AJ42" s="33" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="AK42" s="34"/>
       <c r="AL42" s="34"/>
@@ -6816,13 +6798,13 @@
         <v>28</v>
       </c>
       <c r="F43" s="27">
-        <v>101640</v>
+        <v>109998</v>
       </c>
       <c r="G43" s="25" t="s">
-        <v>102</v>
+        <v>88</v>
       </c>
       <c r="H43" s="28">
-        <v>45104</v>
+        <v>45596</v>
       </c>
       <c r="I43" s="29" t="s">
         <v>30</v>
@@ -6837,16 +6819,16 @@
         <v>0</v>
       </c>
       <c r="M43" s="31">
-        <v>0</v>
+        <v>162.5</v>
       </c>
       <c r="N43" s="31">
         <v>0</v>
       </c>
       <c r="O43" s="29">
-        <v>0</v>
+        <v>162.5</v>
       </c>
       <c r="P43" s="32">
-        <v>0</v>
+        <v>1E-4</v>
       </c>
       <c r="Q43" s="30">
         <v>0</v>
@@ -6864,7 +6846,7 @@
         <v>0</v>
       </c>
       <c r="V43" s="29">
-        <v>0</v>
+        <v>162.5</v>
       </c>
       <c r="W43" s="29">
         <v>0</v>
@@ -6876,13 +6858,13 @@
         <v>0</v>
       </c>
       <c r="Z43" s="31">
-        <v>0</v>
+        <v>21.66</v>
       </c>
       <c r="AA43" s="31">
         <v>0</v>
       </c>
       <c r="AB43" s="29">
-        <v>0</v>
+        <v>21.66</v>
       </c>
       <c r="AC43" s="32">
         <v>0</v>
@@ -6903,10 +6885,10 @@
         <v>0</v>
       </c>
       <c r="AI43" s="29">
-        <v>0</v>
+        <v>21.66</v>
       </c>
       <c r="AJ43" s="33" t="s">
-        <v>103</v>
+        <v>89</v>
       </c>
       <c r="AK43" s="34"/>
       <c r="AL43" s="34"/>
@@ -6924,19 +6906,19 @@
         <v>2043</v>
       </c>
       <c r="D44" s="26">
-        <v>2043</v>
+        <v>2511</v>
       </c>
       <c r="E44" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F44" s="27">
-        <v>103982</v>
+        <v>69684</v>
       </c>
       <c r="G44" s="25" t="s">
-        <v>138</v>
+        <v>86</v>
       </c>
       <c r="H44" s="28">
-        <v>45216</v>
+        <v>44771</v>
       </c>
       <c r="I44" s="29" t="s">
         <v>30</v>
@@ -6951,16 +6933,16 @@
         <v>0</v>
       </c>
       <c r="M44" s="31">
-        <v>0</v>
+        <v>142.55000000000001</v>
       </c>
       <c r="N44" s="31">
         <v>0</v>
       </c>
       <c r="O44" s="29">
-        <v>0</v>
+        <v>142.55000000000001</v>
       </c>
       <c r="P44" s="32">
-        <v>0</v>
+        <v>1E-4</v>
       </c>
       <c r="Q44" s="30">
         <v>0</v>
@@ -6978,7 +6960,7 @@
         <v>0</v>
       </c>
       <c r="V44" s="29">
-        <v>0</v>
+        <v>142.55000000000001</v>
       </c>
       <c r="W44" s="29">
         <v>0</v>
@@ -6990,13 +6972,13 @@
         <v>0</v>
       </c>
       <c r="Z44" s="31">
-        <v>0</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="AA44" s="31">
         <v>0</v>
       </c>
       <c r="AB44" s="29">
-        <v>0</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="AC44" s="32">
         <v>0</v>
@@ -7017,10 +6999,10 @@
         <v>0</v>
       </c>
       <c r="AI44" s="29">
-        <v>0</v>
+        <v>19.010000000000002</v>
       </c>
       <c r="AJ44" s="33" t="s">
-        <v>139</v>
+        <v>87</v>
       </c>
       <c r="AK44" s="34"/>
       <c r="AL44" s="34"/>
@@ -7038,19 +7020,19 @@
         <v>2043</v>
       </c>
       <c r="D45" s="26">
-        <v>2043</v>
+        <v>2511</v>
       </c>
       <c r="E45" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F45" s="27">
-        <v>109007</v>
+        <v>59120</v>
       </c>
       <c r="G45" s="25" t="s">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="H45" s="28">
-        <v>45525</v>
+        <v>44708</v>
       </c>
       <c r="I45" s="29" t="s">
         <v>30</v>
@@ -7134,7 +7116,7 @@
         <v>0</v>
       </c>
       <c r="AJ45" s="33" t="s">
-        <v>107</v>
+        <v>91</v>
       </c>
       <c r="AK45" s="34"/>
       <c r="AL45" s="34"/>
@@ -7152,19 +7134,19 @@
         <v>2043</v>
       </c>
       <c r="D46" s="26">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E46" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F46" s="27">
-        <v>109819</v>
+        <v>94205</v>
       </c>
       <c r="G46" s="25" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="H46" s="28">
-        <v>45562</v>
+        <v>44116</v>
       </c>
       <c r="I46" s="29" t="s">
         <v>30</v>
@@ -7248,7 +7230,7 @@
         <v>0</v>
       </c>
       <c r="AJ46" s="33" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="AK46" s="34"/>
       <c r="AL46" s="34"/>
@@ -7266,19 +7248,19 @@
         <v>2043</v>
       </c>
       <c r="D47" s="26">
-        <v>2692</v>
+        <v>2043</v>
       </c>
       <c r="E47" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F47" s="27">
-        <v>110575</v>
+        <v>103982</v>
       </c>
       <c r="G47" s="25" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="H47" s="28">
-        <v>45583</v>
+        <v>45216</v>
       </c>
       <c r="I47" s="29" t="s">
         <v>30</v>
@@ -7362,7 +7344,7 @@
         <v>0</v>
       </c>
       <c r="AJ47" s="33" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="AK47" s="34"/>
       <c r="AL47" s="34"/>
@@ -7380,19 +7362,19 @@
         <v>2043</v>
       </c>
       <c r="D48" s="26">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E48" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F48" s="27">
-        <v>111960</v>
+        <v>109007</v>
       </c>
       <c r="G48" s="25" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="H48" s="28">
-        <v>45707</v>
+        <v>45525</v>
       </c>
       <c r="I48" s="29" t="s">
         <v>30</v>
@@ -7476,7 +7458,7 @@
         <v>0</v>
       </c>
       <c r="AJ48" s="33" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="AK48" s="34"/>
       <c r="AL48" s="34"/>
@@ -7494,19 +7476,19 @@
         <v>2043</v>
       </c>
       <c r="D49" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E49" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F49" s="27">
-        <v>112083</v>
+        <v>109819</v>
       </c>
       <c r="G49" s="25" t="s">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="H49" s="28">
-        <v>45736</v>
+        <v>45562</v>
       </c>
       <c r="I49" s="29" t="s">
         <v>30</v>
@@ -7590,7 +7572,7 @@
         <v>0</v>
       </c>
       <c r="AJ49" s="33" t="s">
-        <v>144</v>
+        <v>105</v>
       </c>
       <c r="AK49" s="34"/>
       <c r="AL49" s="34"/>
@@ -7608,19 +7590,19 @@
         <v>2043</v>
       </c>
       <c r="D50" s="26">
-        <v>2856</v>
+        <v>2043</v>
       </c>
       <c r="E50" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F50" s="27">
-        <v>112522</v>
+        <v>110575</v>
       </c>
       <c r="G50" s="25" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="H50" s="28">
-        <v>45776</v>
+        <v>45583</v>
       </c>
       <c r="I50" s="29" t="s">
         <v>30</v>
@@ -7704,7 +7686,7 @@
         <v>0</v>
       </c>
       <c r="AJ50" s="33" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="AK50" s="34"/>
       <c r="AL50" s="34"/>
@@ -7722,19 +7704,19 @@
         <v>2043</v>
       </c>
       <c r="D51" s="26">
-        <v>2043</v>
+        <v>2856</v>
       </c>
       <c r="E51" s="25" t="s">
         <v>28</v>
       </c>
       <c r="F51" s="27">
-        <v>113076</v>
+        <v>112522</v>
       </c>
       <c r="G51" s="25" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="H51" s="28">
-        <v>45806</v>
+        <v>45776</v>
       </c>
       <c r="I51" s="29" t="s">
         <v>30</v>
@@ -7818,7 +7800,7 @@
         <v>0</v>
       </c>
       <c r="AJ51" s="33" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="AK51" s="34"/>
       <c r="AL51" s="34"/>
@@ -7826,371 +7808,175 @@
       <c r="AN51" s="35"/>
     </row>
     <row r="52" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A52" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B52" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C52" s="26">
-        <v>2043</v>
-      </c>
-      <c r="D52" s="26">
-        <v>2856</v>
-      </c>
-      <c r="E52" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="F52" s="27">
-        <v>114100</v>
-      </c>
-      <c r="G52" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="H52" s="28">
-        <v>45863</v>
-      </c>
-      <c r="I52" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="J52" s="30">
-        <v>0</v>
-      </c>
-      <c r="K52" s="30">
-        <v>0</v>
-      </c>
-      <c r="L52" s="29">
-        <v>0</v>
-      </c>
-      <c r="M52" s="31">
-        <v>0</v>
-      </c>
-      <c r="N52" s="31">
-        <v>0</v>
-      </c>
-      <c r="O52" s="29">
-        <v>0</v>
-      </c>
-      <c r="P52" s="32">
-        <v>0</v>
-      </c>
-      <c r="Q52" s="30">
-        <v>0</v>
-      </c>
-      <c r="R52" s="30">
-        <v>0</v>
-      </c>
-      <c r="S52" s="30">
-        <v>0</v>
-      </c>
-      <c r="T52" s="29">
-        <v>0</v>
-      </c>
-      <c r="U52" s="29">
-        <v>0</v>
-      </c>
-      <c r="V52" s="29">
-        <v>0</v>
-      </c>
-      <c r="W52" s="29">
-        <v>0</v>
-      </c>
-      <c r="X52" s="29">
-        <v>0</v>
-      </c>
-      <c r="Y52" s="29">
-        <v>0</v>
-      </c>
-      <c r="Z52" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA52" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB52" s="29">
-        <v>0</v>
-      </c>
-      <c r="AC52" s="32">
-        <v>0</v>
-      </c>
-      <c r="AD52" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE52" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF52" s="29">
-        <v>0</v>
-      </c>
-      <c r="AG52" s="29">
-        <v>0</v>
-      </c>
-      <c r="AH52" s="29">
-        <v>0</v>
-      </c>
-      <c r="AI52" s="29">
-        <v>0</v>
-      </c>
-      <c r="AJ52" s="33" t="s">
-        <v>119</v>
-      </c>
+      <c r="A52" s="25"/>
+      <c r="B52" s="25"/>
+      <c r="C52" s="26"/>
+      <c r="D52" s="26"/>
+      <c r="E52" s="25"/>
+      <c r="F52" s="27"/>
+      <c r="G52" s="25"/>
+      <c r="H52" s="28"/>
+      <c r="I52" s="29"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="29"/>
+      <c r="M52" s="31"/>
+      <c r="N52" s="31"/>
+      <c r="O52" s="29"/>
+      <c r="P52" s="32"/>
+      <c r="Q52" s="30"/>
+      <c r="R52" s="30"/>
+      <c r="S52" s="30"/>
+      <c r="T52" s="29"/>
+      <c r="U52" s="29"/>
+      <c r="V52" s="29"/>
+      <c r="W52" s="29"/>
+      <c r="X52" s="29"/>
+      <c r="Y52" s="29"/>
+      <c r="Z52" s="31"/>
+      <c r="AA52" s="31"/>
+      <c r="AB52" s="29"/>
+      <c r="AC52" s="32"/>
+      <c r="AD52" s="29"/>
+      <c r="AE52" s="29"/>
+      <c r="AF52" s="29"/>
+      <c r="AG52" s="29"/>
+      <c r="AH52" s="29"/>
+      <c r="AI52" s="29"/>
+      <c r="AJ52" s="33"/>
       <c r="AK52" s="34"/>
       <c r="AL52" s="34"/>
       <c r="AM52" s="34"/>
       <c r="AN52" s="35"/>
     </row>
     <row r="53" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A53" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B53" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C53" s="26">
-        <v>2043</v>
-      </c>
-      <c r="D53" s="26">
-        <v>2043</v>
-      </c>
-      <c r="E53" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="F53" s="27">
-        <v>95148</v>
-      </c>
-      <c r="G53" s="25" t="s">
-        <v>54</v>
-      </c>
-      <c r="H53" s="28">
-        <v>44916</v>
-      </c>
-      <c r="I53" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="J53" s="30">
-        <v>46057.760000000002</v>
-      </c>
-      <c r="K53" s="30">
-        <v>0</v>
-      </c>
-      <c r="L53" s="29">
-        <v>0</v>
-      </c>
-      <c r="M53" s="31">
-        <v>0</v>
-      </c>
-      <c r="N53" s="31">
-        <v>0</v>
-      </c>
-      <c r="O53" s="29">
-        <v>46057.760000000002</v>
-      </c>
-      <c r="P53" s="32">
-        <v>2.5399999999999999E-2</v>
-      </c>
-      <c r="Q53" s="30">
-        <v>23133.08</v>
-      </c>
-      <c r="R53" s="30">
-        <v>0</v>
-      </c>
-      <c r="S53" s="30">
-        <v>69825</v>
-      </c>
-      <c r="T53" s="29">
-        <v>-46691.92</v>
-      </c>
-      <c r="U53" s="29">
-        <v>0</v>
-      </c>
-      <c r="V53" s="29">
-        <v>-634.16</v>
-      </c>
-      <c r="W53" s="29">
-        <v>13817.33</v>
-      </c>
-      <c r="X53" s="29">
-        <v>0</v>
-      </c>
-      <c r="Y53" s="29">
-        <v>0</v>
-      </c>
-      <c r="Z53" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA53" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB53" s="29">
-        <v>13817.33</v>
-      </c>
-      <c r="AC53" s="32">
-        <v>1.5299999999999999E-2</v>
-      </c>
-      <c r="AD53" s="29">
-        <v>4744.3599999999997</v>
-      </c>
-      <c r="AE53" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF53" s="29">
-        <v>15103</v>
-      </c>
-      <c r="AG53" s="29">
-        <v>-10358.64</v>
-      </c>
-      <c r="AH53" s="29">
-        <v>0</v>
-      </c>
-      <c r="AI53" s="29">
-        <v>3458.69</v>
-      </c>
-      <c r="AJ53" s="33" t="s">
-        <v>55</v>
-      </c>
+      <c r="A53" s="25"/>
+      <c r="B53" s="25"/>
+      <c r="C53" s="26"/>
+      <c r="D53" s="26"/>
+      <c r="E53" s="25"/>
+      <c r="F53" s="27"/>
+      <c r="G53" s="25"/>
+      <c r="H53" s="28"/>
+      <c r="I53" s="29"/>
+      <c r="J53" s="30"/>
+      <c r="K53" s="30"/>
+      <c r="L53" s="29"/>
+      <c r="M53" s="31"/>
+      <c r="N53" s="31"/>
+      <c r="O53" s="29"/>
+      <c r="P53" s="32"/>
+      <c r="Q53" s="30"/>
+      <c r="R53" s="30"/>
+      <c r="S53" s="30"/>
+      <c r="T53" s="29"/>
+      <c r="U53" s="29"/>
+      <c r="V53" s="29"/>
+      <c r="W53" s="29"/>
+      <c r="X53" s="29"/>
+      <c r="Y53" s="29"/>
+      <c r="Z53" s="31"/>
+      <c r="AA53" s="31"/>
+      <c r="AB53" s="29"/>
+      <c r="AC53" s="32"/>
+      <c r="AD53" s="29"/>
+      <c r="AE53" s="29"/>
+      <c r="AF53" s="29"/>
+      <c r="AG53" s="29"/>
+      <c r="AH53" s="29"/>
+      <c r="AI53" s="29"/>
+      <c r="AJ53" s="33"/>
       <c r="AK53" s="34"/>
       <c r="AL53" s="34"/>
       <c r="AM53" s="34"/>
       <c r="AN53" s="35"/>
     </row>
     <row r="54" spans="1:40" x14ac:dyDescent="0.2">
-      <c r="A54" s="25" t="s">
-        <v>26</v>
-      </c>
-      <c r="B54" s="25" t="s">
-        <v>27</v>
-      </c>
-      <c r="C54" s="26">
-        <v>2043</v>
-      </c>
-      <c r="D54" s="26">
-        <v>2692</v>
-      </c>
-      <c r="E54" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="F54" s="27">
-        <v>114431</v>
-      </c>
-      <c r="G54" s="25" t="s">
-        <v>122</v>
-      </c>
-      <c r="H54" s="28">
-        <v>45930</v>
-      </c>
-      <c r="I54" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="J54" s="30">
-        <v>0</v>
-      </c>
-      <c r="K54" s="30">
-        <v>0</v>
-      </c>
-      <c r="L54" s="29">
-        <v>0</v>
-      </c>
-      <c r="M54" s="31">
-        <v>0</v>
-      </c>
-      <c r="N54" s="31">
-        <v>17664.759999999998</v>
-      </c>
-      <c r="O54" s="29">
-        <v>-17664.759999999998</v>
-      </c>
-      <c r="P54" s="32">
-        <v>-9.7999999999999997E-3</v>
-      </c>
-      <c r="Q54" s="30">
-        <v>0</v>
-      </c>
-      <c r="R54" s="30">
-        <v>0</v>
-      </c>
-      <c r="S54" s="30">
-        <v>0</v>
-      </c>
-      <c r="T54" s="29">
-        <v>0</v>
-      </c>
-      <c r="U54" s="29">
-        <v>0</v>
-      </c>
-      <c r="V54" s="29">
-        <v>-17664.759999999998</v>
-      </c>
-      <c r="W54" s="29">
-        <v>0</v>
-      </c>
-      <c r="X54" s="29">
-        <v>0</v>
-      </c>
-      <c r="Y54" s="29">
-        <v>0</v>
-      </c>
-      <c r="Z54" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA54" s="31">
-        <v>5504.42</v>
-      </c>
-      <c r="AB54" s="29">
-        <v>-5504.42</v>
-      </c>
-      <c r="AC54" s="32">
-        <v>-6.1000000000000004E-3</v>
-      </c>
-      <c r="AD54" s="29">
-        <v>0</v>
-      </c>
-      <c r="AE54" s="29">
-        <v>0</v>
-      </c>
-      <c r="AF54" s="29">
-        <v>0</v>
-      </c>
-      <c r="AG54" s="29">
-        <v>0</v>
-      </c>
-      <c r="AH54" s="29">
-        <v>0</v>
-      </c>
-      <c r="AI54" s="29">
-        <v>-5504.42</v>
-      </c>
-      <c r="AJ54" s="33" t="s">
-        <v>123</v>
-      </c>
+      <c r="A54" s="25"/>
+      <c r="B54" s="25"/>
+      <c r="C54" s="26"/>
+      <c r="D54" s="26"/>
+      <c r="E54" s="25"/>
+      <c r="F54" s="27"/>
+      <c r="G54" s="25"/>
+      <c r="H54" s="28"/>
+      <c r="I54" s="29"/>
+      <c r="J54" s="30"/>
+      <c r="K54" s="30"/>
+      <c r="L54" s="29"/>
+      <c r="M54" s="31"/>
+      <c r="N54" s="31"/>
+      <c r="O54" s="29"/>
+      <c r="P54" s="32"/>
+      <c r="Q54" s="30"/>
+      <c r="R54" s="30"/>
+      <c r="S54" s="30"/>
+      <c r="T54" s="29"/>
+      <c r="U54" s="29"/>
+      <c r="V54" s="29"/>
+      <c r="W54" s="29"/>
+      <c r="X54" s="29"/>
+      <c r="Y54" s="29"/>
+      <c r="Z54" s="31"/>
+      <c r="AA54" s="31"/>
+      <c r="AB54" s="29"/>
+      <c r="AC54" s="32"/>
+      <c r="AD54" s="29"/>
+      <c r="AE54" s="29"/>
+      <c r="AF54" s="29"/>
+      <c r="AG54" s="29"/>
+      <c r="AH54" s="29"/>
+      <c r="AI54" s="29"/>
+      <c r="AJ54" s="33"/>
       <c r="AK54" s="34"/>
       <c r="AL54" s="34"/>
       <c r="AM54" s="34"/>
       <c r="AN54" s="35"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A6:AI54 AK6:AK54 AM6:AN54">
+  <conditionalFormatting sqref="A52:AI54 AM52:AN54 AK52:AK54">
+    <cfRule type="expression" dxfId="8" priority="10" stopIfTrue="1">
+      <formula>$B52&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AK52:AN54">
+    <cfRule type="expression" dxfId="7" priority="6" stopIfTrue="1">
+      <formula>$B52&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL52:AL54">
+    <cfRule type="expression" dxfId="6" priority="8" stopIfTrue="1">
+      <formula>$B52&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AN52:AN54 V52:V54 AI52:AI54">
+    <cfRule type="expression" dxfId="5" priority="9" stopIfTrue="1">
+      <formula>$B52&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A6:AI51 AK6:AK51 AM6:AN51">
     <cfRule type="expression" dxfId="4" priority="5" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V6:V54 AI6:AI54 AN6:AN54">
+  <conditionalFormatting sqref="V6:V51 AI6:AI51 AN6:AN51">
     <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL6:AL54">
+  <conditionalFormatting sqref="AL6:AL51">
     <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK42:AN42">
+  <conditionalFormatting sqref="AK46:AN46">
     <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
-      <formula>$B42&lt;&gt;""</formula>
+      <formula>$B46&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AK43:AN54">
+  <conditionalFormatting sqref="AK47:AN51">
     <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
-      <formula>$B43&lt;&gt;""</formula>
+      <formula>$B47&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/mdrt/MDRT.xlsx
+++ b/mdrt/MDRT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/diego/Desktop/panel de campañas/mdrt/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFE5E8F-1F47-2343-973D-98C2FD681F03}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18D04F39-F1A7-574A-A1F4-FB1A39450675}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="4340" yWindow="500" windowWidth="24460" windowHeight="16320" xr2:uid="{263D14F0-BAEF-1E4F-83AF-E2F80B31AC70}"/>
   </bookViews>
@@ -776,92 +776,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="50">
-    <dxf>
-      <border>
-        <left style="hair">
-          <color rgb="FF002060"/>
-        </left>
-        <right style="hair">
-          <color rgb="FF002060"/>
-        </right>
-        <top style="hair">
-          <color rgb="FF002060"/>
-        </top>
-        <bottom style="hair">
-          <color rgb="FF002060"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="hair">
-          <color rgb="FF002060"/>
-        </left>
-        <right style="hair">
-          <color rgb="FF002060"/>
-        </right>
-        <top style="hair">
-          <color rgb="FF002060"/>
-        </top>
-        <bottom style="hair">
-          <color rgb="FF002060"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.79998168889431442"/>
-        </patternFill>
-      </fill>
-      <border>
-        <left style="hair">
-          <color rgb="FF002060"/>
-        </left>
-        <right style="hair">
-          <color rgb="FF002060"/>
-        </right>
-        <top style="hair">
-          <color rgb="FF002060"/>
-        </top>
-        <bottom style="hair">
-          <color rgb="FF002060"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <left style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </left>
-        <right style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </right>
-        <top style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0" tint="-0.14996795556505021"/>
-        </bottom>
-      </border>
-    </dxf>
+  <dxfs count="45">
     <dxf>
       <fill>
         <patternFill>
@@ -1983,49 +1898,49 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}" name="Tabla1" displayName="Tabla1" ref="A4:AN54" totalsRowShown="0" dataDxfId="49" dataCellStyle="Millares">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}" name="Tabla1" displayName="Tabla1" ref="A4:AN54" totalsRowShown="0" dataDxfId="44" dataCellStyle="Millares">
   <autoFilter ref="A4:AN54" xr:uid="{BCF95067-B771-3C4D-AD63-C29CB67B4C88}"/>
   <tableColumns count="40">
-    <tableColumn id="1" xr3:uid="{1B45D68F-9E92-9A48-B147-43382D17EADB}" name="Dir / Zona" dataDxfId="48"/>
-    <tableColumn id="2" xr3:uid="{8141432D-DFE6-034B-8474-F9783519965C}" name="Oficina" dataDxfId="47"/>
-    <tableColumn id="3" xr3:uid="{3026117E-099F-6549-A16F-3CA4F85DA282}" name="Mat" dataDxfId="46"/>
-    <tableColumn id="4" xr3:uid="{80621F5B-C573-8944-AF37-DC364F1BE0A9}" name="Suc" dataDxfId="45"/>
-    <tableColumn id="5" xr3:uid="{9D7D11D1-2D98-5646-92D8-F8703E85240A}" name="Promotor / Partner" dataDxfId="44"/>
-    <tableColumn id="6" xr3:uid="{870F3B42-A14B-1947-827D-9A6082152D25}" name="Asesor" dataDxfId="43"/>
-    <tableColumn id="7" xr3:uid="{CA38BEAA-FBC9-474E-8C66-960105DEBCF2}" name="Nombre del Asesor" dataDxfId="42"/>
-    <tableColumn id="8" xr3:uid="{8B8898BF-4E49-0543-9598-18FF2D3F6340}" name="Conexión" dataDxfId="41"/>
-    <tableColumn id="9" xr3:uid="{49ED1251-337D-EC49-A858-207AB60B673C}" name="Grupo" dataDxfId="40" dataCellStyle="Millares"/>
-    <tableColumn id="10" xr3:uid="{26692A66-EA2C-DD40-AAC8-07A5FE32BC7D}" name="Vida Individual" dataDxfId="39" dataCellStyle="Millares"/>
-    <tableColumn id="11" xr3:uid="{45DC445E-D43B-394B-91CD-B3001CC307CC}" name="Vida G&amp;C" dataDxfId="38" dataCellStyle="Millares"/>
-    <tableColumn id="12" xr3:uid="{953B1F2A-AB88-8A40-B82F-B5DBE8FAEA70}" name="Segudescuento" dataDxfId="37" dataCellStyle="Millares"/>
-    <tableColumn id="13" xr3:uid="{27E03CF4-3925-2045-BF66-C5BB1ECC7061}" name="Aportaciones Adicionales (AVEs)" dataDxfId="36" dataCellStyle="Millares"/>
-    <tableColumn id="14" xr3:uid="{7375183C-90AB-0B47-A516-65079E7802F1}" name="Cancelacion de Pólizas" dataDxfId="35" dataCellStyle="Millares"/>
-    <tableColumn id="15" xr3:uid="{B0F3DBFB-9B00-894E-8929-BF5CA63336C6}" name="Total de Productos Ilimitados" dataDxfId="34" dataCellStyle="Millares"/>
-    <tableColumn id="16" xr3:uid="{3C9D5C71-B64C-434C-8D65-968245DAE09C}" name="%Vida vs Meta" dataDxfId="33" dataCellStyle="Porcentaje"/>
-    <tableColumn id="17" xr3:uid="{088A86A3-8B28-DE4E-A384-CA0EA913DA34}" name="GMM Individual" dataDxfId="32" dataCellStyle="Millares"/>
-    <tableColumn id="18" xr3:uid="{A8791E9D-69D9-C844-AE4C-8AEEFA976B8B}" name="GMM G&amp;C" dataDxfId="31" dataCellStyle="Millares"/>
-    <tableColumn id="19" xr3:uid="{0FFCB5A1-F8D9-2344-9DC7-667454959C98}" name="Cancelacion de Pólizas2" dataDxfId="30" dataCellStyle="Millares"/>
-    <tableColumn id="20" xr3:uid="{FDCA43A0-92B9-954B-B283-ABAD7C194405}" name="Total Productos Limitados" dataDxfId="29" dataCellStyle="Millares"/>
-    <tableColumn id="21" xr3:uid="{7C93BB8B-9213-EA49-A648-EF5192999BF7}" name="Tope personales" dataDxfId="28" dataCellStyle="Millares"/>
-    <tableColumn id="22" xr3:uid="{70D3FAB6-79FB-994B-AB69-F0BBB15C6AFD}" name="Total Prima" dataDxfId="27" dataCellStyle="Millares"/>
-    <tableColumn id="23" xr3:uid="{0E0D17EB-06B5-AF45-9773-7D3921FC5B9C}" name="Vida Individual3" dataDxfId="26" dataCellStyle="Millares"/>
-    <tableColumn id="24" xr3:uid="{2A25EC7F-F387-9948-8D9A-38BFD2316AB4}" name="Vida G&amp;C4" dataDxfId="25" dataCellStyle="Millares"/>
-    <tableColumn id="25" xr3:uid="{F7E8005C-762C-7146-A541-3589C41B3DA2}" name="Segudescuento5" dataDxfId="24" dataCellStyle="Millares"/>
-    <tableColumn id="26" xr3:uid="{278BB65E-357A-1D4C-B1D0-5880BBD354CD}" name="Aportaciones Adicionales (AVEs)6" dataDxfId="23" dataCellStyle="Millares"/>
-    <tableColumn id="27" xr3:uid="{0490A388-0C84-C043-A7E8-E5DC8A03AF3F}" name="Cancelacion de Pólizas7" dataDxfId="22" dataCellStyle="Millares"/>
-    <tableColumn id="28" xr3:uid="{C06E1BE2-8968-A045-B8AB-E420B9B469A1}" name="Total de Productos Ilimitados8" dataDxfId="21" dataCellStyle="Millares"/>
-    <tableColumn id="29" xr3:uid="{BEBE08BA-F641-3141-BCA9-713FD1C7CEC2}" name="%Vida vs Meta9" dataDxfId="20" dataCellStyle="Porcentaje"/>
-    <tableColumn id="30" xr3:uid="{E7FB912B-27FD-1345-845F-E51E648031F5}" name="GMM Individual10" dataDxfId="19" dataCellStyle="Millares"/>
-    <tableColumn id="31" xr3:uid="{D5FF299C-A405-CE44-B4CD-CED400EFE81F}" name="GMM G&amp;C11" dataDxfId="18" dataCellStyle="Millares"/>
-    <tableColumn id="32" xr3:uid="{D7EFF89B-8E34-EA46-B72C-61EE3166E416}" name="Cancelacion de Pólizas12" dataDxfId="17" dataCellStyle="Millares"/>
-    <tableColumn id="33" xr3:uid="{81E1798B-3D20-E748-BDAB-7A2A6F5BF33B}" name="Total Productos Limitados13" dataDxfId="16" dataCellStyle="Millares"/>
-    <tableColumn id="34" xr3:uid="{7A820362-E31F-4D41-B400-9AD11AE00577}" name="Tope personales14" dataDxfId="15" dataCellStyle="Millares"/>
-    <tableColumn id="35" xr3:uid="{09E5F95B-08D0-B946-B14E-3F06BC9C57F0}" name="Total Comisión" dataDxfId="14" dataCellStyle="Millares"/>
-    <tableColumn id="36" xr3:uid="{523C81DC-6FA9-A24D-AF9B-9D74B552A8BA}" name="Columna15" dataDxfId="13" dataCellStyle="Millares"/>
-    <tableColumn id="37" xr3:uid="{ACF68D6F-CC4F-F94A-A3AE-C7407A1AC3DE}" name="Camino Prima" dataDxfId="12" dataCellStyle="Millares"/>
-    <tableColumn id="38" xr3:uid="{39FE9301-7AE9-0A42-B79D-CA4998AB76AE}" name="OBSERVACIÓN" dataDxfId="11" dataCellStyle="Millares"/>
-    <tableColumn id="39" xr3:uid="{99E25200-803C-E54D-88BD-27CB86CAED40}" name="Camino  Comisión" dataDxfId="10" dataCellStyle="Millares"/>
-    <tableColumn id="40" xr3:uid="{45B29C50-720D-8F4E-9803-310BA4AC814E}" name="NIVEL_x000a_" dataDxfId="9" dataCellStyle="Millares"/>
+    <tableColumn id="1" xr3:uid="{1B45D68F-9E92-9A48-B147-43382D17EADB}" name="Dir / Zona" dataDxfId="43"/>
+    <tableColumn id="2" xr3:uid="{8141432D-DFE6-034B-8474-F9783519965C}" name="Oficina" dataDxfId="42"/>
+    <tableColumn id="3" xr3:uid="{3026117E-099F-6549-A16F-3CA4F85DA282}" name="Mat" dataDxfId="41"/>
+    <tableColumn id="4" xr3:uid="{80621F5B-C573-8944-AF37-DC364F1BE0A9}" name="Suc" dataDxfId="40"/>
+    <tableColumn id="5" xr3:uid="{9D7D11D1-2D98-5646-92D8-F8703E85240A}" name="Promotor / Partner" dataDxfId="39"/>
+    <tableColumn id="6" xr3:uid="{870F3B42-A14B-1947-827D-9A6082152D25}" name="Asesor" dataDxfId="38"/>
+    <tableColumn id="7" xr3:uid="{CA38BEAA-FBC9-474E-8C66-960105DEBCF2}" name="Nombre del Asesor" dataDxfId="37"/>
+    <tableColumn id="8" xr3:uid="{8B8898BF-4E49-0543-9598-18FF2D3F6340}" name="Conexión" dataDxfId="36"/>
+    <tableColumn id="9" xr3:uid="{49ED1251-337D-EC49-A858-207AB60B673C}" name="Grupo" dataDxfId="35" dataCellStyle="Millares"/>
+    <tableColumn id="10" xr3:uid="{26692A66-EA2C-DD40-AAC8-07A5FE32BC7D}" name="Vida Individual" dataDxfId="34" dataCellStyle="Millares"/>
+    <tableColumn id="11" xr3:uid="{45DC445E-D43B-394B-91CD-B3001CC307CC}" name="Vida G&amp;C" dataDxfId="33" dataCellStyle="Millares"/>
+    <tableColumn id="12" xr3:uid="{953B1F2A-AB88-8A40-B82F-B5DBE8FAEA70}" name="Segudescuento" dataDxfId="32" dataCellStyle="Millares"/>
+    <tableColumn id="13" xr3:uid="{27E03CF4-3925-2045-BF66-C5BB1ECC7061}" name="Aportaciones Adicionales (AVEs)" dataDxfId="31" dataCellStyle="Millares"/>
+    <tableColumn id="14" xr3:uid="{7375183C-90AB-0B47-A516-65079E7802F1}" name="Cancelacion de Pólizas" dataDxfId="30" dataCellStyle="Millares"/>
+    <tableColumn id="15" xr3:uid="{B0F3DBFB-9B00-894E-8929-BF5CA63336C6}" name="Total de Productos Ilimitados" dataDxfId="29" dataCellStyle="Millares"/>
+    <tableColumn id="16" xr3:uid="{3C9D5C71-B64C-434C-8D65-968245DAE09C}" name="%Vida vs Meta" dataDxfId="28" dataCellStyle="Porcentaje"/>
+    <tableColumn id="17" xr3:uid="{088A86A3-8B28-DE4E-A384-CA0EA913DA34}" name="GMM Individual" dataDxfId="27" dataCellStyle="Millares"/>
+    <tableColumn id="18" xr3:uid="{A8791E9D-69D9-C844-AE4C-8AEEFA976B8B}" name="GMM G&amp;C" dataDxfId="26" dataCellStyle="Millares"/>
+    <tableColumn id="19" xr3:uid="{0FFCB5A1-F8D9-2344-9DC7-667454959C98}" name="Cancelacion de Pólizas2" dataDxfId="25" dataCellStyle="Millares"/>
+    <tableColumn id="20" xr3:uid="{FDCA43A0-92B9-954B-B283-ABAD7C194405}" name="Total Productos Limitados" dataDxfId="24" dataCellStyle="Millares"/>
+    <tableColumn id="21" xr3:uid="{7C93BB8B-9213-EA49-A648-EF5192999BF7}" name="Tope personales" dataDxfId="23" dataCellStyle="Millares"/>
+    <tableColumn id="22" xr3:uid="{70D3FAB6-79FB-994B-AB69-F0BBB15C6AFD}" name="Total Prima" dataDxfId="22" dataCellStyle="Millares"/>
+    <tableColumn id="23" xr3:uid="{0E0D17EB-06B5-AF45-9773-7D3921FC5B9C}" name="Vida Individual3" dataDxfId="21" dataCellStyle="Millares"/>
+    <tableColumn id="24" xr3:uid="{2A25EC7F-F387-9948-8D9A-38BFD2316AB4}" name="Vida G&amp;C4" dataDxfId="20" dataCellStyle="Millares"/>
+    <tableColumn id="25" xr3:uid="{F7E8005C-762C-7146-A541-3589C41B3DA2}" name="Segudescuento5" dataDxfId="19" dataCellStyle="Millares"/>
+    <tableColumn id="26" xr3:uid="{278BB65E-357A-1D4C-B1D0-5880BBD354CD}" name="Aportaciones Adicionales (AVEs)6" dataDxfId="18" dataCellStyle="Millares"/>
+    <tableColumn id="27" xr3:uid="{0490A388-0C84-C043-A7E8-E5DC8A03AF3F}" name="Cancelacion de Pólizas7" dataDxfId="17" dataCellStyle="Millares"/>
+    <tableColumn id="28" xr3:uid="{C06E1BE2-8968-A045-B8AB-E420B9B469A1}" name="Total de Productos Ilimitados8" dataDxfId="16" dataCellStyle="Millares"/>
+    <tableColumn id="29" xr3:uid="{BEBE08BA-F641-3141-BCA9-713FD1C7CEC2}" name="%Vida vs Meta9" dataDxfId="15" dataCellStyle="Porcentaje"/>
+    <tableColumn id="30" xr3:uid="{E7FB912B-27FD-1345-845F-E51E648031F5}" name="GMM Individual10" dataDxfId="14" dataCellStyle="Millares"/>
+    <tableColumn id="31" xr3:uid="{D5FF299C-A405-CE44-B4CD-CED400EFE81F}" name="GMM G&amp;C11" dataDxfId="13" dataCellStyle="Millares"/>
+    <tableColumn id="32" xr3:uid="{D7EFF89B-8E34-EA46-B72C-61EE3166E416}" name="Cancelacion de Pólizas12" dataDxfId="12" dataCellStyle="Millares"/>
+    <tableColumn id="33" xr3:uid="{81E1798B-3D20-E748-BDAB-7A2A6F5BF33B}" name="Total Productos Limitados13" dataDxfId="11" dataCellStyle="Millares"/>
+    <tableColumn id="34" xr3:uid="{7A820362-E31F-4D41-B400-9AD11AE00577}" name="Tope personales14" dataDxfId="10" dataCellStyle="Millares"/>
+    <tableColumn id="35" xr3:uid="{09E5F95B-08D0-B946-B14E-3F06BC9C57F0}" name="Total Comisión" dataDxfId="9" dataCellStyle="Millares"/>
+    <tableColumn id="36" xr3:uid="{523C81DC-6FA9-A24D-AF9B-9D74B552A8BA}" name="Columna15" dataDxfId="8" dataCellStyle="Millares"/>
+    <tableColumn id="37" xr3:uid="{ACF68D6F-CC4F-F94A-A3AE-C7407A1AC3DE}" name="Camino Prima" dataDxfId="7" dataCellStyle="Millares"/>
+    <tableColumn id="38" xr3:uid="{39FE9301-7AE9-0A42-B79D-CA4998AB76AE}" name="OBSERVACIÓN" dataDxfId="6" dataCellStyle="Millares"/>
+    <tableColumn id="39" xr3:uid="{99E25200-803C-E54D-88BD-27CB86CAED40}" name="Camino  Comisión" dataDxfId="5" dataCellStyle="Millares"/>
+    <tableColumn id="40" xr3:uid="{45B29C50-720D-8F4E-9803-310BA4AC814E}" name="NIVEL_x000a_" dataDxfId="4" dataCellStyle="Millares"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -7934,49 +7849,24 @@
       <c r="AN54" s="35"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A52:AI54 AM52:AN54 AK52:AK54">
-    <cfRule type="expression" dxfId="8" priority="10" stopIfTrue="1">
-      <formula>$B52&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK52:AN54">
-    <cfRule type="expression" dxfId="7" priority="6" stopIfTrue="1">
-      <formula>$B52&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AL52:AL54">
-    <cfRule type="expression" dxfId="6" priority="8" stopIfTrue="1">
-      <formula>$B52&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AN52:AN54 V52:V54 AI52:AI54">
-    <cfRule type="expression" dxfId="5" priority="9" stopIfTrue="1">
-      <formula>$B52&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A6:AI51 AK6:AK51 AM6:AN51">
-    <cfRule type="expression" dxfId="4" priority="5" stopIfTrue="1">
+  <conditionalFormatting sqref="A6:AI54 AM6:AN54 AK6:AK54">
+    <cfRule type="expression" dxfId="3" priority="5" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="V6:V51 AI6:AI51 AN6:AN51">
-    <cfRule type="expression" dxfId="3" priority="4" stopIfTrue="1">
+  <conditionalFormatting sqref="AK46:AN54">
+    <cfRule type="expression" dxfId="2" priority="1" stopIfTrue="1">
+      <formula>$B46&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AL6:AL54">
+    <cfRule type="expression" dxfId="1" priority="3" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AL6:AL51">
-    <cfRule type="expression" dxfId="2" priority="3" stopIfTrue="1">
+  <conditionalFormatting sqref="AN6:AN54 V6:V54 AI6:AI54">
+    <cfRule type="expression" dxfId="0" priority="4" stopIfTrue="1">
       <formula>$B6&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK46:AN46">
-    <cfRule type="expression" dxfId="1" priority="2" stopIfTrue="1">
-      <formula>$B46&lt;&gt;""</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AK47:AN51">
-    <cfRule type="expression" dxfId="0" priority="1" stopIfTrue="1">
-      <formula>$B47&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
